--- a/Översikt RAGUNDA.xlsx
+++ b/Översikt RAGUNDA.xlsx
@@ -567,7 +567,7 @@
         <v>45622</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>45376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>45622</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>45560.34460648148</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>45673</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44917</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45838.67753472222</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>45804.67787037037</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>44504</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45590.42736111111</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>44644</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>45622</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>45560.34532407407</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45104</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>45113</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>44813</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>44644.93650462963</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>45367.04916666666</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>44473</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>45639.55269675926</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>45622</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>44088</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>44062</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>45482.63819444444</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>45182</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>45790.57334490741</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>45839.42482638889</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>45803.59474537037</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>45358.99375</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>44776</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>44805</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>45560.34484953704</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>44645.99859953704</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45327</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>44888</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>45790.57349537037</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45779.57335648148</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44504</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>45378</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>45190.96092592592</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>45685.36501157407</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>45799.63574074074</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>45799.34461805555</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>45510</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>45174</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>45769.53180555555</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5463,7 +5463,7 @@
         <v>45832.34461805555</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>45121</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>44133</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>45723.40688657408</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>45320</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>45622</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>45827.5110300926</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>45120</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>45113</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>44133</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>44662</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>44438</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>44336</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>45405.57392361111</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>45155</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44994</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>45176</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>45810.55061342593</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>45121</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>45769.67740740741</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44915</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>45475.94796296296</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>45435.54734953704</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>45176</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44111</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>44209</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>45728.65684027778</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>45238</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>45471.94783564815</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>44875</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>44911</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>44994</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>45846.41361111111</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>45468.97528935185</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>45457</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>45867.63619212963</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         <v>45832.34564814815</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>45786.61517361111</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>45769.67778935185</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>44932</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>44656</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>44911</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45400.94002314815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>45545.45748842593</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>45674.67744212963</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>45744.61550925926</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>45551.46912037037</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>45495.56244212963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>45002.94356481481</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>45446.95087962963</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>45579.53179398148</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>45425.96472222222</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10493,7 +10493,7 @@
         <v>45182</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
         <v>45195</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>45471.94623842592</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10774,7 +10774,7 @@
         <v>45244</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>45779.49012731481</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>45832.34578703704</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>44245</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>44334.62565972222</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>44696</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>44662</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>44334</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>44334</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>45187</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>44911</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>45455.96195601852</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>45491</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>45384</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>45378</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>45510</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>45404</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45610.34415509259</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>45805.34415509259</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44113</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>44677</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>45786.61534722222</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12854,7 +12854,7 @@
         <v>45595.44886574074</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>45491</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>44855</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>44369.92025462963</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>45071</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>45733</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>45397.95748842593</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>44855</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>45265</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>45516.94723379629</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>44902</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>45691.44769675926</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>45751.34650462963</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>45436.94686342592</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>45093</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>45491.94715277778</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>44111</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>44971</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
         <v>45632.69822916666</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>45631</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>45209</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45152</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>45804.34474537037</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>45847.61498842593</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>45188</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>45838</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>44788</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>45789.36503472222</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>44875</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>45425.96285879629</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>44676</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>44855</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>45153</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>45769.65692129629</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>45321</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>45238</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>45723.57329861111</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
         <v>45378</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>44826.94976851852</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>45551.65726851852</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         <v>44852</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>44865</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>45372.95680555556</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>45121</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>45190</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45394</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17087,7 +17087,7 @@
         <v>45188</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>44680</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>45171</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>45089</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>45583.49642361111</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>45852.63597222222</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>45854.61494212963</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>45722.61543981481</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>45191</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>45241</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>44855</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45205</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>45526.56393518519</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>45631</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45468.97495370371</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>44993</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>44462</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>44166</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>44319</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>44705</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>44741</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>44062</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>44832</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>44774.94347222222</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>44741</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>45751.34795138889</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>45208</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45301</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45301</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45315</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45600.55265046296</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         <v>45252</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>45455.96184027778</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>45771.3859837963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>45636.3863425926</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>45468.97461805555</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
         <v>45341</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>45457.9640625</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20509,7 +20509,7 @@
         <v>45149</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45779.48993055556</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>45205</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>45033</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>44991</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45789.6360300926</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>44860</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45754.51064814815</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45266</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>45089</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>45838.38627314815</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45597.34461805555</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>45835.344375</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>45153</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>45183</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>45847.36528935185</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>45646.34438657408</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>45769.65736111111</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>45153</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>45154</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>45147</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>45775.67769675926</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>45813.49061342593</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>45722.65670138889</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45771.36548611111</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>45510</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22855,7 +22855,7 @@
         <v>45436.94644675926</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>45827.57371527778</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>44119</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>45468</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>45487.92863425926</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -23303,7 +23303,7 @@
         <v>45785.36525462963</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45491.95008101852</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>44369</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45206</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23662,7 +23662,7 @@
         <v>45624.40665509259</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>45044</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>44141</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>44157</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>44195</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>44214</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>44168</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>44517</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
         <v>44846</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>44817</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>44880.95712962963</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>44880.95719907407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44855.94125</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44425</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>44447.92069444444</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>44490.94109953703</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24680,7 +24680,7 @@
         <v>44519.94534722222</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44349</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>44210</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>44243</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>44280</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>44280</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44385.33887731482</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>44051</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>44292</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -25198,7 +25198,7 @@
         <v>44705</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>44518.94394675926</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>44362</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         <v>44426.94077546296</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -25431,7 +25431,7 @@
         <v>44846.9522337963</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>44399</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>44818.94929398148</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>44860</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         <v>44111</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>44774.94414351852</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>44425</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>44823.48666666666</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>44663</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>44874.95553240741</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44784.9408912037</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -26098,7 +26098,7 @@
         <v>44714</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -26155,7 +26155,7 @@
         <v>44837</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -26217,7 +26217,7 @@
         <v>44670</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
         <v>44858</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>44704.94234953704</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>44855</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>44078</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -26517,7 +26517,7 @@
         <v>44175</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>44194</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44239</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>44443</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>44273.92081018518</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>44132</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>44741</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>44495.93966435185</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44126</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -27050,7 +27050,7 @@
         <v>44854</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>44859.95710648148</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>44530</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44823.94993055556</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>44125.94493055555</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>44833.95405092592</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>44579.68604166667</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>44084</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>44056</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>44883</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>44728.94398148148</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>44287</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>44629.56258101852</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>44308</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>44308</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>44259</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -27997,7 +27997,7 @@
         <v>44452</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>44281</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>44836.9491087963</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>44421.97322916667</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>44351</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>44069</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>44051</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>44832.95435185185</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>44586</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>44434.94559027778</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>44867</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28664,7 +28664,7 @@
         <v>44690</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         <v>44876.95104166667</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44111</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>44500.93887731482</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>44476</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -28969,7 +28969,7 @@
         <v>44601</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         <v>44714.94162037037</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
         <v>44477.48994212963</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
         <v>44357</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>44228</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -29259,7 +29259,7 @@
         <v>44696.93986111111</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>44515.93767361111</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>44783</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>44802</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>44805</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>44315</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -29631,7 +29631,7 @@
         <v>44861</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29693,7 +29693,7 @@
         <v>44864.94835648148</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29755,7 +29755,7 @@
         <v>44308</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>44832.95300925926</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>44830</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>44776</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -29998,7 +29998,7 @@
         <v>44482.92271990741</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44853.9499537037</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>44512</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -30174,7 +30174,7 @@
         <v>44349.92013888889</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44349.91995370371</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>44824.94635416667</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -30350,7 +30350,7 @@
         <v>44662</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -30412,7 +30412,7 @@
         <v>44308</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44704</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>44685</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>44671</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>44615</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -30697,7 +30697,7 @@
         <v>44851.95488425926</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>44379</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>44075</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>44434.94517361111</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>44071</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -30997,7 +30997,7 @@
         <v>44704.94229166667</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>44861</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -31121,7 +31121,7 @@
         <v>44729.94136574074</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>44818</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -31245,7 +31245,7 @@
         <v>44833.9519212963</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>44777.95504629629</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -31369,7 +31369,7 @@
         <v>44855.9471875</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
         <v>44099</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
         <v>44621</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>44138</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>44418.9369212963</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>44140</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>44074</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31793,7 +31793,7 @@
         <v>44074</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>44650</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -31912,7 +31912,7 @@
         <v>44788</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>44853</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -32031,7 +32031,7 @@
         <v>44799.94394675926</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44463.94077546296</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>44574</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -32212,7 +32212,7 @@
         <v>44883.94918981481</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>44431</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>44124</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44615</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -32445,7 +32445,7 @@
         <v>44140</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>44599.98685185185</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>44815</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>44578.92284722222</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -32688,7 +32688,7 @@
         <v>44489.94711805556</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -32750,7 +32750,7 @@
         <v>44823</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>44727</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -32869,7 +32869,7 @@
         <v>44494.93930555556</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -32931,7 +32931,7 @@
         <v>44858</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -32993,7 +32993,7 @@
         <v>44425</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -33055,7 +33055,7 @@
         <v>44068.62614583333</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>44322</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>44846</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -33231,7 +33231,7 @@
         <v>44704.9422337963</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>44495</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>44781</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -33412,7 +33412,7 @@
         <v>44361.55445601852</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44889</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>44595</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>44854.95390046296</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>44831.94846064815</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -33712,7 +33712,7 @@
         <v>44831.9485300926</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>44728.94392361111</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>44784.94157407407</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>44496</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>44734.94193287037</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -34017,7 +34017,7 @@
         <v>44402.42243055555</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -34074,7 +34074,7 @@
         <v>44704.94217592593</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>45715.59405092592</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>45000</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>45681.5315625</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>44356.91935185185</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>45673.66358796296</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>44680.95246527778</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>45007</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>45042</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44889</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>45601.59518518519</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>45723.67777777778</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -34793,7 +34793,7 @@
         <v>44336</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>44879</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -34912,7 +34912,7 @@
         <v>45743.36</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -34974,7 +34974,7 @@
         <v>45735.53177083333</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -35036,7 +35036,7 @@
         <v>45735.5517824074</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>45009</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>45730.42738425926</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>45733.61554398148</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>45436.94628472222</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>45425.96263888889</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>45267</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>45769.51087962963</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -35522,7 +35522,7 @@
         <v>45197.94152777778</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>45700.57324074074</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -35646,7 +35646,7 @@
         <v>45615.50034722222</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>45112</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>45048.94340277778</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>45075.945</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -35889,7 +35889,7 @@
         <v>44929.92489583333</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -35946,7 +35946,7 @@
         <v>45596.61553240741</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>45435</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>45491</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>45280.92645833334</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -36184,7 +36184,7 @@
         <v>45559.67759259259</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>45636.57329861111</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -36308,7 +36308,7 @@
         <v>44356</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -36365,7 +36365,7 @@
         <v>44593</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>44629</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>45053.94305555556</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -36541,7 +36541,7 @@
         <v>45306</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -36598,7 +36598,7 @@
         <v>44802.94811342593</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>45068</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>45735.69842592593</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -36784,7 +36784,7 @@
         <v>45314.92758101852</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>45379.93637731481</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -36903,7 +36903,7 @@
         <v>45401</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -36965,7 +36965,7 @@
         <v>45401</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -37027,7 +37027,7 @@
         <v>45166</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>45374</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -37141,7 +37141,7 @@
         <v>45723.51079861111</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -37203,7 +37203,7 @@
         <v>45735</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -37265,7 +37265,7 @@
         <v>44323</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -37327,7 +37327,7 @@
         <v>45253</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -37384,7 +37384,7 @@
         <v>45208</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -37441,7 +37441,7 @@
         <v>45540.38586805556</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -37503,7 +37503,7 @@
         <v>44813</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -37565,7 +37565,7 @@
         <v>44074</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>44832</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>44825</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>44812.94709490741</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>44299</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>44805.94592592592</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -37932,7 +37932,7 @@
         <v>44917</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -37989,7 +37989,7 @@
         <v>45747.67739583334</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -38051,7 +38051,7 @@
         <v>45741.63675925926</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -38113,7 +38113,7 @@
         <v>45629.42759259259</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>44915</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>45358.95818287037</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>45107</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45078</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>45441.33313657407</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>44518</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>45702.63572916666</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>45071</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>45764.51113425926</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -38703,7 +38703,7 @@
         <v>45133</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>44405.92065972222</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>45688.67542824074</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         <v>45391.95329861111</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45659.69822916666</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>45712.61502314815</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45054</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -39132,7 +39132,7 @@
         <v>45712.61510416667</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>45630.7862037037</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -39251,7 +39251,7 @@
         <v>45329.95806712963</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -39313,7 +39313,7 @@
         <v>45426</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -39370,7 +39370,7 @@
         <v>45251</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -39427,7 +39427,7 @@
         <v>45145</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -39489,7 +39489,7 @@
         <v>45331.92746527777</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -39546,7 +39546,7 @@
         <v>45254.96516203704</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>45279.94564814815</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>44900.95700231481</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -39732,7 +39732,7 @@
         <v>45091</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -39794,7 +39794,7 @@
         <v>45761.67744212963</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>44869</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>45638</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>45093.92207175926</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>45386.68003472222</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -40084,7 +40084,7 @@
         <v>45645.55672453704</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -40141,7 +40141,7 @@
         <v>44894</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -40198,7 +40198,7 @@
         <v>45223</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>45103</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         <v>45448.94600694445</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>45096.93866898148</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -40436,7 +40436,7 @@
         <v>44879.95768518518</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -40498,7 +40498,7 @@
         <v>44173</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -40555,7 +40555,7 @@
         <v>45393.94459490741</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -40617,7 +40617,7 @@
         <v>45751.34873842593</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -40679,7 +40679,7 @@
         <v>45367.67256944445</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>44888</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -40798,7 +40798,7 @@
         <v>44174</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -40860,7 +40860,7 @@
         <v>45072.92737268518</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -40917,7 +40917,7 @@
         <v>45771.51074074074</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -40979,7 +40979,7 @@
         <v>45341</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -41036,7 +41036,7 @@
         <v>45495.57677083334</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -41093,7 +41093,7 @@
         <v>45065.42894675926</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -41150,7 +41150,7 @@
         <v>45622.46910879629</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -41207,7 +41207,7 @@
         <v>45457.96372685185</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -41269,7 +41269,7 @@
         <v>44932.93927083333</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>45540.34428240741</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -41393,7 +41393,7 @@
         <v>45714.55064814815</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>44866</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45175</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -41574,7 +41574,7 @@
         <v>45534.63537037037</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -41636,7 +41636,7 @@
         <v>45754</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>45257</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -41755,7 +41755,7 @@
         <v>45149.95372685185</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -41817,7 +41817,7 @@
         <v>44944</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -41874,7 +41874,7 @@
         <v>45156</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>44922</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>44517.58137731482</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>45516.94732638889</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>44904.94824074074</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -42174,7 +42174,7 @@
         <v>45665.65684027778</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -42236,7 +42236,7 @@
         <v>44971</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -42298,7 +42298,7 @@
         <v>45614.63869212963</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -42360,7 +42360,7 @@
         <v>44880.95741898148</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -42422,7 +42422,7 @@
         <v>45715.61523148148</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -42484,7 +42484,7 @@
         <v>44876</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -42546,7 +42546,7 @@
         <v>45215</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -42603,7 +42603,7 @@
         <v>45105</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -42665,7 +42665,7 @@
         <v>45756.63601851852</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -42727,7 +42727,7 @@
         <v>45453.95016203704</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -42789,7 +42789,7 @@
         <v>45446.68947916666</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -42846,7 +42846,7 @@
         <v>45456.96569444444</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -42908,7 +42908,7 @@
         <v>45429</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -42965,7 +42965,7 @@
         <v>45737.69822916666</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -43027,7 +43027,7 @@
         <v>44475</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -43084,7 +43084,7 @@
         <v>45561.34663194444</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>45092</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>45384</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>45086.94010416666</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -43322,7 +43322,7 @@
         <v>45726.3860300926</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -43379,7 +43379,7 @@
         <v>44741.94070601852</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>45119</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         <v>45182</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>44336</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>45596.61569444444</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -43679,7 +43679,7 @@
         <v>45596.61582175926</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45338.95405092592</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45356.03784722222</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -43865,7 +43865,7 @@
         <v>45358.95813657407</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>44953</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -43984,7 +43984,7 @@
         <v>44977.98660879629</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45098</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -44103,7 +44103,7 @@
         <v>45309.92524305556</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>45258</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -44217,7 +44217,7 @@
         <v>45574.61634259259</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>45666.44943287037</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45629.35326388889</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45645.36740740741</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -44450,7 +44450,7 @@
         <v>45243</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -44512,7 +44512,7 @@
         <v>45275.95060185185</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>45645.36743055555</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -44631,7 +44631,7 @@
         <v>45469.94876157407</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45769.67767361111</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45534.64285879629</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>45392</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>45392.92903935185</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>45695.44724537037</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -44988,7 +44988,7 @@
         <v>45574.57967592592</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>45063</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>45216.92424768519</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -45159,7 +45159,7 @@
         <v>45344</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -45216,7 +45216,7 @@
         <v>45636.3864699074</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -45278,7 +45278,7 @@
         <v>45769.65659722222</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>45769.67790509259</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>44979</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>44903</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>44980.93865740741</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -45578,7 +45578,7 @@
         <v>44914</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -45640,7 +45640,7 @@
         <v>44519.94440972222</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -45702,7 +45702,7 @@
         <v>45511</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -45764,7 +45764,7 @@
         <v>44972.94140046297</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -45826,7 +45826,7 @@
         <v>45776.40311342593</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -45883,7 +45883,7 @@
         <v>45776.59422453704</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -45945,7 +45945,7 @@
         <v>45426</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -46002,7 +46002,7 @@
         <v>45426</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>45033</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>45751.34859953704</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>45776.50651620371</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -46240,7 +46240,7 @@
         <v>45776.51130787037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -46302,7 +46302,7 @@
         <v>45614.34541666666</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -46359,7 +46359,7 @@
         <v>45635.57331018519</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>44656</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -46483,7 +46483,7 @@
         <v>45372.95762731481</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -46545,7 +46545,7 @@
         <v>44993.94950231481</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -46607,7 +46607,7 @@
         <v>44993</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>45782.36506944444</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45782.51099537037</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -46793,7 +46793,7 @@
         <v>44897</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -46855,7 +46855,7 @@
         <v>45782.44871527778</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -46917,7 +46917,7 @@
         <v>45779.57350694444</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -46979,7 +46979,7 @@
         <v>45779.57392361111</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -47041,7 +47041,7 @@
         <v>44911.93846064815</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -47103,7 +47103,7 @@
         <v>45782.49032407408</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45782.49046296296</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -47227,7 +47227,7 @@
         <v>45782.51109953703</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -47289,7 +47289,7 @@
         <v>45782.67758101852</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -47351,7 +47351,7 @@
         <v>45782.55287037037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -47413,7 +47413,7 @@
         <v>45779.34417824074</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -47475,7 +47475,7 @@
         <v>45779.4281712963</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>45782.36494212963</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -47599,7 +47599,7 @@
         <v>45779.49025462963</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -47661,7 +47661,7 @@
         <v>45448.94520833333</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -47723,7 +47723,7 @@
         <v>44958.94298611111</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
         <v>45488.94747685185</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45609.34412037037</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>45638</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -47966,7 +47966,7 @@
         <v>45187</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45540.38564814815</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>45559.67745370371</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>45425.96239583333</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -48209,7 +48209,7 @@
         <v>45590.40675925926</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -48271,7 +48271,7 @@
         <v>44995.98341435185</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -48333,7 +48333,7 @@
         <v>44995.98644675926</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -48395,7 +48395,7 @@
         <v>45314</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -48452,7 +48452,7 @@
         <v>45154.95525462963</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -48514,7 +48514,7 @@
         <v>45393.94431712963</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -48576,7 +48576,7 @@
         <v>44917</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -48638,7 +48638,7 @@
         <v>44993.94958333333</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>45040.94277777777</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -48762,7 +48762,7 @@
         <v>45211.95061342593</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -48824,7 +48824,7 @@
         <v>44900</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -48886,7 +48886,7 @@
         <v>45566.68125</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -48943,7 +48943,7 @@
         <v>45006</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -49005,7 +49005,7 @@
         <v>45259</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -49062,7 +49062,7 @@
         <v>45572.60363425926</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -49119,7 +49119,7 @@
         <v>45404.99792824074</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -49201,7 +49201,7 @@
         <v>45631.46665509259</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>45158.94231481481</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>44587.92149305555</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>44943.94802083333</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -49439,7 +49439,7 @@
         <v>44903</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -49501,7 +49501,7 @@
         <v>45786.51077546296</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>45611.65679398148</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -49625,7 +49625,7 @@
         <v>44587.92144675926</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -49682,7 +49682,7 @@
         <v>45351.98532407408</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -49744,7 +49744,7 @@
         <v>45306</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -49801,7 +49801,7 @@
         <v>45342</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>45279.94572916667</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -49925,7 +49925,7 @@
         <v>45342.9462037037</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -49987,7 +49987,7 @@
         <v>45574.51185185185</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>45049</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>45616.34479166667</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>45180</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>45180.95927083334</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>44991</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         <v>44153</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -50416,7 +50416,7 @@
         <v>45028</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>45611.5953125</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45608.6078587963</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>45638.34431712963</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45656</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>45327.94459490741</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>45790.40670138889</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>45315.9492824074</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>45197.94171296297</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -50959,7 +50959,7 @@
         <v>45204.94399305555</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>45574.51087962963</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -51083,7 +51083,7 @@
         <v>45574.51090277778</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -51145,7 +51145,7 @@
         <v>45211.95134259259</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>45454.95960648148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -51269,7 +51269,7 @@
         <v>45384</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -51326,7 +51326,7 @@
         <v>45139.94681712963</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -51388,7 +51388,7 @@
         <v>45453.95538194444</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -51450,7 +51450,7 @@
         <v>44886</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -51512,7 +51512,7 @@
         <v>45629.36513888889</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -51569,7 +51569,7 @@
         <v>45545.64957175926</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -51626,7 +51626,7 @@
         <v>45714.60649305556</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -51683,7 +51683,7 @@
         <v>45412.02506944445</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -51745,7 +51745,7 @@
         <v>45554.61583333334</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -51802,7 +51802,7 @@
         <v>45635.47243055556</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -51859,7 +51859,7 @@
         <v>45611</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -51921,7 +51921,7 @@
         <v>45694.69826388889</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -51983,7 +51983,7 @@
         <v>45516.94934027778</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -52045,7 +52045,7 @@
         <v>45436.94636574074</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -52107,7 +52107,7 @@
         <v>45442.96296296296</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>45208</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>45098</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>45792.34527777778</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -52345,7 +52345,7 @@
         <v>45555.38509259259</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>45792.71905092592</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -52464,7 +52464,7 @@
         <v>45792.49023148148</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -52526,7 +52526,7 @@
         <v>45792.63584490741</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -52588,7 +52588,7 @@
         <v>45792.34606481482</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -52650,7 +52650,7 @@
         <v>45009.0897337963</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -52712,7 +52712,7 @@
         <v>45258</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -52769,7 +52769,7 @@
         <v>45191</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -52831,7 +52831,7 @@
         <v>45791.53238425926</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -52888,7 +52888,7 @@
         <v>44628</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -52945,7 +52945,7 @@
         <v>44901</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -53007,7 +53007,7 @@
         <v>44901</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -53069,7 +53069,7 @@
         <v>45182</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -53131,7 +53131,7 @@
         <v>45838.36532407408</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -53193,7 +53193,7 @@
         <v>45762.39876157408</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -53270,7 +53270,7 @@
         <v>45595.42738425926</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -53332,7 +53332,7 @@
         <v>45341.95381944445</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -53394,7 +53394,7 @@
         <v>45835.53166666667</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -53456,7 +53456,7 @@
         <v>45835.40668981482</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -53518,7 +53518,7 @@
         <v>45622.47435185185</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -53575,7 +53575,7 @@
         <v>45429</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -53632,7 +53632,7 @@
         <v>45439.92752314815</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -53689,7 +53689,7 @@
         <v>45639.55240740741</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -53751,7 +53751,7 @@
         <v>45729.51074074074</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -53813,7 +53813,7 @@
         <v>45726.38575231482</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -53870,7 +53870,7 @@
         <v>45737.63574074074</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -53932,7 +53932,7 @@
         <v>45835.4506712963</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -53989,7 +53989,7 @@
         <v>45769.51075231482</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -54051,7 +54051,7 @@
         <v>45793</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -54108,7 +54108,7 @@
         <v>45838.67800925926</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -54165,7 +54165,7 @@
         <v>45838.67887731481</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -54227,7 +54227,7 @@
         <v>45796</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -54284,7 +54284,7 @@
         <v>45796</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -54341,7 +54341,7 @@
         <v>45835.72046296296</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -54398,7 +54398,7 @@
         <v>45323</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -54455,7 +54455,7 @@
         <v>45835.45686342593</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -54512,7 +54512,7 @@
         <v>45190</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -54574,7 +54574,7 @@
         <v>45835.46334490741</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -54631,7 +54631,7 @@
         <v>45581.55260416667</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -54688,7 +54688,7 @@
         <v>45838.48996527777</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -54745,7 +54745,7 @@
         <v>44977.98670138889</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -54807,7 +54807,7 @@
         <v>45796</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -54864,7 +54864,7 @@
         <v>45793.61523148148</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -54926,7 +54926,7 @@
         <v>45392</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -54983,7 +54983,7 @@
         <v>44743</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -55040,7 +55040,7 @@
         <v>45238</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -55102,7 +55102,7 @@
         <v>45603.67850694444</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -55159,7 +55159,7 @@
         <v>45653.44836805556</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -55221,7 +55221,7 @@
         <v>45601.5315625</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -55283,7 +55283,7 @@
         <v>45230</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -55345,7 +55345,7 @@
         <v>45796</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -55402,7 +55402,7 @@
         <v>45638.63600694444</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -55464,7 +55464,7 @@
         <v>45616.5108912037</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -55526,7 +55526,7 @@
         <v>44644</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -55588,7 +55588,7 @@
         <v>45796</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -55645,7 +55645,7 @@
         <v>45441</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -55702,7 +55702,7 @@
         <v>45558.63575231482</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -55764,7 +55764,7 @@
         <v>45420</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -55826,7 +55826,7 @@
         <v>45839.42822916667</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>44657</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -55945,7 +55945,7 @@
         <v>45839.42810185185</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -56007,7 +56007,7 @@
         <v>45838</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -56064,7 +56064,7 @@
         <v>45839.49082175926</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -56121,7 +56121,7 @@
         <v>45590</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -56178,7 +56178,7 @@
         <v>44641</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>44641</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -56302,7 +56302,7 @@
         <v>45646.63605324074</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -56364,7 +56364,7 @@
         <v>45344</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -56421,7 +56421,7 @@
         <v>45840.52225694444</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -56478,7 +56478,7 @@
         <v>45063</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -56535,7 +56535,7 @@
         <v>45645.55665509259</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -56592,7 +56592,7 @@
         <v>45692.51069444444</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -56654,7 +56654,7 @@
         <v>45692.57326388889</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -56716,7 +56716,7 @@
         <v>45266</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -56773,7 +56773,7 @@
         <v>45839.57331018519</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -56835,7 +56835,7 @@
         <v>45574.39081018518</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -56897,7 +56897,7 @@
         <v>45734.4633912037</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -56954,7 +56954,7 @@
         <v>45545.49078703704</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -57011,7 +57011,7 @@
         <v>45839.42864583333</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -57073,7 +57073,7 @@
         <v>45838</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -57130,7 +57130,7 @@
         <v>45839.46915509259</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -57192,7 +57192,7 @@
         <v>45552.44096064815</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -57249,7 +57249,7 @@
         <v>44685</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -57311,7 +57311,7 @@
         <v>45579.47052083333</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -57368,7 +57368,7 @@
         <v>45622</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -57425,7 +57425,7 @@
         <v>45656.64223379629</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -57482,7 +57482,7 @@
         <v>44614</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -57539,7 +57539,7 @@
         <v>44942</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -57601,7 +57601,7 @@
         <v>44994.94296296296</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -57663,7 +57663,7 @@
         <v>45716</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -57725,7 +57725,7 @@
         <v>45716.61487268518</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -57787,7 +57787,7 @@
         <v>45614.34545138889</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -57844,7 +57844,7 @@
         <v>45601.40686342592</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -57906,7 +57906,7 @@
         <v>45056</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -57963,7 +57963,7 @@
         <v>45056</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -58020,7 +58020,7 @@
         <v>45797.63627314815</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -58082,7 +58082,7 @@
         <v>45800.63619212963</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -58144,7 +58144,7 @@
         <v>45751.36490740741</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -58206,7 +58206,7 @@
         <v>44601</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -58263,7 +58263,7 @@
         <v>45453.42041666667</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -58320,7 +58320,7 @@
         <v>45615.47091435185</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -58377,7 +58377,7 @@
         <v>45667.57342592593</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -58439,7 +58439,7 @@
         <v>45667.57347222222</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -58501,7 +58501,7 @@
         <v>45799.34421296296</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -58563,7 +58563,7 @@
         <v>45344.92865740741</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -58620,7 +58620,7 @@
         <v>45344.92873842592</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -58677,7 +58677,7 @@
         <v>45309</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45309</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -58791,7 +58791,7 @@
         <v>44231</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -58848,7 +58848,7 @@
         <v>44655</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -58910,7 +58910,7 @@
         <v>45456.96601851852</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -58972,7 +58972,7 @@
         <v>45688.68196759259</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -59034,7 +59034,7 @@
         <v>45841.57427083333</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -59096,7 +59096,7 @@
         <v>45842.42608796297</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -59153,7 +59153,7 @@
         <v>45195</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -59215,7 +59215,7 @@
         <v>45195.94679398148</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -59277,7 +59277,7 @@
         <v>45195.94685185186</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -59339,7 +59339,7 @@
         <v>45800</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -59396,7 +59396,7 @@
         <v>45730.56346064815</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -59458,7 +59458,7 @@
         <v>44614</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -59515,7 +59515,7 @@
         <v>45692.49008101852</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -59577,7 +59577,7 @@
         <v>45800.42743055556</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -59639,7 +59639,7 @@
         <v>45800.44822916666</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -59701,7 +59701,7 @@
         <v>45800.44862268519</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -59763,7 +59763,7 @@
         <v>45842.38579861111</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -59825,7 +59825,7 @@
         <v>45187</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -59882,7 +59882,7 @@
         <v>45075.94506944445</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -59944,7 +59944,7 @@
         <v>45800.42782407408</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -60006,7 +60006,7 @@
         <v>45841.6571412037</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -60063,7 +60063,7 @@
         <v>45678.67761574074</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -60125,7 +60125,7 @@
         <v>44956.93924768519</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -60187,7 +60187,7 @@
         <v>45314</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>45629.36486111111</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -60301,7 +60301,7 @@
         <v>44803.94351851852</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -60363,7 +60363,7 @@
         <v>45803.5946875</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -60420,7 +60420,7 @@
         <v>45803.61552083334</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -60477,7 +60477,7 @@
         <v>45803.61557870371</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -60534,7 +60534,7 @@
         <v>45758.36487268518</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -60596,7 +60596,7 @@
         <v>45804.59487268519</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -60658,7 +60658,7 @@
         <v>44958</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -60715,7 +60715,7 @@
         <v>45804.42642361111</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -60772,7 +60772,7 @@
         <v>45603.44644675926</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -60834,7 +60834,7 @@
         <v>45148</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -60891,7 +60891,7 @@
         <v>44684.94032407407</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -60953,7 +60953,7 @@
         <v>45622.44774305556</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -61010,7 +61010,7 @@
         <v>45138.94925925926</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -61072,7 +61072,7 @@
         <v>45009.089375</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -61134,7 +61134,7 @@
         <v>45636.38599537037</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>45618.46921296296</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -61258,7 +61258,7 @@
         <v>45195.94672453704</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -61320,7 +61320,7 @@
         <v>45803.53157407408</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -61382,7 +61382,7 @@
         <v>45803.59417824074</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -61439,7 +61439,7 @@
         <v>45112.94303240741</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -61501,7 +61501,7 @@
         <v>45112.94310185185</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -61563,7 +61563,7 @@
         <v>45050.94020833333</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -61625,7 +61625,7 @@
         <v>45804.65672453704</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -61687,7 +61687,7 @@
         <v>45730.53208333333</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -61749,7 +61749,7 @@
         <v>45846.34454861111</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -61811,7 +61811,7 @@
         <v>45847.34474537037</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -61873,7 +61873,7 @@
         <v>45847.61548611111</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45505</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -61992,7 +61992,7 @@
         <v>45847.61513888889</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -62049,7 +62049,7 @@
         <v>45805.61495370371</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -62111,7 +62111,7 @@
         <v>45621.57395833333</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -62173,7 +62173,7 @@
         <v>45847.65703703704</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -62235,7 +62235,7 @@
         <v>45847.34565972222</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -62297,7 +62297,7 @@
         <v>45848.65658564815</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -62359,7 +62359,7 @@
         <v>45574.61184027778</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45574.62297453704</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -62473,7 +62473,7 @@
         <v>45574.63355324074</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -62530,7 +62530,7 @@
         <v>45344.92822916667</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -62587,7 +62587,7 @@
         <v>44614</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -62644,7 +62644,7 @@
         <v>44656.94708333333</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -62706,7 +62706,7 @@
         <v>45671.48989583334</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -62768,7 +62768,7 @@
         <v>45128</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -62830,7 +62830,7 @@
         <v>45797.40800925926</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -62887,7 +62887,7 @@
         <v>45805.46613425926</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -62944,7 +62944,7 @@
         <v>45847.34515046296</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -63006,7 +63006,7 @@
         <v>45847.34597222223</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -63068,7 +63068,7 @@
         <v>44984</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -63125,7 +63125,7 @@
         <v>45847.34528935186</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -63187,7 +63187,7 @@
         <v>44130.9416550926</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -63249,7 +63249,7 @@
         <v>45722.48982638889</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -63306,7 +63306,7 @@
         <v>44571</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -63363,7 +63363,7 @@
         <v>45698.59409722222</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -63425,7 +63425,7 @@
         <v>45180.95907407408</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -63487,7 +63487,7 @@
         <v>45805.57390046296</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -63549,7 +63549,7 @@
         <v>44977.44373842593</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -63606,7 +63606,7 @@
         <v>45672.44898148148</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -63668,7 +63668,7 @@
         <v>45852.53185185185</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -63730,7 +63730,7 @@
         <v>45170</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -63792,7 +63792,7 @@
         <v>45474.50608796296</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -63849,7 +63849,7 @@
         <v>45608.52354166667</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -63911,7 +63911,7 @@
         <v>45253</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -63968,7 +63968,7 @@
         <v>44929</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -64025,7 +64025,7 @@
         <v>45850.34450231482</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -64087,7 +64087,7 @@
         <v>45702.63604166666</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
         <v>44550.92168981482</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -64206,7 +64206,7 @@
         <v>45850.34434027778</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -64263,7 +64263,7 @@
         <v>45469.94667824074</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -64325,7 +64325,7 @@
         <v>45848.49774305556</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -64382,7 +64382,7 @@
         <v>44113</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -64444,7 +64444,7 @@
         <v>45511</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -64506,7 +64506,7 @@
         <v>45257</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -64568,7 +64568,7 @@
         <v>45772.6565625</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -64630,7 +64630,7 @@
         <v>45852.53168981482</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -64692,7 +64692,7 @@
         <v>45145.95326388889</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -64754,7 +64754,7 @@
         <v>44774</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -64811,7 +64811,7 @@
         <v>45604.4190625</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -64868,7 +64868,7 @@
         <v>45849.65663194445</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -64930,7 +64930,7 @@
         <v>45215.94657407407</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -64992,7 +64992,7 @@
         <v>45810.36495370371</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -65054,7 +65054,7 @@
         <v>45848.49761574074</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -65111,7 +65111,7 @@
         <v>44286</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -65168,7 +65168,7 @@
         <v>45210</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -65225,7 +65225,7 @@
         <v>45664.55241898148</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -65287,7 +65287,7 @@
         <v>45230.96376157407</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -65349,7 +65349,7 @@
         <v>44671</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -65406,7 +65406,7 @@
         <v>44820</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -65468,7 +65468,7 @@
         <v>45428.00471064815</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -65530,7 +65530,7 @@
         <v>44839</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -65587,7 +65587,7 @@
         <v>45681.60203703704</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -65644,7 +65644,7 @@
         <v>45679.40362268518</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -65701,7 +65701,7 @@
         <v>45149.95241898148</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -65763,7 +65763,7 @@
         <v>45667.55239583334</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -65825,7 +65825,7 @@
         <v>45854.65663194445</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -65887,7 +65887,7 @@
         <v>45722.44849537037</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -65949,7 +65949,7 @@
         <v>45224</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -66006,7 +66006,7 @@
         <v>45233.92591435185</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -66063,7 +66063,7 @@
         <v>44424</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -66120,7 +66120,7 @@
         <v>45149</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -66177,7 +66177,7 @@
         <v>45367.04693287037</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -66239,7 +66239,7 @@
         <v>45604.63575231482</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -66301,7 +66301,7 @@
         <v>45712.61552083334</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -66363,7 +66363,7 @@
         <v>45775.67747685185</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -66425,7 +66425,7 @@
         <v>44672.94018518519</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -66487,7 +66487,7 @@
         <v>45244.96774305555</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -66549,7 +66549,7 @@
         <v>45769.67802083334</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -66611,7 +66611,7 @@
         <v>45734.45268518518</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -66668,7 +66668,7 @@
         <v>45241.95741898148</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -66730,7 +66730,7 @@
         <v>45241</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -66792,7 +66792,7 @@
         <v>45856.46931712963</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -66854,7 +66854,7 @@
         <v>45855.61523148148</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -66916,7 +66916,7 @@
         <v>45254.96402777778</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -66978,7 +66978,7 @@
         <v>45855.67899305555</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -67035,7 +67035,7 @@
         <v>44746</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -67092,7 +67092,7 @@
         <v>45813.42790509259</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -67154,7 +67154,7 @@
         <v>44806</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -67211,7 +67211,7 @@
         <v>45764</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -67268,7 +67268,7 @@
         <v>45771.36538194444</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -67330,7 +67330,7 @@
         <v>45266.95082175926</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -67392,7 +67392,7 @@
         <v>45184</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -67449,7 +67449,7 @@
         <v>45327.94443287037</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -67511,7 +67511,7 @@
         <v>45860.30229166667</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -67568,7 +67568,7 @@
         <v>45817.71910879629</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -67630,7 +67630,7 @@
         <v>45000</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -67692,7 +67692,7 @@
         <v>45000</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -67754,7 +67754,7 @@
         <v>45818.46898148148</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -67811,7 +67811,7 @@
         <v>45044</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -67873,7 +67873,7 @@
         <v>45351.98496527778</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -67935,7 +67935,7 @@
         <v>45741.63659722222</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -67997,7 +67997,7 @@
         <v>45859.594375</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -68059,7 +68059,7 @@
         <v>45534</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -68116,7 +68116,7 @@
         <v>45222</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -68178,7 +68178,7 @@
         <v>45257.92826388889</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -68235,7 +68235,7 @@
         <v>45306</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -68292,7 +68292,7 @@
         <v>45510</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -68354,7 +68354,7 @@
         <v>45819.6359375</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -68416,7 +68416,7 @@
         <v>45692.48993055556</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -68478,7 +68478,7 @@
         <v>45482.94815972223</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -68540,7 +68540,7 @@
         <v>44855</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -68602,7 +68602,7 @@
         <v>44349.91978009259</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -68659,7 +68659,7 @@
         <v>44067</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -68721,7 +68721,7 @@
         <v>45238</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -68778,7 +68778,7 @@
         <v>45625.51068287037</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -68840,7 +68840,7 @@
         <v>45436.94613425926</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -68902,7 +68902,7 @@
         <v>45695.45868055556</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -68959,7 +68959,7 @@
         <v>45769.65688657408</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -69021,7 +69021,7 @@
         <v>45821.34513888889</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -69083,7 +69083,7 @@
         <v>45825.57675925926</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -69140,7 +69140,7 @@
         <v>45825.58252314815</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -69197,7 +69197,7 @@
         <v>45000</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -69254,7 +69254,7 @@
         <v>45530</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -69311,7 +69311,7 @@
         <v>45476.94533564815</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -69373,7 +69373,7 @@
         <v>44384</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -69430,7 +69430,7 @@
         <v>45825.56762731481</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -69487,7 +69487,7 @@
         <v>45826.65759259259</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -69549,7 +69549,7 @@
         <v>45870.34439814815</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -69611,7 +69611,7 @@
         <v>45505</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -69673,7 +69673,7 @@
         <v>45040</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -69730,7 +69730,7 @@
         <v>44844.95368055555</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -69792,7 +69792,7 @@
         <v>44362</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -69849,7 +69849,7 @@
         <v>45827.53178240741</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -69911,7 +69911,7 @@
         <v>45827.63582175926</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -69973,7 +69973,7 @@
         <v>45482.94891203703</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -70035,7 +70035,7 @@
         <v>45482.9491087963</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -70097,7 +70097,7 @@
         <v>45869.65666666667</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -70159,7 +70159,7 @@
         <v>45869.67744212963</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -70221,7 +70221,7 @@
         <v>45008.01408564814</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -70283,7 +70283,7 @@
         <v>45176</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -70340,7 +70340,7 @@
         <v>45874.69844907407</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -70402,7 +70402,7 @@
         <v>45260</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -70459,7 +70459,7 @@
         <v>45681.6050925926</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -70516,7 +70516,7 @@
         <v>45726.38615740741</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -70573,7 +70573,7 @@
         <v>45726.3862037037</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -70630,7 +70630,7 @@
         <v>45706.34450231482</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -70692,7 +70692,7 @@
         <v>45832.34552083333</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -70754,7 +70754,7 @@
         <v>45103</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -70811,7 +70811,7 @@
         <v>44649.47048611111</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -70873,7 +70873,7 @@
         <v>45069</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -70930,7 +70930,7 @@
         <v>45324</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -70987,7 +70987,7 @@
         <v>45874.67746527777</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -71049,7 +71049,7 @@
         <v>45832.34524305556</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -71106,7 +71106,7 @@
         <v>45832.3459375</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -71168,7 +71168,7 @@
         <v>45183.95563657407</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -71230,7 +71230,7 @@
         <v>44894.79018518519</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -71287,7 +71287,7 @@
         <v>44963</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -71349,7 +71349,7 @@
         <v>45874.59496527778</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -71411,7 +71411,7 @@
         <v>45839</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -71468,7 +71468,7 @@
         <v>45601.55331018518</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -71530,7 +71530,7 @@
         <v>45487.92856481481</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -71587,7 +71587,7 @@
         <v>44914</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -71644,7 +71644,7 @@
         <v>45876.53188657408</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -71706,7 +71706,7 @@
         <v>45834.65662037037</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -71768,7 +71768,7 @@
         <v>45446.57052083333</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -71825,7 +71825,7 @@
         <v>45053.94313657407</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -71887,7 +71887,7 @@
         <v>44880</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -71949,7 +71949,7 @@
         <v>45714</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -72006,7 +72006,7 @@
         <v>45425.96494212963</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -72068,7 +72068,7 @@
         <v>45733.61497685185</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -72130,7 +72130,7 @@
         <v>44991</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -72192,7 +72192,7 @@
         <v>44635</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -72254,7 +72254,7 @@
         <v>44530.94694444445</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -72316,7 +72316,7 @@
         <v>44957.94075231482</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -72378,7 +72378,7 @@
         <v>45552.39113425926</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -72435,7 +72435,7 @@
         <v>44305.92047453704</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -72492,7 +72492,7 @@
         <v>45092</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -72549,7 +72549,7 @@
         <v>44966.95328703704</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -72611,7 +72611,7 @@
         <v>44231</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -72668,7 +72668,7 @@
         <v>45367.69850694444</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -72725,7 +72725,7 @@
         <v>45367.71348379629</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -72782,7 +72782,7 @@
         <v>45034</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -72839,7 +72839,7 @@
         <v>45112</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -72901,7 +72901,7 @@
         <v>44889.95015046297</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -72963,7 +72963,7 @@
         <v>44680</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -73020,7 +73020,7 @@
         <v>45119</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -73077,7 +73077,7 @@
         <v>45289</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -73134,7 +73134,7 @@
         <v>45260.92561342593</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -73191,7 +73191,7 @@
         <v>44939</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -73253,7 +73253,7 @@
         <v>45596.61533564814</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -73315,7 +73315,7 @@
         <v>44236</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -73372,7 +73372,7 @@
         <v>45280</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -73429,7 +73429,7 @@
         <v>44410</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -73486,7 +73486,7 @@
         <v>44670</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -73543,7 +73543,7 @@
         <v>45386</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -73600,7 +73600,7 @@
         <v>45238.96797453704</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -73662,7 +73662,7 @@
         <v>45604.40540509259</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -73719,7 +73719,7 @@
         <v>45604.41625</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -73776,7 +73776,7 @@
         <v>45568.51075231482</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -73838,7 +73838,7 @@
         <v>45546</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -73895,7 +73895,7 @@
         <v>45086</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -73957,7 +73957,7 @@
         <v>45467.96207175926</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -74019,7 +74019,7 @@
         <v>45695.51070601852</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -74081,7 +74081,7 @@
         <v>44869</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -74138,7 +74138,7 @@
         <v>45002.0328125</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -74200,7 +74200,7 @@
         <v>45712.65671296296</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -74257,7 +74257,7 @@
         <v>45241.95724537037</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -74319,7 +74319,7 @@
         <v>45425.96230324074</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -74381,7 +74381,7 @@
         <v>45111.92793981481</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -74443,7 +74443,7 @@
         <v>45357.05300925926</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -74505,7 +74505,7 @@
         <v>45425.96275462963</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -74567,7 +74567,7 @@
         <v>45453.4444212963</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -74624,7 +74624,7 @@
         <v>44929</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -74681,7 +74681,7 @@
         <v>44375</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -74738,7 +74738,7 @@
         <v>45322</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -74795,7 +74795,7 @@
         <v>44918</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -74857,7 +74857,7 @@
         <v>45622.46200231482</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>

--- a/Översikt RAGUNDA.xlsx
+++ b/Översikt RAGUNDA.xlsx
@@ -567,7 +567,7 @@
         <v>45622</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>45376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>45622</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>45560.34460648148</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>45673</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44917</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45804.67787037037</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>45590.42736111111</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45838.67753472222</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44504</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44644</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>45622</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>45560.34532407407</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45104</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45579.53179398148</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>45113</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44644.93650462963</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44473</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>44813</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45367.04916666666</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>45639.55269675926</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45622</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>45790.57334490741</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>44088</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>44062</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>45482.63819444444</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45182</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>45779.49012731481</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45803.59474537037</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44776</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>45790.57349537037</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>45839.42482638889</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>45358.99375</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44805</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>44645.99859953704</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>45327</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44888</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>45779.57335648148</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>45560.34484953704</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>45378</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>45685.36501157407</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>45799.63574074074</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>45799.34461805555</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>45510</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45174</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>45832.34461805555</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>45769.53180555555</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>45121</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>44504</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>45190.96092592592</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>44133</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>45622</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>45827.5110300926</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>45320</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>45120</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>45113</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>45723.40688657408</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>44133</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>44662</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44438</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>45176</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>45810.55061342593</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>45769.67740740741</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>45786.61517361111</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44915</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>45475.94796296296</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>45435.54734953704</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45176</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>45121</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>44336</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         <v>45155</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>45405.57392361111</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44994</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>44111</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>44209</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>45846.41361111111</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>45471.94783564815</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>44875</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>44911</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>45867.63619212963</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>45832.34564814815</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>45769.67778935185</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>45595.44886574074</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>45495.56244212963</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>44994</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>44932</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>45468.97528935185</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>45457</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45728.65684027778</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>45238</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44656</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45002.94356481481</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>45446.95087962963</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45195</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>45244</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>45551.46912037037</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>45832.34578703704</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>45425.96472222222</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>45182</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>45471.94623842592</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>44911</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>45400.94002314815</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>45545.45748842593</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>45674.67744212963</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>45744.61550925926</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>44245</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>44334.62565972222</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>44696</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>44662</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
         <v>44334</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>44334</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>44911</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>45782.44871527778</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>45384</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>45378</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>45610.34415509259</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>45805.34415509259</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>45455.96195601852</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>44113</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>45491</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>45510</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>44677</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>45404</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>45786.61534722222</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>45491</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>45187</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>44855</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>44369.92025462963</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>45071</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>45733</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>45397.95748842593</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>45779.57392361111</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>45751.34650462963</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>45093</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44111</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45631</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>45804.34474537037</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>45847.61498842593</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
         <v>44855</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>45265</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>45516.94723379629</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>44902</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>45209</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>45152</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>45436.94686342592</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>45188</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>45491.94715277778</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45789.36503472222</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>44971</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>44788</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>45838</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         <v>45632.69822916666</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44875</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>45425.96285879629</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
         <v>45691.44769675926</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>44676</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>44855</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>45321</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>45378</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45779.57350694444</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>44865</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>45121</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>45190</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>45800.42782407408</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>45188</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>44680</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>45171</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>45551.65726851852</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44852</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>45852.63597222222</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45854.61494212963</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>45372.95680555556</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45191</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>45241</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>45205</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>45835.344375</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>45526.56393518519</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>45631</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>45394</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>45468.97495370371</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>44993</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>45089</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45583.49642361111</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45722.61543981481</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>44855</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>45153</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45769.65692129629</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>45723.57329861111</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>44826.94976851852</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>45238</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>44462</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>44166</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>44319</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         <v>44705</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44741</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>44062</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>44774.94347222222</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>44741</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>44832</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19845,7 +19845,7 @@
         <v>45751.34795138889</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45636.3863425926</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20025,7 +20025,7 @@
         <v>45468.97461805555</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>45771.3859837963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45301</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>45301</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>45149</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>45779.48993055556</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>45033</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>45789.6360300926</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45754.51064814815</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>45252</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>45266</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45089</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45597.34461805555</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>45153</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>45847.36528935185</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>45183</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>45455.96184027778</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45646.34438657408</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>45341</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>45813.49061342593</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45457.9640625</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45205</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>45769.65736111111</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>45775.67769675926</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>44991</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>45827.57371527778</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -22384,7 +22384,7 @@
         <v>45771.36548611111</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>45785.36525462963</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>44860</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45436.94644675926</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>45838.38627314815</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>44119</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         <v>45468</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>45487.92863425926</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45491.95008101852</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>44369</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>45206</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45624.40665509259</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>45153</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>45154</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>45147</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23729,7 +23729,7 @@
         <v>45722.65670138889</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>45044</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45510</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>45208</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45315</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>45600.55265046296</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44141</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>44157</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
         <v>44195</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
         <v>44214</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         <v>44846</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>44168</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -24611,7 +24611,7 @@
         <v>44517</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>44817</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>44880.95712962963</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>44880.95719907407</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>44855.94125</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>44425</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>44447.92069444444</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>44490.94109953703</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>44519.94534722222</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -25159,7 +25159,7 @@
         <v>44349</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>44210</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44243</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>44280</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>44385.33887731482</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>44280</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>44705</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>44292</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>44518.94394675926</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>44362</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>44846.9522337963</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>44426.94077546296</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>44399</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44818.94929398148</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44860</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>44111</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>44774.94414351852</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>44425</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>44663</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>44823.48666666666</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>44874.95553240741</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>44784.9408912037</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>44837</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44714</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>44670</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>44704.94234953704</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>44855</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>44078</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>44175</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>44194</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>44239</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>44443</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>44273.92081018518</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>44741</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>44132</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>44495.93966435185</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>44126</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>44854</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>44859.95710648148</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>44530</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>44823.94993055556</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>44836.9491087963</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>44125.94493055555</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>44833.95405092592</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27839,7 +27839,7 @@
         <v>44579.68604166667</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44084</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>44883</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>44728.94398148148</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>44287</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>44259</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>44308</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>44308</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>44452</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>44629.56258101852</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>44281</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>44421.97322916667</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>44351</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>44069</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44832.95435185185</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>44586</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44434.94559027778</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44690</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44867</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>44876.95104166667</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>44500.93887731482</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>44111</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>44476</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>44601</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>44714.94162037037</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>44357</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -29391,7 +29391,7 @@
         <v>44477.48994212963</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -29448,7 +29448,7 @@
         <v>44696.93986111111</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>44228</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>44515.93767361111</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>44783</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>44802</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>44864.94835648148</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44308</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44482.92271990741</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44662</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29991,7 +29991,7 @@
         <v>44349.92013888889</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -30048,7 +30048,7 @@
         <v>44824.94635416667</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>44704</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>44685</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -30224,7 +30224,7 @@
         <v>44349.91995370371</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>44308</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>44615</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>44851.95488425926</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>44671</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>44379</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>44075</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>44071</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>44434.94517361111</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>44729.94136574074</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44704.94229166667</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44861</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>44818</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>44777.95504629629</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -31062,7 +31062,7 @@
         <v>44855.9471875</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44833.9519212963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>44099</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>44138</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>44418.9369212963</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>44621</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>44140</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
         <v>44074</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>44074</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -31610,7 +31610,7 @@
         <v>44650</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>44788</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -31724,7 +31724,7 @@
         <v>44853</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>44799.94394675926</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>44574</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>44463.94077546296</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>44431</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>44883.94918981481</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>44124</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>44615</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>44140</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -32262,7 +32262,7 @@
         <v>44815</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -32324,7 +32324,7 @@
         <v>44578.92284722222</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -32381,7 +32381,7 @@
         <v>44599.98685185185</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>44489.94711805556</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -32505,7 +32505,7 @@
         <v>44823</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -32562,7 +32562,7 @@
         <v>44727</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>44494.93930555556</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>44858</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -32748,7 +32748,7 @@
         <v>44425</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>44846</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>44068.62614583333</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>44322</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32986,7 +32986,7 @@
         <v>44361.55445601852</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>44704.9422337963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>44781</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>44495</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>44728.94392361111</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>44854.95390046296</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>44831.94846064815</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -33410,7 +33410,7 @@
         <v>44831.9485300926</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>44784.94157407407</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>44889</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>44402.42243055555</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -33653,7 +33653,7 @@
         <v>44595</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>44356.91935185185</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>44496</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>44734.94193287037</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>44832.95300925926</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>44830</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>44776</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -34072,7 +34072,7 @@
         <v>44704.94217592593</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>44805</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>44315</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -34258,7 +34258,7 @@
         <v>44861</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -34320,7 +34320,7 @@
         <v>45374</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>44512</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>45007</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>45042</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -34548,7 +34548,7 @@
         <v>45384</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>45086.94010416666</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -34667,7 +34667,7 @@
         <v>45726.3860300926</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>45723.67777777778</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>44336</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>45119</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>45182</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>44853.9499537037</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -35024,7 +35024,7 @@
         <v>44323</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45253</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -35143,7 +35143,7 @@
         <v>45743.36</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>45208</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>44813</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>44832</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>45356.03784722222</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -35448,7 +35448,7 @@
         <v>45358.95813657407</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>44812.94709490741</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -35567,7 +35567,7 @@
         <v>44805.94592592592</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -35629,7 +35629,7 @@
         <v>44953</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>44977.98660879629</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>45645.36743055555</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         <v>45098</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>45267</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -35929,7 +35929,7 @@
         <v>45741.63675925926</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>45769.51087962963</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -36053,7 +36053,7 @@
         <v>45769.67767361111</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>45534.64285879629</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -36177,7 +36177,7 @@
         <v>45075.945</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>45358.95818287037</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>45441.33313657407</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>45280.92645833334</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>45645.36740740741</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>45695.44724537037</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>45702.63572916666</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>45764.51113425926</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>44356</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45391.95329861111</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -36767,7 +36767,7 @@
         <v>45392</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>45392.92903935185</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>44802.94811342593</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -36943,7 +36943,7 @@
         <v>45636.3864699074</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>45574.57967592592</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -37062,7 +37062,7 @@
         <v>45426</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45063</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>45254.96516203704</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>44972.94140046297</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>45379.93637731481</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45401</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45401</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>44900.95700231481</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45344</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>45776.40311342593</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -37662,7 +37662,7 @@
         <v>45776.59422453704</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>45761.67744212963</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>45769.65659722222</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -37848,7 +37848,7 @@
         <v>45769.67790509259</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -37910,7 +37910,7 @@
         <v>45093.92207175926</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>45776.50651620371</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -38029,7 +38029,7 @@
         <v>45776.51130787037</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>44903</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45386.68003472222</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>44914</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>44894</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>45782.36506944444</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>45782.51099537037</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>45751.34859953704</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -38510,7 +38510,7 @@
         <v>45782.49032407408</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -38572,7 +38572,7 @@
         <v>45782.49046296296</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45782.51109953703</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -38696,7 +38696,7 @@
         <v>45223</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>45782.67758101852</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45782.55287037037</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>45779.34417824074</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -38939,7 +38939,7 @@
         <v>45779.4281712963</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45782.36494212963</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -39063,7 +39063,7 @@
         <v>44993.94950231481</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>44993</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -39187,7 +39187,7 @@
         <v>45779.49025462963</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -39249,7 +39249,7 @@
         <v>45448.94520833333</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>44958.94298611111</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>45187</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45609.34412037037</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -39492,7 +39492,7 @@
         <v>45559.67745370371</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -39554,7 +39554,7 @@
         <v>44995.98341435185</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -39616,7 +39616,7 @@
         <v>44995.98644675926</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -39678,7 +39678,7 @@
         <v>45314</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -39735,7 +39735,7 @@
         <v>45154.95525462963</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45393.94431712963</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45040.94277777777</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -39921,7 +39921,7 @@
         <v>45259</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>45572.60363425926</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -40035,7 +40035,7 @@
         <v>45006</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>45631.46665509259</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>45786.51077546296</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>45158.94231481481</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45611.65679398148</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>45306</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45279.94572916667</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -40459,7 +40459,7 @@
         <v>45574.51185185185</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>45448.94600694445</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>45049</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>45790.40670138889</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>45611.5953125</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
         <v>45608.6078587963</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -40826,7 +40826,7 @@
         <v>45638.34431712963</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>45656</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>45327.94459490741</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>45315.9492824074</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45204.94399305555</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>45574.51087962963</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>45574.51090277778</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -41255,7 +41255,7 @@
         <v>45211.95134259259</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -41317,7 +41317,7 @@
         <v>45454.95960648148</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>45384</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>45792.34527777778</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -41498,7 +41498,7 @@
         <v>45792.71905092592</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -41560,7 +41560,7 @@
         <v>45792.49023148148</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>45139.94681712963</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -41684,7 +41684,7 @@
         <v>45453.95538194444</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45792.63584490741</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45792.34606481482</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -41870,7 +41870,7 @@
         <v>45629.36513888889</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>45545.64957175926</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>45714.60649305556</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>45412.02506944445</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>44879.95768518518</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>45393.94459490741</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -42227,7 +42227,7 @@
         <v>45791.53238425926</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>45635.47243055556</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -42341,7 +42341,7 @@
         <v>45367.67256944445</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>45611</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>45762.39876157408</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>45694.69826388889</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>45516.94934027778</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>45436.94636574074</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>45769.51075231482</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         <v>45793</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -42842,7 +42842,7 @@
         <v>45796</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -42899,7 +42899,7 @@
         <v>45796</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>45009.0897337963</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>45191</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>44628</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>45796</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45793.61523148148</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>45796</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -43313,7 +43313,7 @@
         <v>45182</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -43375,7 +43375,7 @@
         <v>45796</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>45441</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>45341.95381944445</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -43551,7 +43551,7 @@
         <v>45266</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>45545.49078703704</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         <v>45439.92752314815</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -43722,7 +43722,7 @@
         <v>45639.55240740741</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>45729.51074074074</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>45797.63627314815</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>45800.63619212963</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>45726.38575231482</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -44027,7 +44027,7 @@
         <v>45737.63574074074</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         <v>45799.34421296296</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>45800</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -44208,7 +44208,7 @@
         <v>45800.42743055556</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>45800.44822916666</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
         <v>45800.44862268519</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>45323</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45190</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45803.5946875</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -44570,7 +44570,7 @@
         <v>45803.61552083334</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -44627,7 +44627,7 @@
         <v>45803.61557870371</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -44684,7 +44684,7 @@
         <v>45804.59487268519</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -44746,7 +44746,7 @@
         <v>45804.42642361111</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -44803,7 +44803,7 @@
         <v>44743</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -44860,7 +44860,7 @@
         <v>45603.67850694444</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>45653.44836805556</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45601.5315625</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45638.63600694444</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>45616.5108912037</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>44644</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>45420</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>45803.53157407408</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -45351,7 +45351,7 @@
         <v>45803.59417824074</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>45646.63605324074</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -45470,7 +45470,7 @@
         <v>45050.94020833333</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -45532,7 +45532,7 @@
         <v>45344</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45804.65672453704</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -45651,7 +45651,7 @@
         <v>45063</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -45708,7 +45708,7 @@
         <v>45645.55665509259</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -45765,7 +45765,7 @@
         <v>45846.34454861111</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -45827,7 +45827,7 @@
         <v>45847.34474537037</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -45889,7 +45889,7 @@
         <v>45692.51069444444</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -45951,7 +45951,7 @@
         <v>45692.57326388889</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -46013,7 +46013,7 @@
         <v>45847.61548611111</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -46070,7 +46070,7 @@
         <v>45847.61513888889</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -46127,7 +46127,7 @@
         <v>45805.61495370371</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -46189,7 +46189,7 @@
         <v>45847.65703703704</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45847.34565972222</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -46313,7 +46313,7 @@
         <v>45848.65658564815</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -46375,7 +46375,7 @@
         <v>44866</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>45574.39081018518</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>45734.4633912037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>45552.44096064815</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -46613,7 +46613,7 @@
         <v>45257</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -46670,7 +46670,7 @@
         <v>45579.47052083333</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>45797.40800925926</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -46784,7 +46784,7 @@
         <v>45805.46613425926</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>45656.64223379629</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>45847.34515046296</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -46960,7 +46960,7 @@
         <v>45847.34597222223</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -47022,7 +47022,7 @@
         <v>44614</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>44944</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -47136,7 +47136,7 @@
         <v>45847.34528935186</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -47198,7 +47198,7 @@
         <v>44130.9416550926</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -47260,7 +47260,7 @@
         <v>45722.48982638889</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>45716</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -47379,7 +47379,7 @@
         <v>45716.61487268518</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -47441,7 +47441,7 @@
         <v>44922</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -47498,7 +47498,7 @@
         <v>44517.58137731482</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -47555,7 +47555,7 @@
         <v>45056</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -47612,7 +47612,7 @@
         <v>45056</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -47669,7 +47669,7 @@
         <v>45516.94732638889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -47731,7 +47731,7 @@
         <v>44601</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -47788,7 +47788,7 @@
         <v>45805.57390046296</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -47850,7 +47850,7 @@
         <v>45453.42041666667</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -47907,7 +47907,7 @@
         <v>45615.47091435185</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45667.57342592593</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -48026,7 +48026,7 @@
         <v>45667.57347222222</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         <v>45672.44898148148</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -48150,7 +48150,7 @@
         <v>45852.53185185185</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -48212,7 +48212,7 @@
         <v>44655</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45453.95016203704</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -48336,7 +48336,7 @@
         <v>45446.68947916666</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>45456.96569444444</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>45850.34450231482</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44550.92168981482</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>45850.34434027778</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         <v>45195</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>45195.94679398148</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -48755,7 +48755,7 @@
         <v>45195.94685185186</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>44475</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -48874,7 +48874,7 @@
         <v>44614</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45692.49008101852</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45848.49774305556</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>44113</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45187</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -49169,7 +49169,7 @@
         <v>45678.67761574074</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>44336</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -49288,7 +49288,7 @@
         <v>45148</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -49345,7 +49345,7 @@
         <v>44684.94032407407</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>45138.94925925926</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>45309.92524305556</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>45636.38599537037</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45195.94672453704</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>45852.53168981482</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -49712,7 +49712,7 @@
         <v>45604.4190625</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>45849.65663194445</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45243</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45275.95060185185</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -49955,7 +49955,7 @@
         <v>45810.36495370371</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -50017,7 +50017,7 @@
         <v>45112.94303240741</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>45112.94310185185</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -50141,7 +50141,7 @@
         <v>45730.53208333333</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -50203,7 +50203,7 @@
         <v>45848.49761574074</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>45469.94876157407</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -50322,7 +50322,7 @@
         <v>45505</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -50384,7 +50384,7 @@
         <v>45230.96376157407</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -50446,7 +50446,7 @@
         <v>45621.57395833333</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>45428.00471064815</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>45574.61184027778</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>45574.62297453704</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -50684,7 +50684,7 @@
         <v>45574.63355324074</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -50741,7 +50741,7 @@
         <v>44614</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -50798,7 +50798,7 @@
         <v>44656.94708333333</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -50860,7 +50860,7 @@
         <v>45854.65663194445</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45216.92424768519</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -50979,7 +50979,7 @@
         <v>45698.59409722222</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -51041,7 +51041,7 @@
         <v>45180.95907407408</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -51103,7 +51103,7 @@
         <v>44979</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -51160,7 +51160,7 @@
         <v>44980.93865740741</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>44519.94440972222</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -51284,7 +51284,7 @@
         <v>45253</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>45511</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -51403,7 +51403,7 @@
         <v>45769.67802083334</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -51465,7 +51465,7 @@
         <v>45426</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -51522,7 +51522,7 @@
         <v>45426</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>45033</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -51636,7 +51636,7 @@
         <v>45856.46931712963</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -51698,7 +51698,7 @@
         <v>45855.61523148148</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         <v>45855.67899305555</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -51817,7 +51817,7 @@
         <v>45614.34541666666</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -51874,7 +51874,7 @@
         <v>45813.42790509259</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -51936,7 +51936,7 @@
         <v>45635.57331018519</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45702.63604166666</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -52060,7 +52060,7 @@
         <v>44656</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -52122,7 +52122,7 @@
         <v>45372.95762731481</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -52184,7 +52184,7 @@
         <v>44897</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -52246,7 +52246,7 @@
         <v>44911.93846064815</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -52308,7 +52308,7 @@
         <v>45257</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -52370,7 +52370,7 @@
         <v>45772.6565625</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -52432,7 +52432,7 @@
         <v>45764</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -52489,7 +52489,7 @@
         <v>45488.94747685185</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>45638</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         <v>45540.38564814815</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -52670,7 +52670,7 @@
         <v>45425.96239583333</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -52732,7 +52732,7 @@
         <v>45590.40675925926</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -52794,7 +52794,7 @@
         <v>45860.30229166667</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>45145.95326388889</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -52913,7 +52913,7 @@
         <v>44774</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -52970,7 +52970,7 @@
         <v>45215.94657407407</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -53032,7 +53032,7 @@
         <v>45817.71910879629</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -53094,7 +53094,7 @@
         <v>45818.46898148148</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -53151,7 +53151,7 @@
         <v>45859.594375</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -53213,7 +53213,7 @@
         <v>44917</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -53275,7 +53275,7 @@
         <v>44993.94958333333</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>44671</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -53394,7 +53394,7 @@
         <v>44820</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -53456,7 +53456,7 @@
         <v>45211.95061342593</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -53518,7 +53518,7 @@
         <v>44839</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -53575,7 +53575,7 @@
         <v>45149.95241898148</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -53637,7 +53637,7 @@
         <v>45722.44849537037</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -53699,7 +53699,7 @@
         <v>45224</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -53756,7 +53756,7 @@
         <v>45233.92591435185</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -53813,7 +53813,7 @@
         <v>45819.6359375</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -53875,7 +53875,7 @@
         <v>44900</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -53937,7 +53937,7 @@
         <v>45367.04693287037</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -53999,7 +53999,7 @@
         <v>45566.68125</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -54056,7 +54056,7 @@
         <v>45712.61552083334</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -54118,7 +54118,7 @@
         <v>45775.67747685185</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -54180,7 +54180,7 @@
         <v>44672.94018518519</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>45404.99792824074</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -54324,7 +54324,7 @@
         <v>45244.96774305555</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -54386,7 +54386,7 @@
         <v>44587.92149305555</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -54443,7 +54443,7 @@
         <v>45821.34513888889</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -54505,7 +54505,7 @@
         <v>44943.94802083333</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -54567,7 +54567,7 @@
         <v>45825.57675925926</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -54624,7 +54624,7 @@
         <v>45825.58252314815</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -54681,7 +54681,7 @@
         <v>45734.45268518518</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -54738,7 +54738,7 @@
         <v>44903</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -54800,7 +54800,7 @@
         <v>44587.92144675926</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -54857,7 +54857,7 @@
         <v>45351.98532407408</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>45342</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -54981,7 +54981,7 @@
         <v>45342.9462037037</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -55043,7 +55043,7 @@
         <v>45241.95741898148</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -55105,7 +55105,7 @@
         <v>45241</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -55167,7 +55167,7 @@
         <v>45254.96402777778</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -55229,7 +55229,7 @@
         <v>45616.34479166667</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45180</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -55353,7 +55353,7 @@
         <v>45180.95927083334</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -55415,7 +55415,7 @@
         <v>45825.56762731481</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>44991</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -55534,7 +55534,7 @@
         <v>44746</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>45826.65759259259</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -55653,7 +55653,7 @@
         <v>45870.34439814815</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -55715,7 +55715,7 @@
         <v>45505</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -55777,7 +55777,7 @@
         <v>44806</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -55834,7 +55834,7 @@
         <v>44153</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -55891,7 +55891,7 @@
         <v>45028</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -55948,7 +55948,7 @@
         <v>45827.53178240741</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -56010,7 +56010,7 @@
         <v>45827.63582175926</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -56072,7 +56072,7 @@
         <v>45869.65666666667</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -56134,7 +56134,7 @@
         <v>45869.67744212963</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -56196,7 +56196,7 @@
         <v>45771.36538194444</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -56258,7 +56258,7 @@
         <v>45874.69844907407</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -56320,7 +56320,7 @@
         <v>45266.95082175926</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -56382,7 +56382,7 @@
         <v>45197.94171296297</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -56444,7 +56444,7 @@
         <v>45327.94443287037</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -56506,7 +56506,7 @@
         <v>45044</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -56568,7 +56568,7 @@
         <v>45351.98496527778</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -56630,7 +56630,7 @@
         <v>45741.63659722222</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -56692,7 +56692,7 @@
         <v>45832.34552083333</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -56754,7 +56754,7 @@
         <v>44886</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -56816,7 +56816,7 @@
         <v>45222</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -56878,7 +56878,7 @@
         <v>45257.92826388889</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -56935,7 +56935,7 @@
         <v>45306</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -56992,7 +56992,7 @@
         <v>45874.67746527777</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -57054,7 +57054,7 @@
         <v>45832.34524305556</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -57111,7 +57111,7 @@
         <v>45832.3459375</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>45554.61583333334</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -57230,7 +57230,7 @@
         <v>45482.94815972223</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -57292,7 +57292,7 @@
         <v>45874.59496527778</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -57354,7 +57354,7 @@
         <v>45839</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -57411,7 +57411,7 @@
         <v>44067</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -57473,7 +57473,7 @@
         <v>45238</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -57530,7 +57530,7 @@
         <v>45436.94613425926</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -57592,7 +57592,7 @@
         <v>45876.53188657408</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -57654,7 +57654,7 @@
         <v>45834.65662037037</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -57716,7 +57716,7 @@
         <v>45769.65688657408</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -57778,7 +57778,7 @@
         <v>45000</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -57835,7 +57835,7 @@
         <v>45530</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -57892,7 +57892,7 @@
         <v>45835.4506712963</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -57949,7 +57949,7 @@
         <v>45838</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -58006,7 +58006,7 @@
         <v>45260</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>45442.96296296296</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -58125,7 +58125,7 @@
         <v>45835.72046296296</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -58182,7 +58182,7 @@
         <v>45208</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -58239,7 +58239,7 @@
         <v>45098</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -58296,7 +58296,7 @@
         <v>45838</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -58353,7 +58353,7 @@
         <v>45838.67887731481</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>45555.38509259259</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>45838.48996527777</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -58529,7 +58529,7 @@
         <v>45103</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -58586,7 +58586,7 @@
         <v>44649.47048611111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -58648,7 +58648,7 @@
         <v>45835.40668981482</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -58710,7 +58710,7 @@
         <v>45069</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -58767,7 +58767,7 @@
         <v>45838.67800925926</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -58824,7 +58824,7 @@
         <v>45835.53166666667</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -58886,7 +58886,7 @@
         <v>45324</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -58943,7 +58943,7 @@
         <v>45835.46334490741</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -59000,7 +59000,7 @@
         <v>45835.45686342593</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -59057,7 +59057,7 @@
         <v>45183.95563657407</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -59119,7 +59119,7 @@
         <v>45839.42822916667</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -59181,7 +59181,7 @@
         <v>45839.46915509259</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -59243,7 +59243,7 @@
         <v>45838.36532407408</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -59305,7 +59305,7 @@
         <v>45258</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -59362,7 +59362,7 @@
         <v>44894.79018518519</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -59419,7 +59419,7 @@
         <v>45839.49082175926</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -59476,7 +59476,7 @@
         <v>45839.42810185185</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -59538,7 +59538,7 @@
         <v>44963</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -59600,7 +59600,7 @@
         <v>44901</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -59662,7 +59662,7 @@
         <v>44901</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -59724,7 +59724,7 @@
         <v>45601.55331018518</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -59786,7 +59786,7 @@
         <v>45839.42864583333</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -59848,7 +59848,7 @@
         <v>45487.92856481481</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -59905,7 +59905,7 @@
         <v>45839.57331018519</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -59967,7 +59967,7 @@
         <v>44914</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -60024,7 +60024,7 @@
         <v>45840.52225694444</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -60081,7 +60081,7 @@
         <v>45595.42738425926</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -60143,7 +60143,7 @@
         <v>45622.47435185185</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -60200,7 +60200,7 @@
         <v>45429</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -60257,7 +60257,7 @@
         <v>45446.57052083333</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -60314,7 +60314,7 @@
         <v>45053.94313657407</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -60376,7 +60376,7 @@
         <v>44880</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -60438,7 +60438,7 @@
         <v>45714</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -60495,7 +60495,7 @@
         <v>45425.96494212963</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -60557,7 +60557,7 @@
         <v>45842.38579861111</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -60619,7 +60619,7 @@
         <v>45841.57427083333</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -60681,7 +60681,7 @@
         <v>45581.55260416667</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -60738,7 +60738,7 @@
         <v>45842.42608796297</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -60795,7 +60795,7 @@
         <v>45733.61497685185</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -60857,7 +60857,7 @@
         <v>44977.98670138889</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -60919,7 +60919,7 @@
         <v>45392</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -60976,7 +60976,7 @@
         <v>45841.6571412037</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -61033,7 +61033,7 @@
         <v>45238</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -61095,7 +61095,7 @@
         <v>44991</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -61157,7 +61157,7 @@
         <v>45230</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -61219,7 +61219,7 @@
         <v>44635</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -61281,7 +61281,7 @@
         <v>45558.63575231482</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -61343,7 +61343,7 @@
         <v>44657</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -61400,7 +61400,7 @@
         <v>45590</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -61457,7 +61457,7 @@
         <v>44530.94694444445</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -61519,7 +61519,7 @@
         <v>44641</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -61581,7 +61581,7 @@
         <v>44641</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -61643,7 +61643,7 @@
         <v>44957.94075231482</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -61705,7 +61705,7 @@
         <v>45552.39113425926</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -61762,7 +61762,7 @@
         <v>44305.92047453704</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -61819,7 +61819,7 @@
         <v>45092</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -61876,7 +61876,7 @@
         <v>44685</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -61938,7 +61938,7 @@
         <v>45622</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -61995,7 +61995,7 @@
         <v>44942</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -62057,7 +62057,7 @@
         <v>44994.94296296296</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -62119,7 +62119,7 @@
         <v>45614.34545138889</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -62176,7 +62176,7 @@
         <v>44966.95328703704</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -62238,7 +62238,7 @@
         <v>44231</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -62295,7 +62295,7 @@
         <v>45601.40686342592</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -62357,7 +62357,7 @@
         <v>45751.36490740741</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -62419,7 +62419,7 @@
         <v>45344.92865740741</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -62476,7 +62476,7 @@
         <v>45344.92873842592</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -62533,7 +62533,7 @@
         <v>45309</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -62590,7 +62590,7 @@
         <v>45309</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -62647,7 +62647,7 @@
         <v>44231</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -62704,7 +62704,7 @@
         <v>45456.96601851852</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -62766,7 +62766,7 @@
         <v>45688.68196759259</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -62828,7 +62828,7 @@
         <v>45367.69850694444</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -62885,7 +62885,7 @@
         <v>45367.71348379629</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -62942,7 +62942,7 @@
         <v>45034</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -62999,7 +62999,7 @@
         <v>45730.56346064815</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -63061,7 +63061,7 @@
         <v>45112</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -63123,7 +63123,7 @@
         <v>45075.94506944445</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -63185,7 +63185,7 @@
         <v>44889.95015046297</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -63247,7 +63247,7 @@
         <v>44680</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -63304,7 +63304,7 @@
         <v>44956.93924768519</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -63366,7 +63366,7 @@
         <v>45314</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -63423,7 +63423,7 @@
         <v>45119</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -63480,7 +63480,7 @@
         <v>45289</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -63537,7 +63537,7 @@
         <v>45629.36486111111</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -63594,7 +63594,7 @@
         <v>44803.94351851852</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -63656,7 +63656,7 @@
         <v>45260.92561342593</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -63713,7 +63713,7 @@
         <v>45758.36487268518</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -63775,7 +63775,7 @@
         <v>44939</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -63837,7 +63837,7 @@
         <v>44958</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -63894,7 +63894,7 @@
         <v>45603.44644675926</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -63956,7 +63956,7 @@
         <v>45622.44774305556</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -64013,7 +64013,7 @@
         <v>45009.089375</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -64075,7 +64075,7 @@
         <v>45618.46921296296</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -64137,7 +64137,7 @@
         <v>45596.61533564814</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -64199,7 +64199,7 @@
         <v>45344.92822916667</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -64256,7 +64256,7 @@
         <v>44236</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -64313,7 +64313,7 @@
         <v>45280</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -64370,7 +64370,7 @@
         <v>45671.48989583334</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -64432,7 +64432,7 @@
         <v>45128</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -64494,7 +64494,7 @@
         <v>44410</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -64551,7 +64551,7 @@
         <v>44670</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -64608,7 +64608,7 @@
         <v>44984</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -64665,7 +64665,7 @@
         <v>44571</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -64722,7 +64722,7 @@
         <v>45386</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -64779,7 +64779,7 @@
         <v>44977.44373842593</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -64836,7 +64836,7 @@
         <v>45170</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -64898,7 +64898,7 @@
         <v>45238.96797453704</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -64960,7 +64960,7 @@
         <v>45474.50608796296</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -65017,7 +65017,7 @@
         <v>45604.40540509259</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -65074,7 +65074,7 @@
         <v>45604.41625</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -65131,7 +65131,7 @@
         <v>45608.52354166667</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -65193,7 +65193,7 @@
         <v>45568.51075231482</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -65255,7 +65255,7 @@
         <v>45546</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -65312,7 +65312,7 @@
         <v>44929</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -65369,7 +65369,7 @@
         <v>45086</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -65431,7 +65431,7 @@
         <v>45467.96207175926</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -65493,7 +65493,7 @@
         <v>45469.94667824074</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -65555,7 +65555,7 @@
         <v>45695.51070601852</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -65617,7 +65617,7 @@
         <v>45511</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -65679,7 +65679,7 @@
         <v>44869</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -65736,7 +65736,7 @@
         <v>44286</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -65793,7 +65793,7 @@
         <v>45210</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -65850,7 +65850,7 @@
         <v>45664.55241898148</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -65912,7 +65912,7 @@
         <v>45002.0328125</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -65974,7 +65974,7 @@
         <v>45712.65671296296</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -66031,7 +66031,7 @@
         <v>45681.60203703704</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -66088,7 +66088,7 @@
         <v>45679.40362268518</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -66145,7 +66145,7 @@
         <v>45667.55239583334</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -66207,7 +66207,7 @@
         <v>45241.95724537037</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -66269,7 +66269,7 @@
         <v>45425.96230324074</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -66331,7 +66331,7 @@
         <v>44424</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -66388,7 +66388,7 @@
         <v>45149</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -66445,7 +66445,7 @@
         <v>45604.63575231482</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -66507,7 +66507,7 @@
         <v>45111.92793981481</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -66569,7 +66569,7 @@
         <v>45357.05300925926</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -66631,7 +66631,7 @@
         <v>45425.96275462963</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -66693,7 +66693,7 @@
         <v>45184</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -66750,7 +66750,7 @@
         <v>45000</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -66812,7 +66812,7 @@
         <v>45000</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -66874,7 +66874,7 @@
         <v>45453.4444212963</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -66931,7 +66931,7 @@
         <v>44929</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -66988,7 +66988,7 @@
         <v>44375</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -67045,7 +67045,7 @@
         <v>45322</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -67102,7 +67102,7 @@
         <v>44918</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -67164,7 +67164,7 @@
         <v>45534</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -67221,7 +67221,7 @@
         <v>45510</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -67283,7 +67283,7 @@
         <v>45692.48993055556</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -67345,7 +67345,7 @@
         <v>44855</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -67407,7 +67407,7 @@
         <v>45622.46200231482</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -67464,7 +67464,7 @@
         <v>44349.91978009259</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -67521,7 +67521,7 @@
         <v>45625.51068287037</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -67583,7 +67583,7 @@
         <v>45695.45868055556</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -67640,7 +67640,7 @@
         <v>45000</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -67702,7 +67702,7 @@
         <v>45681.5315625</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -67764,7 +67764,7 @@
         <v>45476.94533564815</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -67826,7 +67826,7 @@
         <v>45673.66358796296</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -67883,7 +67883,7 @@
         <v>44680.95246527778</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -67945,7 +67945,7 @@
         <v>44384</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -68002,7 +68002,7 @@
         <v>45601.59518518519</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -68064,7 +68064,7 @@
         <v>44879</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -68126,7 +68126,7 @@
         <v>45040</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -68183,7 +68183,7 @@
         <v>44844.95368055555</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -68245,7 +68245,7 @@
         <v>45009</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -68302,7 +68302,7 @@
         <v>44362</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -68359,7 +68359,7 @@
         <v>45482.94891203703</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -68421,7 +68421,7 @@
         <v>45482.9491087963</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -68483,7 +68483,7 @@
         <v>45436.94628472222</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -68545,7 +68545,7 @@
         <v>45425.96263888889</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -68607,7 +68607,7 @@
         <v>45008.01408564814</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -68669,7 +68669,7 @@
         <v>45176</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -68726,7 +68726,7 @@
         <v>45615.50034722222</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -68783,7 +68783,7 @@
         <v>45048.94340277778</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -68845,7 +68845,7 @@
         <v>44929.92489583333</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -68902,7 +68902,7 @@
         <v>45596.61553240741</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -68964,7 +68964,7 @@
         <v>45435</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -69021,7 +69021,7 @@
         <v>45681.6050925926</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -69078,7 +69078,7 @@
         <v>45559.67759259259</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -69140,7 +69140,7 @@
         <v>45636.57329861111</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -69202,7 +69202,7 @@
         <v>44593</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -69259,7 +69259,7 @@
         <v>45726.38615740741</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -69316,7 +69316,7 @@
         <v>45726.3862037037</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -69373,7 +69373,7 @@
         <v>45706.34450231482</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -69435,7 +69435,7 @@
         <v>45715.59405092592</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -69497,7 +69497,7 @@
         <v>45166</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -69554,7 +69554,7 @@
         <v>44889</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -69611,7 +69611,7 @@
         <v>45723.51079861111</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -69673,7 +69673,7 @@
         <v>45735.53177083333</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -69735,7 +69735,7 @@
         <v>45735.5517824074</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -69792,7 +69792,7 @@
         <v>45730.42738425926</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -69854,7 +69854,7 @@
         <v>45733.61554398148</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -69916,7 +69916,7 @@
         <v>45197.94152777778</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -69978,7 +69978,7 @@
         <v>45700.57324074074</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -70040,7 +70040,7 @@
         <v>45112</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -70102,7 +70102,7 @@
         <v>45747.67739583334</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -70164,7 +70164,7 @@
         <v>45491</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -70226,7 +70226,7 @@
         <v>45629.42759259259</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -70288,7 +70288,7 @@
         <v>44629</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -70345,7 +70345,7 @@
         <v>45053.94305555556</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -70407,7 +70407,7 @@
         <v>45306</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -70464,7 +70464,7 @@
         <v>45107</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -70521,7 +70521,7 @@
         <v>45068</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -70583,7 +70583,7 @@
         <v>44518</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -70640,7 +70640,7 @@
         <v>45735.69842592593</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -70702,7 +70702,7 @@
         <v>45071</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -70759,7 +70759,7 @@
         <v>45314.92758101852</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -70816,7 +70816,7 @@
         <v>45133</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -70878,7 +70878,7 @@
         <v>45712.61502314815</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -70940,7 +70940,7 @@
         <v>45735</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -71002,7 +71002,7 @@
         <v>45712.61510416667</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -71064,7 +71064,7 @@
         <v>45630.7862037037</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -71121,7 +71121,7 @@
         <v>45329.95806712963</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -71183,7 +71183,7 @@
         <v>45540.38586805556</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -71245,7 +71245,7 @@
         <v>44074</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -71307,7 +71307,7 @@
         <v>45331.92746527777</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -71364,7 +71364,7 @@
         <v>44825</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -71426,7 +71426,7 @@
         <v>44299</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -71483,7 +71483,7 @@
         <v>44917</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -71540,7 +71540,7 @@
         <v>45103</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -71597,7 +71597,7 @@
         <v>44915</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -71659,7 +71659,7 @@
         <v>45078</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -71716,7 +71716,7 @@
         <v>44405.92065972222</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -71773,7 +71773,7 @@
         <v>45688.67542824074</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -71835,7 +71835,7 @@
         <v>45072.92737268518</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -71892,7 +71892,7 @@
         <v>45065.42894675926</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -71949,7 +71949,7 @@
         <v>45622.46910879629</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -72006,7 +72006,7 @@
         <v>45659.69822916666</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -72068,7 +72068,7 @@
         <v>45457.96372685185</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -72130,7 +72130,7 @@
         <v>45054</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -72192,7 +72192,7 @@
         <v>44932.93927083333</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -72254,7 +72254,7 @@
         <v>45540.34428240741</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -72316,7 +72316,7 @@
         <v>45714.55064814815</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -72373,7 +72373,7 @@
         <v>45175</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -72435,7 +72435,7 @@
         <v>45534.63537037037</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -72497,7 +72497,7 @@
         <v>45251</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -72554,7 +72554,7 @@
         <v>45145</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -72616,7 +72616,7 @@
         <v>45279.94564814815</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -72678,7 +72678,7 @@
         <v>45149.95372685185</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -72740,7 +72740,7 @@
         <v>45091</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -72802,7 +72802,7 @@
         <v>44904.94824074074</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -72864,7 +72864,7 @@
         <v>45665.65684027778</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -72926,7 +72926,7 @@
         <v>44869</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -72983,7 +72983,7 @@
         <v>45638</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -73040,7 +73040,7 @@
         <v>45645.55672453704</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -73097,7 +73097,7 @@
         <v>44971</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -73159,7 +73159,7 @@
         <v>45614.63869212963</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -73221,7 +73221,7 @@
         <v>45096.93866898148</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -73283,7 +73283,7 @@
         <v>44880.95741898148</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -73345,7 +73345,7 @@
         <v>44173</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -73402,7 +73402,7 @@
         <v>45715.61523148148</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -73464,7 +73464,7 @@
         <v>44876</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -73526,7 +73526,7 @@
         <v>45751.34873842593</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -73588,7 +73588,7 @@
         <v>45215</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -73645,7 +73645,7 @@
         <v>44888</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -73707,7 +73707,7 @@
         <v>44174</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -73769,7 +73769,7 @@
         <v>45105</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -73831,7 +73831,7 @@
         <v>45756.63601851852</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -73893,7 +73893,7 @@
         <v>45771.51074074074</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -73955,7 +73955,7 @@
         <v>45341</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -74012,7 +74012,7 @@
         <v>45495.57677083334</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -74069,7 +74069,7 @@
         <v>45429</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -74126,7 +74126,7 @@
         <v>45737.69822916666</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -74188,7 +74188,7 @@
         <v>45092</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -74245,7 +74245,7 @@
         <v>45754</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -74307,7 +74307,7 @@
         <v>44741.94070601852</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -74369,7 +74369,7 @@
         <v>45596.61569444444</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -74431,7 +74431,7 @@
         <v>45596.61582175926</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -74493,7 +74493,7 @@
         <v>45156</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -74555,7 +74555,7 @@
         <v>45338.95405092592</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -74617,7 +74617,7 @@
         <v>45258</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -74674,7 +74674,7 @@
         <v>45561.34663194444</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -74736,7 +74736,7 @@
         <v>45574.61634259259</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -74793,7 +74793,7 @@
         <v>45666.44943287037</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -74850,7 +74850,7 @@
         <v>45629.35326388889</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>

--- a/Översikt RAGUNDA.xlsx
+++ b/Översikt RAGUNDA.xlsx
@@ -567,7 +567,7 @@
         <v>45622</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>45376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>45622</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>45560.34460648148</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>45673</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44917</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45804.67787037037</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>45590.42736111111</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45838.67753472222</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44504</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44644</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>45622</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>45560.34532407407</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45104</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45579.53179398148</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>45113</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44644.93650462963</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44473</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>44813</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45367.04916666666</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>45639.55269675926</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45622</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>45790.57334490741</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>44088</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>44062</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>45482.63819444444</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45182</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>45779.49012731481</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45803.59474537037</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44776</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>45790.57349537037</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         <v>45839.42482638889</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>45358.99375</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>44805</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>44645.99859953704</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>45327</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>44888</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>45779.57335648148</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>45560.34484953704</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>45378</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>45685.36501157407</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>45799.63574074074</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>45799.34461805555</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>45510</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>45174</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>45832.34461805555</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         <v>45769.53180555555</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>45121</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>44504</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>45190.96092592592</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>44133</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>45622</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>45827.5110300926</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>45320</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>45120</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>45113</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>45723.40688657408</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>44133</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>44662</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44438</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
         <v>45176</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>45810.55061342593</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>45769.67740740741</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>45786.61517361111</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44915</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>45475.94796296296</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>45435.54734953704</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45176</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7646,7 +7646,7 @@
         <v>45121</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>44336</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         <v>45155</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>45405.57392361111</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44994</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>44111</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>44209</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>45846.41361111111</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>45471.94783564815</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>44875</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>44911</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>45867.63619212963</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
         <v>45832.34564814815</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>45769.67778935185</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>45595.44886574074</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>45495.56244212963</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>44994</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>44932</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>45468.97528935185</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>45457</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         <v>45728.65684027778</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>45238</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44656</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45002.94356481481</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>45446.95087962963</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45195</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>45244</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>45551.46912037037</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>45832.34578703704</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>45425.96472222222</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>45182</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         <v>45471.94623842592</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>44911</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>45400.94002314815</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>45545.45748842593</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>45674.67744212963</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
         <v>45744.61550925926</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>44245</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>44334.62565972222</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>44696</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>44662</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
         <v>44334</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>44334</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>44911</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>45782.44871527778</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>45384</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>45378</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>45610.34415509259</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>45805.34415509259</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>45455.96195601852</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>44113</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>45491</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>45510</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>44677</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>45404</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>45786.61534722222</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>45491</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>45187</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>44855</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>44369.92025462963</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>45071</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>45733</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>45397.95748842593</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>45779.57392361111</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>45751.34650462963</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>45093</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>44111</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45631</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>45804.34474537037</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>45847.61498842593</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
         <v>44855</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>45265</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>45516.94723379629</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>44902</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>45209</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>45152</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>45436.94686342592</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>45188</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>45491.94715277778</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45789.36503472222</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>44971</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>44788</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>45838</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         <v>45632.69822916666</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44875</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>45425.96285879629</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
         <v>45691.44769675926</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>44676</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>44855</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>45321</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>45378</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45779.57350694444</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>44865</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>45121</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>45190</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>45800.42782407408</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>45188</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>44680</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>45171</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>45551.65726851852</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44852</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>45852.63597222222</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45854.61494212963</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>45372.95680555556</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45191</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>45241</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>45205</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         <v>45835.344375</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>45526.56393518519</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>45631</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>45394</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18040,7 +18040,7 @@
         <v>45468.97495370371</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>44993</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>45089</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45583.49642361111</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45722.61543981481</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>44855</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>45153</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45769.65692129629</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>45723.57329861111</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>44826.94976851852</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>45238</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>44462</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>44166</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>44319</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         <v>44705</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44741</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
         <v>44062</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>44774.94347222222</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>44741</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>44832</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19845,7 +19845,7 @@
         <v>45751.34795138889</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45636.3863425926</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20025,7 +20025,7 @@
         <v>45468.97461805555</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>45771.3859837963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45301</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>45301</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>45149</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>45779.48993055556</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>45033</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>45789.6360300926</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45754.51064814815</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>45252</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>45266</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45089</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45597.34461805555</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21195,7 +21195,7 @@
         <v>45153</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>45847.36528935185</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>45183</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>45455.96184027778</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>45646.34438657408</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>45341</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>45813.49061342593</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21836,7 +21836,7 @@
         <v>45457.9640625</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45205</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>45769.65736111111</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>45775.67769675926</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>44991</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>45827.57371527778</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -22384,7 +22384,7 @@
         <v>45771.36548611111</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>45785.36525462963</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>44860</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45436.94644675926</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>45838.38627314815</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>44119</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         <v>45468</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>45487.92863425926</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45491.95008101852</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>44369</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>45206</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45624.40665509259</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>45153</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>45154</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>45147</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23729,7 +23729,7 @@
         <v>45722.65670138889</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>45044</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45510</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>45208</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45315</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>45600.55265046296</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44141</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>44157</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
         <v>44195</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
         <v>44214</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         <v>44846</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>44168</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -24611,7 +24611,7 @@
         <v>44517</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>44817</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>44880.95712962963</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>44880.95719907407</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>44855.94125</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>44425</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>44447.92069444444</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         <v>44490.94109953703</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>44519.94534722222</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -25159,7 +25159,7 @@
         <v>44349</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>44210</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44243</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>44280</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>44385.33887731482</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>44280</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>44705</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>44292</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>44518.94394675926</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>44362</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>44846.9522337963</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>44426.94077546296</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>44399</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44818.94929398148</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44860</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>44111</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>44774.94414351852</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>44425</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>44663</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>44823.48666666666</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -26334,7 +26334,7 @@
         <v>44874.95553240741</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>44784.9408912037</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>44837</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44714</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>44670</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>44704.94234953704</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -26758,7 +26758,7 @@
         <v>44855</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>44078</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>44175</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26939,7 +26939,7 @@
         <v>44194</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>44239</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>44443</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>44273.92081018518</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>44741</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>44132</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>44495.93966435185</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -27353,7 +27353,7 @@
         <v>44126</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -27410,7 +27410,7 @@
         <v>44854</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>44859.95710648148</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>44530</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>44823.94993055556</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>44836.9491087963</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         <v>44125.94493055555</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>44833.95405092592</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27839,7 +27839,7 @@
         <v>44579.68604166667</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44084</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>44883</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>44728.94398148148</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>44287</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>44259</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>44308</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>44308</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>44452</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>44629.56258101852</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>44281</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>44421.97322916667</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>44351</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>44069</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44832.95435185185</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>44586</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>44434.94559027778</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>44690</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44867</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>44876.95104166667</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>44500.93887731482</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>44111</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>44476</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>44601</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>44714.94162037037</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -29334,7 +29334,7 @@
         <v>44357</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -29391,7 +29391,7 @@
         <v>44477.48994212963</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -29448,7 +29448,7 @@
         <v>44696.93986111111</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>44228</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>44515.93767361111</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         <v>44783</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -29691,7 +29691,7 @@
         <v>44802</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>44864.94835648148</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44308</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44482.92271990741</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44662</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29991,7 +29991,7 @@
         <v>44349.92013888889</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -30048,7 +30048,7 @@
         <v>44824.94635416667</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>44704</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>44685</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -30224,7 +30224,7 @@
         <v>44349.91995370371</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>44308</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>44615</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>44851.95488425926</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>44671</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -30514,7 +30514,7 @@
         <v>44379</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>44075</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>44071</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>44434.94517361111</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>44729.94136574074</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>44704.94229166667</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44861</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>44818</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>44777.95504629629</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -31062,7 +31062,7 @@
         <v>44855.9471875</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>44833.9519212963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>44099</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>44138</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>44418.9369212963</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>44621</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>44140</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
         <v>44074</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>44074</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -31610,7 +31610,7 @@
         <v>44650</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>44788</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -31724,7 +31724,7 @@
         <v>44853</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>44799.94394675926</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>44574</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>44463.94077546296</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>44431</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -32024,7 +32024,7 @@
         <v>44883.94918981481</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>44124</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -32143,7 +32143,7 @@
         <v>44615</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>44140</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -32262,7 +32262,7 @@
         <v>44815</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -32324,7 +32324,7 @@
         <v>44578.92284722222</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -32381,7 +32381,7 @@
         <v>44599.98685185185</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>44489.94711805556</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -32505,7 +32505,7 @@
         <v>44823</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -32562,7 +32562,7 @@
         <v>44727</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>44494.93930555556</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>44858</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -32748,7 +32748,7 @@
         <v>44425</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>44846</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>44068.62614583333</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>44322</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32986,7 +32986,7 @@
         <v>44361.55445601852</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>44704.9422337963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>44781</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>44495</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>44728.94392361111</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>44854.95390046296</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>44831.94846064815</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -33410,7 +33410,7 @@
         <v>44831.9485300926</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>44784.94157407407</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>44889</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>44402.42243055555</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -33653,7 +33653,7 @@
         <v>44595</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>44356.91935185185</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>44496</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>44734.94193287037</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>44832.95300925926</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -33948,7 +33948,7 @@
         <v>44830</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>44776</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -34072,7 +34072,7 @@
         <v>44704.94217592593</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>44805</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>44315</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -34258,7 +34258,7 @@
         <v>44861</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -34320,7 +34320,7 @@
         <v>45374</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -34377,7 +34377,7 @@
         <v>44512</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -34434,7 +34434,7 @@
         <v>45007</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>45042</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -34548,7 +34548,7 @@
         <v>45384</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>45086.94010416666</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -34667,7 +34667,7 @@
         <v>45726.3860300926</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>45723.67777777778</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>44336</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>45119</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>45182</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>44853.9499537037</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -35024,7 +35024,7 @@
         <v>44323</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45253</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -35143,7 +35143,7 @@
         <v>45743.36</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>45208</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -35262,7 +35262,7 @@
         <v>44813</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -35324,7 +35324,7 @@
         <v>44832</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>45356.03784722222</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -35448,7 +35448,7 @@
         <v>45358.95813657407</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>44812.94709490741</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -35567,7 +35567,7 @@
         <v>44805.94592592592</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -35629,7 +35629,7 @@
         <v>44953</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>44977.98660879629</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>45645.36743055555</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         <v>45098</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>45267</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -35929,7 +35929,7 @@
         <v>45741.63675925926</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>45769.51087962963</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -36053,7 +36053,7 @@
         <v>45769.67767361111</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -36115,7 +36115,7 @@
         <v>45534.64285879629</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -36177,7 +36177,7 @@
         <v>45075.945</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>45358.95818287037</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>45441.33313657407</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -36353,7 +36353,7 @@
         <v>45280.92645833334</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -36410,7 +36410,7 @@
         <v>45645.36740740741</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -36467,7 +36467,7 @@
         <v>45695.44724537037</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>45702.63572916666</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>45764.51113425926</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -36648,7 +36648,7 @@
         <v>44356</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45391.95329861111</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -36767,7 +36767,7 @@
         <v>45392</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>45392.92903935185</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>44802.94811342593</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -36943,7 +36943,7 @@
         <v>45636.3864699074</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>45574.57967592592</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -37062,7 +37062,7 @@
         <v>45426</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45063</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>45254.96516203704</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>44972.94140046297</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>45379.93637731481</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45401</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45401</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>44900.95700231481</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>45344</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -37605,7 +37605,7 @@
         <v>45776.40311342593</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -37662,7 +37662,7 @@
         <v>45776.59422453704</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>45761.67744212963</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>45769.65659722222</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -37848,7 +37848,7 @@
         <v>45769.67790509259</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -37910,7 +37910,7 @@
         <v>45093.92207175926</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -37967,7 +37967,7 @@
         <v>45776.50651620371</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -38029,7 +38029,7 @@
         <v>45776.51130787037</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>44903</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45386.68003472222</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>44914</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>44894</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>45782.36506944444</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>45782.51099537037</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -38448,7 +38448,7 @@
         <v>45751.34859953704</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -38510,7 +38510,7 @@
         <v>45782.49032407408</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -38572,7 +38572,7 @@
         <v>45782.49046296296</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45782.51109953703</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -38696,7 +38696,7 @@
         <v>45223</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         <v>45782.67758101852</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45782.55287037037</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>45779.34417824074</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -38939,7 +38939,7 @@
         <v>45779.4281712963</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45782.36494212963</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -39063,7 +39063,7 @@
         <v>44993.94950231481</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>44993</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -39187,7 +39187,7 @@
         <v>45779.49025462963</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -39249,7 +39249,7 @@
         <v>45448.94520833333</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>44958.94298611111</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -39373,7 +39373,7 @@
         <v>45187</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -39430,7 +39430,7 @@
         <v>45609.34412037037</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -39492,7 +39492,7 @@
         <v>45559.67745370371</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -39554,7 +39554,7 @@
         <v>44995.98341435185</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -39616,7 +39616,7 @@
         <v>44995.98644675926</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -39678,7 +39678,7 @@
         <v>45314</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -39735,7 +39735,7 @@
         <v>45154.95525462963</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>45393.94431712963</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45040.94277777777</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -39921,7 +39921,7 @@
         <v>45259</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -39978,7 +39978,7 @@
         <v>45572.60363425926</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -40035,7 +40035,7 @@
         <v>45006</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>45631.46665509259</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -40154,7 +40154,7 @@
         <v>45786.51077546296</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>45158.94231481481</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -40278,7 +40278,7 @@
         <v>45611.65679398148</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>45306</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45279.94572916667</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -40459,7 +40459,7 @@
         <v>45574.51185185185</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -40521,7 +40521,7 @@
         <v>45448.94600694445</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>45049</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -40645,7 +40645,7 @@
         <v>45790.40670138889</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>45611.5953125</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
         <v>45608.6078587963</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -40826,7 +40826,7 @@
         <v>45638.34431712963</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>45656</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>45327.94459490741</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>45315.9492824074</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45204.94399305555</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>45574.51087962963</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -41193,7 +41193,7 @@
         <v>45574.51090277778</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -41255,7 +41255,7 @@
         <v>45211.95134259259</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -41317,7 +41317,7 @@
         <v>45454.95960648148</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -41379,7 +41379,7 @@
         <v>45384</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>45792.34527777778</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -41498,7 +41498,7 @@
         <v>45792.71905092592</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -41560,7 +41560,7 @@
         <v>45792.49023148148</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>45139.94681712963</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -41684,7 +41684,7 @@
         <v>45453.95538194444</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45792.63584490741</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>45792.34606481482</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -41870,7 +41870,7 @@
         <v>45629.36513888889</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>45545.64957175926</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>45714.60649305556</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -42041,7 +42041,7 @@
         <v>45412.02506944445</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>44879.95768518518</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>45393.94459490741</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -42227,7 +42227,7 @@
         <v>45791.53238425926</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>45635.47243055556</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -42341,7 +42341,7 @@
         <v>45367.67256944445</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -42398,7 +42398,7 @@
         <v>45611</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>45762.39876157408</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>45694.69826388889</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>45516.94934027778</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>45436.94636574074</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>45769.51075231482</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         <v>45793</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -42842,7 +42842,7 @@
         <v>45796</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -42899,7 +42899,7 @@
         <v>45796</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>45009.0897337963</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>45191</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>44628</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>45796</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45793.61523148148</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>45796</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -43313,7 +43313,7 @@
         <v>45182</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -43375,7 +43375,7 @@
         <v>45796</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>45441</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>45341.95381944445</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -43551,7 +43551,7 @@
         <v>45266</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>45545.49078703704</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         <v>45439.92752314815</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -43722,7 +43722,7 @@
         <v>45639.55240740741</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>45729.51074074074</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>45797.63627314815</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -43908,7 +43908,7 @@
         <v>45800.63619212963</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -43970,7 +43970,7 @@
         <v>45726.38575231482</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -44027,7 +44027,7 @@
         <v>45737.63574074074</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -44089,7 +44089,7 @@
         <v>45799.34421296296</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>45800</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -44208,7 +44208,7 @@
         <v>45800.42743055556</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>45800.44822916666</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
         <v>45800.44862268519</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -44394,7 +44394,7 @@
         <v>45323</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>45190</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45803.5946875</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -44570,7 +44570,7 @@
         <v>45803.61552083334</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -44627,7 +44627,7 @@
         <v>45803.61557870371</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -44684,7 +44684,7 @@
         <v>45804.59487268519</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -44746,7 +44746,7 @@
         <v>45804.42642361111</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -44803,7 +44803,7 @@
         <v>44743</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -44860,7 +44860,7 @@
         <v>45603.67850694444</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>45653.44836805556</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45601.5315625</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -45041,7 +45041,7 @@
         <v>45638.63600694444</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>45616.5108912037</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>44644</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>45420</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -45289,7 +45289,7 @@
         <v>45803.53157407408</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -45351,7 +45351,7 @@
         <v>45803.59417824074</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -45408,7 +45408,7 @@
         <v>45646.63605324074</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -45470,7 +45470,7 @@
         <v>45050.94020833333</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -45532,7 +45532,7 @@
         <v>45344</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45804.65672453704</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -45651,7 +45651,7 @@
         <v>45063</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -45708,7 +45708,7 @@
         <v>45645.55665509259</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -45765,7 +45765,7 @@
         <v>45846.34454861111</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -45827,7 +45827,7 @@
         <v>45847.34474537037</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -45889,7 +45889,7 @@
         <v>45692.51069444444</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -45951,7 +45951,7 @@
         <v>45692.57326388889</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -46013,7 +46013,7 @@
         <v>45847.61548611111</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -46070,7 +46070,7 @@
         <v>45847.61513888889</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -46127,7 +46127,7 @@
         <v>45805.61495370371</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -46189,7 +46189,7 @@
         <v>45847.65703703704</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45847.34565972222</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -46313,7 +46313,7 @@
         <v>45848.65658564815</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -46375,7 +46375,7 @@
         <v>44866</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>45574.39081018518</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>45734.4633912037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>45552.44096064815</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -46613,7 +46613,7 @@
         <v>45257</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -46670,7 +46670,7 @@
         <v>45579.47052083333</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -46727,7 +46727,7 @@
         <v>45797.40800925926</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -46784,7 +46784,7 @@
         <v>45805.46613425926</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>45656.64223379629</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>45847.34515046296</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -46960,7 +46960,7 @@
         <v>45847.34597222223</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -47022,7 +47022,7 @@
         <v>44614</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>44944</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -47136,7 +47136,7 @@
         <v>45847.34528935186</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -47198,7 +47198,7 @@
         <v>44130.9416550926</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -47260,7 +47260,7 @@
         <v>45722.48982638889</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>45716</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -47379,7 +47379,7 @@
         <v>45716.61487268518</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -47441,7 +47441,7 @@
         <v>44922</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -47498,7 +47498,7 @@
         <v>44517.58137731482</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -47555,7 +47555,7 @@
         <v>45056</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -47612,7 +47612,7 @@
         <v>45056</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -47669,7 +47669,7 @@
         <v>45516.94732638889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -47731,7 +47731,7 @@
         <v>44601</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -47788,7 +47788,7 @@
         <v>45805.57390046296</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -47850,7 +47850,7 @@
         <v>45453.42041666667</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -47907,7 +47907,7 @@
         <v>45615.47091435185</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45667.57342592593</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -48026,7 +48026,7 @@
         <v>45667.57347222222</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         <v>45672.44898148148</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -48150,7 +48150,7 @@
         <v>45852.53185185185</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -48212,7 +48212,7 @@
         <v>44655</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>45453.95016203704</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -48336,7 +48336,7 @@
         <v>45446.68947916666</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>45456.96569444444</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>45850.34450231482</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44550.92168981482</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>45850.34434027778</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         <v>45195</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>45195.94679398148</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -48755,7 +48755,7 @@
         <v>45195.94685185186</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>44475</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -48874,7 +48874,7 @@
         <v>44614</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45692.49008101852</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45848.49774305556</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>44113</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45187</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -49169,7 +49169,7 @@
         <v>45678.67761574074</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>44336</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -49288,7 +49288,7 @@
         <v>45148</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -49345,7 +49345,7 @@
         <v>44684.94032407407</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>45138.94925925926</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>45309.92524305556</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>45636.38599537037</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45195.94672453704</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>45852.53168981482</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -49712,7 +49712,7 @@
         <v>45604.4190625</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>45849.65663194445</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45243</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45275.95060185185</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -49955,7 +49955,7 @@
         <v>45810.36495370371</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -50017,7 +50017,7 @@
         <v>45112.94303240741</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>45112.94310185185</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -50141,7 +50141,7 @@
         <v>45730.53208333333</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -50203,7 +50203,7 @@
         <v>45848.49761574074</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>45469.94876157407</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -50322,7 +50322,7 @@
         <v>45505</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -50384,7 +50384,7 @@
         <v>45230.96376157407</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -50446,7 +50446,7 @@
         <v>45621.57395833333</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>45428.00471064815</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -50570,7 +50570,7 @@
         <v>45574.61184027778</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>45574.62297453704</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -50684,7 +50684,7 @@
         <v>45574.63355324074</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -50741,7 +50741,7 @@
         <v>44614</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -50798,7 +50798,7 @@
         <v>44656.94708333333</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -50860,7 +50860,7 @@
         <v>45854.65663194445</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -50922,7 +50922,7 @@
         <v>45216.92424768519</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -50979,7 +50979,7 @@
         <v>45698.59409722222</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -51041,7 +51041,7 @@
         <v>45180.95907407408</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -51103,7 +51103,7 @@
         <v>44979</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -51160,7 +51160,7 @@
         <v>44980.93865740741</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -51222,7 +51222,7 @@
         <v>44519.94440972222</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -51284,7 +51284,7 @@
         <v>45253</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -51341,7 +51341,7 @@
         <v>45511</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -51403,7 +51403,7 @@
         <v>45769.67802083334</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -51465,7 +51465,7 @@
         <v>45426</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -51522,7 +51522,7 @@
         <v>45426</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>45033</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -51636,7 +51636,7 @@
         <v>45856.46931712963</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -51698,7 +51698,7 @@
         <v>45855.61523148148</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         <v>45855.67899305555</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -51817,7 +51817,7 @@
         <v>45614.34541666666</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -51874,7 +51874,7 @@
         <v>45813.42790509259</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -51936,7 +51936,7 @@
         <v>45635.57331018519</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -51998,7 +51998,7 @@
         <v>45702.63604166666</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -52060,7 +52060,7 @@
         <v>44656</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -52122,7 +52122,7 @@
         <v>45372.95762731481</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -52184,7 +52184,7 @@
         <v>44897</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -52246,7 +52246,7 @@
         <v>44911.93846064815</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -52308,7 +52308,7 @@
         <v>45257</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -52370,7 +52370,7 @@
         <v>45772.6565625</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -52432,7 +52432,7 @@
         <v>45764</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -52489,7 +52489,7 @@
         <v>45488.94747685185</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
         <v>45638</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         <v>45540.38564814815</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -52670,7 +52670,7 @@
         <v>45425.96239583333</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -52732,7 +52732,7 @@
         <v>45590.40675925926</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -52794,7 +52794,7 @@
         <v>45860.30229166667</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>45145.95326388889</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -52913,7 +52913,7 @@
         <v>44774</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -52970,7 +52970,7 @@
         <v>45215.94657407407</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -53032,7 +53032,7 @@
         <v>45817.71910879629</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -53094,7 +53094,7 @@
         <v>45818.46898148148</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -53151,7 +53151,7 @@
         <v>45859.594375</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -53213,7 +53213,7 @@
         <v>44917</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -53275,7 +53275,7 @@
         <v>44993.94958333333</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>44671</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -53394,7 +53394,7 @@
         <v>44820</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -53456,7 +53456,7 @@
         <v>45211.95061342593</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -53518,7 +53518,7 @@
         <v>44839</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -53575,7 +53575,7 @@
         <v>45149.95241898148</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -53637,7 +53637,7 @@
         <v>45722.44849537037</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -53699,7 +53699,7 @@
         <v>45224</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -53756,7 +53756,7 @@
         <v>45233.92591435185</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -53813,7 +53813,7 @@
         <v>45819.6359375</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -53875,7 +53875,7 @@
         <v>44900</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -53937,7 +53937,7 @@
         <v>45367.04693287037</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -53999,7 +53999,7 @@
         <v>45566.68125</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -54056,7 +54056,7 @@
         <v>45712.61552083334</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -54118,7 +54118,7 @@
         <v>45775.67747685185</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -54180,7 +54180,7 @@
         <v>44672.94018518519</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -54242,7 +54242,7 @@
         <v>45404.99792824074</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -54324,7 +54324,7 @@
         <v>45244.96774305555</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -54386,7 +54386,7 @@
         <v>44587.92149305555</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -54443,7 +54443,7 @@
         <v>45821.34513888889</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -54505,7 +54505,7 @@
         <v>44943.94802083333</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -54567,7 +54567,7 @@
         <v>45825.57675925926</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -54624,7 +54624,7 @@
         <v>45825.58252314815</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -54681,7 +54681,7 @@
         <v>45734.45268518518</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -54738,7 +54738,7 @@
         <v>44903</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -54800,7 +54800,7 @@
         <v>44587.92144675926</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -54857,7 +54857,7 @@
         <v>45351.98532407408</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -54919,7 +54919,7 @@
         <v>45342</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -54981,7 +54981,7 @@
         <v>45342.9462037037</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -55043,7 +55043,7 @@
         <v>45241.95741898148</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -55105,7 +55105,7 @@
         <v>45241</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -55167,7 +55167,7 @@
         <v>45254.96402777778</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -55229,7 +55229,7 @@
         <v>45616.34479166667</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45180</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -55353,7 +55353,7 @@
         <v>45180.95927083334</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -55415,7 +55415,7 @@
         <v>45825.56762731481</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>44991</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -55534,7 +55534,7 @@
         <v>44746</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>45826.65759259259</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -55653,7 +55653,7 @@
         <v>45870.34439814815</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -55715,7 +55715,7 @@
         <v>45505</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -55777,7 +55777,7 @@
         <v>44806</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -55834,7 +55834,7 @@
         <v>44153</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -55891,7 +55891,7 @@
         <v>45028</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -55948,7 +55948,7 @@
         <v>45827.53178240741</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -56010,7 +56010,7 @@
         <v>45827.63582175926</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -56072,7 +56072,7 @@
         <v>45869.65666666667</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -56134,7 +56134,7 @@
         <v>45869.67744212963</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -56196,7 +56196,7 @@
         <v>45771.36538194444</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -56258,7 +56258,7 @@
         <v>45874.69844907407</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -56320,7 +56320,7 @@
         <v>45266.95082175926</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -56382,7 +56382,7 @@
         <v>45197.94171296297</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -56444,7 +56444,7 @@
         <v>45327.94443287037</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -56506,7 +56506,7 @@
         <v>45044</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -56568,7 +56568,7 @@
         <v>45351.98496527778</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -56630,7 +56630,7 @@
         <v>45741.63659722222</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -56692,7 +56692,7 @@
         <v>45832.34552083333</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -56754,7 +56754,7 @@
         <v>44886</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -56816,7 +56816,7 @@
         <v>45222</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -56878,7 +56878,7 @@
         <v>45257.92826388889</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -56935,7 +56935,7 @@
         <v>45306</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -56992,7 +56992,7 @@
         <v>45874.67746527777</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -57054,7 +57054,7 @@
         <v>45832.34524305556</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -57111,7 +57111,7 @@
         <v>45832.3459375</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>45554.61583333334</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -57230,7 +57230,7 @@
         <v>45482.94815972223</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -57292,7 +57292,7 @@
         <v>45874.59496527778</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -57354,7 +57354,7 @@
         <v>45839</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -57411,7 +57411,7 @@
         <v>44067</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -57473,7 +57473,7 @@
         <v>45238</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -57530,7 +57530,7 @@
         <v>45436.94613425926</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -57592,7 +57592,7 @@
         <v>45876.53188657408</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -57654,7 +57654,7 @@
         <v>45834.65662037037</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -57716,7 +57716,7 @@
         <v>45769.65688657408</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -57778,7 +57778,7 @@
         <v>45000</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -57835,7 +57835,7 @@
         <v>45530</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -57892,7 +57892,7 @@
         <v>45835.4506712963</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -57949,7 +57949,7 @@
         <v>45838</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -58006,7 +58006,7 @@
         <v>45260</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>45442.96296296296</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -58125,7 +58125,7 @@
         <v>45835.72046296296</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -58182,7 +58182,7 @@
         <v>45208</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -58239,7 +58239,7 @@
         <v>45098</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -58296,7 +58296,7 @@
         <v>45838</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -58353,7 +58353,7 @@
         <v>45838.67887731481</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>45555.38509259259</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -58472,7 +58472,7 @@
         <v>45838.48996527777</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -58529,7 +58529,7 @@
         <v>45103</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -58586,7 +58586,7 @@
         <v>44649.47048611111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -58648,7 +58648,7 @@
         <v>45835.40668981482</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -58710,7 +58710,7 @@
         <v>45069</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -58767,7 +58767,7 @@
         <v>45838.67800925926</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -58824,7 +58824,7 @@
         <v>45835.53166666667</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -58886,7 +58886,7 @@
         <v>45324</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -58943,7 +58943,7 @@
         <v>45835.46334490741</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -59000,7 +59000,7 @@
         <v>45835.45686342593</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -59057,7 +59057,7 @@
         <v>45183.95563657407</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -59119,7 +59119,7 @@
         <v>45839.42822916667</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -59181,7 +59181,7 @@
         <v>45839.46915509259</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -59243,7 +59243,7 @@
         <v>45838.36532407408</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -59305,7 +59305,7 @@
         <v>45258</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -59362,7 +59362,7 @@
         <v>44894.79018518519</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -59419,7 +59419,7 @@
         <v>45839.49082175926</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -59476,7 +59476,7 @@
         <v>45839.42810185185</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -59538,7 +59538,7 @@
         <v>44963</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -59600,7 +59600,7 @@
         <v>44901</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -59662,7 +59662,7 @@
         <v>44901</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -59724,7 +59724,7 @@
         <v>45601.55331018518</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -59786,7 +59786,7 @@
         <v>45839.42864583333</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -59848,7 +59848,7 @@
         <v>45487.92856481481</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -59905,7 +59905,7 @@
         <v>45839.57331018519</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -59967,7 +59967,7 @@
         <v>44914</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -60024,7 +60024,7 @@
         <v>45840.52225694444</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -60081,7 +60081,7 @@
         <v>45595.42738425926</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -60143,7 +60143,7 @@
         <v>45622.47435185185</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -60200,7 +60200,7 @@
         <v>45429</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -60257,7 +60257,7 @@
         <v>45446.57052083333</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -60314,7 +60314,7 @@
         <v>45053.94313657407</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -60376,7 +60376,7 @@
         <v>44880</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -60438,7 +60438,7 @@
         <v>45714</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -60495,7 +60495,7 @@
         <v>45425.96494212963</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -60557,7 +60557,7 @@
         <v>45842.38579861111</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -60619,7 +60619,7 @@
         <v>45841.57427083333</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -60681,7 +60681,7 @@
         <v>45581.55260416667</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -60738,7 +60738,7 @@
         <v>45842.42608796297</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -60795,7 +60795,7 @@
         <v>45733.61497685185</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -60857,7 +60857,7 @@
         <v>44977.98670138889</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -60919,7 +60919,7 @@
         <v>45392</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -60976,7 +60976,7 @@
         <v>45841.6571412037</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -61033,7 +61033,7 @@
         <v>45238</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -61095,7 +61095,7 @@
         <v>44991</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -61157,7 +61157,7 @@
         <v>45230</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -61219,7 +61219,7 @@
         <v>44635</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -61281,7 +61281,7 @@
         <v>45558.63575231482</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -61343,7 +61343,7 @@
         <v>44657</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -61400,7 +61400,7 @@
         <v>45590</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -61457,7 +61457,7 @@
         <v>44530.94694444445</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -61519,7 +61519,7 @@
         <v>44641</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -61581,7 +61581,7 @@
         <v>44641</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -61643,7 +61643,7 @@
         <v>44957.94075231482</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -61705,7 +61705,7 @@
         <v>45552.39113425926</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -61762,7 +61762,7 @@
         <v>44305.92047453704</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -61819,7 +61819,7 @@
         <v>45092</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -61876,7 +61876,7 @@
         <v>44685</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -61938,7 +61938,7 @@
         <v>45622</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -61995,7 +61995,7 @@
         <v>44942</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -62057,7 +62057,7 @@
         <v>44994.94296296296</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -62119,7 +62119,7 @@
         <v>45614.34545138889</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -62176,7 +62176,7 @@
         <v>44966.95328703704</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -62238,7 +62238,7 @@
         <v>44231</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -62295,7 +62295,7 @@
         <v>45601.40686342592</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -62357,7 +62357,7 @@
         <v>45751.36490740741</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -62419,7 +62419,7 @@
         <v>45344.92865740741</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -62476,7 +62476,7 @@
         <v>45344.92873842592</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -62533,7 +62533,7 @@
         <v>45309</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -62590,7 +62590,7 @@
         <v>45309</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -62647,7 +62647,7 @@
         <v>44231</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -62704,7 +62704,7 @@
         <v>45456.96601851852</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -62766,7 +62766,7 @@
         <v>45688.68196759259</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -62828,7 +62828,7 @@
         <v>45367.69850694444</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -62885,7 +62885,7 @@
         <v>45367.71348379629</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -62942,7 +62942,7 @@
         <v>45034</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -62999,7 +62999,7 @@
         <v>45730.56346064815</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -63061,7 +63061,7 @@
         <v>45112</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -63123,7 +63123,7 @@
         <v>45075.94506944445</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -63185,7 +63185,7 @@
         <v>44889.95015046297</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -63247,7 +63247,7 @@
         <v>44680</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -63304,7 +63304,7 @@
         <v>44956.93924768519</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -63366,7 +63366,7 @@
         <v>45314</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -63423,7 +63423,7 @@
         <v>45119</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -63480,7 +63480,7 @@
         <v>45289</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -63537,7 +63537,7 @@
         <v>45629.36486111111</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -63594,7 +63594,7 @@
         <v>44803.94351851852</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -63656,7 +63656,7 @@
         <v>45260.92561342593</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -63713,7 +63713,7 @@
         <v>45758.36487268518</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -63775,7 +63775,7 @@
         <v>44939</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -63837,7 +63837,7 @@
         <v>44958</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -63894,7 +63894,7 @@
         <v>45603.44644675926</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -63956,7 +63956,7 @@
         <v>45622.44774305556</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -64013,7 +64013,7 @@
         <v>45009.089375</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -64075,7 +64075,7 @@
         <v>45618.46921296296</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -64137,7 +64137,7 @@
         <v>45596.61533564814</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -64199,7 +64199,7 @@
         <v>45344.92822916667</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -64256,7 +64256,7 @@
         <v>44236</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -64313,7 +64313,7 @@
         <v>45280</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -64370,7 +64370,7 @@
         <v>45671.48989583334</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -64432,7 +64432,7 @@
         <v>45128</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -64494,7 +64494,7 @@
         <v>44410</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -64551,7 +64551,7 @@
         <v>44670</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -64608,7 +64608,7 @@
         <v>44984</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -64665,7 +64665,7 @@
         <v>44571</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -64722,7 +64722,7 @@
         <v>45386</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -64779,7 +64779,7 @@
         <v>44977.44373842593</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -64836,7 +64836,7 @@
         <v>45170</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -64898,7 +64898,7 @@
         <v>45238.96797453704</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -64960,7 +64960,7 @@
         <v>45474.50608796296</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -65017,7 +65017,7 @@
         <v>45604.40540509259</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -65074,7 +65074,7 @@
         <v>45604.41625</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -65131,7 +65131,7 @@
         <v>45608.52354166667</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -65193,7 +65193,7 @@
         <v>45568.51075231482</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -65255,7 +65255,7 @@
         <v>45546</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -65312,7 +65312,7 @@
         <v>44929</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -65369,7 +65369,7 @@
         <v>45086</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -65431,7 +65431,7 @@
         <v>45467.96207175926</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -65493,7 +65493,7 @@
         <v>45469.94667824074</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -65555,7 +65555,7 @@
         <v>45695.51070601852</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -65617,7 +65617,7 @@
         <v>45511</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -65679,7 +65679,7 @@
         <v>44869</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -65736,7 +65736,7 @@
         <v>44286</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -65793,7 +65793,7 @@
         <v>45210</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -65850,7 +65850,7 @@
         <v>45664.55241898148</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -65912,7 +65912,7 @@
         <v>45002.0328125</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -65974,7 +65974,7 @@
         <v>45712.65671296296</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -66031,7 +66031,7 @@
         <v>45681.60203703704</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -66088,7 +66088,7 @@
         <v>45679.40362268518</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -66145,7 +66145,7 @@
         <v>45667.55239583334</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -66207,7 +66207,7 @@
         <v>45241.95724537037</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -66269,7 +66269,7 @@
         <v>45425.96230324074</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -66331,7 +66331,7 @@
         <v>44424</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -66388,7 +66388,7 @@
         <v>45149</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -66445,7 +66445,7 @@
         <v>45604.63575231482</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -66507,7 +66507,7 @@
         <v>45111.92793981481</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -66569,7 +66569,7 @@
         <v>45357.05300925926</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -66631,7 +66631,7 @@
         <v>45425.96275462963</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -66693,7 +66693,7 @@
         <v>45184</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -66750,7 +66750,7 @@
         <v>45000</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -66812,7 +66812,7 @@
         <v>45000</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -66874,7 +66874,7 @@
         <v>45453.4444212963</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -66931,7 +66931,7 @@
         <v>44929</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -66988,7 +66988,7 @@
         <v>44375</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -67045,7 +67045,7 @@
         <v>45322</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -67102,7 +67102,7 @@
         <v>44918</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -67164,7 +67164,7 @@
         <v>45534</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -67221,7 +67221,7 @@
         <v>45510</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -67283,7 +67283,7 @@
         <v>45692.48993055556</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -67345,7 +67345,7 @@
         <v>44855</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -67407,7 +67407,7 @@
         <v>45622.46200231482</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -67464,7 +67464,7 @@
         <v>44349.91978009259</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -67521,7 +67521,7 @@
         <v>45625.51068287037</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -67583,7 +67583,7 @@
         <v>45695.45868055556</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -67640,7 +67640,7 @@
         <v>45000</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -67702,7 +67702,7 @@
         <v>45681.5315625</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -67764,7 +67764,7 @@
         <v>45476.94533564815</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -67826,7 +67826,7 @@
         <v>45673.66358796296</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -67883,7 +67883,7 @@
         <v>44680.95246527778</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -67945,7 +67945,7 @@
         <v>44384</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -68002,7 +68002,7 @@
         <v>45601.59518518519</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -68064,7 +68064,7 @@
         <v>44879</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -68126,7 +68126,7 @@
         <v>45040</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -68183,7 +68183,7 @@
         <v>44844.95368055555</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -68245,7 +68245,7 @@
         <v>45009</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -68302,7 +68302,7 @@
         <v>44362</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -68359,7 +68359,7 @@
         <v>45482.94891203703</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -68421,7 +68421,7 @@
         <v>45482.9491087963</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -68483,7 +68483,7 @@
         <v>45436.94628472222</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -68545,7 +68545,7 @@
         <v>45425.96263888889</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -68607,7 +68607,7 @@
         <v>45008.01408564814</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -68669,7 +68669,7 @@
         <v>45176</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -68726,7 +68726,7 @@
         <v>45615.50034722222</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -68783,7 +68783,7 @@
         <v>45048.94340277778</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -68845,7 +68845,7 @@
         <v>44929.92489583333</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -68902,7 +68902,7 @@
         <v>45596.61553240741</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -68964,7 +68964,7 @@
         <v>45435</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -69021,7 +69021,7 @@
         <v>45681.6050925926</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -69078,7 +69078,7 @@
         <v>45559.67759259259</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -69140,7 +69140,7 @@
         <v>45636.57329861111</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -69202,7 +69202,7 @@
         <v>44593</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -69259,7 +69259,7 @@
         <v>45726.38615740741</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -69316,7 +69316,7 @@
         <v>45726.3862037037</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -69373,7 +69373,7 @@
         <v>45706.34450231482</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -69435,7 +69435,7 @@
         <v>45715.59405092592</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -69497,7 +69497,7 @@
         <v>45166</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -69554,7 +69554,7 @@
         <v>44889</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -69611,7 +69611,7 @@
         <v>45723.51079861111</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -69673,7 +69673,7 @@
         <v>45735.53177083333</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -69735,7 +69735,7 @@
         <v>45735.5517824074</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -69792,7 +69792,7 @@
         <v>45730.42738425926</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -69854,7 +69854,7 @@
         <v>45733.61554398148</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -69916,7 +69916,7 @@
         <v>45197.94152777778</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -69978,7 +69978,7 @@
         <v>45700.57324074074</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -70040,7 +70040,7 @@
         <v>45112</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -70102,7 +70102,7 @@
         <v>45747.67739583334</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -70164,7 +70164,7 @@
         <v>45491</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -70226,7 +70226,7 @@
         <v>45629.42759259259</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -70288,7 +70288,7 @@
         <v>44629</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -70345,7 +70345,7 @@
         <v>45053.94305555556</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -70407,7 +70407,7 @@
         <v>45306</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -70464,7 +70464,7 @@
         <v>45107</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -70521,7 +70521,7 @@
         <v>45068</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -70583,7 +70583,7 @@
         <v>44518</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -70640,7 +70640,7 @@
         <v>45735.69842592593</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -70702,7 +70702,7 @@
         <v>45071</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -70759,7 +70759,7 @@
         <v>45314.92758101852</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -70816,7 +70816,7 @@
         <v>45133</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -70878,7 +70878,7 @@
         <v>45712.61502314815</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -70940,7 +70940,7 @@
         <v>45735</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -71002,7 +71002,7 @@
         <v>45712.61510416667</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -71064,7 +71064,7 @@
         <v>45630.7862037037</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -71121,7 +71121,7 @@
         <v>45329.95806712963</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -71183,7 +71183,7 @@
         <v>45540.38586805556</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -71245,7 +71245,7 @@
         <v>44074</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -71307,7 +71307,7 @@
         <v>45331.92746527777</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -71364,7 +71364,7 @@
         <v>44825</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -71426,7 +71426,7 @@
         <v>44299</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -71483,7 +71483,7 @@
         <v>44917</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -71540,7 +71540,7 @@
         <v>45103</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -71597,7 +71597,7 @@
         <v>44915</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -71659,7 +71659,7 @@
         <v>45078</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -71716,7 +71716,7 @@
         <v>44405.92065972222</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -71773,7 +71773,7 @@
         <v>45688.67542824074</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -71835,7 +71835,7 @@
         <v>45072.92737268518</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -71892,7 +71892,7 @@
         <v>45065.42894675926</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -71949,7 +71949,7 @@
         <v>45622.46910879629</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -72006,7 +72006,7 @@
         <v>45659.69822916666</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -72068,7 +72068,7 @@
         <v>45457.96372685185</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -72130,7 +72130,7 @@
         <v>45054</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -72192,7 +72192,7 @@
         <v>44932.93927083333</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -72254,7 +72254,7 @@
         <v>45540.34428240741</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -72316,7 +72316,7 @@
         <v>45714.55064814815</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -72373,7 +72373,7 @@
         <v>45175</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -72435,7 +72435,7 @@
         <v>45534.63537037037</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -72497,7 +72497,7 @@
         <v>45251</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -72554,7 +72554,7 @@
         <v>45145</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -72616,7 +72616,7 @@
         <v>45279.94564814815</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -72678,7 +72678,7 @@
         <v>45149.95372685185</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -72740,7 +72740,7 @@
         <v>45091</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -72802,7 +72802,7 @@
         <v>44904.94824074074</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -72864,7 +72864,7 @@
         <v>45665.65684027778</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -72926,7 +72926,7 @@
         <v>44869</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -72983,7 +72983,7 @@
         <v>45638</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -73040,7 +73040,7 @@
         <v>45645.55672453704</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -73097,7 +73097,7 @@
         <v>44971</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -73159,7 +73159,7 @@
         <v>45614.63869212963</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -73221,7 +73221,7 @@
         <v>45096.93866898148</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -73283,7 +73283,7 @@
         <v>44880.95741898148</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -73345,7 +73345,7 @@
         <v>44173</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -73402,7 +73402,7 @@
         <v>45715.61523148148</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -73464,7 +73464,7 @@
         <v>44876</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -73526,7 +73526,7 @@
         <v>45751.34873842593</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -73588,7 +73588,7 @@
         <v>45215</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -73645,7 +73645,7 @@
         <v>44888</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -73707,7 +73707,7 @@
         <v>44174</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -73769,7 +73769,7 @@
         <v>45105</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -73831,7 +73831,7 @@
         <v>45756.63601851852</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -73893,7 +73893,7 @@
         <v>45771.51074074074</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -73955,7 +73955,7 @@
         <v>45341</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -74012,7 +74012,7 @@
         <v>45495.57677083334</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -74069,7 +74069,7 @@
         <v>45429</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -74126,7 +74126,7 @@
         <v>45737.69822916666</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -74188,7 +74188,7 @@
         <v>45092</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -74245,7 +74245,7 @@
         <v>45754</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -74307,7 +74307,7 @@
         <v>44741.94070601852</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -74369,7 +74369,7 @@
         <v>45596.61569444444</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -74431,7 +74431,7 @@
         <v>45596.61582175926</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -74493,7 +74493,7 @@
         <v>45156</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -74555,7 +74555,7 @@
         <v>45338.95405092592</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -74617,7 +74617,7 @@
         <v>45258</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -74674,7 +74674,7 @@
         <v>45561.34663194444</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -74736,7 +74736,7 @@
         <v>45574.61634259259</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -74793,7 +74793,7 @@
         <v>45666.44943287037</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -74850,7 +74850,7 @@
         <v>45629.35326388889</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>

--- a/Översikt RAGUNDA.xlsx
+++ b/Översikt RAGUNDA.xlsx
@@ -567,7 +567,7 @@
         <v>45622</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>45376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>45560.34460648148</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>45622</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>45673</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44917</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45804.67787037037</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>45590.42736111111</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45838.67753472222</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44504</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>45622</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44644</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>45560.34532407407</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45104</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45579.53179398148</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>45113</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44644.93650462963</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>45367.04916666666</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>44813</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>44473</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>44088</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>45639.55269675926</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>45622</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45790.57334490741</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>45482.63819444444</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>45779.49012731481</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45182</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>44776</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>45803.59474537037</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>45790.57349537037</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>45358.99375</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>45839.42482638889</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44805</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>45560.34484953704</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44888</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>44645.99859953704</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>45327</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>45779.57335648148</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>45121</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>45685.36501157407</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>45510</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>45174</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>45799.63574074074</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>45799.34461805555</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>45190.96092592592</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>44504</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>45832.34461805555</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>45378</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>45769.53180555555</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44133</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>45320</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>45622</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>45723.40688657408</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>45120</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>45827.5110300926</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>45113</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44133</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>44662</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>44438</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>45435.54734953704</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45176</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45405.57392361111</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>45176</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44994</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>45121</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>44336</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>45810.55061342593</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>45155</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>45769.67740740741</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>45786.61517361111</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>44915</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>45475.94796296296</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>44111</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44209</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>44932</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>44994</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>45457</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>45728.65684027778</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>45238</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>44911</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>44875</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>45867.63619212963</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>45769.67778935185</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>45832.34564814815</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>45595.44886574074</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>45468.97528935185</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>45471.94783564815</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>45495.56244212963</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>45846.41361111111</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>44656</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>45400.94002314815</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>45545.45748842593</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>45195</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>45446.95087962963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>45551.46912037037</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>45744.61550925926</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>45182</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>45471.94623842592</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>45244</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>45832.34578703704</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>44911</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>45674.67744212963</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>45002.94356481481</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>45425.96472222222</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>44245</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>44334.62565972222</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>44696</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>44662</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>44334</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>44334</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>44677</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>44911</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>45782.44871527778</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>45610.34415509259</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>45384</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>45378</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>45187</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>45491</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>45455.96195601852</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>45805.34415509259</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>44113</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>45491</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>45510</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>45404</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>45786.61534722222</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>44855</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44369.92025462963</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>45632.69822916666</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>45733</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45691.44769675926</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>45425.96285879629</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>45516.94723379629</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>45265</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>45779.57392361111</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44875</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>45188</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>45631</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>45491.94715277778</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
         <v>44855</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>44902</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>45804.34474537037</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>45436.94686342592</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>45152</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>45093</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>45209</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>45789.36503472222</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>45751.34650462963</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45071</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>45838</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>44111</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>45397.95748842593</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>45847.61498842593</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>44788</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>44971</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>44676</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>44855</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>45394</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>45583.49642361111</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>45188</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>45769.65692129629</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>45378</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>45526.56393518519</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16486,7 +16486,7 @@
         <v>44855</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>45722.61543981481</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>45468.97495370371</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45779.57350694444</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>45631</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>45321</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>45121</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>45153</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>45241</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45238</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>45551.65726851852</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>45800.42782407408</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>44852</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>45190</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>45852.63597222222</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>45191</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>45854.61494212963</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>45372.95680555556</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>44865</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>45205</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>44993</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>44680</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>45835.344375</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>45723.57329861111</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>45171</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>45089</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>44826.94976851852</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>44462</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>44166</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>44319</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>44705</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>44741</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>44832</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44774.94347222222</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>44741</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>45341</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>45751.34795138889</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         <v>45775.67769675926</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>45252</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>45206</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         <v>45754.51064814815</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45597.34461805555</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>45089</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>44991</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>45487.92863425926</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45436.94644675926</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45154</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45722.65670138889</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>45600.55265046296</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>45646.34438657408</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>45153</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45779.48993055556</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>45149</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>45510</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45771.3859837963</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>45183</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>44119</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>45457.9640625</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>45455.96184027778</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>45769.65736111111</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>45315</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>45771.36548611111</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>45636.3863425926</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45301</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>45301</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45153</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>45044</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>45813.49061342593</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>45491.95008101852</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44369</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>45147</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45827.57371527778</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>45468</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45785.36525462963</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>44860</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>45838.38627314815</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>45208</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>45205</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -23518,7 +23518,7 @@
         <v>45847.36528935185</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>45266</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23701,7 +23701,7 @@
         <v>45033</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>45468.97461805555</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>44157</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44141</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44195</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>44214</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>44846</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44168</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44517</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44817</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>44880.95712962963</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>44880.95719907407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>44855.94125</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>44425</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>44447.92069444444</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>44490.94109953703</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>44519.94534722222</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>44349</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>44210</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -24898,7 +24898,7 @@
         <v>44280</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>44385.33887731482</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>44243</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>44280</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>44292</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>44705</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>44518.94394675926</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>44846.9522337963</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>44362</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>44399</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44426.94077546296</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44818.94929398148</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>44774.94414351852</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>44425</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>44823.48666666666</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25778,7 +25778,7 @@
         <v>44663</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>44111</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25897,7 +25897,7 @@
         <v>44874.95553240741</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>44784.9408912037</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -26021,7 +26021,7 @@
         <v>44837</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>44714</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -26140,7 +26140,7 @@
         <v>44670</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>44858</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>44704.94234953704</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44855</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44078</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>44175</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>44194</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -26559,7 +26559,7 @@
         <v>44239</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>44443</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>44860</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>44741</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>44132</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>44495.93966435185</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>44126</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>44854</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>44859.95710648148</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>44530</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>44823.94993055556</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>44836.9491087963</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>44125.94493055555</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -27345,7 +27345,7 @@
         <v>44273.92081018518</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>44833.95405092592</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>44579.68604166667</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>44084</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>44883</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>44728.94398148148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>44259</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>44287</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>44629.56258101852</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>44308</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>44308</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>44452</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>44281</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>44421.97322916667</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>44351</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>44069</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -28292,7 +28292,7 @@
         <v>44832.95435185185</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44586</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44434.94559027778</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>44690</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         <v>44867</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>44876.95104166667</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>44111</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>44500.93887731482</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>44476</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28840,7 +28840,7 @@
         <v>44601</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>44714.94162037037</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44357</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44477.48994212963</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>44228</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>44515.93767361111</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>44696.93986111111</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>44783</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -29316,7 +29316,7 @@
         <v>44802</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>44805</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>44315</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -29502,7 +29502,7 @@
         <v>44861</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>44864.94835648148</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>44308</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -29683,7 +29683,7 @@
         <v>44832.95300925926</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29745,7 +29745,7 @@
         <v>44830</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>44776</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>44482.92271990741</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>44853.9499537037</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>44512</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -30045,7 +30045,7 @@
         <v>44349.91995370371</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>44824.94635416667</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>44349.92013888889</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -30221,7 +30221,7 @@
         <v>44308</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>44662</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>44851.95488425926</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>44704</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -30459,7 +30459,7 @@
         <v>44685</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>44379</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44671</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44615</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44075</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>44434.94517361111</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30806,7 +30806,7 @@
         <v>44071</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>44704.94229166667</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44861</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -30992,7 +30992,7 @@
         <v>44818</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -31054,7 +31054,7 @@
         <v>44729.94136574074</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>44833.9519212963</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>44777.95504629629</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>44855.9471875</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>44099</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>44138</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>44418.9369212963</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -31483,7 +31483,7 @@
         <v>44621</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>44074</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>44074</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>44650</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>44463.94077546296</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44788</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44853</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>44431</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>44615</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>44140</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>44815</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>44140</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -32202,7 +32202,7 @@
         <v>44578.92284722222</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -32259,7 +32259,7 @@
         <v>44799.94394675926</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>44599.98685185185</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -32383,7 +32383,7 @@
         <v>44574</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -32440,7 +32440,7 @@
         <v>44494.93930555556</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>44883.94918981481</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>44124</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>44846</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -32683,7 +32683,7 @@
         <v>44489.94711805556</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>44322</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>44068.62614583333</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>44823</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>44704.9422337963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44727</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -33040,7 +33040,7 @@
         <v>44495</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>44781</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>44858</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -33221,7 +33221,7 @@
         <v>44425</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>44854.95390046296</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>44889</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44595</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44831.94846064815</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>44831.9485300926</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>44784.94157407407</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>44496</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>44734.94193287037</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44704.94217592593</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>44349.91978009259</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>44361.55445601852</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>45456.96601851852</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>44402.42243055555</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>45324</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -34121,7 +34121,7 @@
         <v>44728.94392361111</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>44958.94298611111</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -34245,7 +34245,7 @@
         <v>45714.60649305556</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -34302,7 +34302,7 @@
         <v>44656</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>45197.94152777778</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         <v>45775.67747685185</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>45053.94305555556</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>44356.91935185185</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>44894</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -34664,7 +34664,7 @@
         <v>45530</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>45534</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>45456.96569444444</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>44993.94958333333</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>45257</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>44879</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>45664.55241898148</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>45184</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>45601.59518518519</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>45625.51068287037</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>45254.96402777778</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>44932.93927083333</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>44802.94811342593</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>44897</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>45596.61553240741</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -35579,7 +35579,7 @@
         <v>45176</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -35636,7 +35636,7 @@
         <v>45314.92758101852</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -35693,7 +35693,7 @@
         <v>45392</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>45392.92903935185</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -35807,7 +35807,7 @@
         <v>44879.95768518518</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -35869,7 +35869,7 @@
         <v>44635</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>45615.47091435185</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>45638.34431712963</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>45075.94506944445</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>45054</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>45761.67744212963</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>45420</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -36298,7 +36298,7 @@
         <v>45618.46921296296</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -36360,7 +36360,7 @@
         <v>45516.94732638889</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>44957.94075231482</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -36484,7 +36484,7 @@
         <v>45000</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -36546,7 +36546,7 @@
         <v>45000</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>45734.45268518518</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>45253</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>44286</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>45747.67739583334</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>45078</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -36898,7 +36898,7 @@
         <v>45341</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -36955,7 +36955,7 @@
         <v>45289</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -37012,7 +37012,7 @@
         <v>45608.52354166667</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -37074,7 +37074,7 @@
         <v>45737.63574074074</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>45737.69822916666</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -37198,7 +37198,7 @@
         <v>44153</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -37255,7 +37255,7 @@
         <v>45210</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -37312,7 +37312,7 @@
         <v>45559.67759259259</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -37374,7 +37374,7 @@
         <v>45208</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -37431,7 +37431,7 @@
         <v>45603.67850694444</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -37488,7 +37488,7 @@
         <v>45735.5517824074</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -37545,7 +37545,7 @@
         <v>45191</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>45238</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -37664,7 +37664,7 @@
         <v>44305.92047453704</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -37721,7 +37721,7 @@
         <v>44880.95741898148</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>44980.93865740741</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -37845,7 +37845,7 @@
         <v>44649.47048611111</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45561.34663194444</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -37969,7 +37969,7 @@
         <v>45667.55239583334</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44628</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44994.94296296296</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -38150,7 +38150,7 @@
         <v>45726.38615740741</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -38207,7 +38207,7 @@
         <v>45726.3862037037</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -38264,7 +38264,7 @@
         <v>45069</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -38321,7 +38321,7 @@
         <v>45254.96516203704</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>45034</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>45545.64957175926</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>44375</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>45068</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>44991</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44991</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -38740,7 +38740,7 @@
         <v>45622.46200231482</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -38797,7 +38797,7 @@
         <v>45638</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>45629.35326388889</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>45436.94628472222</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>45714</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>45615.50034722222</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>45730.56346064815</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -39154,7 +39154,7 @@
         <v>45516.94934027778</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>45392</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -39273,7 +39273,7 @@
         <v>45700.57324074074</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -39335,7 +39335,7 @@
         <v>45622.47435185185</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>45180.95907407408</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -39454,7 +39454,7 @@
         <v>45086.94010416666</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -39516,7 +39516,7 @@
         <v>45053.94313657407</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -39578,7 +39578,7 @@
         <v>45487.92856481481</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>45145</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -39697,7 +39697,7 @@
         <v>45442.96296296296</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>45351.98496527778</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -39821,7 +39821,7 @@
         <v>45555.38509259259</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -39878,7 +39878,7 @@
         <v>45436.94613425926</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -39940,7 +39940,7 @@
         <v>45681.60203703704</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -39997,7 +39997,7 @@
         <v>45344</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -40054,7 +40054,7 @@
         <v>45734.4633912037</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>44299</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>45574.63355324074</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -40225,7 +40225,7 @@
         <v>45314</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -40282,7 +40282,7 @@
         <v>45280.92645833334</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -40339,7 +40339,7 @@
         <v>45344</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -40396,7 +40396,7 @@
         <v>45344.92865740741</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -40453,7 +40453,7 @@
         <v>45344.92873842592</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -40510,7 +40510,7 @@
         <v>45322</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -40567,7 +40567,7 @@
         <v>45223</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -40624,7 +40624,7 @@
         <v>45393.94431712963</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -40686,7 +40686,7 @@
         <v>45049</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -40748,7 +40748,7 @@
         <v>45611</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -40810,7 +40810,7 @@
         <v>45260.92561342593</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -40867,7 +40867,7 @@
         <v>45128</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -40929,7 +40929,7 @@
         <v>45715.59405092592</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>45000</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>45611.65679398148</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -41110,7 +41110,7 @@
         <v>45616.34479166667</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -41172,7 +41172,7 @@
         <v>45344.92822916667</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45446.57052083333</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>45401</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>45401</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>45453.95016203704</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45233.92591435185</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45327.94459490741</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>45769.67790509259</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>45112.94303240741</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>45384</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>45754</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -41834,7 +41834,7 @@
         <v>44587.92144675926</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>45238</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -41953,7 +41953,7 @@
         <v>45723.67777777778</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -42015,7 +42015,7 @@
         <v>45716.61487268518</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>45609.34412037037</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         <v>45000</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45476.94533564815</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>45454.95960648148</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>44812.94709490741</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -42387,7 +42387,7 @@
         <v>45002.0328125</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -42449,7 +42449,7 @@
         <v>45574.61184027778</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -42506,7 +42506,7 @@
         <v>45574.62297453704</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>45105</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -42625,7 +42625,7 @@
         <v>44672.94018518519</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>45425.96239583333</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>45622</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>44929.92489583333</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>45574.51087962963</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -42925,7 +42925,7 @@
         <v>45574.51090277778</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -42987,7 +42987,7 @@
         <v>45230</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45306</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>45608.6078587963</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>44410</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45776.51130787037</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45309</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>45309</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -43401,7 +43401,7 @@
         <v>45425.96230324074</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45629.36513888889</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45776.40311342593</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45769.51087962963</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -43639,7 +43639,7 @@
         <v>45776.50651620371</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>45482.94891203703</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>45678.67761574074</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45712.65671296296</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45776.59422453704</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -43944,7 +43944,7 @@
         <v>45779.34417824074</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45779.4281712963</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>45482.9491087963</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -44130,7 +44130,7 @@
         <v>45779.49025462963</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>44741.94070601852</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -44254,7 +44254,7 @@
         <v>45712.61510416667</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -44316,7 +44316,7 @@
         <v>45448.94520833333</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -44378,7 +44378,7 @@
         <v>45782.51099537037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -44440,7 +44440,7 @@
         <v>45187</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -44497,7 +44497,7 @@
         <v>45743.36</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -44559,7 +44559,7 @@
         <v>45782.55287037037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>45782.36506944444</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -44683,7 +44683,7 @@
         <v>45782.49032407408</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45782.49046296296</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>44803.94351851852</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45782.51109953703</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>45782.36494212963</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>44977.98670138889</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45554.61583333334</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>44593</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>44889</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>45358.95813657407</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45695.44724537037</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>45782.67758101852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45629.42759259259</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>44939</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -45526,7 +45526,7 @@
         <v>45429</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -45583,7 +45583,7 @@
         <v>45769.65688657408</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>44173</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -45702,7 +45702,7 @@
         <v>45595.42738425926</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -45764,7 +45764,7 @@
         <v>45006</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -45826,7 +45826,7 @@
         <v>45604.40540509259</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -45883,7 +45883,7 @@
         <v>45604.41625</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -45940,7 +45940,7 @@
         <v>44614</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -45997,7 +45997,7 @@
         <v>45631.46665509259</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -46054,7 +46054,7 @@
         <v>45145.95326388889</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>44958</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -46173,7 +46173,7 @@
         <v>44518</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45426</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>45638.63600694444</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45056</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45056</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45238.96797453704</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45259</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>45510</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>45367.69850694444</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>45367.71348379629</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>45435</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -46815,7 +46815,7 @@
         <v>44680.95246527778</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>44671</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45572.60363425926</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>44917</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -47053,7 +47053,7 @@
         <v>45112.94310185185</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -47115,7 +47115,7 @@
         <v>44977.98660879629</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>45786.51077546296</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>44979</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>45103</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45358.95818287037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45756.63601851852</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>44971</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>45063</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -47591,7 +47591,7 @@
         <v>45028</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -47648,7 +47648,7 @@
         <v>45790.40670138889</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -47710,7 +47710,7 @@
         <v>45251</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -47767,7 +47767,7 @@
         <v>45574.57967592592</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -47824,7 +47824,7 @@
         <v>45791.53238425926</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -47881,7 +47881,7 @@
         <v>45792.34606481482</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>45211.95134259259</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -48005,7 +48005,7 @@
         <v>45792.63584490741</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -48067,7 +48067,7 @@
         <v>45793.61523148148</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -48129,7 +48129,7 @@
         <v>45792.49023148148</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>45793</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>45792.71905092592</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>45439.92752314815</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -48367,7 +48367,7 @@
         <v>44929</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45792.34527777778</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>44995.98644675926</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45601.55331018518</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45267</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45688.68196759259</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45253</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>45042</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>45796</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45211.95061342593</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -48967,7 +48967,7 @@
         <v>45629.36486111111</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -49024,7 +49024,7 @@
         <v>45611.5953125</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -49081,7 +49081,7 @@
         <v>44869</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -49138,7 +49138,7 @@
         <v>44903</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -49200,7 +49200,7 @@
         <v>45762.39876157408</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -49277,7 +49277,7 @@
         <v>44963</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -49339,7 +49339,7 @@
         <v>45119</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -49396,7 +49396,7 @@
         <v>45341.95381944445</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -49458,7 +49458,7 @@
         <v>45769.51075231482</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>45306</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>45796</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -49634,7 +49634,7 @@
         <v>45796</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>45712.61552083334</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>45645.36740740741</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -49810,7 +49810,7 @@
         <v>44067</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -49872,7 +49872,7 @@
         <v>44915</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -49934,7 +49934,7 @@
         <v>45698.59409722222</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>44953</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -50058,7 +50058,7 @@
         <v>45796</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -50115,7 +50115,7 @@
         <v>45009.089375</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -50177,7 +50177,7 @@
         <v>45540.38564814815</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -50239,7 +50239,7 @@
         <v>45241.95741898148</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -50301,7 +50301,7 @@
         <v>45241</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -50363,7 +50363,7 @@
         <v>45797.63627314815</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         <v>45656.64223379629</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -50482,7 +50482,7 @@
         <v>45040</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -50539,7 +50539,7 @@
         <v>44614</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -50596,7 +50596,7 @@
         <v>45166</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -50653,7 +50653,7 @@
         <v>45266</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -50710,7 +50710,7 @@
         <v>44886</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -50772,7 +50772,7 @@
         <v>45426</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -50829,7 +50829,7 @@
         <v>45635.47243055556</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -50886,7 +50886,7 @@
         <v>45351.98532407408</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -50948,7 +50948,7 @@
         <v>45667.57342592593</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -51010,7 +51010,7 @@
         <v>45040.94277777777</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -51072,7 +51072,7 @@
         <v>45429</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -51129,7 +51129,7 @@
         <v>45667.57347222222</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -51191,7 +51191,7 @@
         <v>45495.57677083334</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -51248,7 +51248,7 @@
         <v>45666.44943287037</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -51305,7 +51305,7 @@
         <v>44900.95700231481</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -51367,7 +51367,7 @@
         <v>44746</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -51424,7 +51424,7 @@
         <v>44972.94140046297</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -51486,7 +51486,7 @@
         <v>45729.51074074074</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -51548,7 +51548,7 @@
         <v>45441</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -51605,7 +51605,7 @@
         <v>45799.34421296296</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>45545.49078703704</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>45386.68003472222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>44657</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>45603.44644675926</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -51900,7 +51900,7 @@
         <v>45574.61634259259</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -51957,7 +51957,7 @@
         <v>44806</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -52014,7 +52014,7 @@
         <v>44571</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -52071,7 +52071,7 @@
         <v>45559.67745370371</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>45195.94672453704</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -52195,7 +52195,7 @@
         <v>45412.02506944445</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -52257,7 +52257,7 @@
         <v>45149</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -52314,7 +52314,7 @@
         <v>45243</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -52376,7 +52376,7 @@
         <v>45596.61569444444</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -52438,7 +52438,7 @@
         <v>45596.61582175926</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -52500,7 +52500,7 @@
         <v>45511</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -52562,7 +52562,7 @@
         <v>45803.5946875</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -52619,7 +52619,7 @@
         <v>45803.59417824074</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -52676,7 +52676,7 @@
         <v>45803.53157407408</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -52738,7 +52738,7 @@
         <v>45800.63619212963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -52800,7 +52800,7 @@
         <v>45800.44822916666</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -52862,7 +52862,7 @@
         <v>45800.44862268519</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -52924,7 +52924,7 @@
         <v>45803.61552083334</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -52981,7 +52981,7 @@
         <v>45803.61557870371</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -53038,7 +53038,7 @@
         <v>45800</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -53095,7 +53095,7 @@
         <v>45692.51069444444</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -53157,7 +53157,7 @@
         <v>45692.57326388889</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -53219,7 +53219,7 @@
         <v>45315.9492824074</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -53281,7 +53281,7 @@
         <v>45800.42743055556</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -53343,7 +53343,7 @@
         <v>45574.51185185185</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>45436.94636574074</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -53467,7 +53467,7 @@
         <v>45138.94925925926</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -53529,7 +53529,7 @@
         <v>45279.94564814815</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45050.94020833333</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>45804.42642361111</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>45804.59487268519</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -53772,7 +53772,7 @@
         <v>45805.61495370371</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -53834,7 +53834,7 @@
         <v>45216.92424768519</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -53891,7 +53891,7 @@
         <v>45722.48982638889</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>45797.40800925926</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -54005,7 +54005,7 @@
         <v>44869</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -54062,7 +54062,7 @@
         <v>45804.65672453704</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -54124,7 +54124,7 @@
         <v>44130.9416550926</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -54186,7 +54186,7 @@
         <v>45771.36538194444</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -54248,7 +54248,7 @@
         <v>45771.51074074074</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -54310,7 +54310,7 @@
         <v>45805.46613425926</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -54367,7 +54367,7 @@
         <v>44832</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -54429,7 +54429,7 @@
         <v>45601.5315625</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -54491,7 +54491,7 @@
         <v>45367.04693287037</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -54553,7 +54553,7 @@
         <v>45805.57390046296</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -54615,7 +54615,7 @@
         <v>45441.33313657407</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -54672,7 +54672,7 @@
         <v>44984</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -54729,7 +54729,7 @@
         <v>45275.95060185185</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -54791,7 +54791,7 @@
         <v>44670</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -54848,7 +54848,7 @@
         <v>45107</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>44911.93846064815</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -54967,7 +54967,7 @@
         <v>44550.92168981482</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -55024,7 +55024,7 @@
         <v>45636.3864699074</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -55086,7 +55086,7 @@
         <v>45850.34450231482</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -55148,7 +55148,7 @@
         <v>44743</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -55205,7 +55205,7 @@
         <v>45604.4190625</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -55262,7 +55262,7 @@
         <v>45852.53185185185</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -55324,7 +55324,7 @@
         <v>45810.36495370371</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -55386,7 +55386,7 @@
         <v>45453.4444212963</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -55443,7 +55443,7 @@
         <v>45566.68125</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -55500,7 +55500,7 @@
         <v>45659.69822916666</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -55562,7 +55562,7 @@
         <v>45446.68947916666</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -55619,7 +55619,7 @@
         <v>45386</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -55676,7 +55676,7 @@
         <v>45258</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -55733,7 +55733,7 @@
         <v>44880</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -55795,7 +55795,7 @@
         <v>45065.42894675926</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>45852.53168981482</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -55914,7 +55914,7 @@
         <v>44424</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -55971,7 +55971,7 @@
         <v>45195</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -56033,7 +56033,7 @@
         <v>45195.94679398148</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -56095,7 +56095,7 @@
         <v>45195.94685185186</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>44113</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -56219,7 +56219,7 @@
         <v>45672.44898148148</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -56281,7 +56281,7 @@
         <v>45230.96376157407</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -56343,7 +56343,7 @@
         <v>45258</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -56400,7 +56400,7 @@
         <v>45751.36490740741</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -56462,7 +56462,7 @@
         <v>44901</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -56524,7 +56524,7 @@
         <v>44901</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -56586,7 +56586,7 @@
         <v>45694.69826388889</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -56648,7 +56648,7 @@
         <v>44825</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -56710,7 +56710,7 @@
         <v>45772.6565625</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -56772,7 +56772,7 @@
         <v>44587.92149305555</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -56829,7 +56829,7 @@
         <v>44977.44373842593</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -56886,7 +56886,7 @@
         <v>45187</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -56943,7 +56943,7 @@
         <v>45393.94459490741</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -57005,7 +57005,7 @@
         <v>45646.63605324074</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -57067,7 +57067,7 @@
         <v>45758.36487268518</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -57129,7 +57129,7 @@
         <v>45208</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -57186,7 +57186,7 @@
         <v>45730.42738425926</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -57248,7 +57248,7 @@
         <v>45154.95525462963</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -57310,7 +57310,7 @@
         <v>45850.34434027778</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -57367,7 +57367,7 @@
         <v>45428.00471064815</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -57429,7 +57429,7 @@
         <v>45855.61523148148</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -57491,7 +57491,7 @@
         <v>45855.67899305555</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -57548,7 +57548,7 @@
         <v>45854.65663194445</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -57610,7 +57610,7 @@
         <v>44922</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -57667,7 +57667,7 @@
         <v>44601</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -57724,7 +57724,7 @@
         <v>44236</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -57781,7 +57781,7 @@
         <v>45338.95405092592</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -57843,7 +57843,7 @@
         <v>45813.42790509259</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -57905,7 +57905,7 @@
         <v>45769.67802083334</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -57967,7 +57967,7 @@
         <v>45309.92524305556</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -58024,7 +58024,7 @@
         <v>45306</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -58081,7 +58081,7 @@
         <v>44684.94032407407</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -58143,7 +58143,7 @@
         <v>45372.95762731481</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -58205,7 +58205,7 @@
         <v>45596.61533564814</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -58267,7 +58267,7 @@
         <v>45859.594375</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -58329,7 +58329,7 @@
         <v>45730.53208333333</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -58391,7 +58391,7 @@
         <v>45635.57331018519</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -58453,7 +58453,7 @@
         <v>45614.34545138889</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -58510,7 +58510,7 @@
         <v>45735.69842592593</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -58572,7 +58572,7 @@
         <v>45197.94171296297</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -58634,7 +58634,7 @@
         <v>45511</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -58696,7 +58696,7 @@
         <v>44405.92065972222</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -58753,7 +58753,7 @@
         <v>45579.47052083333</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -58810,7 +58810,7 @@
         <v>45856.46931712963</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -58872,7 +58872,7 @@
         <v>45482.94815972223</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -58934,7 +58934,7 @@
         <v>45096.93866898148</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -58996,7 +58996,7 @@
         <v>45656</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -59053,7 +59053,7 @@
         <v>45384</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -59110,7 +59110,7 @@
         <v>45215.94657407407</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -59172,7 +59172,7 @@
         <v>45764</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -59229,7 +59229,7 @@
         <v>44475</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -59286,7 +59286,7 @@
         <v>45818.46898148148</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -59343,7 +59343,7 @@
         <v>45714.55064814815</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -59400,7 +59400,7 @@
         <v>45098</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -59457,7 +59457,7 @@
         <v>45491</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -59519,7 +59519,7 @@
         <v>45574.39081018518</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -59581,7 +59581,7 @@
         <v>45860.30229166667</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -59638,7 +59638,7 @@
         <v>45008.01408564814</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -59700,7 +59700,7 @@
         <v>45819.6359375</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -59762,7 +59762,7 @@
         <v>45741.63675925926</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -59824,7 +59824,7 @@
         <v>44888</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -59886,7 +59886,7 @@
         <v>45467.96207175926</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -59948,7 +59948,7 @@
         <v>45821.34513888889</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -60010,7 +60010,7 @@
         <v>45702.63572916666</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -60072,7 +60072,7 @@
         <v>45590</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -60129,7 +60129,7 @@
         <v>44943.94802083333</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -60191,7 +60191,7 @@
         <v>45590.40675925926</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -60253,7 +60253,7 @@
         <v>45825.56762731481</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -60310,7 +60310,7 @@
         <v>45279.94572916667</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -60372,7 +60372,7 @@
         <v>45331.92746527777</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -60429,7 +60429,7 @@
         <v>45722.44849537037</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -60491,7 +60491,7 @@
         <v>45825.58252314815</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -60548,7 +60548,7 @@
         <v>44519.94440972222</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45681.5315625</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -60672,7 +60672,7 @@
         <v>45681.6050925926</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>45825.57675925926</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -60786,7 +60786,7 @@
         <v>45488.94747685185</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -60848,7 +60848,7 @@
         <v>45604.63575231482</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -60910,7 +60910,7 @@
         <v>45712.61502314815</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -60972,7 +60972,7 @@
         <v>45621.57395833333</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -61034,7 +61034,7 @@
         <v>45581.55260416667</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -61091,7 +61091,7 @@
         <v>44774</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -61148,7 +61148,7 @@
         <v>45869.67744212963</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -61210,7 +61210,7 @@
         <v>45869.65666666667</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -61272,7 +61272,7 @@
         <v>45552.39113425926</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -61329,7 +61329,7 @@
         <v>45552.44096064815</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -61386,7 +61386,7 @@
         <v>45673.66358796296</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -61443,7 +61443,7 @@
         <v>45826.65759259259</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -61505,7 +61505,7 @@
         <v>45474.50608796296</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -61562,7 +61562,7 @@
         <v>45827.53178240741</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -61624,7 +61624,7 @@
         <v>44894.79018518519</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -61681,7 +61681,7 @@
         <v>45244.96774305555</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -61743,7 +61743,7 @@
         <v>44904.94824074074</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -61805,7 +61805,7 @@
         <v>45827.63582175926</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -61867,7 +61867,7 @@
         <v>45735</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -61929,7 +61929,7 @@
         <v>44966.95328703704</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -61991,7 +61991,7 @@
         <v>45175</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -62053,7 +62053,7 @@
         <v>45692.48993055556</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -62115,7 +62115,7 @@
         <v>45505</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -62177,7 +62177,7 @@
         <v>45546</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -62234,7 +62234,7 @@
         <v>45215</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -62291,7 +62291,7 @@
         <v>45870.34439814815</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -62353,7 +62353,7 @@
         <v>44942</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -62415,7 +62415,7 @@
         <v>45540.38586805556</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -62477,7 +62477,7 @@
         <v>45391.95329861111</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -62539,7 +62539,7 @@
         <v>45692.49008101852</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -62601,7 +62601,7 @@
         <v>44900</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -62663,7 +62663,7 @@
         <v>45741.63659722222</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -62725,7 +62725,7 @@
         <v>45832.3459375</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -62787,7 +62787,7 @@
         <v>45839</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -62844,7 +62844,7 @@
         <v>45832.34552083333</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -62906,7 +62906,7 @@
         <v>44336</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -62963,7 +62963,7 @@
         <v>44866</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -63025,7 +63025,7 @@
         <v>45636.38599537037</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -63087,7 +63087,7 @@
         <v>45874.69844907407</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -63149,7 +63149,7 @@
         <v>45639.55240740741</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -63211,7 +63211,7 @@
         <v>44384</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -63268,7 +63268,7 @@
         <v>44944</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -63325,7 +63325,7 @@
         <v>45874.67746527777</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -63387,7 +63387,7 @@
         <v>44839</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -63444,7 +63444,7 @@
         <v>45832.34524305556</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -63501,7 +63501,7 @@
         <v>44876</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -63563,7 +63563,7 @@
         <v>45751.34859953704</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -63625,7 +63625,7 @@
         <v>45751.34873842593</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -63687,7 +63687,7 @@
         <v>45874.59496527778</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -63749,7 +63749,7 @@
         <v>45835.45686342593</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -63806,7 +63806,7 @@
         <v>44655</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -63868,7 +63868,7 @@
         <v>45622.46910879629</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -63925,7 +63925,7 @@
         <v>44685</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -63987,7 +63987,7 @@
         <v>45033</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -64044,7 +64044,7 @@
         <v>44914</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -64101,7 +64101,7 @@
         <v>44993.94950231481</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -64163,7 +64163,7 @@
         <v>44993</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -64225,7 +64225,7 @@
         <v>45835.46334490741</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -64282,7 +64282,7 @@
         <v>44362</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -64339,7 +64339,7 @@
         <v>45835.53166666667</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -64401,7 +64401,7 @@
         <v>44323</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -64463,7 +64463,7 @@
         <v>45695.51070601852</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -64525,7 +64525,7 @@
         <v>45111.92793981481</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -64587,7 +64587,7 @@
         <v>45149.95241898148</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -64649,7 +64649,7 @@
         <v>45835.72046296296</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -64706,7 +64706,7 @@
         <v>44641</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -64768,7 +64768,7 @@
         <v>44641</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -64830,7 +64830,7 @@
         <v>45158.94231481481</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -64892,7 +64892,7 @@
         <v>45329.95806712963</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -64954,7 +64954,7 @@
         <v>45706.34450231482</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -65016,7 +65016,7 @@
         <v>44656.94708333333</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -65078,7 +65078,7 @@
         <v>45148</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -65135,7 +65135,7 @@
         <v>44074</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -65197,7 +65197,7 @@
         <v>45835.40668981482</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -65259,7 +65259,7 @@
         <v>45835.4506712963</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -65316,7 +65316,7 @@
         <v>45834.65662037037</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -65378,7 +65378,7 @@
         <v>45876.53188657408</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -65440,7 +65440,7 @@
         <v>45098</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -65497,7 +65497,7 @@
         <v>45645.55665509259</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -65554,7 +65554,7 @@
         <v>45453.42041666667</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -65611,7 +65611,7 @@
         <v>44805.94592592592</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -65673,7 +65673,7 @@
         <v>45091</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -65735,7 +65735,7 @@
         <v>45726.3860300926</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -65792,7 +65792,7 @@
         <v>45356.03784722222</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -65854,7 +65854,7 @@
         <v>45139.94681712963</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -65916,7 +65916,7 @@
         <v>45086</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -65978,7 +65978,7 @@
         <v>45342</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -66040,7 +66040,7 @@
         <v>45342.9462037037</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -66102,7 +66102,7 @@
         <v>45071</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -66159,7 +66159,7 @@
         <v>45839.49082175926</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -66216,7 +66216,7 @@
         <v>45726.38575231482</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -66273,7 +66273,7 @@
         <v>45653.44836805556</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -66335,7 +66335,7 @@
         <v>45448.94600694445</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -66397,7 +66397,7 @@
         <v>45838.67800925926</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -66454,7 +66454,7 @@
         <v>45839.42864583333</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -66516,7 +66516,7 @@
         <v>45453.95538194444</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -66578,7 +66578,7 @@
         <v>45048.94340277778</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -66640,7 +66640,7 @@
         <v>45645.55672453704</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -66697,7 +66697,7 @@
         <v>45839.46915509259</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -66759,7 +66759,7 @@
         <v>45636.57329861111</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -66821,7 +66821,7 @@
         <v>45838.36532407408</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -66883,7 +66883,7 @@
         <v>45839.42810185185</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -66945,7 +66945,7 @@
         <v>45838</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -67002,7 +67002,7 @@
         <v>45839.57331018519</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -67064,7 +67064,7 @@
         <v>45133</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -67126,7 +67126,7 @@
         <v>45839.42822916667</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -67188,7 +67188,7 @@
         <v>44917</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -67245,7 +67245,7 @@
         <v>45838</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -67302,7 +67302,7 @@
         <v>45838.67887731481</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -67364,7 +67364,7 @@
         <v>45715.61523148148</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -67426,7 +67426,7 @@
         <v>45075.945</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -67488,7 +67488,7 @@
         <v>45838.48996527777</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -67545,7 +67545,7 @@
         <v>45063</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -67602,7 +67602,7 @@
         <v>45149.95372685185</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -67664,7 +67664,7 @@
         <v>45425.96275462963</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -67726,7 +67726,7 @@
         <v>44820</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -67788,7 +67788,7 @@
         <v>45540.34428240741</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -67850,7 +67850,7 @@
         <v>45840.52225694444</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -67907,7 +67907,7 @@
         <v>45841.57427083333</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -67969,7 +67969,7 @@
         <v>44680</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -68026,7 +68026,7 @@
         <v>44844.95368055555</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -68088,7 +68088,7 @@
         <v>44889.95015046297</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -68150,7 +68150,7 @@
         <v>45112</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -68212,7 +68212,7 @@
         <v>45841.6571412037</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -68269,7 +68269,7 @@
         <v>45568.51075231482</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -68331,7 +68331,7 @@
         <v>45182</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -68393,7 +68393,7 @@
         <v>44530.94694444445</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -68455,7 +68455,7 @@
         <v>45379.93637731481</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -68517,7 +68517,7 @@
         <v>45622.44774305556</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -68574,7 +68574,7 @@
         <v>45716</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -68636,7 +68636,7 @@
         <v>45425.96494212963</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -68698,7 +68698,7 @@
         <v>45007</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -68755,7 +68755,7 @@
         <v>45842.38579861111</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -68817,7 +68817,7 @@
         <v>45222</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -68879,7 +68879,7 @@
         <v>45092</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -68936,7 +68936,7 @@
         <v>45009</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -68993,7 +68993,7 @@
         <v>45183.95563657407</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -69055,7 +69055,7 @@
         <v>45638</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -69112,7 +69112,7 @@
         <v>45257.92826388889</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -69169,7 +69169,7 @@
         <v>45266.95082175926</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -69231,7 +69231,7 @@
         <v>45190</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -69293,7 +69293,7 @@
         <v>45426</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -69350,7 +69350,7 @@
         <v>45009.0897337963</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -69412,7 +69412,7 @@
         <v>44918</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -69474,7 +69474,7 @@
         <v>45616.5108912037</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -69536,7 +69536,7 @@
         <v>45842.42608796297</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -69593,7 +69593,7 @@
         <v>45733.61497685185</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -69655,7 +69655,7 @@
         <v>45733.61554398148</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -69717,7 +69717,7 @@
         <v>45847.65703703704</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -69779,7 +69779,7 @@
         <v>45847.34474537037</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -69841,7 +69841,7 @@
         <v>45847.34528935186</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -69903,7 +69903,7 @@
         <v>45888.6775</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -69965,7 +69965,7 @@
         <v>44956.93924768519</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -70027,7 +70027,7 @@
         <v>45112</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -70089,7 +70089,7 @@
         <v>45695.45868055556</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -70146,7 +70146,7 @@
         <v>45614.34541666666</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -70203,7 +70203,7 @@
         <v>45847.34597222223</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -70265,7 +70265,7 @@
         <v>45323</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -70322,7 +70322,7 @@
         <v>45847.34565972222</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -70384,7 +70384,7 @@
         <v>45614.63869212963</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -70446,7 +70446,7 @@
         <v>45847.34515046296</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -70508,7 +70508,7 @@
         <v>45889.61517361111</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -70570,7 +70570,7 @@
         <v>45469.94667824074</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -70632,7 +70632,7 @@
         <v>45665.65684027778</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -70694,7 +70694,7 @@
         <v>45103</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -70751,7 +70751,7 @@
         <v>45702.63604166666</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -70813,7 +70813,7 @@
         <v>45505</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -70875,7 +70875,7 @@
         <v>45847.61513888889</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -70932,7 +70932,7 @@
         <v>45769.65659722222</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -70994,7 +70994,7 @@
         <v>45847.61548611111</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -71051,7 +71051,7 @@
         <v>45846.34454861111</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -71113,7 +71113,7 @@
         <v>45156</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -71175,7 +71175,7 @@
         <v>44231</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -71232,7 +71232,7 @@
         <v>45848.49761574074</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -71289,7 +71289,7 @@
         <v>45671.48989583334</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -71351,7 +71351,7 @@
         <v>45848.65658564815</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -71413,7 +71413,7 @@
         <v>45688.67542824074</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -71475,7 +71475,7 @@
         <v>45182</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -71537,7 +71537,7 @@
         <v>45848.49774305556</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -71594,7 +71594,7 @@
         <v>45374</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -71651,7 +71651,7 @@
         <v>45849.65663194445</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -71713,7 +71713,7 @@
         <v>45241.95724537037</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -71775,7 +71775,7 @@
         <v>44629</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -71832,7 +71832,7 @@
         <v>45044</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -71894,7 +71894,7 @@
         <v>44517.58137731482</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -71951,7 +71951,7 @@
         <v>45180</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -72013,7 +72013,7 @@
         <v>45119</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -72070,7 +72070,7 @@
         <v>45180.95927083334</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -72132,7 +72132,7 @@
         <v>44914</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -72194,7 +72194,7 @@
         <v>45769.67767361111</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -72256,7 +72256,7 @@
         <v>45224</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -72313,7 +72313,7 @@
         <v>44174</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -72375,7 +72375,7 @@
         <v>45260</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -72432,7 +72432,7 @@
         <v>45735.53177083333</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -72494,7 +72494,7 @@
         <v>44995.98341435185</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -72556,7 +72556,7 @@
         <v>44855</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -72618,7 +72618,7 @@
         <v>45093.92207175926</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -72675,7 +72675,7 @@
         <v>45280</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -72732,7 +72732,7 @@
         <v>44903</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -72789,7 +72789,7 @@
         <v>45404.99792824074</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -72871,7 +72871,7 @@
         <v>44644</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -72933,7 +72933,7 @@
         <v>45469.94876157407</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -72995,7 +72995,7 @@
         <v>45630.7862037037</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -73052,7 +73052,7 @@
         <v>44336</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -73109,7 +73109,7 @@
         <v>45558.63575231482</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -73171,7 +73171,7 @@
         <v>45679.40362268518</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -73228,7 +73228,7 @@
         <v>45357.05300925926</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -73290,7 +73290,7 @@
         <v>44929</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -73347,7 +73347,7 @@
         <v>44356</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -73404,7 +73404,7 @@
         <v>45092</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -73461,7 +73461,7 @@
         <v>45367.67256944445</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -73518,7 +73518,7 @@
         <v>45314</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -73575,7 +73575,7 @@
         <v>45723.51079861111</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -73637,7 +73637,7 @@
         <v>45534.63537037037</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -73699,7 +73699,7 @@
         <v>45425.96263888889</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -73761,7 +73761,7 @@
         <v>44813</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -73823,7 +73823,7 @@
         <v>44614</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -73880,7 +73880,7 @@
         <v>44231</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -73937,7 +73937,7 @@
         <v>45601.40686342592</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -73999,7 +73999,7 @@
         <v>45457.96372685185</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -74061,7 +74061,7 @@
         <v>45170</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -74123,7 +74123,7 @@
         <v>45645.36743055555</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -74180,7 +74180,7 @@
         <v>45204.94399305555</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -74242,7 +74242,7 @@
         <v>45327.94443287037</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -74304,7 +74304,7 @@
         <v>45257</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -74361,7 +74361,7 @@
         <v>45072.92737268518</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>

--- a/Översikt RAGUNDA.xlsx
+++ b/Översikt RAGUNDA.xlsx
@@ -567,7 +567,7 @@
         <v>45622</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>45376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>45560.34460648148</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>45622</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>45673</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44917</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45804.67787037037</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>45590.42736111111</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45838.67753472222</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44504</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>45622</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44644</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>45560.34532407407</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45104</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45579.53179398148</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>45113</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44644.93650462963</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>45367.04916666666</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>44813</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>44473</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>44088</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>45639.55269675926</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>45622</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45790.57334490741</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>45482.63819444444</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>45779.49012731481</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45182</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>44776</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>45803.59474537037</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>45790.57349537037</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>45358.99375</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>45839.42482638889</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44805</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>45560.34484953704</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44888</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>44645.99859953704</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>45327</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>45779.57335648148</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>45121</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>45685.36501157407</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>45510</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>45174</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>45799.63574074074</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>45799.34461805555</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>45190.96092592592</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>44504</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>45832.34461805555</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>45378</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>45769.53180555555</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44133</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>45320</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>45622</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>45723.40688657408</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>45120</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>45827.5110300926</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>45113</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44133</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>44662</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>44438</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>45435.54734953704</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>45176</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45405.57392361111</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7051,7 +7051,7 @@
         <v>45176</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44994</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>45121</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>44336</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>45810.55061342593</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>45155</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>45769.67740740741</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>45786.61517361111</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>44915</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>45475.94796296296</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>44111</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44209</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>44932</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>44994</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>45457</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>45728.65684027778</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>45238</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>44911</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>44875</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>45867.63619212963</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>45769.67778935185</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>45832.34564814815</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>45595.44886574074</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>45468.97528935185</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>45471.94783564815</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>45495.56244212963</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>45846.41361111111</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>44656</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>45400.94002314815</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>45545.45748842593</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>45195</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>45446.95087962963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>45551.46912037037</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>45744.61550925926</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>45182</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>45471.94623842592</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>45244</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>45832.34578703704</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>44911</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>45674.67744212963</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>45002.94356481481</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>45425.96472222222</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>44245</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>44334.62565972222</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>44696</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>44662</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>44334</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>44334</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>44677</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>44911</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>45782.44871527778</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>45610.34415509259</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>45384</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>45378</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>45187</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>45491</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>45455.96195601852</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>45805.34415509259</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>44113</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>45491</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>45510</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>45404</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>45786.61534722222</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>44855</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44369.92025462963</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>45632.69822916666</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>45733</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45691.44769675926</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>45425.96285879629</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13627,7 +13627,7 @@
         <v>45516.94723379629</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>45265</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>45779.57392361111</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>44875</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>45188</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>45631</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>45491.94715277778</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
         <v>44855</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>44902</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14470,7 +14470,7 @@
         <v>45804.34474537037</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>45436.94686342592</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>45152</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>45093</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>45209</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>45789.36503472222</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>45751.34650462963</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45071</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>45838</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>44111</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>45397.95748842593</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>45847.61498842593</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>44788</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>44971</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>44676</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>44855</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>45394</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>45583.49642361111</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>45188</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>45769.65692129629</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>45378</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>45526.56393518519</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16486,7 +16486,7 @@
         <v>44855</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>45722.61543981481</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>45468.97495370371</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45779.57350694444</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>45631</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>45321</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>45121</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>45153</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>45241</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45238</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>45551.65726851852</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>45800.42782407408</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>44852</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>45190</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>45852.63597222222</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>45191</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>45854.61494212963</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>45372.95680555556</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18134,7 +18134,7 @@
         <v>44865</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>45205</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>44993</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>44680</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>45835.344375</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>45723.57329861111</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>45171</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>45089</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>44826.94976851852</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>44462</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>44166</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>44319</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>44705</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>44741</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>44832</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>44774.94347222222</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>44741</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>45341</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>45751.34795138889</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         <v>45775.67769675926</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>45252</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>45206</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         <v>45754.51064814815</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45597.34461805555</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>45089</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>44991</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>45487.92863425926</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45436.94644675926</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>45154</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45722.65670138889</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         <v>45600.55265046296</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>45646.34438657408</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>45153</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>45779.48993055556</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>45149</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>45510</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45771.3859837963</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>45183</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>44119</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>45457.9640625</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>45455.96184027778</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>45769.65736111111</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>45315</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>45771.36548611111</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>45636.3863425926</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45301</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>45301</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45153</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -22437,7 +22437,7 @@
         <v>45044</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
         <v>45813.49061342593</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>45491.95008101852</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>44369</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>45147</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45827.57371527778</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -22980,7 +22980,7 @@
         <v>45468</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45785.36525462963</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>44860</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>45838.38627314815</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>45208</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>45205</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -23518,7 +23518,7 @@
         <v>45847.36528935185</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>45266</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23701,7 +23701,7 @@
         <v>45033</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>45468.97461805555</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23884,7 +23884,7 @@
         <v>44157</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>44141</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44195</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>44214</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>44846</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44168</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44517</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44817</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>44880.95712962963</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -24417,7 +24417,7 @@
         <v>44880.95719907407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>44855.94125</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>44425</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>44447.92069444444</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>44490.94109953703</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24722,7 +24722,7 @@
         <v>44519.94534722222</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>44349</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>44210</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -24898,7 +24898,7 @@
         <v>44280</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>44385.33887731482</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>44243</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>44280</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>44292</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>44705</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>44518.94394675926</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>44846.9522337963</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>44362</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>44399</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>44426.94077546296</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>44818.94929398148</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>44774.94414351852</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25659,7 +25659,7 @@
         <v>44425</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>44823.48666666666</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25778,7 +25778,7 @@
         <v>44663</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25840,7 +25840,7 @@
         <v>44111</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25897,7 +25897,7 @@
         <v>44874.95553240741</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>44784.9408912037</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -26021,7 +26021,7 @@
         <v>44837</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         <v>44714</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -26140,7 +26140,7 @@
         <v>44670</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>44858</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>44704.94234953704</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>44855</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44078</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>44175</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>44194</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -26559,7 +26559,7 @@
         <v>44239</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>44443</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>44860</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>44741</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>44132</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>44495.93966435185</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>44126</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -26978,7 +26978,7 @@
         <v>44854</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>44859.95710648148</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>44530</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>44823.94993055556</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>44836.9491087963</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>44125.94493055555</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -27345,7 +27345,7 @@
         <v>44273.92081018518</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>44833.95405092592</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>44579.68604166667</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>44084</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>44883</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>44728.94398148148</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>44259</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>44287</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>44629.56258101852</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>44308</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>44308</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>44452</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>44281</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>44421.97322916667</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>44351</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>44069</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -28292,7 +28292,7 @@
         <v>44832.95435185185</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -28354,7 +28354,7 @@
         <v>44586</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>44434.94559027778</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>44690</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         <v>44867</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>44876.95104166667</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>44111</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>44500.93887731482</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>44476</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28840,7 +28840,7 @@
         <v>44601</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>44714.94162037037</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>44357</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>44477.48994212963</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>44228</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>44515.93767361111</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>44696.93986111111</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>44783</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -29316,7 +29316,7 @@
         <v>44802</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>44805</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>44315</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -29502,7 +29502,7 @@
         <v>44861</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>44864.94835648148</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         <v>44308</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -29683,7 +29683,7 @@
         <v>44832.95300925926</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29745,7 +29745,7 @@
         <v>44830</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>44776</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>44482.92271990741</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>44853.9499537037</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>44512</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -30045,7 +30045,7 @@
         <v>44349.91995370371</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>44824.94635416667</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>44349.92013888889</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -30221,7 +30221,7 @@
         <v>44308</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>44662</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -30340,7 +30340,7 @@
         <v>44851.95488425926</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>44704</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -30459,7 +30459,7 @@
         <v>44685</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>44379</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44671</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>44615</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>44075</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>44434.94517361111</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30806,7 +30806,7 @@
         <v>44071</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>44704.94229166667</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>44861</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -30992,7 +30992,7 @@
         <v>44818</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -31054,7 +31054,7 @@
         <v>44729.94136574074</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>44833.9519212963</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -31178,7 +31178,7 @@
         <v>44777.95504629629</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>44855.9471875</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>44099</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>44138</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -31421,7 +31421,7 @@
         <v>44418.9369212963</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -31483,7 +31483,7 @@
         <v>44621</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>44074</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>44074</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>44650</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>44463.94077546296</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44788</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44853</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>44431</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>44615</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>44140</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>44815</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>44140</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -32202,7 +32202,7 @@
         <v>44578.92284722222</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -32259,7 +32259,7 @@
         <v>44799.94394675926</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>44599.98685185185</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -32383,7 +32383,7 @@
         <v>44574</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -32440,7 +32440,7 @@
         <v>44494.93930555556</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>44883.94918981481</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>44124</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -32621,7 +32621,7 @@
         <v>44846</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -32683,7 +32683,7 @@
         <v>44489.94711805556</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>44322</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>44068.62614583333</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>44823</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>44704.9422337963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>44727</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -33040,7 +33040,7 @@
         <v>44495</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>44781</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>44858</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -33221,7 +33221,7 @@
         <v>44425</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -33283,7 +33283,7 @@
         <v>44854.95390046296</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
         <v>44889</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44595</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44831.94846064815</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -33526,7 +33526,7 @@
         <v>44831.9485300926</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>44784.94157407407</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>44496</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>44734.94193287037</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -33769,7 +33769,7 @@
         <v>44704.94217592593</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>44349.91978009259</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>44361.55445601852</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -33945,7 +33945,7 @@
         <v>45456.96601851852</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>44402.42243055555</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>45324</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -34121,7 +34121,7 @@
         <v>44728.94392361111</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -34183,7 +34183,7 @@
         <v>44958.94298611111</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -34245,7 +34245,7 @@
         <v>45714.60649305556</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -34302,7 +34302,7 @@
         <v>44656</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -34364,7 +34364,7 @@
         <v>45197.94152777778</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -34426,7 +34426,7 @@
         <v>45775.67747685185</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -34488,7 +34488,7 @@
         <v>45053.94305555556</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>44356.91935185185</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>44894</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -34664,7 +34664,7 @@
         <v>45530</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -34721,7 +34721,7 @@
         <v>45534</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>45456.96569444444</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -34840,7 +34840,7 @@
         <v>44993.94958333333</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>45257</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>44879</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>45664.55241898148</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>45184</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>45601.59518518519</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>45625.51068287037</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -35269,7 +35269,7 @@
         <v>45254.96402777778</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>44932.93927083333</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>44802.94811342593</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>44897</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>45596.61553240741</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -35579,7 +35579,7 @@
         <v>45176</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -35636,7 +35636,7 @@
         <v>45314.92758101852</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -35693,7 +35693,7 @@
         <v>45392</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>45392.92903935185</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -35807,7 +35807,7 @@
         <v>44879.95768518518</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -35869,7 +35869,7 @@
         <v>44635</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>45615.47091435185</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>45638.34431712963</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>45075.94506944445</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>45054</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>45761.67744212963</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>45420</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -36298,7 +36298,7 @@
         <v>45618.46921296296</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -36360,7 +36360,7 @@
         <v>45516.94732638889</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>44957.94075231482</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -36484,7 +36484,7 @@
         <v>45000</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -36546,7 +36546,7 @@
         <v>45000</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>45734.45268518518</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -36665,7 +36665,7 @@
         <v>45253</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>44286</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>45747.67739583334</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>45078</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -36898,7 +36898,7 @@
         <v>45341</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -36955,7 +36955,7 @@
         <v>45289</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -37012,7 +37012,7 @@
         <v>45608.52354166667</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -37074,7 +37074,7 @@
         <v>45737.63574074074</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>45737.69822916666</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -37198,7 +37198,7 @@
         <v>44153</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -37255,7 +37255,7 @@
         <v>45210</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -37312,7 +37312,7 @@
         <v>45559.67759259259</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -37374,7 +37374,7 @@
         <v>45208</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -37431,7 +37431,7 @@
         <v>45603.67850694444</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -37488,7 +37488,7 @@
         <v>45735.5517824074</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -37545,7 +37545,7 @@
         <v>45191</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>45238</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -37664,7 +37664,7 @@
         <v>44305.92047453704</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -37721,7 +37721,7 @@
         <v>44880.95741898148</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>44980.93865740741</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -37845,7 +37845,7 @@
         <v>44649.47048611111</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45561.34663194444</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -37969,7 +37969,7 @@
         <v>45667.55239583334</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>44628</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -38088,7 +38088,7 @@
         <v>44994.94296296296</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -38150,7 +38150,7 @@
         <v>45726.38615740741</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -38207,7 +38207,7 @@
         <v>45726.3862037037</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -38264,7 +38264,7 @@
         <v>45069</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -38321,7 +38321,7 @@
         <v>45254.96516203704</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>45034</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>45545.64957175926</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>44375</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>45068</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>44991</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44991</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -38740,7 +38740,7 @@
         <v>45622.46200231482</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -38797,7 +38797,7 @@
         <v>45638</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>45629.35326388889</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>45436.94628472222</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>45714</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>45615.50034722222</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>45730.56346064815</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -39154,7 +39154,7 @@
         <v>45516.94934027778</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>45392</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -39273,7 +39273,7 @@
         <v>45700.57324074074</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -39335,7 +39335,7 @@
         <v>45622.47435185185</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>45180.95907407408</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -39454,7 +39454,7 @@
         <v>45086.94010416666</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -39516,7 +39516,7 @@
         <v>45053.94313657407</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -39578,7 +39578,7 @@
         <v>45487.92856481481</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>45145</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -39697,7 +39697,7 @@
         <v>45442.96296296296</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>45351.98496527778</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -39821,7 +39821,7 @@
         <v>45555.38509259259</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -39878,7 +39878,7 @@
         <v>45436.94613425926</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -39940,7 +39940,7 @@
         <v>45681.60203703704</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -39997,7 +39997,7 @@
         <v>45344</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -40054,7 +40054,7 @@
         <v>45734.4633912037</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>44299</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>45574.63355324074</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -40225,7 +40225,7 @@
         <v>45314</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -40282,7 +40282,7 @@
         <v>45280.92645833334</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -40339,7 +40339,7 @@
         <v>45344</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -40396,7 +40396,7 @@
         <v>45344.92865740741</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -40453,7 +40453,7 @@
         <v>45344.92873842592</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -40510,7 +40510,7 @@
         <v>45322</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -40567,7 +40567,7 @@
         <v>45223</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -40624,7 +40624,7 @@
         <v>45393.94431712963</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -40686,7 +40686,7 @@
         <v>45049</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -40748,7 +40748,7 @@
         <v>45611</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -40810,7 +40810,7 @@
         <v>45260.92561342593</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -40867,7 +40867,7 @@
         <v>45128</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -40929,7 +40929,7 @@
         <v>45715.59405092592</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -40991,7 +40991,7 @@
         <v>45000</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -41048,7 +41048,7 @@
         <v>45611.65679398148</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -41110,7 +41110,7 @@
         <v>45616.34479166667</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -41172,7 +41172,7 @@
         <v>45344.92822916667</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -41229,7 +41229,7 @@
         <v>45446.57052083333</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>45401</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -41348,7 +41348,7 @@
         <v>45401</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>45453.95016203704</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45233.92591435185</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45327.94459490741</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>45769.67790509259</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -41653,7 +41653,7 @@
         <v>45112.94303240741</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -41715,7 +41715,7 @@
         <v>45384</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>45754</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -41834,7 +41834,7 @@
         <v>44587.92144675926</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>45238</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -41953,7 +41953,7 @@
         <v>45723.67777777778</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -42015,7 +42015,7 @@
         <v>45716.61487268518</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>45609.34412037037</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         <v>45000</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>45476.94533564815</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>45454.95960648148</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>44812.94709490741</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -42387,7 +42387,7 @@
         <v>45002.0328125</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -42449,7 +42449,7 @@
         <v>45574.61184027778</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -42506,7 +42506,7 @@
         <v>45574.62297453704</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -42563,7 +42563,7 @@
         <v>45105</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -42625,7 +42625,7 @@
         <v>44672.94018518519</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>45425.96239583333</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>45622</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>44929.92489583333</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -42863,7 +42863,7 @@
         <v>45574.51087962963</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -42925,7 +42925,7 @@
         <v>45574.51090277778</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -42987,7 +42987,7 @@
         <v>45230</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45306</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>45608.6078587963</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>44410</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45776.51130787037</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -43287,7 +43287,7 @@
         <v>45309</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>45309</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -43401,7 +43401,7 @@
         <v>45425.96230324074</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45629.36513888889</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45776.40311342593</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45769.51087962963</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -43639,7 +43639,7 @@
         <v>45776.50651620371</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>45482.94891203703</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>45678.67761574074</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45712.65671296296</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45776.59422453704</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -43944,7 +43944,7 @@
         <v>45779.34417824074</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45779.4281712963</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>45482.9491087963</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -44130,7 +44130,7 @@
         <v>45779.49025462963</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>44741.94070601852</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -44254,7 +44254,7 @@
         <v>45712.61510416667</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -44316,7 +44316,7 @@
         <v>45448.94520833333</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -44378,7 +44378,7 @@
         <v>45782.51099537037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -44440,7 +44440,7 @@
         <v>45187</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -44497,7 +44497,7 @@
         <v>45743.36</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -44559,7 +44559,7 @@
         <v>45782.55287037037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>45782.36506944444</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -44683,7 +44683,7 @@
         <v>45782.49032407408</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45782.49046296296</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>44803.94351851852</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -44869,7 +44869,7 @@
         <v>45782.51109953703</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>45782.36494212963</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>44977.98670138889</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45554.61583333334</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>44593</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>44889</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -45226,7 +45226,7 @@
         <v>45358.95813657407</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -45283,7 +45283,7 @@
         <v>45695.44724537037</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>45782.67758101852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>45629.42759259259</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>44939</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -45526,7 +45526,7 @@
         <v>45429</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -45583,7 +45583,7 @@
         <v>45769.65688657408</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>44173</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -45702,7 +45702,7 @@
         <v>45595.42738425926</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -45764,7 +45764,7 @@
         <v>45006</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -45826,7 +45826,7 @@
         <v>45604.40540509259</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -45883,7 +45883,7 @@
         <v>45604.41625</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -45940,7 +45940,7 @@
         <v>44614</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -45997,7 +45997,7 @@
         <v>45631.46665509259</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -46054,7 +46054,7 @@
         <v>45145.95326388889</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>44958</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -46173,7 +46173,7 @@
         <v>44518</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45426</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>45638.63600694444</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45056</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45056</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45238.96797453704</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45259</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -46582,7 +46582,7 @@
         <v>45510</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>45367.69850694444</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -46701,7 +46701,7 @@
         <v>45367.71348379629</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>45435</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -46815,7 +46815,7 @@
         <v>44680.95246527778</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>44671</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -46934,7 +46934,7 @@
         <v>45572.60363425926</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -46991,7 +46991,7 @@
         <v>44917</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -47053,7 +47053,7 @@
         <v>45112.94310185185</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -47115,7 +47115,7 @@
         <v>44977.98660879629</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>45786.51077546296</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>44979</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>45103</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45358.95818287037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45756.63601851852</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -47472,7 +47472,7 @@
         <v>44971</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -47534,7 +47534,7 @@
         <v>45063</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -47591,7 +47591,7 @@
         <v>45028</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -47648,7 +47648,7 @@
         <v>45790.40670138889</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -47710,7 +47710,7 @@
         <v>45251</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -47767,7 +47767,7 @@
         <v>45574.57967592592</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -47824,7 +47824,7 @@
         <v>45791.53238425926</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -47881,7 +47881,7 @@
         <v>45792.34606481482</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>45211.95134259259</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -48005,7 +48005,7 @@
         <v>45792.63584490741</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -48067,7 +48067,7 @@
         <v>45793.61523148148</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -48129,7 +48129,7 @@
         <v>45792.49023148148</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>45793</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>45792.71905092592</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>45439.92752314815</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -48367,7 +48367,7 @@
         <v>44929</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45792.34527777778</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>44995.98644675926</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45601.55331018518</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -48610,7 +48610,7 @@
         <v>45267</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>45688.68196759259</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>45253</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -48791,7 +48791,7 @@
         <v>45042</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>45796</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>45211.95061342593</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -48967,7 +48967,7 @@
         <v>45629.36486111111</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -49024,7 +49024,7 @@
         <v>45611.5953125</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -49081,7 +49081,7 @@
         <v>44869</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -49138,7 +49138,7 @@
         <v>44903</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -49200,7 +49200,7 @@
         <v>45762.39876157408</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -49277,7 +49277,7 @@
         <v>44963</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -49339,7 +49339,7 @@
         <v>45119</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -49396,7 +49396,7 @@
         <v>45341.95381944445</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -49458,7 +49458,7 @@
         <v>45769.51075231482</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>45306</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>45796</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -49634,7 +49634,7 @@
         <v>45796</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>45712.61552083334</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -49753,7 +49753,7 @@
         <v>45645.36740740741</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -49810,7 +49810,7 @@
         <v>44067</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -49872,7 +49872,7 @@
         <v>44915</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -49934,7 +49934,7 @@
         <v>45698.59409722222</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>44953</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -50058,7 +50058,7 @@
         <v>45796</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -50115,7 +50115,7 @@
         <v>45009.089375</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -50177,7 +50177,7 @@
         <v>45540.38564814815</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -50239,7 +50239,7 @@
         <v>45241.95741898148</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -50301,7 +50301,7 @@
         <v>45241</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -50363,7 +50363,7 @@
         <v>45797.63627314815</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         <v>45656.64223379629</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -50482,7 +50482,7 @@
         <v>45040</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -50539,7 +50539,7 @@
         <v>44614</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -50596,7 +50596,7 @@
         <v>45166</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -50653,7 +50653,7 @@
         <v>45266</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -50710,7 +50710,7 @@
         <v>44886</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -50772,7 +50772,7 @@
         <v>45426</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -50829,7 +50829,7 @@
         <v>45635.47243055556</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -50886,7 +50886,7 @@
         <v>45351.98532407408</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -50948,7 +50948,7 @@
         <v>45667.57342592593</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -51010,7 +51010,7 @@
         <v>45040.94277777777</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -51072,7 +51072,7 @@
         <v>45429</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -51129,7 +51129,7 @@
         <v>45667.57347222222</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -51191,7 +51191,7 @@
         <v>45495.57677083334</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -51248,7 +51248,7 @@
         <v>45666.44943287037</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -51305,7 +51305,7 @@
         <v>44900.95700231481</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -51367,7 +51367,7 @@
         <v>44746</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -51424,7 +51424,7 @@
         <v>44972.94140046297</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -51486,7 +51486,7 @@
         <v>45729.51074074074</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -51548,7 +51548,7 @@
         <v>45441</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -51605,7 +51605,7 @@
         <v>45799.34421296296</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>45545.49078703704</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -51724,7 +51724,7 @@
         <v>45386.68003472222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -51781,7 +51781,7 @@
         <v>44657</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>45603.44644675926</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -51900,7 +51900,7 @@
         <v>45574.61634259259</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -51957,7 +51957,7 @@
         <v>44806</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -52014,7 +52014,7 @@
         <v>44571</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -52071,7 +52071,7 @@
         <v>45559.67745370371</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>45195.94672453704</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -52195,7 +52195,7 @@
         <v>45412.02506944445</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -52257,7 +52257,7 @@
         <v>45149</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -52314,7 +52314,7 @@
         <v>45243</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -52376,7 +52376,7 @@
         <v>45596.61569444444</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -52438,7 +52438,7 @@
         <v>45596.61582175926</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -52500,7 +52500,7 @@
         <v>45511</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -52562,7 +52562,7 @@
         <v>45803.5946875</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -52619,7 +52619,7 @@
         <v>45803.59417824074</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -52676,7 +52676,7 @@
         <v>45803.53157407408</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -52738,7 +52738,7 @@
         <v>45800.63619212963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -52800,7 +52800,7 @@
         <v>45800.44822916666</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -52862,7 +52862,7 @@
         <v>45800.44862268519</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -52924,7 +52924,7 @@
         <v>45803.61552083334</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -52981,7 +52981,7 @@
         <v>45803.61557870371</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -53038,7 +53038,7 @@
         <v>45800</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -53095,7 +53095,7 @@
         <v>45692.51069444444</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -53157,7 +53157,7 @@
         <v>45692.57326388889</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -53219,7 +53219,7 @@
         <v>45315.9492824074</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -53281,7 +53281,7 @@
         <v>45800.42743055556</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -53343,7 +53343,7 @@
         <v>45574.51185185185</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         <v>45436.94636574074</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -53467,7 +53467,7 @@
         <v>45138.94925925926</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -53529,7 +53529,7 @@
         <v>45279.94564814815</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45050.94020833333</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>45804.42642361111</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>45804.59487268519</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -53772,7 +53772,7 @@
         <v>45805.61495370371</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -53834,7 +53834,7 @@
         <v>45216.92424768519</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -53891,7 +53891,7 @@
         <v>45722.48982638889</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>45797.40800925926</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -54005,7 +54005,7 @@
         <v>44869</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -54062,7 +54062,7 @@
         <v>45804.65672453704</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -54124,7 +54124,7 @@
         <v>44130.9416550926</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -54186,7 +54186,7 @@
         <v>45771.36538194444</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -54248,7 +54248,7 @@
         <v>45771.51074074074</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -54310,7 +54310,7 @@
         <v>45805.46613425926</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -54367,7 +54367,7 @@
         <v>44832</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -54429,7 +54429,7 @@
         <v>45601.5315625</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -54491,7 +54491,7 @@
         <v>45367.04693287037</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -54553,7 +54553,7 @@
         <v>45805.57390046296</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -54615,7 +54615,7 @@
         <v>45441.33313657407</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -54672,7 +54672,7 @@
         <v>44984</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -54729,7 +54729,7 @@
         <v>45275.95060185185</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -54791,7 +54791,7 @@
         <v>44670</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -54848,7 +54848,7 @@
         <v>45107</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>44911.93846064815</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -54967,7 +54967,7 @@
         <v>44550.92168981482</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -55024,7 +55024,7 @@
         <v>45636.3864699074</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -55086,7 +55086,7 @@
         <v>45850.34450231482</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -55148,7 +55148,7 @@
         <v>44743</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -55205,7 +55205,7 @@
         <v>45604.4190625</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -55262,7 +55262,7 @@
         <v>45852.53185185185</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -55324,7 +55324,7 @@
         <v>45810.36495370371</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -55386,7 +55386,7 @@
         <v>45453.4444212963</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -55443,7 +55443,7 @@
         <v>45566.68125</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -55500,7 +55500,7 @@
         <v>45659.69822916666</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -55562,7 +55562,7 @@
         <v>45446.68947916666</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -55619,7 +55619,7 @@
         <v>45386</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -55676,7 +55676,7 @@
         <v>45258</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -55733,7 +55733,7 @@
         <v>44880</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -55795,7 +55795,7 @@
         <v>45065.42894675926</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>45852.53168981482</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -55914,7 +55914,7 @@
         <v>44424</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -55971,7 +55971,7 @@
         <v>45195</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -56033,7 +56033,7 @@
         <v>45195.94679398148</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -56095,7 +56095,7 @@
         <v>45195.94685185186</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>44113</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -56219,7 +56219,7 @@
         <v>45672.44898148148</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -56281,7 +56281,7 @@
         <v>45230.96376157407</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -56343,7 +56343,7 @@
         <v>45258</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -56400,7 +56400,7 @@
         <v>45751.36490740741</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -56462,7 +56462,7 @@
         <v>44901</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -56524,7 +56524,7 @@
         <v>44901</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -56586,7 +56586,7 @@
         <v>45694.69826388889</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -56648,7 +56648,7 @@
         <v>44825</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -56710,7 +56710,7 @@
         <v>45772.6565625</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -56772,7 +56772,7 @@
         <v>44587.92149305555</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -56829,7 +56829,7 @@
         <v>44977.44373842593</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -56886,7 +56886,7 @@
         <v>45187</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -56943,7 +56943,7 @@
         <v>45393.94459490741</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -57005,7 +57005,7 @@
         <v>45646.63605324074</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -57067,7 +57067,7 @@
         <v>45758.36487268518</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -57129,7 +57129,7 @@
         <v>45208</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -57186,7 +57186,7 @@
         <v>45730.42738425926</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -57248,7 +57248,7 @@
         <v>45154.95525462963</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -57310,7 +57310,7 @@
         <v>45850.34434027778</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -57367,7 +57367,7 @@
         <v>45428.00471064815</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -57429,7 +57429,7 @@
         <v>45855.61523148148</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -57491,7 +57491,7 @@
         <v>45855.67899305555</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -57548,7 +57548,7 @@
         <v>45854.65663194445</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -57610,7 +57610,7 @@
         <v>44922</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -57667,7 +57667,7 @@
         <v>44601</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -57724,7 +57724,7 @@
         <v>44236</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -57781,7 +57781,7 @@
         <v>45338.95405092592</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -57843,7 +57843,7 @@
         <v>45813.42790509259</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -57905,7 +57905,7 @@
         <v>45769.67802083334</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -57967,7 +57967,7 @@
         <v>45309.92524305556</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -58024,7 +58024,7 @@
         <v>45306</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -58081,7 +58081,7 @@
         <v>44684.94032407407</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -58143,7 +58143,7 @@
         <v>45372.95762731481</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -58205,7 +58205,7 @@
         <v>45596.61533564814</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -58267,7 +58267,7 @@
         <v>45859.594375</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -58329,7 +58329,7 @@
         <v>45730.53208333333</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -58391,7 +58391,7 @@
         <v>45635.57331018519</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -58453,7 +58453,7 @@
         <v>45614.34545138889</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -58510,7 +58510,7 @@
         <v>45735.69842592593</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -58572,7 +58572,7 @@
         <v>45197.94171296297</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -58634,7 +58634,7 @@
         <v>45511</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -58696,7 +58696,7 @@
         <v>44405.92065972222</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -58753,7 +58753,7 @@
         <v>45579.47052083333</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -58810,7 +58810,7 @@
         <v>45856.46931712963</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -58872,7 +58872,7 @@
         <v>45482.94815972223</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -58934,7 +58934,7 @@
         <v>45096.93866898148</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -58996,7 +58996,7 @@
         <v>45656</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -59053,7 +59053,7 @@
         <v>45384</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -59110,7 +59110,7 @@
         <v>45215.94657407407</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -59172,7 +59172,7 @@
         <v>45764</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -59229,7 +59229,7 @@
         <v>44475</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -59286,7 +59286,7 @@
         <v>45818.46898148148</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -59343,7 +59343,7 @@
         <v>45714.55064814815</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -59400,7 +59400,7 @@
         <v>45098</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -59457,7 +59457,7 @@
         <v>45491</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -59519,7 +59519,7 @@
         <v>45574.39081018518</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -59581,7 +59581,7 @@
         <v>45860.30229166667</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -59638,7 +59638,7 @@
         <v>45008.01408564814</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -59700,7 +59700,7 @@
         <v>45819.6359375</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -59762,7 +59762,7 @@
         <v>45741.63675925926</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -59824,7 +59824,7 @@
         <v>44888</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -59886,7 +59886,7 @@
         <v>45467.96207175926</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -59948,7 +59948,7 @@
         <v>45821.34513888889</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -60010,7 +60010,7 @@
         <v>45702.63572916666</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -60072,7 +60072,7 @@
         <v>45590</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -60129,7 +60129,7 @@
         <v>44943.94802083333</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -60191,7 +60191,7 @@
         <v>45590.40675925926</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -60253,7 +60253,7 @@
         <v>45825.56762731481</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -60310,7 +60310,7 @@
         <v>45279.94572916667</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -60372,7 +60372,7 @@
         <v>45331.92746527777</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -60429,7 +60429,7 @@
         <v>45722.44849537037</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -60491,7 +60491,7 @@
         <v>45825.58252314815</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -60548,7 +60548,7 @@
         <v>44519.94440972222</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>45681.5315625</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -60672,7 +60672,7 @@
         <v>45681.6050925926</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>45825.57675925926</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -60786,7 +60786,7 @@
         <v>45488.94747685185</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -60848,7 +60848,7 @@
         <v>45604.63575231482</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -60910,7 +60910,7 @@
         <v>45712.61502314815</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -60972,7 +60972,7 @@
         <v>45621.57395833333</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -61034,7 +61034,7 @@
         <v>45581.55260416667</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -61091,7 +61091,7 @@
         <v>44774</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -61148,7 +61148,7 @@
         <v>45869.67744212963</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -61210,7 +61210,7 @@
         <v>45869.65666666667</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -61272,7 +61272,7 @@
         <v>45552.39113425926</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -61329,7 +61329,7 @@
         <v>45552.44096064815</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -61386,7 +61386,7 @@
         <v>45673.66358796296</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -61443,7 +61443,7 @@
         <v>45826.65759259259</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -61505,7 +61505,7 @@
         <v>45474.50608796296</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -61562,7 +61562,7 @@
         <v>45827.53178240741</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -61624,7 +61624,7 @@
         <v>44894.79018518519</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -61681,7 +61681,7 @@
         <v>45244.96774305555</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -61743,7 +61743,7 @@
         <v>44904.94824074074</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -61805,7 +61805,7 @@
         <v>45827.63582175926</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -61867,7 +61867,7 @@
         <v>45735</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -61929,7 +61929,7 @@
         <v>44966.95328703704</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -61991,7 +61991,7 @@
         <v>45175</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -62053,7 +62053,7 @@
         <v>45692.48993055556</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -62115,7 +62115,7 @@
         <v>45505</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -62177,7 +62177,7 @@
         <v>45546</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -62234,7 +62234,7 @@
         <v>45215</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -62291,7 +62291,7 @@
         <v>45870.34439814815</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -62353,7 +62353,7 @@
         <v>44942</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -62415,7 +62415,7 @@
         <v>45540.38586805556</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -62477,7 +62477,7 @@
         <v>45391.95329861111</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -62539,7 +62539,7 @@
         <v>45692.49008101852</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -62601,7 +62601,7 @@
         <v>44900</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -62663,7 +62663,7 @@
         <v>45741.63659722222</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -62725,7 +62725,7 @@
         <v>45832.3459375</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -62787,7 +62787,7 @@
         <v>45839</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -62844,7 +62844,7 @@
         <v>45832.34552083333</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -62906,7 +62906,7 @@
         <v>44336</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -62963,7 +62963,7 @@
         <v>44866</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -63025,7 +63025,7 @@
         <v>45636.38599537037</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -63087,7 +63087,7 @@
         <v>45874.69844907407</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -63149,7 +63149,7 @@
         <v>45639.55240740741</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -63211,7 +63211,7 @@
         <v>44384</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -63268,7 +63268,7 @@
         <v>44944</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -63325,7 +63325,7 @@
         <v>45874.67746527777</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -63387,7 +63387,7 @@
         <v>44839</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -63444,7 +63444,7 @@
         <v>45832.34524305556</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -63501,7 +63501,7 @@
         <v>44876</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -63563,7 +63563,7 @@
         <v>45751.34859953704</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -63625,7 +63625,7 @@
         <v>45751.34873842593</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -63687,7 +63687,7 @@
         <v>45874.59496527778</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -63749,7 +63749,7 @@
         <v>45835.45686342593</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -63806,7 +63806,7 @@
         <v>44655</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -63868,7 +63868,7 @@
         <v>45622.46910879629</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -63925,7 +63925,7 @@
         <v>44685</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -63987,7 +63987,7 @@
         <v>45033</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -64044,7 +64044,7 @@
         <v>44914</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -64101,7 +64101,7 @@
         <v>44993.94950231481</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -64163,7 +64163,7 @@
         <v>44993</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -64225,7 +64225,7 @@
         <v>45835.46334490741</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -64282,7 +64282,7 @@
         <v>44362</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -64339,7 +64339,7 @@
         <v>45835.53166666667</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -64401,7 +64401,7 @@
         <v>44323</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -64463,7 +64463,7 @@
         <v>45695.51070601852</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -64525,7 +64525,7 @@
         <v>45111.92793981481</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -64587,7 +64587,7 @@
         <v>45149.95241898148</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -64649,7 +64649,7 @@
         <v>45835.72046296296</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -64706,7 +64706,7 @@
         <v>44641</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -64768,7 +64768,7 @@
         <v>44641</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -64830,7 +64830,7 @@
         <v>45158.94231481481</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -64892,7 +64892,7 @@
         <v>45329.95806712963</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -64954,7 +64954,7 @@
         <v>45706.34450231482</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -65016,7 +65016,7 @@
         <v>44656.94708333333</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -65078,7 +65078,7 @@
         <v>45148</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -65135,7 +65135,7 @@
         <v>44074</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -65197,7 +65197,7 @@
         <v>45835.40668981482</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -65259,7 +65259,7 @@
         <v>45835.4506712963</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -65316,7 +65316,7 @@
         <v>45834.65662037037</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -65378,7 +65378,7 @@
         <v>45876.53188657408</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -65440,7 +65440,7 @@
         <v>45098</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -65497,7 +65497,7 @@
         <v>45645.55665509259</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -65554,7 +65554,7 @@
         <v>45453.42041666667</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -65611,7 +65611,7 @@
         <v>44805.94592592592</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -65673,7 +65673,7 @@
         <v>45091</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -65735,7 +65735,7 @@
         <v>45726.3860300926</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -65792,7 +65792,7 @@
         <v>45356.03784722222</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -65854,7 +65854,7 @@
         <v>45139.94681712963</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -65916,7 +65916,7 @@
         <v>45086</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -65978,7 +65978,7 @@
         <v>45342</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -66040,7 +66040,7 @@
         <v>45342.9462037037</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -66102,7 +66102,7 @@
         <v>45071</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -66159,7 +66159,7 @@
         <v>45839.49082175926</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -66216,7 +66216,7 @@
         <v>45726.38575231482</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -66273,7 +66273,7 @@
         <v>45653.44836805556</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -66335,7 +66335,7 @@
         <v>45448.94600694445</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -66397,7 +66397,7 @@
         <v>45838.67800925926</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -66454,7 +66454,7 @@
         <v>45839.42864583333</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -66516,7 +66516,7 @@
         <v>45453.95538194444</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -66578,7 +66578,7 @@
         <v>45048.94340277778</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -66640,7 +66640,7 @@
         <v>45645.55672453704</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -66697,7 +66697,7 @@
         <v>45839.46915509259</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -66759,7 +66759,7 @@
         <v>45636.57329861111</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -66821,7 +66821,7 @@
         <v>45838.36532407408</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -66883,7 +66883,7 @@
         <v>45839.42810185185</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -66945,7 +66945,7 @@
         <v>45838</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -67002,7 +67002,7 @@
         <v>45839.57331018519</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -67064,7 +67064,7 @@
         <v>45133</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -67126,7 +67126,7 @@
         <v>45839.42822916667</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -67188,7 +67188,7 @@
         <v>44917</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -67245,7 +67245,7 @@
         <v>45838</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -67302,7 +67302,7 @@
         <v>45838.67887731481</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -67364,7 +67364,7 @@
         <v>45715.61523148148</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -67426,7 +67426,7 @@
         <v>45075.945</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -67488,7 +67488,7 @@
         <v>45838.48996527777</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -67545,7 +67545,7 @@
         <v>45063</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -67602,7 +67602,7 @@
         <v>45149.95372685185</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -67664,7 +67664,7 @@
         <v>45425.96275462963</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -67726,7 +67726,7 @@
         <v>44820</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -67788,7 +67788,7 @@
         <v>45540.34428240741</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -67850,7 +67850,7 @@
         <v>45840.52225694444</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -67907,7 +67907,7 @@
         <v>45841.57427083333</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -67969,7 +67969,7 @@
         <v>44680</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -68026,7 +68026,7 @@
         <v>44844.95368055555</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -68088,7 +68088,7 @@
         <v>44889.95015046297</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -68150,7 +68150,7 @@
         <v>45112</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -68212,7 +68212,7 @@
         <v>45841.6571412037</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -68269,7 +68269,7 @@
         <v>45568.51075231482</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -68331,7 +68331,7 @@
         <v>45182</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -68393,7 +68393,7 @@
         <v>44530.94694444445</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -68455,7 +68455,7 @@
         <v>45379.93637731481</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -68517,7 +68517,7 @@
         <v>45622.44774305556</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -68574,7 +68574,7 @@
         <v>45716</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -68636,7 +68636,7 @@
         <v>45425.96494212963</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -68698,7 +68698,7 @@
         <v>45007</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -68755,7 +68755,7 @@
         <v>45842.38579861111</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -68817,7 +68817,7 @@
         <v>45222</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -68879,7 +68879,7 @@
         <v>45092</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -68936,7 +68936,7 @@
         <v>45009</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -68993,7 +68993,7 @@
         <v>45183.95563657407</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -69055,7 +69055,7 @@
         <v>45638</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -69112,7 +69112,7 @@
         <v>45257.92826388889</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -69169,7 +69169,7 @@
         <v>45266.95082175926</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -69231,7 +69231,7 @@
         <v>45190</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -69293,7 +69293,7 @@
         <v>45426</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -69350,7 +69350,7 @@
         <v>45009.0897337963</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -69412,7 +69412,7 @@
         <v>44918</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -69474,7 +69474,7 @@
         <v>45616.5108912037</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -69536,7 +69536,7 @@
         <v>45842.42608796297</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -69593,7 +69593,7 @@
         <v>45733.61497685185</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -69655,7 +69655,7 @@
         <v>45733.61554398148</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -69717,7 +69717,7 @@
         <v>45847.65703703704</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -69779,7 +69779,7 @@
         <v>45847.34474537037</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -69841,7 +69841,7 @@
         <v>45847.34528935186</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -69903,7 +69903,7 @@
         <v>45888.6775</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -69965,7 +69965,7 @@
         <v>44956.93924768519</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -70027,7 +70027,7 @@
         <v>45112</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -70089,7 +70089,7 @@
         <v>45695.45868055556</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -70146,7 +70146,7 @@
         <v>45614.34541666666</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -70203,7 +70203,7 @@
         <v>45847.34597222223</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -70265,7 +70265,7 @@
         <v>45323</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -70322,7 +70322,7 @@
         <v>45847.34565972222</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -70384,7 +70384,7 @@
         <v>45614.63869212963</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -70446,7 +70446,7 @@
         <v>45847.34515046296</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -70508,7 +70508,7 @@
         <v>45889.61517361111</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -70570,7 +70570,7 @@
         <v>45469.94667824074</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -70632,7 +70632,7 @@
         <v>45665.65684027778</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -70694,7 +70694,7 @@
         <v>45103</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -70751,7 +70751,7 @@
         <v>45702.63604166666</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -70813,7 +70813,7 @@
         <v>45505</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -70875,7 +70875,7 @@
         <v>45847.61513888889</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -70932,7 +70932,7 @@
         <v>45769.65659722222</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -70994,7 +70994,7 @@
         <v>45847.61548611111</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -71051,7 +71051,7 @@
         <v>45846.34454861111</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -71113,7 +71113,7 @@
         <v>45156</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -71175,7 +71175,7 @@
         <v>44231</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -71232,7 +71232,7 @@
         <v>45848.49761574074</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -71289,7 +71289,7 @@
         <v>45671.48989583334</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -71351,7 +71351,7 @@
         <v>45848.65658564815</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -71413,7 +71413,7 @@
         <v>45688.67542824074</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -71475,7 +71475,7 @@
         <v>45182</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -71537,7 +71537,7 @@
         <v>45848.49774305556</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -71594,7 +71594,7 @@
         <v>45374</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -71651,7 +71651,7 @@
         <v>45849.65663194445</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -71713,7 +71713,7 @@
         <v>45241.95724537037</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -71775,7 +71775,7 @@
         <v>44629</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -71832,7 +71832,7 @@
         <v>45044</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -71894,7 +71894,7 @@
         <v>44517.58137731482</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -71951,7 +71951,7 @@
         <v>45180</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -72013,7 +72013,7 @@
         <v>45119</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -72070,7 +72070,7 @@
         <v>45180.95927083334</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -72132,7 +72132,7 @@
         <v>44914</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -72194,7 +72194,7 @@
         <v>45769.67767361111</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -72256,7 +72256,7 @@
         <v>45224</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -72313,7 +72313,7 @@
         <v>44174</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -72375,7 +72375,7 @@
         <v>45260</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -72432,7 +72432,7 @@
         <v>45735.53177083333</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -72494,7 +72494,7 @@
         <v>44995.98341435185</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -72556,7 +72556,7 @@
         <v>44855</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -72618,7 +72618,7 @@
         <v>45093.92207175926</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -72675,7 +72675,7 @@
         <v>45280</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -72732,7 +72732,7 @@
         <v>44903</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -72789,7 +72789,7 @@
         <v>45404.99792824074</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -72871,7 +72871,7 @@
         <v>44644</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -72933,7 +72933,7 @@
         <v>45469.94876157407</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -72995,7 +72995,7 @@
         <v>45630.7862037037</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -73052,7 +73052,7 @@
         <v>44336</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -73109,7 +73109,7 @@
         <v>45558.63575231482</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -73171,7 +73171,7 @@
         <v>45679.40362268518</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -73228,7 +73228,7 @@
         <v>45357.05300925926</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -73290,7 +73290,7 @@
         <v>44929</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -73347,7 +73347,7 @@
         <v>44356</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -73404,7 +73404,7 @@
         <v>45092</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -73461,7 +73461,7 @@
         <v>45367.67256944445</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -73518,7 +73518,7 @@
         <v>45314</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -73575,7 +73575,7 @@
         <v>45723.51079861111</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -73637,7 +73637,7 @@
         <v>45534.63537037037</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -73699,7 +73699,7 @@
         <v>45425.96263888889</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -73761,7 +73761,7 @@
         <v>44813</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -73823,7 +73823,7 @@
         <v>44614</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -73880,7 +73880,7 @@
         <v>44231</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -73937,7 +73937,7 @@
         <v>45601.40686342592</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -73999,7 +73999,7 @@
         <v>45457.96372685185</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -74061,7 +74061,7 @@
         <v>45170</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -74123,7 +74123,7 @@
         <v>45645.36743055555</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -74180,7 +74180,7 @@
         <v>45204.94399305555</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -74242,7 +74242,7 @@
         <v>45327.94443287037</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -74304,7 +74304,7 @@
         <v>45257</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -74361,7 +74361,7 @@
         <v>45072.92737268518</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>

--- a/Översikt RAGUNDA.xlsx
+++ b/Översikt RAGUNDA.xlsx
@@ -567,7 +567,7 @@
         <v>45622</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>45376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>45622</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>45560.34460648148</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>45673</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44917</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45804.67787037037</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>45590.42736111111</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45838.67753472222</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44504</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44644</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>45622</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>45560.34532407407</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45104</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45113</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>45579.53179398148</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44644.93650462963</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44473</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>44813</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45367.04916666666</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>45639.55269675926</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45622</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>45790.57334490741</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>44088</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>45482.63819444444</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>45182</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45779.49012731481</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>45803.59474537037</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>44776</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>45358.99375</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45790.57349537037</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>45839.42482638889</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44805</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>44645.99859953704</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>45327</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>44888</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>45779.57335648148</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>45560.34484953704</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>45378</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45685.36501157407</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>45799.63574074074</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>45799.34461805555</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>45832.34461805555</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>45510</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>45174</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>45769.53180555555</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>44504</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>45121</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>45190.96092592592</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44133</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>45320</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>45827.5110300926</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>45120</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>45622</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>45113</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>45723.40688657408</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44133</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>44662</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>44438</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>45176</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>45810.55061342593</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45769.67740740741</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>45786.61517361111</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>45121</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44915</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>45475.94796296296</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>44336</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>45405.57392361111</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>45435.54734953704</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>44994</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>45176</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>45155</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>44111</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44209</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>45471.94783564815</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>44875</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>44911</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>45867.63619212963</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>45832.34564814815</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>44994</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>45769.67778935185</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>45468.97528935185</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>45893.38584490741</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45846.41361111111</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>45495.56244212963</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>45595.44886574074</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>45457</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>44932</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>45238</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45728.65684027778</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>44656</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>45002.94356481481</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>45446.95087962963</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>45551.46912037037</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>45195</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45425.96472222222</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>45832.34578703704</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>45182</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>45244</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>45674.67744212963</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>45471.94623842592</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>45893.38599537037</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>44911</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>45400.94002314815</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>45545.45748842593</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>45744.61550925926</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44245</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>44334.62565972222</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>44696</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>44662</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>44334</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
         <v>44334</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44911</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>45782.44871527778</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>45384</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45378</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>45455.96195601852</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>45805.34415509259</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>45610.34415509259</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>44113</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>45510</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         <v>45404</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>44677</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>45896.63618055556</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>45786.61534722222</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45491</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>45491</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>45187</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>44855</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>44369.92025462963</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>45071</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>45733</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>45779.57392361111</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>45397.95748842593</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>45751.34650462963</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>45093</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         <v>44855</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>45265</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>45516.94723379629</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>44902</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>44111</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45436.94686342592</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>45631</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>45804.34474537037</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>45491.94715277778</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>45209</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>45152</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>44971</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>45632.69822916666</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>45789.36503472222</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45847.61498842593</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>44788</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>45838</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>44875</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>45425.96285879629</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>45691.44769675926</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>44676</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44855</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16136,7 +16136,7 @@
         <v>45321</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>45779.57350694444</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>45378</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>44865</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>45551.65726851852</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>44852</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>45121</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>45190</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>45800.42782407408</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>45372.95680555556</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17049,7 +17049,7 @@
         <v>45188</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>44680</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>45171</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>45205</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         <v>45394</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>45835.344375</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>45089</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>45191</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45241</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>45583.49642361111</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         <v>45526.56393518519</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>45852.63597222222</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>45722.61543981481</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>45854.61494212963</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>45631</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44855</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>45468.97495370371</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44993</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45769.65692129629</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>45238</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>45153</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>45723.57329861111</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>44826.94976851852</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>44462</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>44166</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         <v>44319</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>44705</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44741</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>44774.94347222222</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>44741</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>44832</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19845,7 +19845,7 @@
         <v>45636.3863425926</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45468.97461805555</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>45751.34795138889</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>45771.3859837963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45301</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>45779.48993055556</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45301</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>45252</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>45149</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45033</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45455.96184027778</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>45754.51064814815</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>45266</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45341</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45457.9640625</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>45089</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>45597.34461805555</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45205</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45153</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>44991</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>45813.49061342593</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>45183</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>44860</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45827.57371527778</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>45646.34438657408</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>45785.36525462963</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45838.38627314815</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45769.65736111111</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>45775.67769675926</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>45771.36548611111</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45436.94644675926</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45847.36528935185</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>44119</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22836,7 +22836,7 @@
         <v>45153</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45154</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>45147</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45468</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45722.65670138889</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>45487.92863425926</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -23374,7 +23374,7 @@
         <v>45897.531875</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>45510</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>45491.95008101852</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>44369</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23729,7 +23729,7 @@
         <v>45206</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>45315</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>45600.55265046296</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45044</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45208</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>44157</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44141</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>44195</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>44214</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>44846</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44168</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44517</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44817</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>44880.95712962963</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44880.95719907407</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>44855.94125</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>44425</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>44447.92069444444</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>44490.94109953703</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>44519.94534722222</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>44349</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>44210</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>44243</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>44280</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>44280</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44385.33887731482</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44292</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>44705</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>44518.94394675926</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>44846.9522337963</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         <v>44362</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>44426.94077546296</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>44399</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>44818.94929398148</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44860</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44111</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>44774.94414351852</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>44425</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>44663</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>44823.48666666666</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>44874.95553240741</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -26306,7 +26306,7 @@
         <v>44784.9408912037</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -26368,7 +26368,7 @@
         <v>44714</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -26425,7 +26425,7 @@
         <v>44670</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>44837</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>44704.94234953704</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>44858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>44855</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>44078</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>44175</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>44194</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>44239</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26968,7 +26968,7 @@
         <v>44443</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>44273.92081018518</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>44741</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>44132</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>44495.93966435185</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44126</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44854</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44859.95710648148</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>44530</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>44823.94993055556</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44125.94493055555</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>44836.9491087963</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>44833.95405092592</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>44579.68604166667</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>44084</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>44883</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>44728.94398148148</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>44287</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>44308</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>44308</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>44259</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -28215,7 +28215,7 @@
         <v>44452</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>44629.56258101852</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>44281</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>44421.97322916667</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>44351</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>44832.95435185185</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>44586</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>44434.94559027778</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>44690</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44867</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>44876.95104166667</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>44111</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44500.93887731482</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>44476</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>44601</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>44714.94162037037</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -29182,7 +29182,7 @@
         <v>44477.48994212963</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>44357</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>44515.93767361111</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>44228</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>44783</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>44696.93986111111</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>44802</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -29601,7 +29601,7 @@
         <v>44864.94835648148</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>44308</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>44853.9499537037</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44482.92271990741</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>44512</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         <v>44662</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44824.94635416667</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>44704</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>44685</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>44615</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -30191,7 +30191,7 @@
         <v>44349.92013888889</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>44349.91995370371</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>44308</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -30362,7 +30362,7 @@
         <v>44851.95488425926</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>44379</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>44075</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>44671</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -30600,7 +30600,7 @@
         <v>44434.94517361111</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>44729.94136574074</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>44704.94229166667</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>44861</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -30843,7 +30843,7 @@
         <v>44777.95504629629</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>44855.9471875</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>44818</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>44833.9519212963</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>44138</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>44418.9369212963</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -31210,7 +31210,7 @@
         <v>44788</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>44853</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>44140</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -31391,7 +31391,7 @@
         <v>44099</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>44799.94394675926</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
         <v>44431</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>44574</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>44621</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>44463.94077546296</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44883.94918981481</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>44124</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>44074</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>44074</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>44650</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>44815</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>44578.92284722222</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>44489.94711805556</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -32229,7 +32229,7 @@
         <v>44615</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -32286,7 +32286,7 @@
         <v>44823</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>44140</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
         <v>44599.98685185185</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>44727</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>44858</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44494.93930555556</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>44425</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -32715,7 +32715,7 @@
         <v>44846</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -32777,7 +32777,7 @@
         <v>44781</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -32834,7 +32834,7 @@
         <v>44322</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -32891,7 +32891,7 @@
         <v>44361.55445601852</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32948,7 +32948,7 @@
         <v>44854.95390046296</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>44704.9422337963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>44831.94846064815</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>44831.9485300926</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -33196,7 +33196,7 @@
         <v>44784.94157407407</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>44495</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>44728.94392361111</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>44889</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>44595</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -33501,7 +33501,7 @@
         <v>44402.42243055555</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -33558,7 +33558,7 @@
         <v>44356.91935185185</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>44832.95300925926</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
         <v>44830</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -33739,7 +33739,7 @@
         <v>44356</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -33796,7 +33796,7 @@
         <v>44496</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -33853,7 +33853,7 @@
         <v>44734.94193287037</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -33915,7 +33915,7 @@
         <v>44776</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>44704.94217592593</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>44802.94811342593</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>44805</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -34163,7 +34163,7 @@
         <v>44315</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44861</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>45384</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>45086.94010416666</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>45726.3860300926</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -34463,7 +34463,7 @@
         <v>45119</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>45182</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -34582,7 +34582,7 @@
         <v>45379.93637731481</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>45401</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>45401</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>45007</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45042</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>45374</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>45723.67777777778</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44336</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -35058,7 +35058,7 @@
         <v>45743.36</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -35120,7 +35120,7 @@
         <v>45356.03784722222</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>45358.95813657407</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>45645.36743055555</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>44953</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>44977.98660879629</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>44323</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>45769.67767361111</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>45253</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>45267</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -35663,7 +35663,7 @@
         <v>45098</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>45208</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -35777,7 +35777,7 @@
         <v>45769.51087962963</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -35839,7 +35839,7 @@
         <v>44813</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45075.945</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>44832</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -36025,7 +36025,7 @@
         <v>45280.92645833334</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>44812.94709490741</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>45695.44724537037</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>44805.94592592592</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>45741.63675925926</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>45645.36740740741</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -36382,7 +36382,7 @@
         <v>45636.3864699074</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>45358.95818287037</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>45441.33313657407</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>45702.63572916666</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>45392</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>45392.92903935185</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>44972.94140046297</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>45391.95329861111</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>45776.40311342593</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>45776.59422453704</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45574.57967592592</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45776.50651620371</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -37096,7 +37096,7 @@
         <v>45776.51130787037</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -37158,7 +37158,7 @@
         <v>45063</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -37215,7 +37215,7 @@
         <v>45426</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>45344</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45782.36506944444</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>45782.51099537037</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>45769.65659722222</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -37515,7 +37515,7 @@
         <v>45769.67790509259</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>45782.49032407408</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
         <v>45782.49046296296</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>45254.96516203704</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -37763,7 +37763,7 @@
         <v>45782.51109953703</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>44903</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45782.67758101852</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>45782.55287037037</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>45779.34417824074</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -38068,7 +38068,7 @@
         <v>45779.4281712963</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>45782.36494212963</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>45779.49025462963</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>44914</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>44900.95700231481</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -38378,7 +38378,7 @@
         <v>45448.94520833333</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>45761.67744212963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>45093.92207175926</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>45386.68003472222</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>44894</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>45223</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>45187</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>45448.94600694445</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>45751.34859953704</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>44879.95768518518</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45393.94459490741</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>45367.67256944445</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>44993.94950231481</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -39154,7 +39154,7 @@
         <v>44993</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>45259</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -39273,7 +39273,7 @@
         <v>45572.60363425926</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -39330,7 +39330,7 @@
         <v>45631.46665509259</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>44866</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>44958.94298611111</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -39511,7 +39511,7 @@
         <v>45786.51077546296</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>45257</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>45609.34412037037</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -39692,7 +39692,7 @@
         <v>44944</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>44922</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>45559.67745370371</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>44517.58137731482</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>44995.98341435185</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -39987,7 +39987,7 @@
         <v>44995.98644675926</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -40049,7 +40049,7 @@
         <v>45516.94732638889</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>45314</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>45154.95525462963</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>45393.94431712963</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -40292,7 +40292,7 @@
         <v>45040.94277777777</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>45453.95016203704</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45790.40670138889</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>45446.68947916666</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -40535,7 +40535,7 @@
         <v>45456.96569444444</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -40597,7 +40597,7 @@
         <v>45006</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>44475</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>45158.94231481481</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -40778,7 +40778,7 @@
         <v>45611.65679398148</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>45306</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>45279.94572916667</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -40959,7 +40959,7 @@
         <v>44336</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -41016,7 +41016,7 @@
         <v>45574.51185185185</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -41078,7 +41078,7 @@
         <v>45049</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>45792.34527777778</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>45309.92524305556</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>45611.5953125</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>45792.71905092592</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>45608.6078587963</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -41440,7 +41440,7 @@
         <v>45792.49023148148</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>45792.63584490741</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>45792.34606481482</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -41626,7 +41626,7 @@
         <v>45638.34431712963</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>45656</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>45327.94459490741</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>45315.9492824074</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>45204.94399305555</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>45574.51087962963</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>45574.51090277778</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45211.95134259259</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -42117,7 +42117,7 @@
         <v>45454.95960648148</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -42179,7 +42179,7 @@
         <v>45384</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -42236,7 +42236,7 @@
         <v>45791.53238425926</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -42293,7 +42293,7 @@
         <v>45139.94681712963</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -42355,7 +42355,7 @@
         <v>45453.95538194444</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>45629.36513888889</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>45545.64957175926</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>45714.60649305556</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>45412.02506944445</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -42650,7 +42650,7 @@
         <v>45762.39876157408</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -42727,7 +42727,7 @@
         <v>45243</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -42789,7 +42789,7 @@
         <v>45275.95060185185</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -42851,7 +42851,7 @@
         <v>45469.94876157407</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>45635.47243055556</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -42970,7 +42970,7 @@
         <v>45769.51075231482</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45611</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45793</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45694.69826388889</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45796</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45796</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>45516.94934027778</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45436.94636574074</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45796</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45793.61523148148</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>45216.92424768519</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45796</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45441</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>44979</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>44980.93865740741</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>44519.94440972222</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45266</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>45545.49078703704</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>45511</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>45009.0897337963</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>45191</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -44222,7 +44222,7 @@
         <v>45797.63627314815</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -44284,7 +44284,7 @@
         <v>45800.63619212963</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>44628</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>45426</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>45426</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45033</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>45799.34421296296</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45614.34541666666</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45635.57331018519</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45182</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>44656</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45372.95762731481</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>45800</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45800.42743055556</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>44897</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -45122,7 +45122,7 @@
         <v>45800.44822916666</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>45800.44862268519</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>44911.93846064815</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>45341.95381944445</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -45370,7 +45370,7 @@
         <v>45803.5946875</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>45439.92752314815</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -45484,7 +45484,7 @@
         <v>45803.61552083334</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>45803.61557870371</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -45598,7 +45598,7 @@
         <v>45804.59487268519</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>45804.42642361111</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45639.55240740741</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45488.94747685185</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45729.51074074074</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45638</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -45960,7 +45960,7 @@
         <v>45540.38564814815</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>45425.96239583333</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -46084,7 +46084,7 @@
         <v>45590.40675925926</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -46146,7 +46146,7 @@
         <v>45803.59417824074</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -46203,7 +46203,7 @@
         <v>45726.38575231482</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -46260,7 +46260,7 @@
         <v>45737.63574074074</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>45050.94020833333</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -46384,7 +46384,7 @@
         <v>45804.65672453704</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>45805.61495370371</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -46508,7 +46508,7 @@
         <v>44917</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>44993.94958333333</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -46632,7 +46632,7 @@
         <v>45797.40800925926</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -46689,7 +46689,7 @@
         <v>45805.46613425926</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -46746,7 +46746,7 @@
         <v>45211.95061342593</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>44130.9416550926</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -46870,7 +46870,7 @@
         <v>45722.48982638889</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45323</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -46984,7 +46984,7 @@
         <v>45805.57390046296</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -47046,7 +47046,7 @@
         <v>45190</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45672.44898148148</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         <v>44900</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -47232,7 +47232,7 @@
         <v>45566.68125</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -47289,7 +47289,7 @@
         <v>45404.99792824074</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>44587.92149305555</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -47428,7 +47428,7 @@
         <v>44943.94802083333</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>44903</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>44743</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>45603.67850694444</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>45653.44836805556</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -47728,7 +47728,7 @@
         <v>45601.5315625</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>44550.92168981482</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45638.63600694444</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>45616.5108912037</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>44644</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -48033,7 +48033,7 @@
         <v>44113</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -48095,7 +48095,7 @@
         <v>45420</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -48157,7 +48157,7 @@
         <v>45646.63605324074</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>45344</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -48276,7 +48276,7 @@
         <v>45063</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -48333,7 +48333,7 @@
         <v>45645.55665509259</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -48390,7 +48390,7 @@
         <v>45604.4190625</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -48447,7 +48447,7 @@
         <v>45810.36495370371</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -48509,7 +48509,7 @@
         <v>45692.51069444444</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -48571,7 +48571,7 @@
         <v>45692.57326388889</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -48633,7 +48633,7 @@
         <v>45230.96376157407</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -48695,7 +48695,7 @@
         <v>45428.00471064815</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -48757,7 +48757,7 @@
         <v>45574.39081018518</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -48819,7 +48819,7 @@
         <v>45734.4633912037</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -48876,7 +48876,7 @@
         <v>44587.92144675926</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>45351.98532407408</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -48995,7 +48995,7 @@
         <v>45342</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -49057,7 +49057,7 @@
         <v>45342.9462037037</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -49119,7 +49119,7 @@
         <v>45552.44096064815</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -49176,7 +49176,7 @@
         <v>45579.47052083333</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -49233,7 +49233,7 @@
         <v>45616.34479166667</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -49295,7 +49295,7 @@
         <v>45180</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -49357,7 +49357,7 @@
         <v>45180.95927083334</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -49419,7 +49419,7 @@
         <v>45656.64223379629</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -49476,7 +49476,7 @@
         <v>44991</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>44614</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -49595,7 +49595,7 @@
         <v>45716</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -49657,7 +49657,7 @@
         <v>45716.61487268518</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45056</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45056</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         <v>44153</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -49890,7 +49890,7 @@
         <v>45028</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>44601</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>45769.67802083334</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -50066,7 +50066,7 @@
         <v>45453.42041666667</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -50123,7 +50123,7 @@
         <v>45615.47091435185</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -50180,7 +50180,7 @@
         <v>45813.42790509259</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -50242,7 +50242,7 @@
         <v>45667.57342592593</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -50304,7 +50304,7 @@
         <v>45667.57347222222</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -50366,7 +50366,7 @@
         <v>44655</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -50428,7 +50428,7 @@
         <v>45197.94171296297</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -50490,7 +50490,7 @@
         <v>45764</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -50547,7 +50547,7 @@
         <v>45195</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -50609,7 +50609,7 @@
         <v>45195.94679398148</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -50671,7 +50671,7 @@
         <v>45195.94685185186</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -50733,7 +50733,7 @@
         <v>44614</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -50790,7 +50790,7 @@
         <v>45692.49008101852</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -50852,7 +50852,7 @@
         <v>44886</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -50914,7 +50914,7 @@
         <v>45860.30229166667</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -50971,7 +50971,7 @@
         <v>45554.61583333334</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -51028,7 +51028,7 @@
         <v>45818.46898148148</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -51085,7 +51085,7 @@
         <v>45187</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -51142,7 +51142,7 @@
         <v>45859.594375</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -51204,7 +51204,7 @@
         <v>45678.67761574074</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -51266,7 +51266,7 @@
         <v>45442.96296296296</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -51328,7 +51328,7 @@
         <v>45819.6359375</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -51390,7 +51390,7 @@
         <v>45208</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -51447,7 +51447,7 @@
         <v>45098</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -51504,7 +51504,7 @@
         <v>45555.38509259259</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -51561,7 +51561,7 @@
         <v>45148</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -51618,7 +51618,7 @@
         <v>44684.94032407407</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -51680,7 +51680,7 @@
         <v>45138.94925925926</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -51742,7 +51742,7 @@
         <v>45636.38599537037</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45821.34513888889</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -51866,7 +51866,7 @@
         <v>45258</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>45195.94672453704</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -51985,7 +51985,7 @@
         <v>44901</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>44901</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -52109,7 +52109,7 @@
         <v>45825.57675925926</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -52166,7 +52166,7 @@
         <v>45825.58252314815</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45112.94303240741</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -52285,7 +52285,7 @@
         <v>45112.94310185185</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -52347,7 +52347,7 @@
         <v>45595.42738425926</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>45730.53208333333</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -52471,7 +52471,7 @@
         <v>45622.47435185185</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45429</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45505</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -52647,7 +52647,7 @@
         <v>45825.56762731481</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>45621.57395833333</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45826.65759259259</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45870.34439814815</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -52890,7 +52890,7 @@
         <v>45505</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45574.61184027778</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45574.62297453704</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>45574.63355324074</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45827.53178240741</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -53185,7 +53185,7 @@
         <v>45827.63582175926</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -53247,7 +53247,7 @@
         <v>45869.65666666667</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -53309,7 +53309,7 @@
         <v>45869.67744212963</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45874.69844907407</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>45581.55260416667</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>44614</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>44977.98670138889</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -53609,7 +53609,7 @@
         <v>44656.94708333333</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -53671,7 +53671,7 @@
         <v>45392</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -53728,7 +53728,7 @@
         <v>45238</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -53790,7 +53790,7 @@
         <v>45230</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -53852,7 +53852,7 @@
         <v>45832.34552083333</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>45698.59409722222</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -53976,7 +53976,7 @@
         <v>45180.95907407408</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -54038,7 +54038,7 @@
         <v>45558.63575231482</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -54100,7 +54100,7 @@
         <v>44657</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -54157,7 +54157,7 @@
         <v>45874.67746527777</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         <v>45832.34524305556</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         <v>45832.3459375</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45590</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -54395,7 +54395,7 @@
         <v>44641</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -54457,7 +54457,7 @@
         <v>44641</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -54519,7 +54519,7 @@
         <v>45874.59496527778</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -54581,7 +54581,7 @@
         <v>45839</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -54638,7 +54638,7 @@
         <v>45253</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -54695,7 +54695,7 @@
         <v>45876.53188657408</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -54757,7 +54757,7 @@
         <v>45702.63604166666</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -54819,7 +54819,7 @@
         <v>44685</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -54881,7 +54881,7 @@
         <v>45622</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -54938,7 +54938,7 @@
         <v>44942</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -55000,7 +55000,7 @@
         <v>44994.94296296296</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -55062,7 +55062,7 @@
         <v>45257</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -55124,7 +55124,7 @@
         <v>45614.34545138889</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -55181,7 +55181,7 @@
         <v>45772.6565625</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -55243,7 +55243,7 @@
         <v>45834.65662037037</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -55305,7 +55305,7 @@
         <v>45601.40686342592</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -55367,7 +55367,7 @@
         <v>45145.95326388889</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -55429,7 +55429,7 @@
         <v>44774</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -55486,7 +55486,7 @@
         <v>45215.94657407407</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -55548,7 +55548,7 @@
         <v>45751.36490740741</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -55610,7 +55610,7 @@
         <v>44671</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -55667,7 +55667,7 @@
         <v>45344.92865740741</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -55724,7 +55724,7 @@
         <v>45344.92873842592</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -55781,7 +55781,7 @@
         <v>44820</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -55843,7 +55843,7 @@
         <v>45309</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -55900,7 +55900,7 @@
         <v>45309</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -55957,7 +55957,7 @@
         <v>44231</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -56014,7 +56014,7 @@
         <v>44839</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -56071,7 +56071,7 @@
         <v>45456.96601851852</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -56133,7 +56133,7 @@
         <v>45688.68196759259</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -56195,7 +56195,7 @@
         <v>45835.4506712963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -56252,7 +56252,7 @@
         <v>45838</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>45149.95241898148</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -56371,7 +56371,7 @@
         <v>45730.56346064815</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -56433,7 +56433,7 @@
         <v>45835.72046296296</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -56490,7 +56490,7 @@
         <v>45722.44849537037</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -56552,7 +56552,7 @@
         <v>45838</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -56609,7 +56609,7 @@
         <v>45838.67887731481</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -56671,7 +56671,7 @@
         <v>45075.94506944445</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -56733,7 +56733,7 @@
         <v>45838.48996527777</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45224</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -56847,7 +56847,7 @@
         <v>45233.92591435185</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -56904,7 +56904,7 @@
         <v>44956.93924768519</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -56966,7 +56966,7 @@
         <v>45314</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -57023,7 +57023,7 @@
         <v>45835.40668981482</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -57085,7 +57085,7 @@
         <v>45629.36486111111</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -57142,7 +57142,7 @@
         <v>44803.94351851852</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -57204,7 +57204,7 @@
         <v>45838.67800925926</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -57261,7 +57261,7 @@
         <v>45835.53166666667</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -57323,7 +57323,7 @@
         <v>45835.46334490741</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -57380,7 +57380,7 @@
         <v>45758.36487268518</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -57442,7 +57442,7 @@
         <v>44958</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -57499,7 +57499,7 @@
         <v>45367.04693287037</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -57561,7 +57561,7 @@
         <v>45835.45686342593</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -57618,7 +57618,7 @@
         <v>45712.61552083334</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>45839.42822916667</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -57742,7 +57742,7 @@
         <v>45839.46915509259</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45603.44644675926</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -57866,7 +57866,7 @@
         <v>45775.67747685185</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>45622.44774305556</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -57985,7 +57985,7 @@
         <v>44672.94018518519</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -58047,7 +58047,7 @@
         <v>45838.36532407408</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -58109,7 +58109,7 @@
         <v>45009.089375</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -58171,7 +58171,7 @@
         <v>45839.49082175926</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -58228,7 +58228,7 @@
         <v>45244.96774305555</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -58290,7 +58290,7 @@
         <v>45618.46921296296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -58352,7 +58352,7 @@
         <v>45839.42810185185</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -58414,7 +58414,7 @@
         <v>45734.45268518518</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -58471,7 +58471,7 @@
         <v>45241.95741898148</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -58533,7 +58533,7 @@
         <v>45241</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -58595,7 +58595,7 @@
         <v>45254.96402777778</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -58657,7 +58657,7 @@
         <v>45839.42864583333</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -58719,7 +58719,7 @@
         <v>45839.57331018519</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -58781,7 +58781,7 @@
         <v>45840.52225694444</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -58838,7 +58838,7 @@
         <v>44746</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -58895,7 +58895,7 @@
         <v>44806</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -58952,7 +58952,7 @@
         <v>45771.36538194444</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -59014,7 +59014,7 @@
         <v>45266.95082175926</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -59076,7 +59076,7 @@
         <v>45327.94443287037</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -59138,7 +59138,7 @@
         <v>45344.92822916667</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -59195,7 +59195,7 @@
         <v>45842.38579861111</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -59257,7 +59257,7 @@
         <v>45044</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -59319,7 +59319,7 @@
         <v>45351.98496527778</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -59381,7 +59381,7 @@
         <v>45741.63659722222</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -59443,7 +59443,7 @@
         <v>45841.57427083333</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -59505,7 +59505,7 @@
         <v>45671.48989583334</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>45128</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -59629,7 +59629,7 @@
         <v>45842.42608796297</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -59686,7 +59686,7 @@
         <v>44984</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -59743,7 +59743,7 @@
         <v>44571</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -59800,7 +59800,7 @@
         <v>45841.6571412037</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -59857,7 +59857,7 @@
         <v>45222</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -59919,7 +59919,7 @@
         <v>45257.92826388889</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -59976,7 +59976,7 @@
         <v>45306</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -60033,7 +60033,7 @@
         <v>45888.6775</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -60095,7 +60095,7 @@
         <v>44977.44373842593</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -60152,7 +60152,7 @@
         <v>45170</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -60214,7 +60214,7 @@
         <v>45846.34454861111</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -60276,7 +60276,7 @@
         <v>45474.50608796296</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -60333,7 +60333,7 @@
         <v>45608.52354166667</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         <v>45482.94815972223</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -60457,7 +60457,7 @@
         <v>44929</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -60514,7 +60514,7 @@
         <v>45469.94667824074</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -60576,7 +60576,7 @@
         <v>45238</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -60633,7 +60633,7 @@
         <v>45511</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -60695,7 +60695,7 @@
         <v>45436.94613425926</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -60757,7 +60757,7 @@
         <v>45847.34474537037</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -60819,7 +60819,7 @@
         <v>45847.34528935186</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -60881,7 +60881,7 @@
         <v>45769.65688657408</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -60943,7 +60943,7 @@
         <v>45847.34597222223</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -61005,7 +61005,7 @@
         <v>45847.61513888889</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -61062,7 +61062,7 @@
         <v>45847.65703703704</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -61124,7 +61124,7 @@
         <v>45848.65658564815</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -61186,7 +61186,7 @@
         <v>45847.34565972222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -61248,7 +61248,7 @@
         <v>44286</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -61305,7 +61305,7 @@
         <v>45210</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -61362,7 +61362,7 @@
         <v>45847.61548611111</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -61419,7 +61419,7 @@
         <v>45664.55241898148</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -61481,7 +61481,7 @@
         <v>45000</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -61538,7 +61538,7 @@
         <v>45530</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -61595,7 +61595,7 @@
         <v>45889.61517361111</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -61657,7 +61657,7 @@
         <v>45847.34515046296</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -61719,7 +61719,7 @@
         <v>45848.49774305556</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -61776,7 +61776,7 @@
         <v>45260</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -61833,7 +61833,7 @@
         <v>45892.34438657408</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -61890,7 +61890,7 @@
         <v>45892.38641203703</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -61947,7 +61947,7 @@
         <v>45892.34423611111</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -62004,7 +62004,7 @@
         <v>45892.38591435185</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -62061,7 +62061,7 @@
         <v>45892.38657407407</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -62118,7 +62118,7 @@
         <v>45681.60203703704</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -62175,7 +62175,7 @@
         <v>45848.49761574074</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -62232,7 +62232,7 @@
         <v>45679.40362268518</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -62289,7 +62289,7 @@
         <v>45852.53185185185</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -62351,7 +62351,7 @@
         <v>45892.44840277778</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -62408,7 +62408,7 @@
         <v>45850.34434027778</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -62465,7 +62465,7 @@
         <v>45103</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -62522,7 +62522,7 @@
         <v>45667.55239583334</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -62584,7 +62584,7 @@
         <v>44649.47048611111</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -62646,7 +62646,7 @@
         <v>45849.65663194445</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -62708,7 +62708,7 @@
         <v>45892.38619212963</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -62765,7 +62765,7 @@
         <v>45069</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -62822,7 +62822,7 @@
         <v>45892.44824074074</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -62879,7 +62879,7 @@
         <v>45850.34450231482</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -62941,7 +62941,7 @@
         <v>45852.53168981482</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -63003,7 +63003,7 @@
         <v>44424</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -63060,7 +63060,7 @@
         <v>45149</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -63117,7 +63117,7 @@
         <v>45324</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -63174,7 +63174,7 @@
         <v>45604.63575231482</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -63236,7 +63236,7 @@
         <v>45183.95563657407</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -63298,7 +63298,7 @@
         <v>44894.79018518519</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -63355,7 +63355,7 @@
         <v>45854.65663194445</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -63417,7 +63417,7 @@
         <v>44963</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -63479,7 +63479,7 @@
         <v>45896.52478009259</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -63536,7 +63536,7 @@
         <v>45601.55331018518</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -63598,7 +63598,7 @@
         <v>45487.92856481481</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -63655,7 +63655,7 @@
         <v>44914</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -63712,7 +63712,7 @@
         <v>45898.53193287037</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -63774,7 +63774,7 @@
         <v>45898.61502314815</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -63836,7 +63836,7 @@
         <v>45855.67899305555</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -63893,7 +63893,7 @@
         <v>45184</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -63950,7 +63950,7 @@
         <v>45856.46931712963</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -64012,7 +64012,7 @@
         <v>45855.61523148148</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -64074,7 +64074,7 @@
         <v>45898.49012731481</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -64136,7 +64136,7 @@
         <v>45000</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -64198,7 +64198,7 @@
         <v>45000</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -64260,7 +64260,7 @@
         <v>45446.57052083333</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -64317,7 +64317,7 @@
         <v>45053.94313657407</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -64379,7 +64379,7 @@
         <v>45898.59295138889</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -64436,7 +64436,7 @@
         <v>44880</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -64498,7 +64498,7 @@
         <v>45714</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -64555,7 +64555,7 @@
         <v>45425.96494212963</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -64617,7 +64617,7 @@
         <v>45534</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -64674,7 +64674,7 @@
         <v>45510</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -64736,7 +64736,7 @@
         <v>45692.48993055556</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -64798,7 +64798,7 @@
         <v>44855</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -64860,7 +64860,7 @@
         <v>44349.91978009259</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -64917,7 +64917,7 @@
         <v>45733.61497685185</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -64979,7 +64979,7 @@
         <v>45625.51068287037</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -65041,7 +65041,7 @@
         <v>45695.45868055556</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -65098,7 +65098,7 @@
         <v>44991</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -65160,7 +65160,7 @@
         <v>45476.94533564815</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -65222,7 +65222,7 @@
         <v>44384</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -65279,7 +65279,7 @@
         <v>44635</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -65341,7 +65341,7 @@
         <v>45040</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -65398,7 +65398,7 @@
         <v>44844.95368055555</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -65460,7 +65460,7 @@
         <v>44530.94694444445</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -65522,7 +65522,7 @@
         <v>44957.94075231482</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -65584,7 +65584,7 @@
         <v>44362</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -65641,7 +65641,7 @@
         <v>45482.94891203703</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -65703,7 +65703,7 @@
         <v>45482.9491087963</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -65765,7 +65765,7 @@
         <v>45552.39113425926</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -65822,7 +65822,7 @@
         <v>45008.01408564814</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -65884,7 +65884,7 @@
         <v>45176</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -65941,7 +65941,7 @@
         <v>44305.92047453704</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -65998,7 +65998,7 @@
         <v>45681.6050925926</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -66055,7 +66055,7 @@
         <v>45726.38615740741</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -66112,7 +66112,7 @@
         <v>45726.3862037037</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -66169,7 +66169,7 @@
         <v>45706.34450231482</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -66231,7 +66231,7 @@
         <v>45715.59405092592</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -66293,7 +66293,7 @@
         <v>45092</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -66350,7 +66350,7 @@
         <v>44966.95328703704</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -66412,7 +66412,7 @@
         <v>44889</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -66469,7 +66469,7 @@
         <v>44231</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -66526,7 +66526,7 @@
         <v>45735.53177083333</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -66588,7 +66588,7 @@
         <v>45735.5517824074</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -66645,7 +66645,7 @@
         <v>45730.42738425926</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -66707,7 +66707,7 @@
         <v>45733.61554398148</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -66769,7 +66769,7 @@
         <v>45197.94152777778</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -66831,7 +66831,7 @@
         <v>45700.57324074074</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -66893,7 +66893,7 @@
         <v>45112</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -66955,7 +66955,7 @@
         <v>45367.69850694444</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -67012,7 +67012,7 @@
         <v>45367.71348379629</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -67069,7 +67069,7 @@
         <v>45034</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -67126,7 +67126,7 @@
         <v>45491</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -67188,7 +67188,7 @@
         <v>45112</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -67250,7 +67250,7 @@
         <v>44629</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -67307,7 +67307,7 @@
         <v>45053.94305555556</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -67369,7 +67369,7 @@
         <v>45306</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -67426,7 +67426,7 @@
         <v>44889.95015046297</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -67488,7 +67488,7 @@
         <v>44680</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -67545,7 +67545,7 @@
         <v>45119</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -67602,7 +67602,7 @@
         <v>45289</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -67659,7 +67659,7 @@
         <v>45260.92561342593</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -67716,7 +67716,7 @@
         <v>45068</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -67778,7 +67778,7 @@
         <v>44939</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -67840,7 +67840,7 @@
         <v>45735.69842592593</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -67902,7 +67902,7 @@
         <v>45314.92758101852</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -67959,7 +67959,7 @@
         <v>45596.61533564814</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -68021,7 +68021,7 @@
         <v>45735</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -68083,7 +68083,7 @@
         <v>45540.38586805556</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -68145,7 +68145,7 @@
         <v>44074</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -68207,7 +68207,7 @@
         <v>44236</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -68264,7 +68264,7 @@
         <v>45280</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -68321,7 +68321,7 @@
         <v>44825</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -68383,7 +68383,7 @@
         <v>44299</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -68440,7 +68440,7 @@
         <v>44917</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -68497,7 +68497,7 @@
         <v>44410</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -68554,7 +68554,7 @@
         <v>44670</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -68611,7 +68611,7 @@
         <v>44915</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -68673,7 +68673,7 @@
         <v>45078</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -68730,7 +68730,7 @@
         <v>45386</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -68787,7 +68787,7 @@
         <v>44405.92065972222</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -68844,7 +68844,7 @@
         <v>45688.67542824074</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -68906,7 +68906,7 @@
         <v>45659.69822916666</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -68968,7 +68968,7 @@
         <v>45054</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -69030,7 +69030,7 @@
         <v>45238.96797453704</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -69092,7 +69092,7 @@
         <v>45604.40540509259</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -69149,7 +69149,7 @@
         <v>45604.41625</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -69206,7 +69206,7 @@
         <v>45568.51075231482</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -69268,7 +69268,7 @@
         <v>45546</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -69325,7 +69325,7 @@
         <v>45086</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -69387,7 +69387,7 @@
         <v>45251</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -69444,7 +69444,7 @@
         <v>45145</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -69506,7 +69506,7 @@
         <v>45467.96207175926</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -69568,7 +69568,7 @@
         <v>45695.51070601852</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -69630,7 +69630,7 @@
         <v>45279.94564814815</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -69692,7 +69692,7 @@
         <v>45091</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -69754,7 +69754,7 @@
         <v>44869</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -69811,7 +69811,7 @@
         <v>45638</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -69868,7 +69868,7 @@
         <v>45645.55672453704</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -69925,7 +69925,7 @@
         <v>44869</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -69982,7 +69982,7 @@
         <v>45096.93866898148</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -70044,7 +70044,7 @@
         <v>44173</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -70101,7 +70101,7 @@
         <v>45751.34873842593</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -70163,7 +70163,7 @@
         <v>44888</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -70225,7 +70225,7 @@
         <v>44174</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -70287,7 +70287,7 @@
         <v>45771.51074074074</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -70349,7 +70349,7 @@
         <v>45341</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -70406,7 +70406,7 @@
         <v>45495.57677083334</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -70463,7 +70463,7 @@
         <v>45002.0328125</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -70525,7 +70525,7 @@
         <v>45712.65671296296</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -70582,7 +70582,7 @@
         <v>45754</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -70644,7 +70644,7 @@
         <v>45156</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -70706,7 +70706,7 @@
         <v>45241.95724537037</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -70768,7 +70768,7 @@
         <v>45425.96230324074</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -70830,7 +70830,7 @@
         <v>45561.34663194444</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -70892,7 +70892,7 @@
         <v>45111.92793981481</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -70954,7 +70954,7 @@
         <v>45357.05300925926</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -71016,7 +71016,7 @@
         <v>45425.96275462963</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -71078,7 +71078,7 @@
         <v>45453.4444212963</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -71135,7 +71135,7 @@
         <v>44929</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -71192,7 +71192,7 @@
         <v>44375</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -71249,7 +71249,7 @@
         <v>45322</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -71306,7 +71306,7 @@
         <v>44918</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -71368,7 +71368,7 @@
         <v>45622.46200231482</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -71425,7 +71425,7 @@
         <v>45000</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -71487,7 +71487,7 @@
         <v>45681.5315625</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -71549,7 +71549,7 @@
         <v>45673.66358796296</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -71606,7 +71606,7 @@
         <v>44680.95246527778</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -71668,7 +71668,7 @@
         <v>45601.59518518519</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -71730,7 +71730,7 @@
         <v>44879</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -71792,7 +71792,7 @@
         <v>45009</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -71849,7 +71849,7 @@
         <v>45436.94628472222</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -71911,7 +71911,7 @@
         <v>45425.96263888889</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -71973,7 +71973,7 @@
         <v>45615.50034722222</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -72030,7 +72030,7 @@
         <v>45048.94340277778</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -72092,7 +72092,7 @@
         <v>44929.92489583333</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -72149,7 +72149,7 @@
         <v>45596.61553240741</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -72211,7 +72211,7 @@
         <v>45435</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -72268,7 +72268,7 @@
         <v>45559.67759259259</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -72330,7 +72330,7 @@
         <v>45636.57329861111</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -72392,7 +72392,7 @@
         <v>44593</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -72449,7 +72449,7 @@
         <v>45166</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -72506,7 +72506,7 @@
         <v>45723.51079861111</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -72568,7 +72568,7 @@
         <v>45747.67739583334</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -72630,7 +72630,7 @@
         <v>45629.42759259259</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -72692,7 +72692,7 @@
         <v>45107</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -72749,7 +72749,7 @@
         <v>44518</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -72806,7 +72806,7 @@
         <v>45071</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -72863,7 +72863,7 @@
         <v>45133</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -72925,7 +72925,7 @@
         <v>45712.61502314815</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -72987,7 +72987,7 @@
         <v>45712.61510416667</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -73049,7 +73049,7 @@
         <v>45630.7862037037</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -73106,7 +73106,7 @@
         <v>45329.95806712963</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -73168,7 +73168,7 @@
         <v>45331.92746527777</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -73225,7 +73225,7 @@
         <v>45103</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -73282,7 +73282,7 @@
         <v>45072.92737268518</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -73339,7 +73339,7 @@
         <v>45065.42894675926</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -73396,7 +73396,7 @@
         <v>45622.46910879629</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -73453,7 +73453,7 @@
         <v>45457.96372685185</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -73515,7 +73515,7 @@
         <v>44932.93927083333</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -73577,7 +73577,7 @@
         <v>45540.34428240741</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -73639,7 +73639,7 @@
         <v>45714.55064814815</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -73696,7 +73696,7 @@
         <v>45175</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -73758,7 +73758,7 @@
         <v>45534.63537037037</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -73820,7 +73820,7 @@
         <v>45149.95372685185</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -73882,7 +73882,7 @@
         <v>44904.94824074074</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -73944,7 +73944,7 @@
         <v>45665.65684027778</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -74006,7 +74006,7 @@
         <v>44971</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -74068,7 +74068,7 @@
         <v>45614.63869212963</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -74130,7 +74130,7 @@
         <v>44880.95741898148</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -74192,7 +74192,7 @@
         <v>45715.61523148148</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -74254,7 +74254,7 @@
         <v>44876</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -74316,7 +74316,7 @@
         <v>45215</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -74373,7 +74373,7 @@
         <v>45105</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -74435,7 +74435,7 @@
         <v>45756.63601851852</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -74497,7 +74497,7 @@
         <v>45429</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -74554,7 +74554,7 @@
         <v>45737.69822916666</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -74616,7 +74616,7 @@
         <v>45092</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -74673,7 +74673,7 @@
         <v>44741.94070601852</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -74735,7 +74735,7 @@
         <v>45596.61569444444</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -74797,7 +74797,7 @@
         <v>45596.61582175926</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -74859,7 +74859,7 @@
         <v>45338.95405092592</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -74921,7 +74921,7 @@
         <v>45258</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -74978,7 +74978,7 @@
         <v>45574.61634259259</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -75035,7 +75035,7 @@
         <v>45666.44943287037</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -75092,7 +75092,7 @@
         <v>45629.35326388889</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>

--- a/Översikt RAGUNDA.xlsx
+++ b/Översikt RAGUNDA.xlsx
@@ -567,7 +567,7 @@
         <v>45622</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>45376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>45622</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>45560.34460648148</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>45673</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44917</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45804.67787037037</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>45590.42736111111</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45838.67753472222</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44504</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44644</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>45622</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>45560.34532407407</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45104</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45113</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>45579.53179398148</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44644.93650462963</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44473</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>44813</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45367.04916666666</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>45639.55269675926</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45622</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>45790.57334490741</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>44088</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>45482.63819444444</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>45182</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45779.49012731481</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>45803.59474537037</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>44776</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>45358.99375</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45790.57349537037</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>45839.42482638889</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44805</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>44645.99859953704</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>45327</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>44888</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>45779.57335648148</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>45560.34484953704</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>45378</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45685.36501157407</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>45799.63574074074</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>45799.34461805555</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>45832.34461805555</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>45510</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>45174</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>45769.53180555555</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>44504</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>45121</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>45190.96092592592</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44133</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>45320</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>45827.5110300926</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>45120</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>45622</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>45113</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>45723.40688657408</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44133</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>44662</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>44438</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>45176</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>45810.55061342593</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45769.67740740741</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>45786.61517361111</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>45121</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44915</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>45475.94796296296</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>44336</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>45405.57392361111</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>45435.54734953704</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>44994</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>45176</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>45155</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>44111</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44209</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>45471.94783564815</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>44875</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>44911</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>45867.63619212963</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>45832.34564814815</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>44994</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>45769.67778935185</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>45468.97528935185</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>45893.38584490741</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45846.41361111111</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>45495.56244212963</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>45595.44886574074</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>45457</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>44932</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>45238</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>45728.65684027778</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         <v>44656</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>45002.94356481481</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>45446.95087962963</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10042,7 +10042,7 @@
         <v>45551.46912037037</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>45195</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>45425.96472222222</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10332,7 +10332,7 @@
         <v>45832.34578703704</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>45182</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>45244</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>45674.67744212963</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>45471.94623842592</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>45893.38599537037</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>44911</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>45400.94002314815</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>45545.45748842593</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11196,7 +11196,7 @@
         <v>45744.61550925926</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44245</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>44334.62565972222</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>44696</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>44662</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
         <v>44334</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
         <v>44334</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>44911</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>45782.44871527778</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>45384</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45378</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>45455.96195601852</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>45805.34415509259</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>45610.34415509259</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>44113</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>45510</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         <v>45404</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>44677</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>45896.63618055556</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>45786.61534722222</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45491</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>45491</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>45187</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>44855</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>44369.92025462963</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>45071</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>45733</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>45779.57392361111</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>45397.95748842593</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13904,7 +13904,7 @@
         <v>45751.34650462963</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>45093</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         <v>44855</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14179,7 +14179,7 @@
         <v>45265</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>45516.94723379629</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>44902</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>44111</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45436.94686342592</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>45631</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>45804.34474537037</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>45491.94715277778</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>45209</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>45152</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>44971</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>45632.69822916666</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>45789.36503472222</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45847.61498842593</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>44788</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>45838</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>44875</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>45425.96285879629</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>45691.44769675926</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>44676</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>44855</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16136,7 +16136,7 @@
         <v>45321</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>45779.57350694444</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>45378</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>44865</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>45551.65726851852</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>44852</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>45121</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>45190</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>45800.42782407408</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>45372.95680555556</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17049,7 +17049,7 @@
         <v>45188</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>44680</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>45171</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>45205</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         <v>45394</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>45835.344375</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>45089</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>45191</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45241</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>45583.49642361111</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         <v>45526.56393518519</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>45852.63597222222</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>45722.61543981481</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>45854.61494212963</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>45631</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44855</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>45468.97495370371</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44993</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45769.65692129629</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>45238</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>45153</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>45723.57329861111</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>44826.94976851852</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>44462</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>44166</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         <v>44319</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>44705</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>44741</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>44774.94347222222</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>44741</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>44832</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19845,7 +19845,7 @@
         <v>45636.3863425926</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45468.97461805555</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>45751.34795138889</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>45771.3859837963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45301</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>45779.48993055556</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45301</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>45252</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>45149</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
         <v>45033</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45455.96184027778</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>45754.51064814815</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>45266</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45341</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45457.9640625</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>45089</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>45597.34461805555</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45205</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45153</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21558,7 +21558,7 @@
         <v>44991</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21648,7 +21648,7 @@
         <v>45813.49061342593</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>45183</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>44860</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45827.57371527778</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22011,7 +22011,7 @@
         <v>45646.34438657408</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>45785.36525462963</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45838.38627314815</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -22293,7 +22293,7 @@
         <v>45769.65736111111</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>45775.67769675926</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -22473,7 +22473,7 @@
         <v>45771.36548611111</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45436.94644675926</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45847.36528935185</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>44119</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22836,7 +22836,7 @@
         <v>45153</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45154</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>45147</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45468</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45722.65670138889</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>45487.92863425926</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -23374,7 +23374,7 @@
         <v>45897.531875</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>45510</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>45491.95008101852</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>44369</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23729,7 +23729,7 @@
         <v>45206</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>45315</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>45600.55265046296</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45044</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -24084,7 +24084,7 @@
         <v>45208</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>44157</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44141</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>44195</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>44214</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>44846</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>44168</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>44517</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44817</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>44880.95712962963</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44880.95719907407</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>44855.94125</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         <v>44425</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>44447.92069444444</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>44490.94109953703</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>44519.94534722222</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>44349</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>44210</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>44243</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>44280</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>44280</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44385.33887731482</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44292</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -25468,7 +25468,7 @@
         <v>44705</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>44518.94394675926</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>44846.9522337963</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -25644,7 +25644,7 @@
         <v>44362</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>44426.94077546296</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>44399</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>44818.94929398148</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25882,7 +25882,7 @@
         <v>44860</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44111</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>44774.94414351852</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>44425</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>44663</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>44823.48666666666</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -26244,7 +26244,7 @@
         <v>44874.95553240741</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -26306,7 +26306,7 @@
         <v>44784.9408912037</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -26368,7 +26368,7 @@
         <v>44714</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -26425,7 +26425,7 @@
         <v>44670</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>44837</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>44704.94234953704</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>44858</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>44855</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>44078</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>44175</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26849,7 +26849,7 @@
         <v>44194</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>44239</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26968,7 +26968,7 @@
         <v>44443</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>44273.92081018518</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>44741</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>44132</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>44495.93966435185</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>44126</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44854</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>44859.95710648148</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>44530</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>44823.94993055556</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44125.94493055555</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -27625,7 +27625,7 @@
         <v>44836.9491087963</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>44833.95405092592</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>44579.68604166667</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>44084</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>44883</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>44728.94398148148</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>44287</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>44308</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>44308</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>44259</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -28215,7 +28215,7 @@
         <v>44452</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>44629.56258101852</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>44281</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>44421.97322916667</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>44351</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>44832.95435185185</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>44586</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>44434.94559027778</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>44690</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44867</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>44876.95104166667</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>44111</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44500.93887731482</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>44476</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>44601</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>44714.94162037037</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -29182,7 +29182,7 @@
         <v>44477.48994212963</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>44357</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>44515.93767361111</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>44228</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>44783</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>44696.93986111111</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>44802</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -29601,7 +29601,7 @@
         <v>44864.94835648148</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>44308</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>44853.9499537037</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44482.92271990741</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>44512</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         <v>44662</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44824.94635416667</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>44704</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>44685</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>44615</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -30191,7 +30191,7 @@
         <v>44349.92013888889</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>44349.91995370371</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>44308</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -30362,7 +30362,7 @@
         <v>44851.95488425926</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>44379</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>44075</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -30543,7 +30543,7 @@
         <v>44671</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -30600,7 +30600,7 @@
         <v>44434.94517361111</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>44729.94136574074</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>44704.94229166667</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>44861</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -30843,7 +30843,7 @@
         <v>44777.95504629629</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>44855.9471875</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>44818</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>44833.9519212963</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>44138</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>44418.9369212963</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -31210,7 +31210,7 @@
         <v>44788</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>44853</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>44140</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -31391,7 +31391,7 @@
         <v>44099</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>44799.94394675926</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
         <v>44431</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>44574</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>44621</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>44463.94077546296</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>44883.94918981481</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -31810,7 +31810,7 @@
         <v>44124</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>44074</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>44074</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>44650</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>44815</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>44578.92284722222</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>44489.94711805556</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -32229,7 +32229,7 @@
         <v>44615</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -32286,7 +32286,7 @@
         <v>44823</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>44140</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
         <v>44599.98685185185</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>44727</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>44858</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>44494.93930555556</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>44425</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -32715,7 +32715,7 @@
         <v>44846</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -32777,7 +32777,7 @@
         <v>44781</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -32834,7 +32834,7 @@
         <v>44322</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -32891,7 +32891,7 @@
         <v>44361.55445601852</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32948,7 +32948,7 @@
         <v>44854.95390046296</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>44704.9422337963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -33072,7 +33072,7 @@
         <v>44831.94846064815</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>44831.9485300926</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -33196,7 +33196,7 @@
         <v>44784.94157407407</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>44495</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>44728.94392361111</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>44889</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>44595</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -33501,7 +33501,7 @@
         <v>44402.42243055555</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -33558,7 +33558,7 @@
         <v>44356.91935185185</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>44832.95300925926</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
         <v>44830</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -33739,7 +33739,7 @@
         <v>44356</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -33796,7 +33796,7 @@
         <v>44496</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -33853,7 +33853,7 @@
         <v>44734.94193287037</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -33915,7 +33915,7 @@
         <v>44776</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>44704.94217592593</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         <v>44802.94811342593</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
         <v>44805</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -34163,7 +34163,7 @@
         <v>44315</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -34225,7 +34225,7 @@
         <v>44861</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -34287,7 +34287,7 @@
         <v>45384</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -34344,7 +34344,7 @@
         <v>45086.94010416666</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>45726.3860300926</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -34463,7 +34463,7 @@
         <v>45119</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>45182</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -34582,7 +34582,7 @@
         <v>45379.93637731481</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>45401</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>45401</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>45007</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45042</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>45374</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>45723.67777777778</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>44336</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -35058,7 +35058,7 @@
         <v>45743.36</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -35120,7 +35120,7 @@
         <v>45356.03784722222</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>45358.95813657407</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>45645.36743055555</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -35296,7 +35296,7 @@
         <v>44953</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>44977.98660879629</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>44323</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>45769.67767361111</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>45253</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>45267</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -35663,7 +35663,7 @@
         <v>45098</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>45208</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -35777,7 +35777,7 @@
         <v>45769.51087962963</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -35839,7 +35839,7 @@
         <v>44813</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45075.945</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>44832</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -36025,7 +36025,7 @@
         <v>45280.92645833334</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>44812.94709490741</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>45695.44724537037</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>44805.94592592592</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>45741.63675925926</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>45645.36740740741</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -36382,7 +36382,7 @@
         <v>45636.3864699074</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>45358.95818287037</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>45441.33313657407</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>45702.63572916666</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>45392</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>45392.92903935185</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>44972.94140046297</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>45391.95329861111</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>45776.40311342593</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>45776.59422453704</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45574.57967592592</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45776.50651620371</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -37096,7 +37096,7 @@
         <v>45776.51130787037</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -37158,7 +37158,7 @@
         <v>45063</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -37215,7 +37215,7 @@
         <v>45426</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>45344</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45782.36506944444</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>45782.51099537037</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>45769.65659722222</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -37515,7 +37515,7 @@
         <v>45769.67790509259</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>45782.49032407408</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
         <v>45782.49046296296</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -37701,7 +37701,7 @@
         <v>45254.96516203704</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -37763,7 +37763,7 @@
         <v>45782.51109953703</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>44903</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45782.67758101852</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>45782.55287037037</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>45779.34417824074</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -38068,7 +38068,7 @@
         <v>45779.4281712963</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>45782.36494212963</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>45779.49025462963</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>44914</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>44900.95700231481</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -38378,7 +38378,7 @@
         <v>45448.94520833333</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -38440,7 +38440,7 @@
         <v>45761.67744212963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>45093.92207175926</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>45386.68003472222</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>44894</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>45223</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>45187</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>45448.94600694445</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>45751.34859953704</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>44879.95768518518</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45393.94459490741</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>45367.67256944445</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>44993.94950231481</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -39154,7 +39154,7 @@
         <v>44993</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>45259</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -39273,7 +39273,7 @@
         <v>45572.60363425926</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -39330,7 +39330,7 @@
         <v>45631.46665509259</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>44866</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>44958.94298611111</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -39511,7 +39511,7 @@
         <v>45786.51077546296</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>45257</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>45609.34412037037</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -39692,7 +39692,7 @@
         <v>44944</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>44922</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>45559.67745370371</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>44517.58137731482</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>44995.98341435185</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -39987,7 +39987,7 @@
         <v>44995.98644675926</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -40049,7 +40049,7 @@
         <v>45516.94732638889</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>45314</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>45154.95525462963</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>45393.94431712963</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -40292,7 +40292,7 @@
         <v>45040.94277777777</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>45453.95016203704</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45790.40670138889</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>45446.68947916666</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -40535,7 +40535,7 @@
         <v>45456.96569444444</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -40597,7 +40597,7 @@
         <v>45006</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>44475</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -40716,7 +40716,7 @@
         <v>45158.94231481481</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -40778,7 +40778,7 @@
         <v>45611.65679398148</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>45306</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -40897,7 +40897,7 @@
         <v>45279.94572916667</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -40959,7 +40959,7 @@
         <v>44336</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -41016,7 +41016,7 @@
         <v>45574.51185185185</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -41078,7 +41078,7 @@
         <v>45049</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -41140,7 +41140,7 @@
         <v>45792.34527777778</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>45309.92524305556</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>45611.5953125</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>45792.71905092592</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -41378,7 +41378,7 @@
         <v>45608.6078587963</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -41440,7 +41440,7 @@
         <v>45792.49023148148</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>45792.63584490741</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>45792.34606481482</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -41626,7 +41626,7 @@
         <v>45638.34431712963</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>45656</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>45327.94459490741</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>45315.9492824074</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>45204.94399305555</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>45574.51087962963</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -41993,7 +41993,7 @@
         <v>45574.51090277778</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>45211.95134259259</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -42117,7 +42117,7 @@
         <v>45454.95960648148</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -42179,7 +42179,7 @@
         <v>45384</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -42236,7 +42236,7 @@
         <v>45791.53238425926</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -42293,7 +42293,7 @@
         <v>45139.94681712963</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -42355,7 +42355,7 @@
         <v>45453.95538194444</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>45629.36513888889</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -42474,7 +42474,7 @@
         <v>45545.64957175926</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -42531,7 +42531,7 @@
         <v>45714.60649305556</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>45412.02506944445</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -42650,7 +42650,7 @@
         <v>45762.39876157408</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -42727,7 +42727,7 @@
         <v>45243</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -42789,7 +42789,7 @@
         <v>45275.95060185185</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -42851,7 +42851,7 @@
         <v>45469.94876157407</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>45635.47243055556</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -42970,7 +42970,7 @@
         <v>45769.51075231482</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45611</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -43094,7 +43094,7 @@
         <v>45793</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>45694.69826388889</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45796</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45796</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>45516.94934027778</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45436.94636574074</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>45796</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45793.61523148148</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>45216.92424768519</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         <v>45796</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45441</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>44979</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>44980.93865740741</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>44519.94440972222</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45266</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>45545.49078703704</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>45511</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>45009.0897337963</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>45191</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -44222,7 +44222,7 @@
         <v>45797.63627314815</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -44284,7 +44284,7 @@
         <v>45800.63619212963</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>44628</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>45426</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>45426</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45033</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>45799.34421296296</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -44636,7 +44636,7 @@
         <v>45614.34541666666</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -44693,7 +44693,7 @@
         <v>45635.57331018519</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -44755,7 +44755,7 @@
         <v>45182</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>44656</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45372.95762731481</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>45800</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45800.42743055556</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>44897</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -45122,7 +45122,7 @@
         <v>45800.44822916666</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>45800.44862268519</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -45246,7 +45246,7 @@
         <v>44911.93846064815</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>45341.95381944445</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -45370,7 +45370,7 @@
         <v>45803.5946875</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>45439.92752314815</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -45484,7 +45484,7 @@
         <v>45803.61552083334</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>45803.61557870371</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -45598,7 +45598,7 @@
         <v>45804.59487268519</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -45660,7 +45660,7 @@
         <v>45804.42642361111</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45639.55240740741</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -45779,7 +45779,7 @@
         <v>45488.94747685185</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45729.51074074074</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45638</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -45960,7 +45960,7 @@
         <v>45540.38564814815</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>45425.96239583333</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -46084,7 +46084,7 @@
         <v>45590.40675925926</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -46146,7 +46146,7 @@
         <v>45803.59417824074</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -46203,7 +46203,7 @@
         <v>45726.38575231482</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -46260,7 +46260,7 @@
         <v>45737.63574074074</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>45050.94020833333</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -46384,7 +46384,7 @@
         <v>45804.65672453704</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>45805.61495370371</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -46508,7 +46508,7 @@
         <v>44917</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>44993.94958333333</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -46632,7 +46632,7 @@
         <v>45797.40800925926</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -46689,7 +46689,7 @@
         <v>45805.46613425926</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -46746,7 +46746,7 @@
         <v>45211.95061342593</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>44130.9416550926</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -46870,7 +46870,7 @@
         <v>45722.48982638889</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45323</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -46984,7 +46984,7 @@
         <v>45805.57390046296</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -47046,7 +47046,7 @@
         <v>45190</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45672.44898148148</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         <v>44900</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -47232,7 +47232,7 @@
         <v>45566.68125</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -47289,7 +47289,7 @@
         <v>45404.99792824074</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>44587.92149305555</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -47428,7 +47428,7 @@
         <v>44943.94802083333</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>44903</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>44743</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>45603.67850694444</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -47666,7 +47666,7 @@
         <v>45653.44836805556</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -47728,7 +47728,7 @@
         <v>45601.5315625</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>44550.92168981482</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -47847,7 +47847,7 @@
         <v>45638.63600694444</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>45616.5108912037</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -47971,7 +47971,7 @@
         <v>44644</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -48033,7 +48033,7 @@
         <v>44113</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -48095,7 +48095,7 @@
         <v>45420</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -48157,7 +48157,7 @@
         <v>45646.63605324074</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>45344</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -48276,7 +48276,7 @@
         <v>45063</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -48333,7 +48333,7 @@
         <v>45645.55665509259</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -48390,7 +48390,7 @@
         <v>45604.4190625</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -48447,7 +48447,7 @@
         <v>45810.36495370371</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -48509,7 +48509,7 @@
         <v>45692.51069444444</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -48571,7 +48571,7 @@
         <v>45692.57326388889</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -48633,7 +48633,7 @@
         <v>45230.96376157407</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -48695,7 +48695,7 @@
         <v>45428.00471064815</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -48757,7 +48757,7 @@
         <v>45574.39081018518</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -48819,7 +48819,7 @@
         <v>45734.4633912037</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -48876,7 +48876,7 @@
         <v>44587.92144675926</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>45351.98532407408</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -48995,7 +48995,7 @@
         <v>45342</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -49057,7 +49057,7 @@
         <v>45342.9462037037</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -49119,7 +49119,7 @@
         <v>45552.44096064815</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -49176,7 +49176,7 @@
         <v>45579.47052083333</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -49233,7 +49233,7 @@
         <v>45616.34479166667</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -49295,7 +49295,7 @@
         <v>45180</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -49357,7 +49357,7 @@
         <v>45180.95927083334</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -49419,7 +49419,7 @@
         <v>45656.64223379629</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -49476,7 +49476,7 @@
         <v>44991</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>44614</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -49595,7 +49595,7 @@
         <v>45716</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -49657,7 +49657,7 @@
         <v>45716.61487268518</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45056</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45056</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -49833,7 +49833,7 @@
         <v>44153</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -49890,7 +49890,7 @@
         <v>45028</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>44601</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>45769.67802083334</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -50066,7 +50066,7 @@
         <v>45453.42041666667</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -50123,7 +50123,7 @@
         <v>45615.47091435185</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -50180,7 +50180,7 @@
         <v>45813.42790509259</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -50242,7 +50242,7 @@
         <v>45667.57342592593</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -50304,7 +50304,7 @@
         <v>45667.57347222222</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -50366,7 +50366,7 @@
         <v>44655</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -50428,7 +50428,7 @@
         <v>45197.94171296297</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -50490,7 +50490,7 @@
         <v>45764</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -50547,7 +50547,7 @@
         <v>45195</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -50609,7 +50609,7 @@
         <v>45195.94679398148</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -50671,7 +50671,7 @@
         <v>45195.94685185186</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -50733,7 +50733,7 @@
         <v>44614</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -50790,7 +50790,7 @@
         <v>45692.49008101852</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -50852,7 +50852,7 @@
         <v>44886</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -50914,7 +50914,7 @@
         <v>45860.30229166667</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -50971,7 +50971,7 @@
         <v>45554.61583333334</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -51028,7 +51028,7 @@
         <v>45818.46898148148</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -51085,7 +51085,7 @@
         <v>45187</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -51142,7 +51142,7 @@
         <v>45859.594375</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -51204,7 +51204,7 @@
         <v>45678.67761574074</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -51266,7 +51266,7 @@
         <v>45442.96296296296</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -51328,7 +51328,7 @@
         <v>45819.6359375</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -51390,7 +51390,7 @@
         <v>45208</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -51447,7 +51447,7 @@
         <v>45098</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -51504,7 +51504,7 @@
         <v>45555.38509259259</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -51561,7 +51561,7 @@
         <v>45148</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -51618,7 +51618,7 @@
         <v>44684.94032407407</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -51680,7 +51680,7 @@
         <v>45138.94925925926</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -51742,7 +51742,7 @@
         <v>45636.38599537037</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45821.34513888889</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -51866,7 +51866,7 @@
         <v>45258</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>45195.94672453704</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -51985,7 +51985,7 @@
         <v>44901</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>44901</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -52109,7 +52109,7 @@
         <v>45825.57675925926</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -52166,7 +52166,7 @@
         <v>45825.58252314815</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45112.94303240741</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -52285,7 +52285,7 @@
         <v>45112.94310185185</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -52347,7 +52347,7 @@
         <v>45595.42738425926</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>45730.53208333333</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -52471,7 +52471,7 @@
         <v>45622.47435185185</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45429</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45505</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -52647,7 +52647,7 @@
         <v>45825.56762731481</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>45621.57395833333</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -52766,7 +52766,7 @@
         <v>45826.65759259259</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45870.34439814815</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -52890,7 +52890,7 @@
         <v>45505</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45574.61184027778</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45574.62297453704</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>45574.63355324074</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45827.53178240741</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -53185,7 +53185,7 @@
         <v>45827.63582175926</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -53247,7 +53247,7 @@
         <v>45869.65666666667</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -53309,7 +53309,7 @@
         <v>45869.67744212963</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45874.69844907407</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>45581.55260416667</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>44614</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>44977.98670138889</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -53609,7 +53609,7 @@
         <v>44656.94708333333</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -53671,7 +53671,7 @@
         <v>45392</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -53728,7 +53728,7 @@
         <v>45238</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -53790,7 +53790,7 @@
         <v>45230</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -53852,7 +53852,7 @@
         <v>45832.34552083333</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>45698.59409722222</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -53976,7 +53976,7 @@
         <v>45180.95907407408</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -54038,7 +54038,7 @@
         <v>45558.63575231482</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -54100,7 +54100,7 @@
         <v>44657</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -54157,7 +54157,7 @@
         <v>45874.67746527777</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         <v>45832.34524305556</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -54276,7 +54276,7 @@
         <v>45832.3459375</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45590</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -54395,7 +54395,7 @@
         <v>44641</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -54457,7 +54457,7 @@
         <v>44641</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -54519,7 +54519,7 @@
         <v>45874.59496527778</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -54581,7 +54581,7 @@
         <v>45839</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -54638,7 +54638,7 @@
         <v>45253</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -54695,7 +54695,7 @@
         <v>45876.53188657408</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -54757,7 +54757,7 @@
         <v>45702.63604166666</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -54819,7 +54819,7 @@
         <v>44685</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -54881,7 +54881,7 @@
         <v>45622</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -54938,7 +54938,7 @@
         <v>44942</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -55000,7 +55000,7 @@
         <v>44994.94296296296</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -55062,7 +55062,7 @@
         <v>45257</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -55124,7 +55124,7 @@
         <v>45614.34545138889</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -55181,7 +55181,7 @@
         <v>45772.6565625</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -55243,7 +55243,7 @@
         <v>45834.65662037037</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -55305,7 +55305,7 @@
         <v>45601.40686342592</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -55367,7 +55367,7 @@
         <v>45145.95326388889</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -55429,7 +55429,7 @@
         <v>44774</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -55486,7 +55486,7 @@
         <v>45215.94657407407</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -55548,7 +55548,7 @@
         <v>45751.36490740741</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -55610,7 +55610,7 @@
         <v>44671</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -55667,7 +55667,7 @@
         <v>45344.92865740741</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -55724,7 +55724,7 @@
         <v>45344.92873842592</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -55781,7 +55781,7 @@
         <v>44820</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -55843,7 +55843,7 @@
         <v>45309</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -55900,7 +55900,7 @@
         <v>45309</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -55957,7 +55957,7 @@
         <v>44231</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -56014,7 +56014,7 @@
         <v>44839</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -56071,7 +56071,7 @@
         <v>45456.96601851852</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -56133,7 +56133,7 @@
         <v>45688.68196759259</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -56195,7 +56195,7 @@
         <v>45835.4506712963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -56252,7 +56252,7 @@
         <v>45838</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>45149.95241898148</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -56371,7 +56371,7 @@
         <v>45730.56346064815</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -56433,7 +56433,7 @@
         <v>45835.72046296296</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -56490,7 +56490,7 @@
         <v>45722.44849537037</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -56552,7 +56552,7 @@
         <v>45838</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -56609,7 +56609,7 @@
         <v>45838.67887731481</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -56671,7 +56671,7 @@
         <v>45075.94506944445</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -56733,7 +56733,7 @@
         <v>45838.48996527777</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45224</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -56847,7 +56847,7 @@
         <v>45233.92591435185</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -56904,7 +56904,7 @@
         <v>44956.93924768519</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -56966,7 +56966,7 @@
         <v>45314</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -57023,7 +57023,7 @@
         <v>45835.40668981482</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -57085,7 +57085,7 @@
         <v>45629.36486111111</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -57142,7 +57142,7 @@
         <v>44803.94351851852</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -57204,7 +57204,7 @@
         <v>45838.67800925926</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -57261,7 +57261,7 @@
         <v>45835.53166666667</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -57323,7 +57323,7 @@
         <v>45835.46334490741</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -57380,7 +57380,7 @@
         <v>45758.36487268518</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -57442,7 +57442,7 @@
         <v>44958</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -57499,7 +57499,7 @@
         <v>45367.04693287037</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -57561,7 +57561,7 @@
         <v>45835.45686342593</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -57618,7 +57618,7 @@
         <v>45712.61552083334</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>45839.42822916667</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -57742,7 +57742,7 @@
         <v>45839.46915509259</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45603.44644675926</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -57866,7 +57866,7 @@
         <v>45775.67747685185</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>45622.44774305556</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -57985,7 +57985,7 @@
         <v>44672.94018518519</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -58047,7 +58047,7 @@
         <v>45838.36532407408</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -58109,7 +58109,7 @@
         <v>45009.089375</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -58171,7 +58171,7 @@
         <v>45839.49082175926</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -58228,7 +58228,7 @@
         <v>45244.96774305555</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -58290,7 +58290,7 @@
         <v>45618.46921296296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -58352,7 +58352,7 @@
         <v>45839.42810185185</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -58414,7 +58414,7 @@
         <v>45734.45268518518</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -58471,7 +58471,7 @@
         <v>45241.95741898148</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -58533,7 +58533,7 @@
         <v>45241</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -58595,7 +58595,7 @@
         <v>45254.96402777778</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -58657,7 +58657,7 @@
         <v>45839.42864583333</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -58719,7 +58719,7 @@
         <v>45839.57331018519</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -58781,7 +58781,7 @@
         <v>45840.52225694444</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -58838,7 +58838,7 @@
         <v>44746</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -58895,7 +58895,7 @@
         <v>44806</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -58952,7 +58952,7 @@
         <v>45771.36538194444</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -59014,7 +59014,7 @@
         <v>45266.95082175926</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -59076,7 +59076,7 @@
         <v>45327.94443287037</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -59138,7 +59138,7 @@
         <v>45344.92822916667</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -59195,7 +59195,7 @@
         <v>45842.38579861111</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -59257,7 +59257,7 @@
         <v>45044</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -59319,7 +59319,7 @@
         <v>45351.98496527778</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -59381,7 +59381,7 @@
         <v>45741.63659722222</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -59443,7 +59443,7 @@
         <v>45841.57427083333</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -59505,7 +59505,7 @@
         <v>45671.48989583334</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>45128</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -59629,7 +59629,7 @@
         <v>45842.42608796297</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -59686,7 +59686,7 @@
         <v>44984</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -59743,7 +59743,7 @@
         <v>44571</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -59800,7 +59800,7 @@
         <v>45841.6571412037</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -59857,7 +59857,7 @@
         <v>45222</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -59919,7 +59919,7 @@
         <v>45257.92826388889</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -59976,7 +59976,7 @@
         <v>45306</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -60033,7 +60033,7 @@
         <v>45888.6775</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -60095,7 +60095,7 @@
         <v>44977.44373842593</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -60152,7 +60152,7 @@
         <v>45170</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -60214,7 +60214,7 @@
         <v>45846.34454861111</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -60276,7 +60276,7 @@
         <v>45474.50608796296</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -60333,7 +60333,7 @@
         <v>45608.52354166667</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         <v>45482.94815972223</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -60457,7 +60457,7 @@
         <v>44929</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -60514,7 +60514,7 @@
         <v>45469.94667824074</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -60576,7 +60576,7 @@
         <v>45238</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -60633,7 +60633,7 @@
         <v>45511</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -60695,7 +60695,7 @@
         <v>45436.94613425926</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -60757,7 +60757,7 @@
         <v>45847.34474537037</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -60819,7 +60819,7 @@
         <v>45847.34528935186</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -60881,7 +60881,7 @@
         <v>45769.65688657408</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -60943,7 +60943,7 @@
         <v>45847.34597222223</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -61005,7 +61005,7 @@
         <v>45847.61513888889</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -61062,7 +61062,7 @@
         <v>45847.65703703704</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -61124,7 +61124,7 @@
         <v>45848.65658564815</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -61186,7 +61186,7 @@
         <v>45847.34565972222</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -61248,7 +61248,7 @@
         <v>44286</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -61305,7 +61305,7 @@
         <v>45210</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -61362,7 +61362,7 @@
         <v>45847.61548611111</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -61419,7 +61419,7 @@
         <v>45664.55241898148</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -61481,7 +61481,7 @@
         <v>45000</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -61538,7 +61538,7 @@
         <v>45530</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -61595,7 +61595,7 @@
         <v>45889.61517361111</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -61657,7 +61657,7 @@
         <v>45847.34515046296</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -61719,7 +61719,7 @@
         <v>45848.49774305556</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -61776,7 +61776,7 @@
         <v>45260</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -61833,7 +61833,7 @@
         <v>45892.34438657408</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -61890,7 +61890,7 @@
         <v>45892.38641203703</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -61947,7 +61947,7 @@
         <v>45892.34423611111</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -62004,7 +62004,7 @@
         <v>45892.38591435185</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -62061,7 +62061,7 @@
         <v>45892.38657407407</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -62118,7 +62118,7 @@
         <v>45681.60203703704</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -62175,7 +62175,7 @@
         <v>45848.49761574074</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -62232,7 +62232,7 @@
         <v>45679.40362268518</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -62289,7 +62289,7 @@
         <v>45852.53185185185</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -62351,7 +62351,7 @@
         <v>45892.44840277778</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -62408,7 +62408,7 @@
         <v>45850.34434027778</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -62465,7 +62465,7 @@
         <v>45103</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -62522,7 +62522,7 @@
         <v>45667.55239583334</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -62584,7 +62584,7 @@
         <v>44649.47048611111</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -62646,7 +62646,7 @@
         <v>45849.65663194445</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -62708,7 +62708,7 @@
         <v>45892.38619212963</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -62765,7 +62765,7 @@
         <v>45069</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -62822,7 +62822,7 @@
         <v>45892.44824074074</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -62879,7 +62879,7 @@
         <v>45850.34450231482</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -62941,7 +62941,7 @@
         <v>45852.53168981482</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -63003,7 +63003,7 @@
         <v>44424</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -63060,7 +63060,7 @@
         <v>45149</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -63117,7 +63117,7 @@
         <v>45324</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -63174,7 +63174,7 @@
         <v>45604.63575231482</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -63236,7 +63236,7 @@
         <v>45183.95563657407</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -63298,7 +63298,7 @@
         <v>44894.79018518519</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -63355,7 +63355,7 @@
         <v>45854.65663194445</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -63417,7 +63417,7 @@
         <v>44963</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -63479,7 +63479,7 @@
         <v>45896.52478009259</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -63536,7 +63536,7 @@
         <v>45601.55331018518</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -63598,7 +63598,7 @@
         <v>45487.92856481481</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -63655,7 +63655,7 @@
         <v>44914</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -63712,7 +63712,7 @@
         <v>45898.53193287037</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -63774,7 +63774,7 @@
         <v>45898.61502314815</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -63836,7 +63836,7 @@
         <v>45855.67899305555</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -63893,7 +63893,7 @@
         <v>45184</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -63950,7 +63950,7 @@
         <v>45856.46931712963</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -64012,7 +64012,7 @@
         <v>45855.61523148148</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -64074,7 +64074,7 @@
         <v>45898.49012731481</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -64136,7 +64136,7 @@
         <v>45000</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -64198,7 +64198,7 @@
         <v>45000</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -64260,7 +64260,7 @@
         <v>45446.57052083333</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -64317,7 +64317,7 @@
         <v>45053.94313657407</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -64379,7 +64379,7 @@
         <v>45898.59295138889</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -64436,7 +64436,7 @@
         <v>44880</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -64498,7 +64498,7 @@
         <v>45714</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -64555,7 +64555,7 @@
         <v>45425.96494212963</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -64617,7 +64617,7 @@
         <v>45534</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -64674,7 +64674,7 @@
         <v>45510</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -64736,7 +64736,7 @@
         <v>45692.48993055556</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -64798,7 +64798,7 @@
         <v>44855</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -64860,7 +64860,7 @@
         <v>44349.91978009259</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -64917,7 +64917,7 @@
         <v>45733.61497685185</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -64979,7 +64979,7 @@
         <v>45625.51068287037</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -65041,7 +65041,7 @@
         <v>45695.45868055556</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -65098,7 +65098,7 @@
         <v>44991</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -65160,7 +65160,7 @@
         <v>45476.94533564815</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -65222,7 +65222,7 @@
         <v>44384</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -65279,7 +65279,7 @@
         <v>44635</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -65341,7 +65341,7 @@
         <v>45040</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -65398,7 +65398,7 @@
         <v>44844.95368055555</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -65460,7 +65460,7 @@
         <v>44530.94694444445</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -65522,7 +65522,7 @@
         <v>44957.94075231482</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -65584,7 +65584,7 @@
         <v>44362</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -65641,7 +65641,7 @@
         <v>45482.94891203703</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -65703,7 +65703,7 @@
         <v>45482.9491087963</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -65765,7 +65765,7 @@
         <v>45552.39113425926</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -65822,7 +65822,7 @@
         <v>45008.01408564814</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -65884,7 +65884,7 @@
         <v>45176</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -65941,7 +65941,7 @@
         <v>44305.92047453704</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -65998,7 +65998,7 @@
         <v>45681.6050925926</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -66055,7 +66055,7 @@
         <v>45726.38615740741</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -66112,7 +66112,7 @@
         <v>45726.3862037037</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -66169,7 +66169,7 @@
         <v>45706.34450231482</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -66231,7 +66231,7 @@
         <v>45715.59405092592</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -66293,7 +66293,7 @@
         <v>45092</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -66350,7 +66350,7 @@
         <v>44966.95328703704</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -66412,7 +66412,7 @@
         <v>44889</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -66469,7 +66469,7 @@
         <v>44231</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -66526,7 +66526,7 @@
         <v>45735.53177083333</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -66588,7 +66588,7 @@
         <v>45735.5517824074</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -66645,7 +66645,7 @@
         <v>45730.42738425926</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -66707,7 +66707,7 @@
         <v>45733.61554398148</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -66769,7 +66769,7 @@
         <v>45197.94152777778</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -66831,7 +66831,7 @@
         <v>45700.57324074074</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -66893,7 +66893,7 @@
         <v>45112</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -66955,7 +66955,7 @@
         <v>45367.69850694444</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -67012,7 +67012,7 @@
         <v>45367.71348379629</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -67069,7 +67069,7 @@
         <v>45034</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -67126,7 +67126,7 @@
         <v>45491</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -67188,7 +67188,7 @@
         <v>45112</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -67250,7 +67250,7 @@
         <v>44629</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -67307,7 +67307,7 @@
         <v>45053.94305555556</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -67369,7 +67369,7 @@
         <v>45306</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -67426,7 +67426,7 @@
         <v>44889.95015046297</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -67488,7 +67488,7 @@
         <v>44680</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -67545,7 +67545,7 @@
         <v>45119</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -67602,7 +67602,7 @@
         <v>45289</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -67659,7 +67659,7 @@
         <v>45260.92561342593</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -67716,7 +67716,7 @@
         <v>45068</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -67778,7 +67778,7 @@
         <v>44939</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -67840,7 +67840,7 @@
         <v>45735.69842592593</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -67902,7 +67902,7 @@
         <v>45314.92758101852</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -67959,7 +67959,7 @@
         <v>45596.61533564814</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -68021,7 +68021,7 @@
         <v>45735</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -68083,7 +68083,7 @@
         <v>45540.38586805556</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -68145,7 +68145,7 @@
         <v>44074</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -68207,7 +68207,7 @@
         <v>44236</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -68264,7 +68264,7 @@
         <v>45280</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -68321,7 +68321,7 @@
         <v>44825</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -68383,7 +68383,7 @@
         <v>44299</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -68440,7 +68440,7 @@
         <v>44917</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -68497,7 +68497,7 @@
         <v>44410</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -68554,7 +68554,7 @@
         <v>44670</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -68611,7 +68611,7 @@
         <v>44915</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -68673,7 +68673,7 @@
         <v>45078</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -68730,7 +68730,7 @@
         <v>45386</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -68787,7 +68787,7 @@
         <v>44405.92065972222</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -68844,7 +68844,7 @@
         <v>45688.67542824074</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -68906,7 +68906,7 @@
         <v>45659.69822916666</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -68968,7 +68968,7 @@
         <v>45054</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -69030,7 +69030,7 @@
         <v>45238.96797453704</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -69092,7 +69092,7 @@
         <v>45604.40540509259</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -69149,7 +69149,7 @@
         <v>45604.41625</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -69206,7 +69206,7 @@
         <v>45568.51075231482</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -69268,7 +69268,7 @@
         <v>45546</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -69325,7 +69325,7 @@
         <v>45086</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -69387,7 +69387,7 @@
         <v>45251</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -69444,7 +69444,7 @@
         <v>45145</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -69506,7 +69506,7 @@
         <v>45467.96207175926</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -69568,7 +69568,7 @@
         <v>45695.51070601852</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -69630,7 +69630,7 @@
         <v>45279.94564814815</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -69692,7 +69692,7 @@
         <v>45091</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -69754,7 +69754,7 @@
         <v>44869</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -69811,7 +69811,7 @@
         <v>45638</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -69868,7 +69868,7 @@
         <v>45645.55672453704</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -69925,7 +69925,7 @@
         <v>44869</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -69982,7 +69982,7 @@
         <v>45096.93866898148</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -70044,7 +70044,7 @@
         <v>44173</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -70101,7 +70101,7 @@
         <v>45751.34873842593</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -70163,7 +70163,7 @@
         <v>44888</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -70225,7 +70225,7 @@
         <v>44174</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -70287,7 +70287,7 @@
         <v>45771.51074074074</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -70349,7 +70349,7 @@
         <v>45341</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -70406,7 +70406,7 @@
         <v>45495.57677083334</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -70463,7 +70463,7 @@
         <v>45002.0328125</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -70525,7 +70525,7 @@
         <v>45712.65671296296</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -70582,7 +70582,7 @@
         <v>45754</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -70644,7 +70644,7 @@
         <v>45156</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -70706,7 +70706,7 @@
         <v>45241.95724537037</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -70768,7 +70768,7 @@
         <v>45425.96230324074</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -70830,7 +70830,7 @@
         <v>45561.34663194444</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -70892,7 +70892,7 @@
         <v>45111.92793981481</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -70954,7 +70954,7 @@
         <v>45357.05300925926</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -71016,7 +71016,7 @@
         <v>45425.96275462963</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -71078,7 +71078,7 @@
         <v>45453.4444212963</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -71135,7 +71135,7 @@
         <v>44929</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -71192,7 +71192,7 @@
         <v>44375</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -71249,7 +71249,7 @@
         <v>45322</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -71306,7 +71306,7 @@
         <v>44918</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -71368,7 +71368,7 @@
         <v>45622.46200231482</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -71425,7 +71425,7 @@
         <v>45000</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -71487,7 +71487,7 @@
         <v>45681.5315625</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -71549,7 +71549,7 @@
         <v>45673.66358796296</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -71606,7 +71606,7 @@
         <v>44680.95246527778</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -71668,7 +71668,7 @@
         <v>45601.59518518519</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -71730,7 +71730,7 @@
         <v>44879</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -71792,7 +71792,7 @@
         <v>45009</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -71849,7 +71849,7 @@
         <v>45436.94628472222</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -71911,7 +71911,7 @@
         <v>45425.96263888889</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -71973,7 +71973,7 @@
         <v>45615.50034722222</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -72030,7 +72030,7 @@
         <v>45048.94340277778</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -72092,7 +72092,7 @@
         <v>44929.92489583333</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -72149,7 +72149,7 @@
         <v>45596.61553240741</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -72211,7 +72211,7 @@
         <v>45435</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -72268,7 +72268,7 @@
         <v>45559.67759259259</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -72330,7 +72330,7 @@
         <v>45636.57329861111</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -72392,7 +72392,7 @@
         <v>44593</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -72449,7 +72449,7 @@
         <v>45166</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -72506,7 +72506,7 @@
         <v>45723.51079861111</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -72568,7 +72568,7 @@
         <v>45747.67739583334</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -72630,7 +72630,7 @@
         <v>45629.42759259259</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -72692,7 +72692,7 @@
         <v>45107</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -72749,7 +72749,7 @@
         <v>44518</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -72806,7 +72806,7 @@
         <v>45071</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -72863,7 +72863,7 @@
         <v>45133</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -72925,7 +72925,7 @@
         <v>45712.61502314815</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -72987,7 +72987,7 @@
         <v>45712.61510416667</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -73049,7 +73049,7 @@
         <v>45630.7862037037</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -73106,7 +73106,7 @@
         <v>45329.95806712963</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -73168,7 +73168,7 @@
         <v>45331.92746527777</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -73225,7 +73225,7 @@
         <v>45103</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -73282,7 +73282,7 @@
         <v>45072.92737268518</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -73339,7 +73339,7 @@
         <v>45065.42894675926</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -73396,7 +73396,7 @@
         <v>45622.46910879629</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -73453,7 +73453,7 @@
         <v>45457.96372685185</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -73515,7 +73515,7 @@
         <v>44932.93927083333</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -73577,7 +73577,7 @@
         <v>45540.34428240741</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -73639,7 +73639,7 @@
         <v>45714.55064814815</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -73696,7 +73696,7 @@
         <v>45175</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -73758,7 +73758,7 @@
         <v>45534.63537037037</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -73820,7 +73820,7 @@
         <v>45149.95372685185</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -73882,7 +73882,7 @@
         <v>44904.94824074074</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -73944,7 +73944,7 @@
         <v>45665.65684027778</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -74006,7 +74006,7 @@
         <v>44971</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -74068,7 +74068,7 @@
         <v>45614.63869212963</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -74130,7 +74130,7 @@
         <v>44880.95741898148</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -74192,7 +74192,7 @@
         <v>45715.61523148148</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -74254,7 +74254,7 @@
         <v>44876</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -74316,7 +74316,7 @@
         <v>45215</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -74373,7 +74373,7 @@
         <v>45105</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -74435,7 +74435,7 @@
         <v>45756.63601851852</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -74497,7 +74497,7 @@
         <v>45429</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -74554,7 +74554,7 @@
         <v>45737.69822916666</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -74616,7 +74616,7 @@
         <v>45092</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -74673,7 +74673,7 @@
         <v>44741.94070601852</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -74735,7 +74735,7 @@
         <v>45596.61569444444</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -74797,7 +74797,7 @@
         <v>45596.61582175926</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -74859,7 +74859,7 @@
         <v>45338.95405092592</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -74921,7 +74921,7 @@
         <v>45258</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -74978,7 +74978,7 @@
         <v>45574.61634259259</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -75035,7 +75035,7 @@
         <v>45666.44943287037</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -75092,7 +75092,7 @@
         <v>45629.35326388889</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>

--- a/Översikt RAGUNDA.xlsx
+++ b/Översikt RAGUNDA.xlsx
@@ -567,7 +567,7 @@
         <v>45622</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>45376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>45622</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>45560.34460648148</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>45673</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44917</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45804.67787037037</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>45838.67753472222</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>45590.42736111111</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44504</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>45622</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>44644</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>45560.34532407407</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45104</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45579.53179398148</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>45113</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44644.93650462963</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>45367.04916666666</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>44813</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>44473</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>44088</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>45622</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>45639.55269675926</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45790.57334490741</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>45482.63819444444</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>45779.49012731481</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45182</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>44776</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
         <v>45803.59474537037</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>45839.42482638889</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>45790.57349537037</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>45358.99375</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44805</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>44888</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>45327</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>45779.57335648148</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>44645.99859953704</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>45560.34484953704</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>45685.36501157407</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>45121</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>45799.63574074074</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>45799.34461805555</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>45510</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>45174</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>45190.96092592592</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>44504</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>45832.34461805555</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>45769.53180555555</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>45378</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44133</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>45320</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>45827.5110300926</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>45723.40688657408</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>45622</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>45120</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>45113</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44133</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>44662</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>44438</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>45435.54734953704</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         <v>44994</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45810.55061342593</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>44336</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>45121</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>45769.67740740741</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>45786.61517361111</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>45155</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>44915</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         <v>45475.94796296296</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>45176</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         <v>45405.57392361111</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>45176</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>44111</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44209</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>44932</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>44994</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>45457</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>45728.65684027778</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>45238</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>45867.63619212963</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>45769.67778935185</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>45832.34564814815</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>45495.56244212963</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>45893.38584490741</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>45846.41361111111</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
         <v>45595.44886574074</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>44875</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>45468.97528935185</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>45471.94783564815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>44656</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>45400.94002314815</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>45195</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45182</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>45551.46912037037</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>45744.61550925926</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>45471.94623842592</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>45832.34578703704</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>45893.38599537037</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>45674.67744212963</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>45244</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>44911</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>45425.96472222222</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>45002.94356481481</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>45545.45748842593</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>45446.95087962963</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>44245</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>44334.62565972222</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>44696</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>44662</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>44334</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>44334</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>44911</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>45782.44871527778</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>45384</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>45378</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12125,7 +12125,7 @@
         <v>45610.34415509259</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>45187</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>45805.34415509259</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>45491</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>45455.96195601852</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>44113</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>45491</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>45896.63618055556</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>45786.61534722222</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45510</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>45404</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>44677</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>44855</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>44369.92025462963</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45632.69822916666</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13539,7 +13539,7 @@
         <v>45425.96285879629</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>45779.57392361111</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>45265</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>45516.94723379629</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>44875</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>45631</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>44855</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14195,7 +14195,7 @@
         <v>45804.34474537037</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>45491.94715277778</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>45436.94686342592</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>44902</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>45152</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>45789.36503472222</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>45847.61498842593</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>45838</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>45903.345625</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>45093</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15125,7 +15125,7 @@
         <v>45751.34650462963</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45071</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>45209</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>44111</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>45397.95748842593</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>44788</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44971</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>45733</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45691.44769675926</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44676</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>44855</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>45722.61543981481</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>45779.57350694444</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45769.65692129629</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16413,7 +16413,7 @@
         <v>45321</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>45631</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>45153</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16689,7 +16689,7 @@
         <v>45241</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>45800.42782407408</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16871,7 +16871,7 @@
         <v>45121</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>45551.65726851852</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>45238</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>45191</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>44852</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>45190</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>45372.95680555556</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>45205</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>45835.344375</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>45852.63597222222</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>45854.61494212963</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>44993</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>44680</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>44865</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>45723.57329861111</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>45171</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>45089</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18405,7 +18405,7 @@
         <v>44826.94976851852</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45394</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>44855</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>45583.49642361111</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>45188</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45468.97495370371</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>45378</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45526.56393518519</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>44462</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>44166</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>44319</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19401,7 +19401,7 @@
         <v>44705</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>44741</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44774.94347222222</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>44741</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>44832</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>45089</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>45341</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>45751.34795138889</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>45775.67769675926</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20201,7 +20201,7 @@
         <v>45153</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>45722.65670138889</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>45779.48993055556</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>44991</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45487.92863425926</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45154</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45646.34438657408</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20833,7 +20833,7 @@
         <v>45252</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>45600.55265046296</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>45510</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>45771.3859837963</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>45149</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>44119</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>45183</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>45769.65736111111</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>45315</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>45457.9640625</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>45455.96184027778</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>45771.36548611111</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>45636.3863425926</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>45813.49061342593</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>45153</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22188,7 +22188,7 @@
         <v>45044</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45491.95008101852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>45827.57371527778</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>45785.36525462963</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>45838.38627314815</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>45147</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>45847.36528935185</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>45301</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>45301</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>45897.531875</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>44369</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>45468</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>44860</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45208</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -23448,7 +23448,7 @@
         <v>45205</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>45266</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>45033</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>45468.97461805555</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45206</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>45754.51064814815</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>45597.34461805555</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45436.94644675926</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>44141</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44157</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44195</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44214</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44846</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44168</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44517</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>44880.95712962963</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>44880.95719907407</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>44817</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>44855.94125</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>44425</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>44447.92069444444</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>44490.94109953703</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
         <v>44519.94534722222</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -25065,7 +25065,7 @@
         <v>44349</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>44210</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>44243</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -25236,7 +25236,7 @@
         <v>44280</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>44280</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>44385.33887731482</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>44292</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>44705</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>44518.94394675926</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -25578,7 +25578,7 @@
         <v>44846.9522337963</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -25640,7 +25640,7 @@
         <v>44362</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -25697,7 +25697,7 @@
         <v>44426.94077546296</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>44399</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25816,7 +25816,7 @@
         <v>44818.94929398148</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>44860</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>44111</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>44774.94414351852</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>44425</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>44823.48666666666</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>44663</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -26240,7 +26240,7 @@
         <v>44874.95553240741</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>44784.9408912037</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>44714</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -26421,7 +26421,7 @@
         <v>44837</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>44670</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>44858</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -26602,7 +26602,7 @@
         <v>44704.94234953704</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -26664,7 +26664,7 @@
         <v>44855</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>44175</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>44194</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>44239</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26907,7 +26907,7 @@
         <v>44443</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>44273.92081018518</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>44741</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>44132</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>44495.93966435185</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -27202,7 +27202,7 @@
         <v>44126</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -27259,7 +27259,7 @@
         <v>44854</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>44859.95710648148</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -27383,7 +27383,7 @@
         <v>44530</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>44823.94993055556</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>44836.9491087963</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -27564,7 +27564,7 @@
         <v>44125.94493055555</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>44833.95405092592</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>44579.68604166667</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -27745,7 +27745,7 @@
         <v>44084</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>44883</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27864,7 +27864,7 @@
         <v>44728.94398148148</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>44287</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27983,7 +27983,7 @@
         <v>44259</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -28040,7 +28040,7 @@
         <v>44629.56258101852</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>44308</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>44308</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>44452</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>44281</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>44421.97322916667</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -28392,7 +28392,7 @@
         <v>44351</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         <v>44832.95435185185</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -28516,7 +28516,7 @@
         <v>44586</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -28573,7 +28573,7 @@
         <v>44434.94559027778</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         <v>44867</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>44690</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>44876.95104166667</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>44111</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44500.93887731482</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>44476</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>44601</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -29059,7 +29059,7 @@
         <v>44714.94162037037</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>44357</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44477.48994212963</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44515.93767361111</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>44228</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>44696.93986111111</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>44783</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -29478,7 +29478,7 @@
         <v>44802</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>44864.94835648148</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>44308</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -29659,7 +29659,7 @@
         <v>44482.92271990741</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>44662</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>44704</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>44824.94635416667</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29897,7 +29897,7 @@
         <v>44349.92013888889</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>44308</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -30011,7 +30011,7 @@
         <v>44349.91995370371</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -30068,7 +30068,7 @@
         <v>44685</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         <v>44851.95488425926</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>44379</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>44615</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -30301,7 +30301,7 @@
         <v>44671</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>44434.94517361111</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44729.94136574074</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44704.94229166667</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>44861</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>44777.95504629629</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
         <v>44855.9471875</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -30725,7 +30725,7 @@
         <v>44140</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>44138</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>44418.9369212963</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>44799.94394675926</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>44574</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -31025,7 +31025,7 @@
         <v>44788</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>44853</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>44883.94918981481</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>44124</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>44818</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -31325,7 +31325,7 @@
         <v>44833.9519212963</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         <v>44431</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -31444,7 +31444,7 @@
         <v>44099</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>44815</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>44489.94711805556</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44621</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>44823</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>44650</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -31801,7 +31801,7 @@
         <v>44578.92284722222</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>44727</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>44615</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>44463.94077546296</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>44140</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -32101,7 +32101,7 @@
         <v>44599.98685185185</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -32163,7 +32163,7 @@
         <v>44846</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>44494.93930555556</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>44781</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         <v>44322</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>44854.95390046296</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>44704.9422337963</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>44831.94846064815</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>44831.9485300926</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>44784.94157407407</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>44495</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -32773,7 +32773,7 @@
         <v>44858</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -32835,7 +32835,7 @@
         <v>44425</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -32897,7 +32897,7 @@
         <v>44889</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>44595</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>44832.95300925926</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>44830</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -33140,7 +33140,7 @@
         <v>44361.55445601852</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>44402.42243055555</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>44496</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>44734.94193287037</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>44704.94217592593</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -33435,7 +33435,7 @@
         <v>44728.94392361111</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>44776</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>44356.91935185185</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -33616,7 +33616,7 @@
         <v>44957.94075231482</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45747.67739583334</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>45289</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -33797,7 +33797,7 @@
         <v>45608.52354166667</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -33859,7 +33859,7 @@
         <v>44805</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -33921,7 +33921,7 @@
         <v>44315</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -33983,7 +33983,7 @@
         <v>44861</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>44512</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>45456.96601851852</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>45735.5517824074</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>45611</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>44958.94298611111</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>44853.9499537037</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -34407,7 +34407,7 @@
         <v>44656</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -34469,7 +34469,7 @@
         <v>45191</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>45238</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -34588,7 +34588,7 @@
         <v>45446.57052083333</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -34645,7 +34645,7 @@
         <v>44305.92047453704</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>45754</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>44587.92144675926</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -34821,7 +34821,7 @@
         <v>45306</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>45775.67747685185</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>44980.93865740741</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>44410</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>45769.67790509259</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -35121,7 +35121,7 @@
         <v>45776.51130787037</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>44649.47048611111</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -35245,7 +35245,7 @@
         <v>45776.40311342593</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -35302,7 +35302,7 @@
         <v>45776.50651620371</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -35364,7 +35364,7 @@
         <v>45667.55239583334</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -35426,7 +35426,7 @@
         <v>45776.59422453704</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -35488,7 +35488,7 @@
         <v>45779.34417824074</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>45779.4281712963</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -35612,7 +35612,7 @@
         <v>45779.49025462963</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>45726.38615740741</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>45726.3862037037</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>45069</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45448.94520833333</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -35907,7 +35907,7 @@
         <v>45782.51099537037</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -35969,7 +35969,7 @@
         <v>45187</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>45723.67777777778</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -36088,7 +36088,7 @@
         <v>45782.55287037037</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -36150,7 +36150,7 @@
         <v>45782.36506944444</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>44991</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>44991</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>45782.51109953703</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>45782.36494212963</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -36460,7 +36460,7 @@
         <v>45629.35326388889</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>45716.61487268518</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>45782.67758101852</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>45622.47435185185</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>45476.94533564815</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -36765,7 +36765,7 @@
         <v>45454.95960648148</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -36827,7 +36827,7 @@
         <v>44894</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45086.94010416666</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -36946,7 +36946,7 @@
         <v>45487.92856481481</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -37003,7 +37003,7 @@
         <v>44812.94709490741</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -37065,7 +37065,7 @@
         <v>45530</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -37122,7 +37122,7 @@
         <v>45681.60203703704</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -37179,7 +37179,7 @@
         <v>45344</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -37236,7 +37236,7 @@
         <v>45534</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -37293,7 +37293,7 @@
         <v>45574.63355324074</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45002.0328125</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -37412,7 +37412,7 @@
         <v>45574.61184027778</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -37469,7 +37469,7 @@
         <v>45574.62297453704</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>45314</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>45280.92645833334</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         <v>45456.96569444444</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -37702,7 +37702,7 @@
         <v>44672.94018518519</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -37764,7 +37764,7 @@
         <v>44993.94958333333</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45393.94431712963</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>45049</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -37950,7 +37950,7 @@
         <v>45622</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -38007,7 +38007,7 @@
         <v>45184</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -38064,7 +38064,7 @@
         <v>45574.51087962963</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>45574.51090277778</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>45000</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>45611.65679398148</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>45344.92822916667</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>45392</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>45392.92903935185</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>45631.46665509259</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>45425.96230324074</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -38597,7 +38597,7 @@
         <v>45629.36513888889</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         <v>45678.67761574074</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>45259</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -38773,7 +38773,7 @@
         <v>45554.61583333334</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -38830,7 +38830,7 @@
         <v>45233.92591435185</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -38887,7 +38887,7 @@
         <v>45572.60363425926</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>44593</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>44889</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>45786.51077546296</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -39120,7 +39120,7 @@
         <v>45384</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -39177,7 +39177,7 @@
         <v>45238</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>44939</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -39301,7 +39301,7 @@
         <v>45429</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>45054</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -39420,7 +39420,7 @@
         <v>45609.34412037037</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>45000</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>45769.65688657408</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>45595.42738425926</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -39668,7 +39668,7 @@
         <v>45006</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -39730,7 +39730,7 @@
         <v>45604.40540509259</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>45604.41625</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -39844,7 +39844,7 @@
         <v>45105</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -39906,7 +39906,7 @@
         <v>45790.40670138889</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -39968,7 +39968,7 @@
         <v>45425.96239583333</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>44929.92489583333</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>45230</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -40149,7 +40149,7 @@
         <v>45791.53238425926</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -40206,7 +40206,7 @@
         <v>45608.6078587963</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>45792.34606481482</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>45792.63584490741</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -40392,7 +40392,7 @@
         <v>45793.61523148148</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>45056</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>45056</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -40568,7 +40568,7 @@
         <v>45309</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -40625,7 +40625,7 @@
         <v>45309</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45792.49023148148</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -40744,7 +40744,7 @@
         <v>45238.96797453704</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>45793</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>45792.71905092592</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -40925,7 +40925,7 @@
         <v>45510</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>45769.51087962963</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45367.69850694444</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45367.71348379629</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>45435</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>45482.94891203703</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45712.65671296296</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -41339,7 +41339,7 @@
         <v>44680.95246527778</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -41401,7 +41401,7 @@
         <v>45482.9491087963</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>44741.94070601852</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>45112.94310185185</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45712.61510416667</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45792.34527777778</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>45743.36</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -41773,7 +41773,7 @@
         <v>45762.39876157408</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -41850,7 +41850,7 @@
         <v>44979</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -41907,7 +41907,7 @@
         <v>44803.94351851852</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>45769.51075231482</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -42031,7 +42031,7 @@
         <v>45796</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -42088,7 +42088,7 @@
         <v>45796</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -42145,7 +42145,7 @@
         <v>45358.95818287037</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -42202,7 +42202,7 @@
         <v>44971</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -42264,7 +42264,7 @@
         <v>44977.98670138889</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>45063</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -42383,7 +42383,7 @@
         <v>45358.95813657407</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -42440,7 +42440,7 @@
         <v>45695.44724537037</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -42497,7 +42497,7 @@
         <v>45796</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -42554,7 +42554,7 @@
         <v>45629.42759259259</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>45797.63627314815</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -42678,7 +42678,7 @@
         <v>45574.57967592592</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>44173</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45439.92752314815</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>44929</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>44614</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45266</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>44995.98644675926</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -43082,7 +43082,7 @@
         <v>45267</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -43144,7 +43144,7 @@
         <v>45145.95326388889</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -43206,7 +43206,7 @@
         <v>44958</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -43263,7 +43263,7 @@
         <v>45042</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -43320,7 +43320,7 @@
         <v>44518</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -43377,7 +43377,7 @@
         <v>45426</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -43434,7 +43434,7 @@
         <v>45638.63600694444</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -43496,7 +43496,7 @@
         <v>45441</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -43553,7 +43553,7 @@
         <v>45211.95061342593</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>45799.34421296296</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -43677,7 +43677,7 @@
         <v>44869</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -43734,7 +43734,7 @@
         <v>44903</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>45545.49078703704</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -43853,7 +43853,7 @@
         <v>44963</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -43915,7 +43915,7 @@
         <v>44671</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -43972,7 +43972,7 @@
         <v>45712.61552083334</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>44915</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -44096,7 +44096,7 @@
         <v>44917</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -44158,7 +44158,7 @@
         <v>44977.98660879629</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>44953</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>45241.95741898148</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -44344,7 +44344,7 @@
         <v>45241</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -44406,7 +44406,7 @@
         <v>45803.5946875</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -44463,7 +44463,7 @@
         <v>45656.64223379629</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -44520,7 +44520,7 @@
         <v>45803.59417824074</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>45103</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -44634,7 +44634,7 @@
         <v>45800.63619212963</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>45040</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>44614</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>45756.63601851852</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -44872,7 +44872,7 @@
         <v>45166</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -44929,7 +44929,7 @@
         <v>44886</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -44991,7 +44991,7 @@
         <v>45028</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -45048,7 +45048,7 @@
         <v>45800.44822916666</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -45110,7 +45110,7 @@
         <v>45800.44862268519</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -45172,7 +45172,7 @@
         <v>45251</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -45229,7 +45229,7 @@
         <v>45803.61552083334</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -45286,7 +45286,7 @@
         <v>45803.61557870371</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -45343,7 +45343,7 @@
         <v>45800</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -45400,7 +45400,7 @@
         <v>45800.42743055556</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -45462,7 +45462,7 @@
         <v>45211.95134259259</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -45524,7 +45524,7 @@
         <v>45050.94020833333</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -45586,7 +45586,7 @@
         <v>45804.42642361111</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -45643,7 +45643,7 @@
         <v>45804.59487268519</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>45805.61495370371</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -45767,7 +45767,7 @@
         <v>45722.48982638889</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -45824,7 +45824,7 @@
         <v>45601.55331018518</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -45886,7 +45886,7 @@
         <v>45688.68196759259</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -45948,7 +45948,7 @@
         <v>45253</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -46005,7 +46005,7 @@
         <v>45797.40800925926</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -46062,7 +46062,7 @@
         <v>44972.94140046297</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45729.51074074074</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -46186,7 +46186,7 @@
         <v>45804.65672453704</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>44130.9416550926</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>45629.36486111111</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -46367,7 +46367,7 @@
         <v>45611.5953125</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45119</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -46481,7 +46481,7 @@
         <v>45341.95381944445</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -46543,7 +46543,7 @@
         <v>45386.68003472222</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -46600,7 +46600,7 @@
         <v>44657</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -46657,7 +46657,7 @@
         <v>45805.46613425926</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -46714,7 +46714,7 @@
         <v>45306</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -46771,7 +46771,7 @@
         <v>44571</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -46828,7 +46828,7 @@
         <v>45805.57390046296</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -46890,7 +46890,7 @@
         <v>45645.36740740741</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -46947,7 +46947,7 @@
         <v>45149</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -47004,7 +47004,7 @@
         <v>45243</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -47066,7 +47066,7 @@
         <v>45698.59409722222</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -47128,7 +47128,7 @@
         <v>45009.089375</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -47190,7 +47190,7 @@
         <v>45540.38564814815</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45511</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>44550.92168981482</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -47371,7 +47371,7 @@
         <v>45604.4190625</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -47428,7 +47428,7 @@
         <v>45692.51069444444</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>45692.57326388889</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>45315.9492824074</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -47614,7 +47614,7 @@
         <v>45574.51185185185</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45810.36495370371</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         <v>45436.94636574074</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -47800,7 +47800,7 @@
         <v>45426</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -47857,7 +47857,7 @@
         <v>45138.94925925926</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -47919,7 +47919,7 @@
         <v>45216.92424768519</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -47976,7 +47976,7 @@
         <v>45635.47243055556</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -48033,7 +48033,7 @@
         <v>44869</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -48090,7 +48090,7 @@
         <v>45771.36538194444</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -48152,7 +48152,7 @@
         <v>45771.51074074074</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -48214,7 +48214,7 @@
         <v>44113</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -48276,7 +48276,7 @@
         <v>45672.44898148148</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
         <v>45230.96376157407</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -48400,7 +48400,7 @@
         <v>45601.5315625</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -48462,7 +48462,7 @@
         <v>45367.04693287037</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -48524,7 +48524,7 @@
         <v>45351.98532407408</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>45667.57342592593</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -48648,7 +48648,7 @@
         <v>45040.94277777777</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -48710,7 +48710,7 @@
         <v>44984</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -48767,7 +48767,7 @@
         <v>45275.95060185185</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -48829,7 +48829,7 @@
         <v>44670</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -48886,7 +48886,7 @@
         <v>45429</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -48943,7 +48943,7 @@
         <v>45667.57347222222</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -49005,7 +49005,7 @@
         <v>44911.93846064815</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -49067,7 +49067,7 @@
         <v>45428.00471064815</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -49129,7 +49129,7 @@
         <v>45495.57677083334</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -49186,7 +49186,7 @@
         <v>45636.3864699074</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -49248,7 +49248,7 @@
         <v>45666.44943287037</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -49305,7 +49305,7 @@
         <v>44743</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -49362,7 +49362,7 @@
         <v>44900.95700231481</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -49424,7 +49424,7 @@
         <v>45566.68125</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -49481,7 +49481,7 @@
         <v>45813.42790509259</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -49543,7 +49543,7 @@
         <v>45769.67802083334</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>44746</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>44880</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -49724,7 +49724,7 @@
         <v>44424</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -49781,7 +49781,7 @@
         <v>45772.6565625</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -49843,7 +49843,7 @@
         <v>44587.92149305555</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         <v>44977.44373842593</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -49957,7 +49957,7 @@
         <v>45187</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>45764</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -50071,7 +50071,7 @@
         <v>45393.94459490741</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -50133,7 +50133,7 @@
         <v>45818.46898148148</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -50190,7 +50190,7 @@
         <v>45603.44644675926</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -50252,7 +50252,7 @@
         <v>45574.61634259259</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -50309,7 +50309,7 @@
         <v>44806</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -50366,7 +50366,7 @@
         <v>45559.67745370371</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -50428,7 +50428,7 @@
         <v>45195.94672453704</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -50490,7 +50490,7 @@
         <v>45412.02506944445</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -50552,7 +50552,7 @@
         <v>45596.61569444444</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -50614,7 +50614,7 @@
         <v>45596.61582175926</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -50676,7 +50676,7 @@
         <v>44922</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -50733,7 +50733,7 @@
         <v>44601</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -50790,7 +50790,7 @@
         <v>45819.6359375</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -50852,7 +50852,7 @@
         <v>44236</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -50909,7 +50909,7 @@
         <v>45338.95405092592</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -50971,7 +50971,7 @@
         <v>45279.94564814815</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -51033,7 +51033,7 @@
         <v>45821.34513888889</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -51095,7 +51095,7 @@
         <v>45825.56762731481</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -51152,7 +51152,7 @@
         <v>44684.94032407407</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -51214,7 +51214,7 @@
         <v>45372.95762731481</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -51276,7 +51276,7 @@
         <v>45825.58252314815</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -51333,7 +51333,7 @@
         <v>45596.61533564814</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -51395,7 +51395,7 @@
         <v>45825.57675925926</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>45869.67744212963</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -51514,7 +51514,7 @@
         <v>45869.65666666667</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>45826.65759259259</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -51638,7 +51638,7 @@
         <v>45827.53178240741</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -51700,7 +51700,7 @@
         <v>45827.63582175926</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>45505</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -51824,7 +51824,7 @@
         <v>45870.34439814815</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -51886,7 +51886,7 @@
         <v>45614.34545138889</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -51943,7 +51943,7 @@
         <v>45832.3459375</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -52005,7 +52005,7 @@
         <v>45839</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -52062,7 +52062,7 @@
         <v>45832.34552083333</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -52124,7 +52124,7 @@
         <v>45874.69844907407</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -52186,7 +52186,7 @@
         <v>44832</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -52248,7 +52248,7 @@
         <v>45874.67746527777</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -52310,7 +52310,7 @@
         <v>45735.69842592593</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -52372,7 +52372,7 @@
         <v>45832.34524305556</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -52429,7 +52429,7 @@
         <v>45874.59496527778</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -52491,7 +52491,7 @@
         <v>45835.45686342593</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -52548,7 +52548,7 @@
         <v>45835.46334490741</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -52605,7 +52605,7 @@
         <v>45835.53166666667</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -52667,7 +52667,7 @@
         <v>45835.72046296296</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>45107</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -52781,7 +52781,7 @@
         <v>45835.40668981482</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -52843,7 +52843,7 @@
         <v>45835.4506712963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>45834.65662037037</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -52962,7 +52962,7 @@
         <v>45876.53188657408</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -53024,7 +53024,7 @@
         <v>45839.49082175926</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -53081,7 +53081,7 @@
         <v>45838.67800925926</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -53138,7 +53138,7 @@
         <v>45839.42864583333</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>45579.47052083333</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -53257,7 +53257,7 @@
         <v>45839.46915509259</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>45838.36532407408</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -53381,7 +53381,7 @@
         <v>45839.42810185185</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -53443,7 +53443,7 @@
         <v>45838</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -53500,7 +53500,7 @@
         <v>45839.57331018519</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -53562,7 +53562,7 @@
         <v>45839.42822916667</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -53624,7 +53624,7 @@
         <v>45838</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -53681,7 +53681,7 @@
         <v>45838.67887731481</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -53743,7 +53743,7 @@
         <v>45838.48996527777</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>45840.52225694444</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>45841.57427083333</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -53919,7 +53919,7 @@
         <v>45453.4444212963</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -53976,7 +53976,7 @@
         <v>45659.69822916666</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -54038,7 +54038,7 @@
         <v>45841.6571412037</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -54095,7 +54095,7 @@
         <v>45446.68947916666</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45842.38579861111</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -54214,7 +54214,7 @@
         <v>44475</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -54271,7 +54271,7 @@
         <v>45386</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -54328,7 +54328,7 @@
         <v>45258</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -54385,7 +54385,7 @@
         <v>45065.42894675926</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -54442,7 +54442,7 @@
         <v>45842.42608796297</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -54499,7 +54499,7 @@
         <v>45847.65703703704</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -54561,7 +54561,7 @@
         <v>45847.34474537037</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -54623,7 +54623,7 @@
         <v>45847.34528935186</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         <v>45888.6775</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -54747,7 +54747,7 @@
         <v>45491</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -54809,7 +54809,7 @@
         <v>45847.34597222223</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -54871,7 +54871,7 @@
         <v>45847.34565972222</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -54933,7 +54933,7 @@
         <v>45847.34515046296</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -54995,7 +54995,7 @@
         <v>45889.61517361111</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -55057,7 +55057,7 @@
         <v>45847.61513888889</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -55114,7 +55114,7 @@
         <v>45847.61548611111</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -55171,7 +55171,7 @@
         <v>45846.34454861111</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -55233,7 +55233,7 @@
         <v>45195</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -55295,7 +55295,7 @@
         <v>45195.94679398148</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -55357,7 +55357,7 @@
         <v>45195.94685185186</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -55419,7 +55419,7 @@
         <v>45848.49761574074</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -55476,7 +55476,7 @@
         <v>45848.65658564815</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -55538,7 +55538,7 @@
         <v>45258</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -55595,7 +55595,7 @@
         <v>45751.36490740741</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -55657,7 +55657,7 @@
         <v>45848.49774305556</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -55714,7 +55714,7 @@
         <v>44901</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -55776,7 +55776,7 @@
         <v>44901</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>45849.65663194445</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -55900,7 +55900,7 @@
         <v>45694.69826388889</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -55962,7 +55962,7 @@
         <v>45892.34423611111</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -56019,7 +56019,7 @@
         <v>45892.38591435185</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -56076,7 +56076,7 @@
         <v>45892.38657407407</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -56133,7 +56133,7 @@
         <v>45850.34434027778</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -56190,7 +56190,7 @@
         <v>45850.34450231482</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -56252,7 +56252,7 @@
         <v>44825</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -56314,7 +56314,7 @@
         <v>45892.44840277778</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -56371,7 +56371,7 @@
         <v>45741.63675925926</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -56433,7 +56433,7 @@
         <v>45852.53185185185</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -56495,7 +56495,7 @@
         <v>45892.34438657408</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -56552,7 +56552,7 @@
         <v>45892.38641203703</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -56609,7 +56609,7 @@
         <v>45852.53168981482</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -56671,7 +56671,7 @@
         <v>45892.38619212963</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>45892.44824074074</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -56785,7 +56785,7 @@
         <v>45896.52478009259</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -56842,7 +56842,7 @@
         <v>45855.61523148148</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -56904,7 +56904,7 @@
         <v>45854.65663194445</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -56966,7 +56966,7 @@
         <v>44888</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -57028,7 +57028,7 @@
         <v>45855.67899305555</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -57085,7 +57085,7 @@
         <v>45898.53193287037</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -57147,7 +57147,7 @@
         <v>45901.38578703703</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -57204,7 +57204,7 @@
         <v>45646.63605324074</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -57266,7 +57266,7 @@
         <v>45856.46931712963</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -57328,7 +57328,7 @@
         <v>45898.49012731481</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -57390,7 +57390,7 @@
         <v>45898.61502314815</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -57452,7 +57452,7 @@
         <v>45898.59295138889</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -57509,7 +57509,7 @@
         <v>45702.63572916666</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -57571,7 +57571,7 @@
         <v>45901.38572916666</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -57628,7 +57628,7 @@
         <v>45901.38584490741</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -57685,7 +57685,7 @@
         <v>45590</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -57742,7 +57742,7 @@
         <v>45758.36487268518</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45859.594375</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -57866,7 +57866,7 @@
         <v>45903.34555555556</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -57923,7 +57923,7 @@
         <v>44943.94802083333</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -57985,7 +57985,7 @@
         <v>45208</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -58042,7 +58042,7 @@
         <v>45590.40675925926</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
         <v>45279.94572916667</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -58166,7 +58166,7 @@
         <v>45860.30229166667</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -58223,7 +58223,7 @@
         <v>45722.44849537037</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -58285,7 +58285,7 @@
         <v>45730.42738425926</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -58347,7 +58347,7 @@
         <v>45902.34423611111</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -58409,7 +58409,7 @@
         <v>44519.94440972222</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -58471,7 +58471,7 @@
         <v>45154.95525462963</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -58533,7 +58533,7 @@
         <v>45621.57395833333</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -58595,7 +58595,7 @@
         <v>45581.55260416667</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -58652,7 +58652,7 @@
         <v>44774</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -58709,7 +58709,7 @@
         <v>45309.92524305556</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -58766,7 +58766,7 @@
         <v>45552.39113425926</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -58823,7 +58823,7 @@
         <v>45552.44096064815</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -58880,7 +58880,7 @@
         <v>45306</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -58937,7 +58937,7 @@
         <v>45904.60431712963</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -58994,7 +58994,7 @@
         <v>44894.79018518519</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -59051,7 +59051,7 @@
         <v>45635.57331018519</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -59113,7 +59113,7 @@
         <v>45441.33313657407</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -59170,7 +59170,7 @@
         <v>45197.94171296297</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -59232,7 +59232,7 @@
         <v>45735</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -59294,7 +59294,7 @@
         <v>45511</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -59356,7 +59356,7 @@
         <v>44405.92065972222</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -59413,7 +59413,7 @@
         <v>45482.94815972223</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -59475,7 +59475,7 @@
         <v>45096.93866898148</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -59537,7 +59537,7 @@
         <v>45656</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -59594,7 +59594,7 @@
         <v>45692.48993055556</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -59656,7 +59656,7 @@
         <v>45546</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -59713,7 +59713,7 @@
         <v>44942</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -59775,7 +59775,7 @@
         <v>45384</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -59832,7 +59832,7 @@
         <v>45391.95329861111</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -59894,7 +59894,7 @@
         <v>45215.94657407407</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -59956,7 +59956,7 @@
         <v>45692.49008101852</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -60018,7 +60018,7 @@
         <v>44900</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -60080,7 +60080,7 @@
         <v>45714.55064814815</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -60137,7 +60137,7 @@
         <v>44336</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -60194,7 +60194,7 @@
         <v>45636.38599537037</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -60256,7 +60256,7 @@
         <v>45098</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -60313,7 +60313,7 @@
         <v>45574.39081018518</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -60375,7 +60375,7 @@
         <v>45008.01408564814</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -60437,7 +60437,7 @@
         <v>44876</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -60499,7 +60499,7 @@
         <v>45751.34859953704</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -60561,7 +60561,7 @@
         <v>45751.34873842593</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -60623,7 +60623,7 @@
         <v>44655</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -60685,7 +60685,7 @@
         <v>45622.46910879629</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -60742,7 +60742,7 @@
         <v>44685</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -60804,7 +60804,7 @@
         <v>45033</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -60861,7 +60861,7 @@
         <v>44914</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -60918,7 +60918,7 @@
         <v>44993.94950231481</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -60980,7 +60980,7 @@
         <v>44993</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -61042,7 +61042,7 @@
         <v>44323</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -61104,7 +61104,7 @@
         <v>45695.51070601852</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -61166,7 +61166,7 @@
         <v>45111.92793981481</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -61228,7 +61228,7 @@
         <v>45467.96207175926</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -61290,7 +61290,7 @@
         <v>45149.95241898148</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -61352,7 +61352,7 @@
         <v>44641</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -61414,7 +61414,7 @@
         <v>44641</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -61476,7 +61476,7 @@
         <v>45331.92746527777</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -61533,7 +61533,7 @@
         <v>45329.95806712963</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -61595,7 +61595,7 @@
         <v>45681.5315625</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -61657,7 +61657,7 @@
         <v>45681.6050925926</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -61714,7 +61714,7 @@
         <v>45488.94747685185</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -61776,7 +61776,7 @@
         <v>44656.94708333333</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -61838,7 +61838,7 @@
         <v>45604.63575231482</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -61900,7 +61900,7 @@
         <v>45712.61502314815</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -61962,7 +61962,7 @@
         <v>45673.66358796296</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -62019,7 +62019,7 @@
         <v>45474.50608796296</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -62076,7 +62076,7 @@
         <v>45244.96774305555</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -62138,7 +62138,7 @@
         <v>45098</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -62195,7 +62195,7 @@
         <v>44904.94824074074</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -62257,7 +62257,7 @@
         <v>45645.55665509259</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -62314,7 +62314,7 @@
         <v>45453.42041666667</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -62371,7 +62371,7 @@
         <v>44966.95328703704</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -62433,7 +62433,7 @@
         <v>45175</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -62495,7 +62495,7 @@
         <v>45215</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -62552,7 +62552,7 @@
         <v>45540.38586805556</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -62614,7 +62614,7 @@
         <v>45741.63659722222</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -62676,7 +62676,7 @@
         <v>44805.94592592592</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -62738,7 +62738,7 @@
         <v>44866</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -62800,7 +62800,7 @@
         <v>45091</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -62862,7 +62862,7 @@
         <v>45639.55240740741</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -62924,7 +62924,7 @@
         <v>44384</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -62981,7 +62981,7 @@
         <v>44944</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -63038,7 +63038,7 @@
         <v>44839</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -63095,7 +63095,7 @@
         <v>45726.3860300926</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -63152,7 +63152,7 @@
         <v>45139.94681712963</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -63214,7 +63214,7 @@
         <v>44362</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -63271,7 +63271,7 @@
         <v>45448.94600694445</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -63333,7 +63333,7 @@
         <v>45158.94231481481</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -63395,7 +63395,7 @@
         <v>45075.945</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -63457,7 +63457,7 @@
         <v>45149.95372685185</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -63519,7 +63519,7 @@
         <v>45706.34450231482</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -63581,7 +63581,7 @@
         <v>45425.96275462963</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -63643,7 +63643,7 @@
         <v>44820</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -63705,7 +63705,7 @@
         <v>45540.34428240741</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -63767,7 +63767,7 @@
         <v>45148</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -63824,7 +63824,7 @@
         <v>44844.95368055555</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -63886,7 +63886,7 @@
         <v>44889.95015046297</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -63948,7 +63948,7 @@
         <v>45112</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -64010,7 +64010,7 @@
         <v>45356.03784722222</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -64072,7 +64072,7 @@
         <v>45086</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -64134,7 +64134,7 @@
         <v>45568.51075231482</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -64196,7 +64196,7 @@
         <v>45342</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -64258,7 +64258,7 @@
         <v>45342.9462037037</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -64320,7 +64320,7 @@
         <v>45071</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -64377,7 +64377,7 @@
         <v>45182</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -64439,7 +64439,7 @@
         <v>45726.38575231482</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -64496,7 +64496,7 @@
         <v>45653.44836805556</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -64558,7 +64558,7 @@
         <v>45453.95538194444</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -64620,7 +64620,7 @@
         <v>45048.94340277778</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -64682,7 +64682,7 @@
         <v>45645.55672453704</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -64739,7 +64739,7 @@
         <v>45636.57329861111</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -64801,7 +64801,7 @@
         <v>45716</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -64863,7 +64863,7 @@
         <v>45007</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -64920,7 +64920,7 @@
         <v>45222</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -64982,7 +64982,7 @@
         <v>45009</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -65039,7 +65039,7 @@
         <v>45133</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -65101,7 +65101,7 @@
         <v>45257.92826388889</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -65158,7 +65158,7 @@
         <v>45190</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -65220,7 +65220,7 @@
         <v>45009.0897337963</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -65282,7 +65282,7 @@
         <v>44917</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -65339,7 +65339,7 @@
         <v>45715.61523148148</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -65401,7 +65401,7 @@
         <v>45616.5108912037</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -65463,7 +65463,7 @@
         <v>45063</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -65520,7 +65520,7 @@
         <v>45733.61497685185</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -65582,7 +65582,7 @@
         <v>45733.61554398148</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -65644,7 +65644,7 @@
         <v>44956.93924768519</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -65706,7 +65706,7 @@
         <v>45695.45868055556</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -65763,7 +65763,7 @@
         <v>45323</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -65820,7 +65820,7 @@
         <v>45614.63869212963</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -65882,7 +65882,7 @@
         <v>45702.63604166666</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -65944,7 +65944,7 @@
         <v>45505</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -66006,7 +66006,7 @@
         <v>45769.65659722222</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -66068,7 +66068,7 @@
         <v>44530.94694444445</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -66130,7 +66130,7 @@
         <v>45156</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -66192,7 +66192,7 @@
         <v>44231</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -66249,7 +66249,7 @@
         <v>45379.93637731481</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -66311,7 +66311,7 @@
         <v>45622.44774305556</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -66368,7 +66368,7 @@
         <v>45671.48989583334</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -66430,7 +66430,7 @@
         <v>45425.96494212963</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -66492,7 +66492,7 @@
         <v>45688.67542824074</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -66554,7 +66554,7 @@
         <v>45092</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -66611,7 +66611,7 @@
         <v>45183.95563657407</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -66673,7 +66673,7 @@
         <v>45638</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -66730,7 +66730,7 @@
         <v>45374</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -66787,7 +66787,7 @@
         <v>45266.95082175926</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -66849,7 +66849,7 @@
         <v>45426</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -66906,7 +66906,7 @@
         <v>44918</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -66968,7 +66968,7 @@
         <v>44629</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -67025,7 +67025,7 @@
         <v>45044</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -67087,7 +67087,7 @@
         <v>44517.58137731482</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -67144,7 +67144,7 @@
         <v>45112</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -67206,7 +67206,7 @@
         <v>45180</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -67268,7 +67268,7 @@
         <v>45614.34541666666</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -67325,7 +67325,7 @@
         <v>45469.94667824074</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -67387,7 +67387,7 @@
         <v>45119</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -67444,7 +67444,7 @@
         <v>45180.95927083334</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -67506,7 +67506,7 @@
         <v>45769.67767361111</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -67568,7 +67568,7 @@
         <v>45665.65684027778</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -67630,7 +67630,7 @@
         <v>45224</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -67687,7 +67687,7 @@
         <v>45103</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -67744,7 +67744,7 @@
         <v>44174</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -67806,7 +67806,7 @@
         <v>44995.98341435185</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -67868,7 +67868,7 @@
         <v>45093.92207175926</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -67925,7 +67925,7 @@
         <v>44644</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -67987,7 +67987,7 @@
         <v>45182</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -68049,7 +68049,7 @@
         <v>45469.94876157407</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -68111,7 +68111,7 @@
         <v>45558.63575231482</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -68173,7 +68173,7 @@
         <v>45679.40362268518</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -68230,7 +68230,7 @@
         <v>44929</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -68287,7 +68287,7 @@
         <v>45241.95724537037</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -68349,7 +68349,7 @@
         <v>45092</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -68406,7 +68406,7 @@
         <v>45367.67256944445</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -68463,7 +68463,7 @@
         <v>45314</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -68520,7 +68520,7 @@
         <v>45534.63537037037</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -68582,7 +68582,7 @@
         <v>45425.96263888889</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -68644,7 +68644,7 @@
         <v>44614</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -68701,7 +68701,7 @@
         <v>44231</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -68758,7 +68758,7 @@
         <v>45601.40686342592</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -68820,7 +68820,7 @@
         <v>44914</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -68882,7 +68882,7 @@
         <v>45645.36743055555</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -68939,7 +68939,7 @@
         <v>45324</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -68996,7 +68996,7 @@
         <v>45714.60649305556</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -69053,7 +69053,7 @@
         <v>45260</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -69110,7 +69110,7 @@
         <v>45735.53177083333</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -69172,7 +69172,7 @@
         <v>44855</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -69234,7 +69234,7 @@
         <v>45280</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -69291,7 +69291,7 @@
         <v>44903</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -69348,7 +69348,7 @@
         <v>45404.99792824074</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -69430,7 +69430,7 @@
         <v>45257</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -69492,7 +69492,7 @@
         <v>45630.7862037037</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -69549,7 +69549,7 @@
         <v>44879</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -69611,7 +69611,7 @@
         <v>44336</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -69668,7 +69668,7 @@
         <v>45357.05300925926</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -69730,7 +69730,7 @@
         <v>44356</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -69787,7 +69787,7 @@
         <v>45723.51079861111</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -69849,7 +69849,7 @@
         <v>44813</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -69911,7 +69911,7 @@
         <v>45625.51068287037</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -69973,7 +69973,7 @@
         <v>45457.96372685185</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -70035,7 +70035,7 @@
         <v>45170</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -70097,7 +70097,7 @@
         <v>44932.93927083333</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -70159,7 +70159,7 @@
         <v>44802.94811342593</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -70221,7 +70221,7 @@
         <v>44897</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -70283,7 +70283,7 @@
         <v>45176</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -70340,7 +70340,7 @@
         <v>45204.94399305555</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -70402,7 +70402,7 @@
         <v>44879.95768518518</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -70464,7 +70464,7 @@
         <v>45327.94443287037</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -70526,7 +70526,7 @@
         <v>45257</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -70583,7 +70583,7 @@
         <v>45072.92737268518</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -70640,7 +70640,7 @@
         <v>45075.94506944445</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -70702,7 +70702,7 @@
         <v>45761.67744212963</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -70764,7 +70764,7 @@
         <v>44349.91978009259</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -70821,7 +70821,7 @@
         <v>45420</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -70883,7 +70883,7 @@
         <v>45618.46921296296</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -70945,7 +70945,7 @@
         <v>45516.94732638889</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -71007,7 +71007,7 @@
         <v>45197.94152777778</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -71069,7 +71069,7 @@
         <v>45734.45268518518</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -71126,7 +71126,7 @@
         <v>45253</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -71183,7 +71183,7 @@
         <v>44286</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -71240,7 +71240,7 @@
         <v>45053.94305555556</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -71302,7 +71302,7 @@
         <v>45341</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -71359,7 +71359,7 @@
         <v>44153</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -71416,7 +71416,7 @@
         <v>45210</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -71473,7 +71473,7 @@
         <v>45559.67759259259</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -71535,7 +71535,7 @@
         <v>45664.55241898148</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -71597,7 +71597,7 @@
         <v>45601.59518518519</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -71659,7 +71659,7 @@
         <v>45254.96516203704</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -71721,7 +71721,7 @@
         <v>45254.96402777778</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -71783,7 +71783,7 @@
         <v>45596.61553240741</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -71845,7 +71845,7 @@
         <v>45622.46200231482</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -71902,7 +71902,7 @@
         <v>45314.92758101852</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -71959,7 +71959,7 @@
         <v>45638</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -72016,7 +72016,7 @@
         <v>45436.94628472222</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -72078,7 +72078,7 @@
         <v>45714</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -72135,7 +72135,7 @@
         <v>45615.50034722222</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -72192,7 +72192,7 @@
         <v>44635</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -72254,7 +72254,7 @@
         <v>45615.47091435185</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -72311,7 +72311,7 @@
         <v>45638.34431712963</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -72373,7 +72373,7 @@
         <v>45700.57324074074</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -72435,7 +72435,7 @@
         <v>45053.94313657407</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -72497,7 +72497,7 @@
         <v>45442.96296296296</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -72559,7 +72559,7 @@
         <v>45000</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -72621,7 +72621,7 @@
         <v>45000</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -72683,7 +72683,7 @@
         <v>45351.98496527778</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -72745,7 +72745,7 @@
         <v>45078</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -72802,7 +72802,7 @@
         <v>45555.38509259259</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -72859,7 +72859,7 @@
         <v>45436.94613425926</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -72921,7 +72921,7 @@
         <v>45737.63574074074</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -72983,7 +72983,7 @@
         <v>45737.69822916666</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -73045,7 +73045,7 @@
         <v>45344</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -73102,7 +73102,7 @@
         <v>45344.92865740741</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -73159,7 +73159,7 @@
         <v>45344.92873842592</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -73216,7 +73216,7 @@
         <v>45208</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -73273,7 +73273,7 @@
         <v>45223</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -73330,7 +73330,7 @@
         <v>45603.67850694444</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -73387,7 +73387,7 @@
         <v>45260.92561342593</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -73444,7 +73444,7 @@
         <v>45128</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -73506,7 +73506,7 @@
         <v>45715.59405092592</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -73568,7 +73568,7 @@
         <v>45616.34479166667</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -73630,7 +73630,7 @@
         <v>44880.95741898148</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -73692,7 +73692,7 @@
         <v>45401</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -73754,7 +73754,7 @@
         <v>45401</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -73816,7 +73816,7 @@
         <v>45453.95016203704</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -73878,7 +73878,7 @@
         <v>45327.94459490741</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -73940,7 +73940,7 @@
         <v>45112.94303240741</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -74002,7 +74002,7 @@
         <v>45561.34663194444</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -74064,7 +74064,7 @@
         <v>44628</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -74121,7 +74121,7 @@
         <v>44994.94296296296</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -74183,7 +74183,7 @@
         <v>45034</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -74240,7 +74240,7 @@
         <v>45545.64957175926</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -74297,7 +74297,7 @@
         <v>44375</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -74354,7 +74354,7 @@
         <v>45068</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -74416,7 +74416,7 @@
         <v>45392</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -74473,7 +74473,7 @@
         <v>45180.95907407408</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -74535,7 +74535,7 @@
         <v>45145</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -74597,7 +74597,7 @@
         <v>45734.4633912037</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -74654,7 +74654,7 @@
         <v>44299</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -74711,7 +74711,7 @@
         <v>45322</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>

--- a/Översikt RAGUNDA.xlsx
+++ b/Översikt RAGUNDA.xlsx
@@ -567,7 +567,7 @@
         <v>45622</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>45376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>45622</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>45560.34460648148</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>45673</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44917</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45804.67787037037</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>45590.42736111111</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45838.67753472222</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44504</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44644</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>45622</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>45560.34532407407</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45104</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45113</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>45579.53179398148</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44644.93650462963</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44473</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>44813</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45367.04916666666</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>45639.55269675926</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45622</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>45790.57334490741</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>44088</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>45482.63819444444</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>45182</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45779.49012731481</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>45803.59474537037</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>44776</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>45358.99375</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45839.42482638889</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>45790.57349537037</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44805</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>44645.99859953704</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>45327</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>44888</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>45779.57335648148</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>45560.34484953704</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>45378</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45685.36501157407</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>45799.63574074074</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>45799.34461805555</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>45510</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45174</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>45832.34461805555</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>44504</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>45121</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>45769.53180555555</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>45190.96092592592</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44133</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>45320</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>45827.5110300926</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>45120</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>45113</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>45723.40688657408</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>45622</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44133</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>44662</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>44438</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>45176</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>45810.55061342593</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45769.67740740741</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>45121</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>44336</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>45405.57392361111</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>44994</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44915</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>45475.94796296296</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>45786.61517361111</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>45435.54734953704</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>45155</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>44111</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44209</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>45471.94783564815</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>44875</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>45832.34564814815</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>45769.67778935185</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>44994</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>45468.97528935185</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>45457</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>45238</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>45893.38584490741</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>44932</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45846.41361111111</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>45495.56244212963</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>45595.44886574074</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>45867.63619212963</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>45728.65684027778</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>44656</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45002.94356481481</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>45446.95087962963</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>45195</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>45551.46912037037</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>45244</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>45832.34578703704</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>45425.96472222222</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>45182</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>45471.94623842592</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>44911</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>45400.94002314815</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>45893.38599537037</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>45674.67744212963</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>45545.45748842593</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>45744.61550925926</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>44245</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>44334.62565972222</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>44696</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>44662</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>44334</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>44334</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>44911</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>45782.44871527778</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45384</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45378</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>45455.96195601852</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45610.34415509259</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>45805.34415509259</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>45510</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>44113</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>45404</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>44677</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>45491</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>45896.63618055556</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>45491</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>45786.61534722222</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>45187</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44855</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>44369.92025462963</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>45071</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>45733</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>45397.95748842593</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45779.57392361111</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>45751.34650462963</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>45093</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>44855</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>45265</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
         <v>45516.94723379629</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44902</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>44111</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>45631</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>45436.94686342592</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>45804.34474537037</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>45491.94715277778</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>45209</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14833,7 +14833,7 @@
         <v>45152</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>44971</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>45632.69822916666</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>45789.36503472222</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>44788</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         <v>44875</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>45425.96285879629</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>45847.61498842593</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>45838</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>45903.345625</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>45691.44769675926</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>44676</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>44855</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>45321</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>45378</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>45779.57350694444</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>44865</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>45551.65726851852</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>44852</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>45121</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>45190</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45188</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45800.42782407408</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>44680</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>45171</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>45372.95680555556</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17218,7 +17218,7 @@
         <v>45205</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>45394</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17395,7 +17395,7 @@
         <v>45191</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>45241</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>45835.344375</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>45089</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45583.49642361111</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>45722.61543981481</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45526.56393518519</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>44855</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>45631</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>45769.65692129629</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>45468.97495370371</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45238</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>44993</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>45852.63597222222</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45854.61494212963</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>45153</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45723.57329861111</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>44826.94976851852</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>44462</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19131,7 +19131,7 @@
         <v>44166</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>44319</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>44705</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>44741</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>44774.94347222222</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>44741</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>45751.34795138889</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45636.3863425926</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>45468.97461805555</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>45301</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20020,7 +20020,7 @@
         <v>45301</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>45771.3859837963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>45779.48993055556</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>45252</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         <v>45149</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>45033</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>45754.51064814815</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>45455.96184027778</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>45266</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -20826,7 +20826,7 @@
         <v>44832</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>45341</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>45089</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21096,7 +21096,7 @@
         <v>45457.9640625</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>45597.34461805555</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>45153</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>45205</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45183</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -21549,7 +21549,7 @@
         <v>44991</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -21639,7 +21639,7 @@
         <v>45813.49061342593</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>44860</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45646.34438657408</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>45769.65736111111</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45827.57371527778</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45775.67769675926</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>45785.36525462963</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>45771.36548611111</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>45838.38627314815</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>45128</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>45436.94644675926</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -22652,7 +22652,7 @@
         <v>45153</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>45154</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>45147</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>44119</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>45722.65670138889</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>45468</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>45510</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>45487.92863425926</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45315</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>45600.55265046296</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>45491.95008101852</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>45847.36528935185</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -23724,7 +23724,7 @@
         <v>44369</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>45897.531875</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -23899,7 +23899,7 @@
         <v>45206</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45044</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>45208</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>44141</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>44157</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>44195</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>44214</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44168</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44517</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44846</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>44817</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>44880.95712962963</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>44880.95719907407</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>44855.94125</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>44425</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>44447.92069444444</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -24940,7 +24940,7 @@
         <v>44490.94109953703</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>44519.94534722222</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>44349</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>44210</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>44243</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>44280</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>44280</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>44385.33887731482</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>44292</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>44705</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>44518.94394675926</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>44362</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>44426.94077546296</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -25696,7 +25696,7 @@
         <v>44399</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>44818.94929398148</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>44846.9522337963</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>44860</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>44111</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>44774.94414351852</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>44425</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>44663</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>44823.48666666666</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>44874.95553240741</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>44784.9408912037</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         <v>44837</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -26425,7 +26425,7 @@
         <v>44714</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>44670</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -26539,7 +26539,7 @@
         <v>44858</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -26601,7 +26601,7 @@
         <v>44704.94234953704</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -26663,7 +26663,7 @@
         <v>44855</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>44175</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>44194</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -26844,7 +26844,7 @@
         <v>44239</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>44273.92081018518</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>44132</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>44741</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>44495.93966435185</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -27144,7 +27144,7 @@
         <v>44126</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>44443</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         <v>44530</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -27315,7 +27315,7 @@
         <v>44823.94993055556</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>44125.94493055555</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>44836.9491087963</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>44833.95405092592</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>44579.68604166667</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>44854</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -27682,7 +27682,7 @@
         <v>44859.95710648148</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>44883</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>44728.94398148148</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>44287</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>44308</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>44308</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>44629.56258101852</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>44452</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -28153,7 +28153,7 @@
         <v>44281</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -28215,7 +28215,7 @@
         <v>44421.97322916667</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>44259</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>44351</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>44832.95435185185</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>44586</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>44434.94559027778</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>44867</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>44876.95104166667</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -28701,7 +28701,7 @@
         <v>44690</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>44111</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>44476</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>44500.93887731482</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -28944,7 +28944,7 @@
         <v>44601</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>44714.94162037037</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>44357</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>44477.48994212963</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>44228</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>44515.93767361111</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>44696.93986111111</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -29358,7 +29358,7 @@
         <v>44783</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -29420,7 +29420,7 @@
         <v>44802</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>44864.94835648148</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>44308</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -29601,7 +29601,7 @@
         <v>44853.9499537037</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -29663,7 +29663,7 @@
         <v>44482.92271990741</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -29720,7 +29720,7 @@
         <v>44512</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>44662</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>44704</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         <v>44685</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>44349.92013888889</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -30010,7 +30010,7 @@
         <v>44824.94635416667</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>44308</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>44615</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>44671</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>44851.95488425926</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -30305,7 +30305,7 @@
         <v>44379</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -30362,7 +30362,7 @@
         <v>44704.94229166667</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>44861</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -30486,7 +30486,7 @@
         <v>44729.94136574074</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>44777.95504629629</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -30610,7 +30610,7 @@
         <v>44855.9471875</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>44349.91995370371</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>44099</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>44138</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>44418.9369212963</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>44621</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>44650</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>44140</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>44615</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>44788</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>44853</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>44799.94394675926</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>44574</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>44140</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>44883.94918981481</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -31505,7 +31505,7 @@
         <v>44124</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -31562,7 +31562,7 @@
         <v>44599.98685185185</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -31624,7 +31624,7 @@
         <v>44431</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>44434.94517361111</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>44815</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>44578.92284722222</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>44489.94711805556</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -31919,7 +31919,7 @@
         <v>44823</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>44727</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>44322</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>44858</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>44425</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>44846</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -32281,7 +32281,7 @@
         <v>44704.9422337963</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>44818</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
         <v>44495</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>44833.9519212963</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>44781</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -32586,7 +32586,7 @@
         <v>44854.95390046296</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>44889</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>44595</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>44831.94846064815</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>44831.9485300926</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -32891,7 +32891,7 @@
         <v>44784.94157407407</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>44361.55445601852</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>44496</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -33067,7 +33067,7 @@
         <v>44734.94193287037</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>44704.94217592593</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>44728.94392361111</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -33253,7 +33253,7 @@
         <v>44832.95300925926</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -33315,7 +33315,7 @@
         <v>44830</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -33377,7 +33377,7 @@
         <v>45075.945</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         <v>45280.92645833334</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -33496,7 +33496,7 @@
         <v>44356</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>44356.91935185185</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>44802.94811342593</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -33672,7 +33672,7 @@
         <v>45007</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -33729,7 +33729,7 @@
         <v>45042</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>45379.93637731481</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -33848,7 +33848,7 @@
         <v>45401</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -33910,7 +33910,7 @@
         <v>45401</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>44805</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -34034,7 +34034,7 @@
         <v>44315</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>45374</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>44861</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -34215,7 +34215,7 @@
         <v>45723.67777777778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>44336</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -34334,7 +34334,7 @@
         <v>44463.94077546296</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>45743.36</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>44323</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>45253</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45208</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>44813</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -34696,7 +34696,7 @@
         <v>44832</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -34758,7 +34758,7 @@
         <v>44812.94709490741</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         <v>44805.94592592592</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>45741.63675925926</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>45267</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -35006,7 +35006,7 @@
         <v>45769.51087962963</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         <v>45384</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -35125,7 +35125,7 @@
         <v>45358.95818287037</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -35182,7 +35182,7 @@
         <v>45086.94010416666</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -35244,7 +35244,7 @@
         <v>45119</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>45182</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>45645.36743055555</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>45702.63572916666</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>45769.67767361111</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>45356.03784722222</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>45358.95813657407</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -35663,7 +35663,7 @@
         <v>44953</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -35725,7 +35725,7 @@
         <v>44977.98660879629</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
         <v>45391.95329861111</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>45098</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>45695.44724537037</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45645.36740740741</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45636.3864699074</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45426</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45392</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>45392.92903935185</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>44972.94140046297</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>45254.96516203704</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>45776.40311342593</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>45574.57967592592</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44900.95700231481</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -36553,7 +36553,7 @@
         <v>45776.59422453704</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -36615,7 +36615,7 @@
         <v>45776.50651620371</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>45761.67744212963</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>45776.51130787037</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>45093.92207175926</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>45063</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>45386.68003472222</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>44894</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>45223</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>45344</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>45769.65659722222</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -37205,7 +37205,7 @@
         <v>45769.67790509259</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>44903</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -37324,7 +37324,7 @@
         <v>45448.94600694445</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>44914</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -37448,7 +37448,7 @@
         <v>45782.36506944444</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>45782.51099537037</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -37572,7 +37572,7 @@
         <v>45782.51109953703</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>45782.67758101852</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -37696,7 +37696,7 @@
         <v>44494.93930555556</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>45782.55287037037</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -37820,7 +37820,7 @@
         <v>45779.34417824074</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45779.4281712963</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>45782.36494212963</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -38006,7 +38006,7 @@
         <v>45779.49025462963</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -38068,7 +38068,7 @@
         <v>45448.94520833333</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>44879.95768518518</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>45393.94459490741</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>45367.67256944445</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45751.34859953704</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>45187</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>44993.94950231481</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -38492,7 +38492,7 @@
         <v>44993</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>44958.94298611111</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>45609.34412037037</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>44866</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -38740,7 +38740,7 @@
         <v>45559.67745370371</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -38802,7 +38802,7 @@
         <v>45259</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>44995.98341435185</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>44995.98644675926</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -38983,7 +38983,7 @@
         <v>45572.60363425926</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -39040,7 +39040,7 @@
         <v>45314</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>45154.95525462963</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>45631.46665509259</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>45393.94431712963</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -39278,7 +39278,7 @@
         <v>45257</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -39335,7 +39335,7 @@
         <v>45040.94277777777</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -39397,7 +39397,7 @@
         <v>45786.51077546296</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -39459,7 +39459,7 @@
         <v>44944</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -39516,7 +39516,7 @@
         <v>44922</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -39573,7 +39573,7 @@
         <v>44517.58137731482</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>45516.94732638889</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -39692,7 +39692,7 @@
         <v>45006</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45158.94231481481</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -39816,7 +39816,7 @@
         <v>45611.65679398148</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -39878,7 +39878,7 @@
         <v>45306</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -39935,7 +39935,7 @@
         <v>45279.94572916667</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -39997,7 +39997,7 @@
         <v>45574.51185185185</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         <v>45049</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -40121,7 +40121,7 @@
         <v>45453.95016203704</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45790.40670138889</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -40245,7 +40245,7 @@
         <v>45446.68947916666</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -40302,7 +40302,7 @@
         <v>45456.96569444444</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -40364,7 +40364,7 @@
         <v>45611.5953125</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -40421,7 +40421,7 @@
         <v>45608.6078587963</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -40483,7 +40483,7 @@
         <v>45638.34431712963</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>44475</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -40602,7 +40602,7 @@
         <v>45656</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>45327.94459490741</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -40721,7 +40721,7 @@
         <v>45315.9492824074</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -40783,7 +40783,7 @@
         <v>44336</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -40840,7 +40840,7 @@
         <v>45204.94399305555</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>45574.51087962963</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -40964,7 +40964,7 @@
         <v>45574.51090277778</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>45211.95134259259</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>45454.95960648148</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -41150,7 +41150,7 @@
         <v>45384</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -41207,7 +41207,7 @@
         <v>45792.34527777778</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -41269,7 +41269,7 @@
         <v>45309.92524305556</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -41326,7 +41326,7 @@
         <v>45139.94681712963</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -41388,7 +41388,7 @@
         <v>45453.95538194444</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>45629.36513888889</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -41507,7 +41507,7 @@
         <v>45792.71905092592</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -41569,7 +41569,7 @@
         <v>45792.49023148148</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -41631,7 +41631,7 @@
         <v>45545.64957175926</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>45714.60649305556</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>45412.02506944445</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>45792.63584490741</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>45792.34606481482</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -41931,7 +41931,7 @@
         <v>45791.53238425926</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -41988,7 +41988,7 @@
         <v>45243</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>45635.47243055556</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>45611</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>45275.95060185185</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -42231,7 +42231,7 @@
         <v>45469.94876157407</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -42293,7 +42293,7 @@
         <v>45694.69826388889</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -42355,7 +42355,7 @@
         <v>45436.94636574074</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -42417,7 +42417,7 @@
         <v>45762.39876157408</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -42494,7 +42494,7 @@
         <v>44402.42243055555</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -42551,7 +42551,7 @@
         <v>45769.51075231482</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -42613,7 +42613,7 @@
         <v>45793</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -42670,7 +42670,7 @@
         <v>45009.0897337963</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>45191</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -42794,7 +42794,7 @@
         <v>45796</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -42851,7 +42851,7 @@
         <v>45796</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -42908,7 +42908,7 @@
         <v>45216.92424768519</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -42965,7 +42965,7 @@
         <v>44628</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -43022,7 +43022,7 @@
         <v>45793.61523148148</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -43084,7 +43084,7 @@
         <v>45182</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>44979</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>44980.93865740741</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -43265,7 +43265,7 @@
         <v>44519.94440972222</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>45796</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>45441</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>45341.95381944445</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -43503,7 +43503,7 @@
         <v>45439.92752314815</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>45511</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45639.55240740741</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45729.51074074074</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>45426</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>45266</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -43860,7 +43860,7 @@
         <v>45545.49078703704</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>45426</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45726.38575231482</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45737.63574074074</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>45033</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45614.34541666666</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45797.63627314815</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>45800.63619212963</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>45635.57331018519</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>44776</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>44656</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45372.95762731481</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -44579,7 +44579,7 @@
         <v>45799.34421296296</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45323</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         <v>45190</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -44760,7 +44760,7 @@
         <v>44897</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>45800</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>44911.93846064815</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>44743</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45603.67850694444</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45800.42743055556</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45800.44822916666</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -45179,7 +45179,7 @@
         <v>45800.44862268519</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>45653.44836805556</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -45303,7 +45303,7 @@
         <v>45601.5315625</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45638.63600694444</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>44644</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -45489,7 +45489,7 @@
         <v>45420</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -45551,7 +45551,7 @@
         <v>45803.5946875</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -45608,7 +45608,7 @@
         <v>45803.61552083334</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -45665,7 +45665,7 @@
         <v>45803.61557870371</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -45722,7 +45722,7 @@
         <v>45804.59487268519</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -45784,7 +45784,7 @@
         <v>45804.42642361111</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -45841,7 +45841,7 @@
         <v>45646.63605324074</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -45903,7 +45903,7 @@
         <v>45488.94747685185</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45344</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>45063</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45645.55665509259</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45638</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45803.59417824074</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45692.51069444444</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -46312,7 +46312,7 @@
         <v>45692.57326388889</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -46374,7 +46374,7 @@
         <v>45540.38564814815</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -46436,7 +46436,7 @@
         <v>45050.94020833333</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -46498,7 +46498,7 @@
         <v>45804.65672453704</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>45425.96239583333</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -46622,7 +46622,7 @@
         <v>45590.40675925926</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -46684,7 +46684,7 @@
         <v>45574.39081018518</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -46746,7 +46746,7 @@
         <v>45805.61495370371</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>45734.4633912037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>45552.44096064815</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -46922,7 +46922,7 @@
         <v>45579.47052083333</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -46979,7 +46979,7 @@
         <v>44917</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -47041,7 +47041,7 @@
         <v>45656.64223379629</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -47098,7 +47098,7 @@
         <v>44993.94958333333</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -47160,7 +47160,7 @@
         <v>44614</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -47217,7 +47217,7 @@
         <v>45716</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -47279,7 +47279,7 @@
         <v>45716.61487268518</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -47341,7 +47341,7 @@
         <v>45056</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -47398,7 +47398,7 @@
         <v>45056</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -47455,7 +47455,7 @@
         <v>45797.40800925926</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -47512,7 +47512,7 @@
         <v>45805.46613425926</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -47569,7 +47569,7 @@
         <v>44130.9416550926</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -47631,7 +47631,7 @@
         <v>45722.48982638889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>44601</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -47745,7 +47745,7 @@
         <v>45211.95061342593</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45453.42041666667</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45615.47091435185</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45667.57342592593</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -47983,7 +47983,7 @@
         <v>45667.57347222222</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -48045,7 +48045,7 @@
         <v>45805.57390046296</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -48107,7 +48107,7 @@
         <v>45672.44898148148</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -48169,7 +48169,7 @@
         <v>44655</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -48231,7 +48231,7 @@
         <v>44900</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -48293,7 +48293,7 @@
         <v>45566.68125</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>45404.99792824074</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -48432,7 +48432,7 @@
         <v>44587.92149305555</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -48489,7 +48489,7 @@
         <v>44550.92168981482</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -48546,7 +48546,7 @@
         <v>44943.94802083333</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -48608,7 +48608,7 @@
         <v>44903</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -48670,7 +48670,7 @@
         <v>45195</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -48732,7 +48732,7 @@
         <v>45195.94679398148</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>45195.94685185186</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
         <v>44587.92144675926</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -48913,7 +48913,7 @@
         <v>45351.98532407408</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -48975,7 +48975,7 @@
         <v>44614</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -49032,7 +49032,7 @@
         <v>45342</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>45692.49008101852</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>45342.9462037037</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -49218,7 +49218,7 @@
         <v>44113</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -49280,7 +49280,7 @@
         <v>45187</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -49337,7 +49337,7 @@
         <v>45616.34479166667</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -49399,7 +49399,7 @@
         <v>45678.67761574074</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -49461,7 +49461,7 @@
         <v>45180</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -49523,7 +49523,7 @@
         <v>45180.95927083334</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -49585,7 +49585,7 @@
         <v>44991</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -49647,7 +49647,7 @@
         <v>45604.4190625</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -49704,7 +49704,7 @@
         <v>45810.36495370371</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -49766,7 +49766,7 @@
         <v>45230.96376157407</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -49828,7 +49828,7 @@
         <v>45428.00471064815</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -49890,7 +49890,7 @@
         <v>44153</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>45028</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>45148</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -50061,7 +50061,7 @@
         <v>44684.94032407407</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -50123,7 +50123,7 @@
         <v>45138.94925925926</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>45636.38599537037</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -50247,7 +50247,7 @@
         <v>45195.94672453704</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -50309,7 +50309,7 @@
         <v>45197.94171296297</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>45112.94303240741</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -50433,7 +50433,7 @@
         <v>45112.94310185185</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -50495,7 +50495,7 @@
         <v>45769.67802083334</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         <v>45813.42790509259</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -50619,7 +50619,7 @@
         <v>45505</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -50681,7 +50681,7 @@
         <v>45621.57395833333</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -50743,7 +50743,7 @@
         <v>44886</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -50805,7 +50805,7 @@
         <v>45574.61184027778</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -50862,7 +50862,7 @@
         <v>45574.62297453704</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -50919,7 +50919,7 @@
         <v>45554.61583333334</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -50976,7 +50976,7 @@
         <v>45574.63355324074</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -51033,7 +51033,7 @@
         <v>45764</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -51090,7 +51090,7 @@
         <v>44614</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -51147,7 +51147,7 @@
         <v>44656.94708333333</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -51209,7 +51209,7 @@
         <v>45698.59409722222</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -51271,7 +51271,7 @@
         <v>45180.95907407408</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -51333,7 +51333,7 @@
         <v>45818.46898148148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -51390,7 +51390,7 @@
         <v>45442.96296296296</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>45208</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>45098</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -51566,7 +51566,7 @@
         <v>45555.38509259259</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>45819.6359375</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>45253</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -51742,7 +51742,7 @@
         <v>45702.63604166666</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -51804,7 +51804,7 @@
         <v>45258</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>45257</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>45772.6565625</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -51985,7 +51985,7 @@
         <v>45821.34513888889</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>44901</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -52109,7 +52109,7 @@
         <v>44901</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -52171,7 +52171,7 @@
         <v>45145.95326388889</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -52233,7 +52233,7 @@
         <v>44774</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -52290,7 +52290,7 @@
         <v>45215.94657407407</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -52352,7 +52352,7 @@
         <v>45825.57675925926</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>45825.58252314815</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45595.42738425926</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>44671</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>44820</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -52647,7 +52647,7 @@
         <v>45622.47435185185</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>45429</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -52761,7 +52761,7 @@
         <v>45825.56762731481</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -52818,7 +52818,7 @@
         <v>45826.65759259259</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -52880,7 +52880,7 @@
         <v>44839</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -52937,7 +52937,7 @@
         <v>45149.95241898148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -52999,7 +52999,7 @@
         <v>45505</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -53061,7 +53061,7 @@
         <v>45827.53178240741</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45827.63582175926</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -53185,7 +53185,7 @@
         <v>45224</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -53242,7 +53242,7 @@
         <v>45233.92591435185</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -53299,7 +53299,7 @@
         <v>45874.69844907407</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -53361,7 +53361,7 @@
         <v>45832.34552083333</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -53423,7 +53423,7 @@
         <v>45367.04693287037</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45581.55260416667</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45712.61552083334</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -53604,7 +53604,7 @@
         <v>45775.67747685185</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -53666,7 +53666,7 @@
         <v>44672.94018518519</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -53728,7 +53728,7 @@
         <v>44977.98670138889</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -53790,7 +53790,7 @@
         <v>45392</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -53847,7 +53847,7 @@
         <v>45244.96774305555</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -53909,7 +53909,7 @@
         <v>45238</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -53971,7 +53971,7 @@
         <v>45874.67746527777</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -54033,7 +54033,7 @@
         <v>45734.45268518518</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -54090,7 +54090,7 @@
         <v>45230</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>45832.34524305556</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -54209,7 +54209,7 @@
         <v>45832.3459375</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -54271,7 +54271,7 @@
         <v>45241.95741898148</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -54333,7 +54333,7 @@
         <v>45241</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -54395,7 +54395,7 @@
         <v>45254.96402777778</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -54457,7 +54457,7 @@
         <v>45874.59496527778</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -54519,7 +54519,7 @@
         <v>45839</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -54576,7 +54576,7 @@
         <v>45558.63575231482</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -54638,7 +54638,7 @@
         <v>44746</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -54695,7 +54695,7 @@
         <v>44657</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -54752,7 +54752,7 @@
         <v>45876.53188657408</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -54814,7 +54814,7 @@
         <v>45834.65662037037</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -54876,7 +54876,7 @@
         <v>45590</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -54933,7 +54933,7 @@
         <v>44806</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -54990,7 +54990,7 @@
         <v>44641</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -55052,7 +55052,7 @@
         <v>44641</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -55114,7 +55114,7 @@
         <v>45771.36538194444</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -55176,7 +55176,7 @@
         <v>45835.4506712963</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -55233,7 +55233,7 @@
         <v>45838</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -55290,7 +55290,7 @@
         <v>44685</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -55352,7 +55352,7 @@
         <v>45622</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -55409,7 +55409,7 @@
         <v>44942</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -55471,7 +55471,7 @@
         <v>44994.94296296296</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -55533,7 +55533,7 @@
         <v>45614.34545138889</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -55590,7 +55590,7 @@
         <v>45601.40686342592</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -55652,7 +55652,7 @@
         <v>45266.95082175926</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -55714,7 +55714,7 @@
         <v>45751.36490740741</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -55776,7 +55776,7 @@
         <v>45344.92865740741</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -55833,7 +55833,7 @@
         <v>45344.92873842592</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -55890,7 +55890,7 @@
         <v>45309</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -55947,7 +55947,7 @@
         <v>45309</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -56004,7 +56004,7 @@
         <v>44231</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -56061,7 +56061,7 @@
         <v>45456.96601851852</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -56123,7 +56123,7 @@
         <v>45688.68196759259</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -56185,7 +56185,7 @@
         <v>45327.94443287037</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>45835.72046296296</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>45838</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -56361,7 +56361,7 @@
         <v>45044</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45838.67887731481</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -56485,7 +56485,7 @@
         <v>45351.98496527778</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -56547,7 +56547,7 @@
         <v>45741.63659722222</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -56609,7 +56609,7 @@
         <v>45838.48996527777</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -56666,7 +56666,7 @@
         <v>45835.40668981482</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>45075.94506944445</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -56790,7 +56790,7 @@
         <v>45838.67800925926</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -56847,7 +56847,7 @@
         <v>45835.53166666667</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -56909,7 +56909,7 @@
         <v>45222</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -56971,7 +56971,7 @@
         <v>45257.92826388889</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -57028,7 +57028,7 @@
         <v>45306</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -57085,7 +57085,7 @@
         <v>44956.93924768519</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -57147,7 +57147,7 @@
         <v>45835.46334490741</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -57204,7 +57204,7 @@
         <v>45314</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -57261,7 +57261,7 @@
         <v>45629.36486111111</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -57318,7 +57318,7 @@
         <v>44803.94351851852</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -57380,7 +57380,7 @@
         <v>45758.36487268518</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -57442,7 +57442,7 @@
         <v>44958</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -57499,7 +57499,7 @@
         <v>45835.45686342593</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -57556,7 +57556,7 @@
         <v>45603.44644675926</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -57618,7 +57618,7 @@
         <v>45622.44774305556</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -57675,7 +57675,7 @@
         <v>45839.42822916667</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -57737,7 +57737,7 @@
         <v>45009.089375</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -57799,7 +57799,7 @@
         <v>45618.46921296296</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -57861,7 +57861,7 @@
         <v>45839.46915509259</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -57923,7 +57923,7 @@
         <v>45482.94815972223</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -57985,7 +57985,7 @@
         <v>45344.92822916667</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -58042,7 +58042,7 @@
         <v>45671.48989583334</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -58104,7 +58104,7 @@
         <v>45238</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -58161,7 +58161,7 @@
         <v>44984</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -58218,7 +58218,7 @@
         <v>45838.36532407408</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -58280,7 +58280,7 @@
         <v>44571</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -58337,7 +58337,7 @@
         <v>45436.94613425926</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -58399,7 +58399,7 @@
         <v>45839.49082175926</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -58456,7 +58456,7 @@
         <v>45769.65688657408</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -58518,7 +58518,7 @@
         <v>45839.42810185185</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -58580,7 +58580,7 @@
         <v>44977.44373842593</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -58637,7 +58637,7 @@
         <v>45170</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -58699,7 +58699,7 @@
         <v>45474.50608796296</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -58756,7 +58756,7 @@
         <v>45608.52354166667</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -58818,7 +58818,7 @@
         <v>44929</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -58875,7 +58875,7 @@
         <v>45000</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -58932,7 +58932,7 @@
         <v>45530</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -58989,7 +58989,7 @@
         <v>45469.94667824074</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -59051,7 +59051,7 @@
         <v>45511</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -59113,7 +59113,7 @@
         <v>44286</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -59170,7 +59170,7 @@
         <v>45210</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -59227,7 +59227,7 @@
         <v>45664.55241898148</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -59289,7 +59289,7 @@
         <v>45839.42864583333</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -59351,7 +59351,7 @@
         <v>45681.60203703704</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -59408,7 +59408,7 @@
         <v>45679.40362268518</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -59465,7 +59465,7 @@
         <v>45667.55239583334</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -59527,7 +59527,7 @@
         <v>45839.57331018519</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -59589,7 +59589,7 @@
         <v>45260</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -59646,7 +59646,7 @@
         <v>44424</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -59703,7 +59703,7 @@
         <v>45149</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -59760,7 +59760,7 @@
         <v>45103</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -59817,7 +59817,7 @@
         <v>45604.63575231482</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -59879,7 +59879,7 @@
         <v>44649.47048611111</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -59941,7 +59941,7 @@
         <v>45840.52225694444</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -59998,7 +59998,7 @@
         <v>45069</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -60055,7 +60055,7 @@
         <v>45184</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -60112,7 +60112,7 @@
         <v>45324</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -60169,7 +60169,7 @@
         <v>45000</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -60231,7 +60231,7 @@
         <v>45000</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -60293,7 +60293,7 @@
         <v>45183.95563657407</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -60355,7 +60355,7 @@
         <v>45534</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -60412,7 +60412,7 @@
         <v>45510</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -60474,7 +60474,7 @@
         <v>44894.79018518519</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -60531,7 +60531,7 @@
         <v>45692.48993055556</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -60593,7 +60593,7 @@
         <v>45842.38579861111</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -60655,7 +60655,7 @@
         <v>44855</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -60717,7 +60717,7 @@
         <v>44349.91978009259</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -60774,7 +60774,7 @@
         <v>45841.57427083333</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -60836,7 +60836,7 @@
         <v>45625.51068287037</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -60898,7 +60898,7 @@
         <v>44963</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -60960,7 +60960,7 @@
         <v>45695.45868055556</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -61017,7 +61017,7 @@
         <v>45476.94533564815</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -61079,7 +61079,7 @@
         <v>44384</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -61136,7 +61136,7 @@
         <v>45601.55331018518</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -61198,7 +61198,7 @@
         <v>45487.92856481481</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -61255,7 +61255,7 @@
         <v>45040</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -61312,7 +61312,7 @@
         <v>44844.95368055555</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -61374,7 +61374,7 @@
         <v>44362</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -61431,7 +61431,7 @@
         <v>45482.94891203703</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -61493,7 +61493,7 @@
         <v>45482.9491087963</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -61555,7 +61555,7 @@
         <v>45008.01408564814</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -61617,7 +61617,7 @@
         <v>45176</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -61674,7 +61674,7 @@
         <v>45681.6050925926</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -61731,7 +61731,7 @@
         <v>45842.42608796297</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -61788,7 +61788,7 @@
         <v>45726.38615740741</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -61845,7 +61845,7 @@
         <v>45706.34450231482</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -61907,7 +61907,7 @@
         <v>45715.59405092592</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -61969,7 +61969,7 @@
         <v>44914</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -62026,7 +62026,7 @@
         <v>44889</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -62083,7 +62083,7 @@
         <v>45735.53177083333</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -62145,7 +62145,7 @@
         <v>45735.5517824074</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -62202,7 +62202,7 @@
         <v>45730.42738425926</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -62264,7 +62264,7 @@
         <v>45733.61554398148</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -62326,7 +62326,7 @@
         <v>45197.94152777778</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -62388,7 +62388,7 @@
         <v>45700.57324074074</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -62450,7 +62450,7 @@
         <v>45112</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -62512,7 +62512,7 @@
         <v>45491</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -62574,7 +62574,7 @@
         <v>45446.57052083333</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -62631,7 +62631,7 @@
         <v>45053.94313657407</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -62693,7 +62693,7 @@
         <v>44629</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -62750,7 +62750,7 @@
         <v>45053.94305555556</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -62812,7 +62812,7 @@
         <v>45306</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -62869,7 +62869,7 @@
         <v>45068</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -62931,7 +62931,7 @@
         <v>45735.69842592593</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -62993,7 +62993,7 @@
         <v>45314.92758101852</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -63050,7 +63050,7 @@
         <v>44880</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -63112,7 +63112,7 @@
         <v>45714</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -63169,7 +63169,7 @@
         <v>45425.96494212963</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -63231,7 +63231,7 @@
         <v>45841.6571412037</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -63288,7 +63288,7 @@
         <v>45735</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -63350,7 +63350,7 @@
         <v>45540.38586805556</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -63412,7 +63412,7 @@
         <v>44825</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -63474,7 +63474,7 @@
         <v>44299</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -63531,7 +63531,7 @@
         <v>44917</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -63588,7 +63588,7 @@
         <v>44915</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -63650,7 +63650,7 @@
         <v>45078</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -63707,7 +63707,7 @@
         <v>44405.92065972222</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -63764,7 +63764,7 @@
         <v>45688.67542824074</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -63826,7 +63826,7 @@
         <v>45888.6775</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -63888,7 +63888,7 @@
         <v>45659.69822916666</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -63950,7 +63950,7 @@
         <v>45733.61497685185</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -64012,7 +64012,7 @@
         <v>45054</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -64074,7 +64074,7 @@
         <v>45251</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -64131,7 +64131,7 @@
         <v>45145</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -64193,7 +64193,7 @@
         <v>45279.94564814815</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -64255,7 +64255,7 @@
         <v>45091</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -64317,7 +64317,7 @@
         <v>44991</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -64379,7 +64379,7 @@
         <v>45846.34454861111</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -64441,7 +64441,7 @@
         <v>44869</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -64498,7 +64498,7 @@
         <v>45638</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -64555,7 +64555,7 @@
         <v>44635</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -64617,7 +64617,7 @@
         <v>45645.55672453704</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -64674,7 +64674,7 @@
         <v>45096.93866898148</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -64736,7 +64736,7 @@
         <v>44173</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -64793,7 +64793,7 @@
         <v>45751.34873842593</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -64855,7 +64855,7 @@
         <v>44888</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -64917,7 +64917,7 @@
         <v>44174</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -64979,7 +64979,7 @@
         <v>45771.51074074074</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -65041,7 +65041,7 @@
         <v>45341</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -65098,7 +65098,7 @@
         <v>45495.57677083334</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -65155,7 +65155,7 @@
         <v>44530.94694444445</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -65217,7 +65217,7 @@
         <v>44957.94075231482</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -65279,7 +65279,7 @@
         <v>45552.39113425926</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -65336,7 +65336,7 @@
         <v>44305.92047453704</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -65393,7 +65393,7 @@
         <v>45847.34474537037</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -65455,7 +65455,7 @@
         <v>45847.34528935186</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -65517,7 +65517,7 @@
         <v>45754</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -65579,7 +65579,7 @@
         <v>45156</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -65641,7 +65641,7 @@
         <v>45092</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -65698,7 +65698,7 @@
         <v>45847.34597222223</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -65760,7 +65760,7 @@
         <v>45847.61513888889</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -65817,7 +65817,7 @@
         <v>45847.65703703704</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -65879,7 +65879,7 @@
         <v>45848.65658564815</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -65941,7 +65941,7 @@
         <v>45847.34565972222</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -66003,7 +66003,7 @@
         <v>45847.61548611111</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -66060,7 +66060,7 @@
         <v>45889.61517361111</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -66122,7 +66122,7 @@
         <v>45561.34663194444</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -66184,7 +66184,7 @@
         <v>45847.34515046296</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -66246,7 +66246,7 @@
         <v>44966.95328703704</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -66308,7 +66308,7 @@
         <v>45848.49774305556</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -66365,7 +66365,7 @@
         <v>44231</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -66422,7 +66422,7 @@
         <v>45892.34438657408</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -66479,7 +66479,7 @@
         <v>45892.38641203703</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -66536,7 +66536,7 @@
         <v>45892.34423611111</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -66593,7 +66593,7 @@
         <v>45892.38591435185</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -66650,7 +66650,7 @@
         <v>45892.38657407407</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -66707,7 +66707,7 @@
         <v>45848.49761574074</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -66764,7 +66764,7 @@
         <v>45367.69850694444</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -66821,7 +66821,7 @@
         <v>45367.71348379629</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -66878,7 +66878,7 @@
         <v>45852.53185185185</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -66940,7 +66940,7 @@
         <v>45034</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -66997,7 +66997,7 @@
         <v>45892.44840277778</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -67054,7 +67054,7 @@
         <v>45850.34434027778</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -67111,7 +67111,7 @@
         <v>45849.65663194445</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -67173,7 +67173,7 @@
         <v>45112</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -67235,7 +67235,7 @@
         <v>45892.38619212963</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -67292,7 +67292,7 @@
         <v>45892.44824074074</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -67349,7 +67349,7 @@
         <v>45850.34450231482</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -67411,7 +67411,7 @@
         <v>45852.53168981482</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -67473,7 +67473,7 @@
         <v>44889.95015046297</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -67535,7 +67535,7 @@
         <v>45119</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -67592,7 +67592,7 @@
         <v>45289</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -67649,7 +67649,7 @@
         <v>45260.92561342593</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -67706,7 +67706,7 @@
         <v>44939</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -67768,7 +67768,7 @@
         <v>45854.65663194445</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -67830,7 +67830,7 @@
         <v>45896.52478009259</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -67887,7 +67887,7 @@
         <v>45596.61533564814</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -67949,7 +67949,7 @@
         <v>45898.53193287037</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -68011,7 +68011,7 @@
         <v>45898.61502314815</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -68073,7 +68073,7 @@
         <v>45855.67899305555</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -68130,7 +68130,7 @@
         <v>45856.46931712963</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -68192,7 +68192,7 @@
         <v>45855.61523148148</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -68254,7 +68254,7 @@
         <v>45898.49012731481</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -68316,7 +68316,7 @@
         <v>44236</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -68373,7 +68373,7 @@
         <v>45280</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -68430,7 +68430,7 @@
         <v>45898.59295138889</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -68487,7 +68487,7 @@
         <v>44410</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -68544,7 +68544,7 @@
         <v>44670</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -68601,7 +68601,7 @@
         <v>45386</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -68658,7 +68658,7 @@
         <v>45860.30229166667</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -68715,7 +68715,7 @@
         <v>45902.34423611111</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -68777,7 +68777,7 @@
         <v>45901.38572916666</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -68834,7 +68834,7 @@
         <v>45901.38584490741</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -68891,7 +68891,7 @@
         <v>45859.594375</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -68953,7 +68953,7 @@
         <v>45238.96797453704</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -69015,7 +69015,7 @@
         <v>45604.40540509259</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -69072,7 +69072,7 @@
         <v>45604.41625</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -69129,7 +69129,7 @@
         <v>45568.51075231482</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -69191,7 +69191,7 @@
         <v>45901.38578703703</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -69248,7 +69248,7 @@
         <v>45546</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -69305,7 +69305,7 @@
         <v>45086</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -69367,7 +69367,7 @@
         <v>45903.34555555556</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -69424,7 +69424,7 @@
         <v>45904.60431712963</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -69481,7 +69481,7 @@
         <v>45467.96207175926</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -69543,7 +69543,7 @@
         <v>45695.51070601852</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -69605,7 +69605,7 @@
         <v>45441.33313657407</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -69662,7 +69662,7 @@
         <v>44869</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -69719,7 +69719,7 @@
         <v>45002.0328125</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -69781,7 +69781,7 @@
         <v>45905</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -69838,7 +69838,7 @@
         <v>45712.65671296296</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -69895,7 +69895,7 @@
         <v>45908.48993055556</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -69952,7 +69952,7 @@
         <v>45616.5108912037</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -70014,7 +70014,7 @@
         <v>45241.95724537037</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -70076,7 +70076,7 @@
         <v>45425.96230324074</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -70138,7 +70138,7 @@
         <v>45910.40667824074</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -70200,7 +70200,7 @@
         <v>45111.92793981481</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -70262,7 +70262,7 @@
         <v>45910.40721064815</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -70324,7 +70324,7 @@
         <v>45910.67766203704</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -70386,7 +70386,7 @@
         <v>45912.59417824074</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -70448,7 +70448,7 @@
         <v>45357.05300925926</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -70510,7 +70510,7 @@
         <v>45425.96275462963</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -70572,7 +70572,7 @@
         <v>45912.51086805556</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -70634,7 +70634,7 @@
         <v>45869.65666666667</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -70696,7 +70696,7 @@
         <v>45869.67744212963</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -70758,7 +70758,7 @@
         <v>45870.34439814815</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -70820,7 +70820,7 @@
         <v>45453.4444212963</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -70877,7 +70877,7 @@
         <v>44929</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -70934,7 +70934,7 @@
         <v>44375</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -70991,7 +70991,7 @@
         <v>45322</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -71048,7 +71048,7 @@
         <v>44918</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -71110,7 +71110,7 @@
         <v>45912.57373842593</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -71172,7 +71172,7 @@
         <v>45622.46200231482</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -71229,7 +71229,7 @@
         <v>45000</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -71291,7 +71291,7 @@
         <v>45681.5315625</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -71353,7 +71353,7 @@
         <v>45673.66358796296</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -71410,7 +71410,7 @@
         <v>44680.95246527778</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -71472,7 +71472,7 @@
         <v>45601.59518518519</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -71534,7 +71534,7 @@
         <v>44879</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -71596,7 +71596,7 @@
         <v>45009</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -71653,7 +71653,7 @@
         <v>45436.94628472222</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -71715,7 +71715,7 @@
         <v>45425.96263888889</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -71777,7 +71777,7 @@
         <v>45615.50034722222</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -71834,7 +71834,7 @@
         <v>45048.94340277778</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -71896,7 +71896,7 @@
         <v>44929.92489583333</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -71953,7 +71953,7 @@
         <v>45596.61553240741</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -72015,7 +72015,7 @@
         <v>45435</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -72072,7 +72072,7 @@
         <v>45559.67759259259</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -72134,7 +72134,7 @@
         <v>45636.57329861111</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -72196,7 +72196,7 @@
         <v>44593</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -72253,7 +72253,7 @@
         <v>45166</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -72310,7 +72310,7 @@
         <v>45723.51079861111</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -72372,7 +72372,7 @@
         <v>45747.67739583334</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -72434,7 +72434,7 @@
         <v>45629.42759259259</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -72496,7 +72496,7 @@
         <v>45107</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -72553,7 +72553,7 @@
         <v>44518</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -72610,7 +72610,7 @@
         <v>45071</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -72667,7 +72667,7 @@
         <v>45133</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -72729,7 +72729,7 @@
         <v>45712.61502314815</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -72791,7 +72791,7 @@
         <v>45712.61510416667</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -72853,7 +72853,7 @@
         <v>45630.7862037037</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -72910,7 +72910,7 @@
         <v>45329.95806712963</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -72972,7 +72972,7 @@
         <v>45331.92746527777</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -73029,7 +73029,7 @@
         <v>45103</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -73086,7 +73086,7 @@
         <v>45072.92737268518</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -73143,7 +73143,7 @@
         <v>45065.42894675926</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -73200,7 +73200,7 @@
         <v>45622.46910879629</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -73257,7 +73257,7 @@
         <v>45457.96372685185</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -73319,7 +73319,7 @@
         <v>44932.93927083333</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -73381,7 +73381,7 @@
         <v>45540.34428240741</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -73443,7 +73443,7 @@
         <v>45714.55064814815</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -73500,7 +73500,7 @@
         <v>45175</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -73562,7 +73562,7 @@
         <v>45534.63537037037</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -73624,7 +73624,7 @@
         <v>45149.95372685185</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -73686,7 +73686,7 @@
         <v>44904.94824074074</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -73748,7 +73748,7 @@
         <v>45665.65684027778</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -73810,7 +73810,7 @@
         <v>44971</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -73872,7 +73872,7 @@
         <v>45614.63869212963</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -73934,7 +73934,7 @@
         <v>44880.95741898148</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -73996,7 +73996,7 @@
         <v>45715.61523148148</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -74058,7 +74058,7 @@
         <v>44876</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -74120,7 +74120,7 @@
         <v>45215</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -74177,7 +74177,7 @@
         <v>45105</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -74239,7 +74239,7 @@
         <v>45756.63601851852</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -74301,7 +74301,7 @@
         <v>45429</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -74358,7 +74358,7 @@
         <v>45737.69822916666</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -74420,7 +74420,7 @@
         <v>45092</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -74477,7 +74477,7 @@
         <v>44741.94070601852</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -74539,7 +74539,7 @@
         <v>45596.61569444444</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -74601,7 +74601,7 @@
         <v>45596.61582175926</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -74663,7 +74663,7 @@
         <v>45338.95405092592</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -74725,7 +74725,7 @@
         <v>45258</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -74782,7 +74782,7 @@
         <v>45574.61634259259</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -74839,7 +74839,7 @@
         <v>45666.44943287037</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -74896,7 +74896,7 @@
         <v>45629.35326388889</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>

--- a/Översikt RAGUNDA.xlsx
+++ b/Översikt RAGUNDA.xlsx
@@ -567,7 +567,7 @@
         <v>45622</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>45376</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>45622</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>45560.34460648148</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>45673</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>44917</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>45804.67787037037</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>45590.42736111111</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>45838.67753472222</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44504</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44644</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>45622</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>45560.34532407407</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45104</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>45113</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>45579.53179398148</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>44644.93650462963</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>44473</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         <v>44813</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45367.04916666666</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>45639.55269675926</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>45622</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>45790.57334490741</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>44088</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>45482.63819444444</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>45182</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45779.49012731481</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>45803.59474537037</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>44776</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>45358.99375</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45839.42482638889</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>45790.57349537037</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44805</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>44645.99859953704</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>45327</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>44888</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>45779.57335648148</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>45560.34484953704</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>45378</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45685.36501157407</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>45799.63574074074</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>45799.34461805555</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>45510</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>45174</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>45832.34461805555</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>44504</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>45121</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>45769.53180555555</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>45190.96092592592</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         <v>44133</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>45320</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>45827.5110300926</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>45120</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>45113</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         <v>45723.40688657408</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>45622</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44133</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>44662</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>44438</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>45176</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6864,7 +6864,7 @@
         <v>45810.55061342593</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45769.67740740741</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>45121</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>44336</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>45405.57392361111</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>44994</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44915</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>45475.94796296296</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>45786.61517361111</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>45435.54734953704</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>45155</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         <v>44111</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>44209</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>45471.94783564815</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>44875</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>45832.34564814815</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>45769.67778935185</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>44994</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>45468.97528935185</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>45457</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>45238</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>45893.38584490741</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>44932</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         <v>45846.41361111111</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>45495.56244212963</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>45595.44886574074</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>45867.63619212963</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>45728.65684027778</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>44656</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45002.94356481481</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>45446.95087962963</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>45195</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>45551.46912037037</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>45244</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>45832.34578703704</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>45425.96472222222</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>45182</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>45471.94623842592</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>44911</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>45400.94002314815</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>45893.38599537037</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>45674.67744212963</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>45545.45748842593</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>45744.61550925926</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>44245</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>44334.62565972222</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>44696</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>44662</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>44334</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>44334</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>44911</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>45782.44871527778</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45384</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45378</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>45455.96195601852</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45610.34415509259</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>45805.34415509259</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>45510</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>44113</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>45404</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>44677</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>45491</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>45896.63618055556</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>45491</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>45786.61534722222</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>45187</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44855</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>44369.92025462963</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>45071</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>45733</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>45397.95748842593</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45779.57392361111</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>45751.34650462963</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>45093</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>44855</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>45265</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
         <v>45516.94723379629</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>44902</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>44111</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>45631</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r=